--- a/docs/Dokumen_Testing_POS.xlsx
+++ b/docs/Dokumen_Testing_POS.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{460CA95C-0E2E-4C22-B4FD-0940403A4954}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60486394-BBF4-45F1-86EB-12E931FA28CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="867" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -11336,8 +11336,8 @@
       <c r="G4" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="2" t="s">
-        <v>5</v>
+      <c r="H4" s="3" t="s">
+        <v>1140</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="29" x14ac:dyDescent="0.35">
@@ -11362,8 +11362,8 @@
       <c r="G5" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="H5" s="2" t="s">
-        <v>5</v>
+      <c r="H5" s="3" t="s">
+        <v>1140</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
@@ -11388,8 +11388,8 @@
       <c r="G6" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="H6" s="2" t="s">
-        <v>5</v>
+      <c r="H6" s="3" t="s">
+        <v>1140</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="29" x14ac:dyDescent="0.35">
@@ -11440,8 +11440,8 @@
       <c r="G8" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="H8" s="2" t="s">
-        <v>5</v>
+      <c r="H8" s="3" t="s">
+        <v>1140</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="29" x14ac:dyDescent="0.35">
@@ -11466,8 +11466,8 @@
       <c r="G9" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="H9" s="2" t="s">
-        <v>5</v>
+      <c r="H9" s="3" t="s">
+        <v>1140</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="58" x14ac:dyDescent="0.35">

--- a/docs/Dokumen_Testing_POS.xlsx
+++ b/docs/Dokumen_Testing_POS.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60486394-BBF4-45F1-86EB-12E931FA28CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B622D1D-8511-4DA0-99AB-06F5CBF0DC2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="867" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="867" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Daftar Isi" sheetId="1" r:id="rId1"/>
@@ -54,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2242" uniqueCount="1141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2248" uniqueCount="1145">
   <si>
     <t>DOKUMEN TESTING APLIKASI POS</t>
   </si>
@@ -767,9 +767,6 @@
   </si>
   <si>
     <t>user: owner (diri sendiri)</t>
-  </si>
-  <si>
-    <t>Idealnya ditolak/diberi warning (cek apakah backend mengizinkan - potensi bug)</t>
   </si>
   <si>
     <t>TEST CASE - ROLE MANAGEMENT</t>
@@ -3616,6 +3613,24 @@
   </si>
   <si>
     <t>PASS</t>
+  </si>
+  <si>
+    <t>Ganti password</t>
+  </si>
+  <si>
+    <t>1. Pilih user
+2. Ganti password
+3. Tulis password baru dan konfirmasi password
+4. Simpan</t>
+  </si>
+  <si>
+    <t>password: kasir12345</t>
+  </si>
+  <si>
+    <t>Data terupdate password lama menjadi password baru</t>
+  </si>
+  <si>
+    <t>Button hapus/nonaktifkan owner yang sedang digunakan disabled. Jadi karena button disabled tidak bisa di klik.</t>
   </si>
 </sst>
 </file>
@@ -3673,7 +3688,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -3711,11 +3726,22 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFDDDDDD"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFDDDDDD"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -3732,6 +3758,9 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4580,7 +4609,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A1" s="4" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="B1" s="4"/>
       <c r="C1" s="4"/>
@@ -4621,19 +4650,19 @@
         <v>1</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C4" s="2" t="s">
+        <v>397</v>
+      </c>
+      <c r="D4" s="2" t="s">
         <v>398</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>399</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>159</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>5</v>
@@ -4647,19 +4676,19 @@
         <v>2</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C5" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="D5" s="2" t="s">
         <v>401</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="E5" s="2" t="s">
         <v>402</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="F5" s="2" t="s">
         <v>403</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>404</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>5</v>
@@ -4673,19 +4702,19 @@
         <v>3</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C6" s="2" t="s">
+        <v>404</v>
+      </c>
+      <c r="D6" s="2" t="s">
         <v>405</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="E6" s="2" t="s">
         <v>406</v>
       </c>
-      <c r="E6" s="2" t="s">
-        <v>407</v>
-      </c>
       <c r="F6" s="2" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>5</v>
@@ -4699,19 +4728,19 @@
         <v>4</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C7" s="2" t="s">
+        <v>407</v>
+      </c>
+      <c r="D7" s="2" t="s">
         <v>408</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="E7" s="2" t="s">
         <v>409</v>
       </c>
-      <c r="E7" s="2" t="s">
-        <v>410</v>
-      </c>
       <c r="F7" s="2" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>5</v>
@@ -4725,19 +4754,19 @@
         <v>5</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C8" s="2" t="s">
+        <v>410</v>
+      </c>
+      <c r="D8" s="2" t="s">
         <v>411</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="E8" s="2" t="s">
         <v>412</v>
       </c>
-      <c r="E8" s="2" t="s">
+      <c r="F8" s="2" t="s">
         <v>413</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>414</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>5</v>
@@ -4751,19 +4780,19 @@
         <v>6</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C9" s="2" t="s">
+        <v>414</v>
+      </c>
+      <c r="D9" s="2" t="s">
         <v>415</v>
       </c>
-      <c r="D9" s="2" t="s">
+      <c r="E9" s="2" t="s">
         <v>416</v>
       </c>
-      <c r="E9" s="2" t="s">
+      <c r="F9" s="2" t="s">
         <v>417</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>418</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>5</v>
@@ -4798,7 +4827,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A1" s="4" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B1" s="4"/>
       <c r="C1" s="4"/>
@@ -4839,19 +4868,19 @@
         <v>1</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C4" s="2" t="s">
+        <v>419</v>
+      </c>
+      <c r="D4" s="2" t="s">
         <v>420</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>421</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>159</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>5</v>
@@ -4865,19 +4894,19 @@
         <v>2</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C5" s="2" t="s">
+        <v>422</v>
+      </c>
+      <c r="D5" s="2" t="s">
         <v>423</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="E5" s="2" t="s">
         <v>424</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="F5" s="2" t="s">
         <v>425</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>426</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>5</v>
@@ -4891,19 +4920,19 @@
         <v>3</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C6" s="2" t="s">
+        <v>426</v>
+      </c>
+      <c r="D6" s="2" t="s">
         <v>427</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="E6" s="2" t="s">
         <v>428</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="F6" s="2" t="s">
         <v>429</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>430</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>5</v>
@@ -4917,19 +4946,19 @@
         <v>4</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C7" s="2" t="s">
+        <v>430</v>
+      </c>
+      <c r="D7" s="2" t="s">
         <v>431</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="E7" s="2" t="s">
         <v>432</v>
       </c>
-      <c r="E7" s="2" t="s">
+      <c r="F7" s="2" t="s">
         <v>433</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>434</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>5</v>
@@ -4943,19 +4972,19 @@
         <v>5</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C8" s="2" t="s">
+        <v>434</v>
+      </c>
+      <c r="D8" s="2" t="s">
         <v>435</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="E8" s="2" t="s">
         <v>436</v>
       </c>
-      <c r="E8" s="2" t="s">
+      <c r="F8" s="2" t="s">
         <v>437</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>438</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>5</v>
@@ -4969,19 +4998,19 @@
         <v>6</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C9" s="2" t="s">
+        <v>438</v>
+      </c>
+      <c r="D9" s="2" t="s">
         <v>439</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>440</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>159</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>5</v>
@@ -4995,19 +5024,19 @@
         <v>7</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C10" s="2" t="s">
+        <v>441</v>
+      </c>
+      <c r="D10" s="2" t="s">
         <v>442</v>
       </c>
-      <c r="D10" s="2" t="s">
+      <c r="E10" s="2" t="s">
         <v>443</v>
       </c>
-      <c r="E10" s="2" t="s">
+      <c r="F10" s="2" t="s">
         <v>444</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>445</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>5</v>
@@ -5021,19 +5050,19 @@
         <v>8</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C11" s="2" t="s">
+        <v>445</v>
+      </c>
+      <c r="D11" s="2" t="s">
         <v>446</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>447</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>159</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>5</v>
@@ -5047,19 +5076,19 @@
         <v>9</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C12" s="2" t="s">
+        <v>448</v>
+      </c>
+      <c r="D12" s="2" t="s">
         <v>449</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>450</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>159</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>5</v>
@@ -5094,7 +5123,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A1" s="4" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="B1" s="4"/>
       <c r="C1" s="4"/>
@@ -5135,19 +5164,19 @@
         <v>1</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C4" s="2" t="s">
+        <v>452</v>
+      </c>
+      <c r="D4" s="2" t="s">
         <v>453</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="E4" s="2" t="s">
         <v>454</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="F4" s="2" t="s">
         <v>455</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>456</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>5</v>
@@ -5161,19 +5190,19 @@
         <v>2</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C5" s="2" t="s">
+        <v>456</v>
+      </c>
+      <c r="D5" s="2" t="s">
         <v>457</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="E5" s="2" t="s">
         <v>458</v>
       </c>
-      <c r="E5" s="2" t="s">
-        <v>459</v>
-      </c>
       <c r="F5" s="2" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>5</v>
@@ -5187,19 +5216,19 @@
         <v>3</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C6" s="2" t="s">
+        <v>459</v>
+      </c>
+      <c r="D6" s="2" t="s">
         <v>460</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="E6" s="2" t="s">
         <v>461</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="F6" s="2" t="s">
         <v>462</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>463</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>5</v>
@@ -5213,19 +5242,19 @@
         <v>4</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C7" s="2" t="s">
+        <v>463</v>
+      </c>
+      <c r="D7" s="2" t="s">
         <v>464</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="E7" s="2" t="s">
         <v>465</v>
       </c>
-      <c r="E7" s="2" t="s">
+      <c r="F7" s="2" t="s">
         <v>466</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>467</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>5</v>
@@ -5239,19 +5268,19 @@
         <v>5</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C8" s="2" t="s">
+        <v>467</v>
+      </c>
+      <c r="D8" s="2" t="s">
         <v>468</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>469</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>159</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>5</v>
@@ -5286,7 +5315,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A1" s="4" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="B1" s="4"/>
       <c r="C1" s="4"/>
@@ -5327,19 +5356,19 @@
         <v>1</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C4" s="2" t="s">
+        <v>471</v>
+      </c>
+      <c r="D4" s="2" t="s">
         <v>472</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>473</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>159</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>5</v>
@@ -5353,19 +5382,19 @@
         <v>2</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C5" s="2" t="s">
+        <v>474</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>401</v>
+      </c>
+      <c r="E5" s="2" t="s">
         <v>475</v>
       </c>
-      <c r="D5" s="2" t="s">
-        <v>402</v>
-      </c>
-      <c r="E5" s="2" t="s">
+      <c r="F5" s="2" t="s">
         <v>476</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>477</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>5</v>
@@ -5379,19 +5408,19 @@
         <v>3</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C6" s="2" t="s">
+        <v>477</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="E6" s="2" t="s">
         <v>478</v>
       </c>
-      <c r="D6" s="2" t="s">
-        <v>291</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>479</v>
-      </c>
       <c r="F6" s="2" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>5</v>
@@ -5405,19 +5434,19 @@
         <v>4</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C7" s="2" t="s">
+        <v>479</v>
+      </c>
+      <c r="D7" s="2" t="s">
         <v>480</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="E7" s="2" t="s">
         <v>481</v>
       </c>
-      <c r="E7" s="2" t="s">
-        <v>482</v>
-      </c>
       <c r="F7" s="2" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>5</v>
@@ -5431,19 +5460,19 @@
         <v>5</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C8" s="2" t="s">
+        <v>482</v>
+      </c>
+      <c r="D8" s="2" t="s">
         <v>483</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="E8" s="2" t="s">
         <v>484</v>
       </c>
-      <c r="E8" s="2" t="s">
+      <c r="F8" s="2" t="s">
         <v>485</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>486</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>5</v>
@@ -5457,19 +5486,19 @@
         <v>6</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C9" s="2" t="s">
+        <v>486</v>
+      </c>
+      <c r="D9" s="2" t="s">
         <v>487</v>
       </c>
-      <c r="D9" s="2" t="s">
+      <c r="E9" s="2" t="s">
         <v>488</v>
       </c>
-      <c r="E9" s="2" t="s">
+      <c r="F9" s="2" t="s">
         <v>489</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>490</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>5</v>
@@ -5504,7 +5533,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A1" s="4" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="B1" s="4"/>
       <c r="C1" s="4"/>
@@ -5545,19 +5574,19 @@
         <v>1</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C4" s="2" t="s">
+        <v>491</v>
+      </c>
+      <c r="D4" s="2" t="s">
         <v>492</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="E4" s="2" t="s">
         <v>493</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="F4" s="2" t="s">
         <v>494</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>495</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>5</v>
@@ -5571,19 +5600,19 @@
         <v>2</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C5" s="2" t="s">
+        <v>495</v>
+      </c>
+      <c r="D5" s="2" t="s">
         <v>496</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>497</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>159</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>5</v>
@@ -5597,19 +5626,19 @@
         <v>3</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C6" s="2" t="s">
+        <v>498</v>
+      </c>
+      <c r="D6" s="2" t="s">
         <v>499</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="E6" s="2" t="s">
         <v>500</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="F6" s="2" t="s">
         <v>501</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>502</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>5</v>
@@ -5623,19 +5652,19 @@
         <v>4</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C7" s="2" t="s">
+        <v>502</v>
+      </c>
+      <c r="D7" s="2" t="s">
         <v>503</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="E7" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="F7" s="2" t="s">
         <v>504</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>437</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>505</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>5</v>
@@ -5649,19 +5678,19 @@
         <v>5</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C8" s="2" t="s">
+        <v>505</v>
+      </c>
+      <c r="D8" s="2" t="s">
         <v>506</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>507</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>159</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>5</v>
@@ -5675,19 +5704,19 @@
         <v>6</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C9" s="2" t="s">
+        <v>508</v>
+      </c>
+      <c r="D9" s="2" t="s">
         <v>509</v>
       </c>
-      <c r="D9" s="2" t="s">
+      <c r="E9" s="2" t="s">
         <v>510</v>
       </c>
-      <c r="E9" s="2" t="s">
+      <c r="F9" s="2" t="s">
         <v>511</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>512</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>5</v>
@@ -5722,7 +5751,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A1" s="4" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="B1" s="4"/>
       <c r="C1" s="4"/>
@@ -5763,19 +5792,19 @@
         <v>1</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C4" s="2" t="s">
+        <v>513</v>
+      </c>
+      <c r="D4" s="2" t="s">
         <v>514</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>515</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>159</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>5</v>
@@ -5789,19 +5818,19 @@
         <v>2</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C5" s="2" t="s">
+        <v>516</v>
+      </c>
+      <c r="D5" s="2" t="s">
         <v>517</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="E5" s="2" t="s">
         <v>518</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="F5" s="2" t="s">
         <v>519</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>520</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>5</v>
@@ -5815,19 +5844,19 @@
         <v>3</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C6" s="2" t="s">
+        <v>520</v>
+      </c>
+      <c r="D6" s="2" t="s">
         <v>521</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="E6" s="2" t="s">
         <v>522</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="F6" s="2" t="s">
         <v>523</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>524</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>5</v>
@@ -5841,19 +5870,19 @@
         <v>4</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C7" s="2" t="s">
+        <v>524</v>
+      </c>
+      <c r="D7" s="2" t="s">
         <v>525</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="E7" s="2" t="s">
         <v>526</v>
       </c>
-      <c r="E7" s="2" t="s">
-        <v>527</v>
-      </c>
       <c r="F7" s="2" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>5</v>
@@ -5867,19 +5896,19 @@
         <v>5</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C8" s="2" t="s">
+        <v>527</v>
+      </c>
+      <c r="D8" s="2" t="s">
         <v>528</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>529</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>159</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>5</v>
@@ -5893,19 +5922,19 @@
         <v>6</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C9" s="2" t="s">
+        <v>530</v>
+      </c>
+      <c r="D9" s="2" t="s">
         <v>531</v>
       </c>
-      <c r="D9" s="2" t="s">
+      <c r="E9" s="2" t="s">
         <v>532</v>
       </c>
-      <c r="E9" s="2" t="s">
+      <c r="F9" s="2" t="s">
         <v>533</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>534</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>5</v>
@@ -5940,7 +5969,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A1" s="4" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="B1" s="4"/>
       <c r="C1" s="4"/>
@@ -5984,16 +6013,16 @@
         <v>128</v>
       </c>
       <c r="C4" s="2" t="s">
+        <v>535</v>
+      </c>
+      <c r="D4" s="2" t="s">
         <v>536</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="E4" s="2" t="s">
         <v>537</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="F4" s="2" t="s">
         <v>538</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>539</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>5</v>
@@ -6010,16 +6039,16 @@
         <v>128</v>
       </c>
       <c r="C5" s="2" t="s">
+        <v>539</v>
+      </c>
+      <c r="D5" s="2" t="s">
         <v>540</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>541</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>159</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>5</v>
@@ -6036,16 +6065,16 @@
         <v>128</v>
       </c>
       <c r="C6" s="2" t="s">
+        <v>542</v>
+      </c>
+      <c r="D6" s="2" t="s">
         <v>543</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="E6" s="2" t="s">
         <v>544</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="F6" s="2" t="s">
         <v>545</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>546</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>5</v>
@@ -6062,16 +6091,16 @@
         <v>128</v>
       </c>
       <c r="C7" s="2" t="s">
+        <v>546</v>
+      </c>
+      <c r="D7" s="2" t="s">
         <v>547</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="E7" s="2" t="s">
         <v>548</v>
       </c>
-      <c r="E7" s="2" t="s">
+      <c r="F7" s="2" t="s">
         <v>549</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>550</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>5</v>
@@ -6088,16 +6117,16 @@
         <v>128</v>
       </c>
       <c r="C8" s="2" t="s">
+        <v>550</v>
+      </c>
+      <c r="D8" s="2" t="s">
         <v>551</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="E8" s="2" t="s">
         <v>552</v>
       </c>
-      <c r="E8" s="2" t="s">
+      <c r="F8" s="2" t="s">
         <v>553</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>554</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>5</v>
@@ -6111,19 +6140,19 @@
         <v>6</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C9" s="2" t="s">
+        <v>554</v>
+      </c>
+      <c r="D9" s="2" t="s">
         <v>555</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>556</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>159</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>5</v>
@@ -6137,19 +6166,19 @@
         <v>7</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C10" s="2" t="s">
+        <v>557</v>
+      </c>
+      <c r="D10" s="2" t="s">
         <v>558</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>559</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>159</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>5</v>
@@ -6184,7 +6213,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A1" s="4" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="B1" s="4"/>
       <c r="C1" s="4"/>
@@ -6225,19 +6254,19 @@
         <v>1</v>
       </c>
       <c r="B4" s="2" t="s">
+        <v>561</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>562</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="D4" s="2" t="s">
         <v>563</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="E4" s="2" t="s">
         <v>564</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="F4" s="2" t="s">
         <v>565</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>566</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>5</v>
@@ -6254,16 +6283,16 @@
         <v>132</v>
       </c>
       <c r="C5" s="2" t="s">
+        <v>566</v>
+      </c>
+      <c r="D5" s="2" t="s">
         <v>567</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="E5" s="2" t="s">
         <v>568</v>
       </c>
-      <c r="E5" s="2" t="s">
-        <v>569</v>
-      </c>
       <c r="F5" s="2" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>5</v>
@@ -6277,19 +6306,19 @@
         <v>3</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C6" s="2" t="s">
+        <v>569</v>
+      </c>
+      <c r="D6" s="2" t="s">
         <v>570</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="E6" s="2" t="s">
         <v>571</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="F6" s="2" t="s">
         <v>572</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>573</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>5</v>
@@ -6303,19 +6332,19 @@
         <v>4</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C7" s="2" t="s">
+        <v>573</v>
+      </c>
+      <c r="D7" s="2" t="s">
         <v>574</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>575</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>159</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>5</v>
@@ -6329,19 +6358,19 @@
         <v>5</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C8" s="2" t="s">
+        <v>576</v>
+      </c>
+      <c r="D8" s="2" t="s">
         <v>577</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="E8" s="2" t="s">
         <v>578</v>
       </c>
-      <c r="E8" s="2" t="s">
+      <c r="F8" s="2" t="s">
         <v>579</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>580</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>5</v>
@@ -6376,7 +6405,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A1" s="4" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="B1" s="4"/>
       <c r="C1" s="4"/>
@@ -6420,16 +6449,16 @@
         <v>128</v>
       </c>
       <c r="C4" s="2" t="s">
+        <v>581</v>
+      </c>
+      <c r="D4" s="2" t="s">
         <v>582</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="E4" s="2" t="s">
         <v>583</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="F4" s="2" t="s">
         <v>584</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>585</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>5</v>
@@ -6446,16 +6475,16 @@
         <v>128</v>
       </c>
       <c r="C5" s="2" t="s">
+        <v>585</v>
+      </c>
+      <c r="D5" s="2" t="s">
         <v>586</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="E5" s="2" t="s">
         <v>587</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="F5" s="2" t="s">
         <v>588</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>589</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>5</v>
@@ -6472,16 +6501,16 @@
         <v>128</v>
       </c>
       <c r="C6" s="2" t="s">
+        <v>589</v>
+      </c>
+      <c r="D6" s="2" t="s">
         <v>590</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="E6" s="2" t="s">
         <v>591</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="F6" s="2" t="s">
         <v>592</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>593</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>5</v>
@@ -6498,16 +6527,16 @@
         <v>128</v>
       </c>
       <c r="C7" s="2" t="s">
+        <v>593</v>
+      </c>
+      <c r="D7" s="2" t="s">
         <v>594</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="E7" s="2" t="s">
         <v>595</v>
       </c>
-      <c r="E7" s="2" t="s">
+      <c r="F7" s="2" t="s">
         <v>596</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>597</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>5</v>
@@ -6524,16 +6553,16 @@
         <v>128</v>
       </c>
       <c r="C8" s="2" t="s">
+        <v>597</v>
+      </c>
+      <c r="D8" s="2" t="s">
         <v>598</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="E8" s="2" t="s">
         <v>599</v>
       </c>
-      <c r="E8" s="2" t="s">
+      <c r="F8" s="2" t="s">
         <v>600</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>601</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>5</v>
@@ -6550,16 +6579,16 @@
         <v>128</v>
       </c>
       <c r="C9" s="2" t="s">
+        <v>601</v>
+      </c>
+      <c r="D9" s="2" t="s">
         <v>602</v>
       </c>
-      <c r="D9" s="2" t="s">
+      <c r="E9" s="2" t="s">
         <v>603</v>
       </c>
-      <c r="E9" s="2" t="s">
+      <c r="F9" s="2" t="s">
         <v>604</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>605</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>5</v>
@@ -6576,16 +6605,16 @@
         <v>128</v>
       </c>
       <c r="C10" s="2" t="s">
+        <v>605</v>
+      </c>
+      <c r="D10" s="2" t="s">
         <v>606</v>
       </c>
-      <c r="D10" s="2" t="s">
-        <v>607</v>
-      </c>
       <c r="E10" s="2" t="s">
+        <v>428</v>
+      </c>
+      <c r="F10" s="2" t="s">
         <v>429</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>430</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>5</v>
@@ -6602,16 +6631,16 @@
         <v>128</v>
       </c>
       <c r="C11" s="2" t="s">
+        <v>607</v>
+      </c>
+      <c r="D11" s="2" t="s">
         <v>608</v>
       </c>
-      <c r="D11" s="2" t="s">
+      <c r="E11" s="2" t="s">
         <v>609</v>
       </c>
-      <c r="E11" s="2" t="s">
-        <v>610</v>
-      </c>
       <c r="F11" s="2" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>5</v>
@@ -6628,16 +6657,16 @@
         <v>128</v>
       </c>
       <c r="C12" s="2" t="s">
+        <v>610</v>
+      </c>
+      <c r="D12" s="2" t="s">
         <v>611</v>
       </c>
-      <c r="D12" s="2" t="s">
+      <c r="E12" s="2" t="s">
         <v>612</v>
       </c>
-      <c r="E12" s="2" t="s">
+      <c r="F12" s="2" t="s">
         <v>613</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>614</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>5</v>
@@ -6654,16 +6683,16 @@
         <v>128</v>
       </c>
       <c r="C13" s="2" t="s">
+        <v>614</v>
+      </c>
+      <c r="D13" s="2" t="s">
         <v>615</v>
       </c>
-      <c r="D13" s="2" t="s">
+      <c r="E13" s="2" t="s">
         <v>616</v>
       </c>
-      <c r="E13" s="2" t="s">
+      <c r="F13" s="2" t="s">
         <v>617</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>618</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>5</v>
@@ -6680,16 +6709,16 @@
         <v>128</v>
       </c>
       <c r="C14" s="2" t="s">
+        <v>618</v>
+      </c>
+      <c r="D14" s="2" t="s">
         <v>619</v>
       </c>
-      <c r="D14" s="2" t="s">
+      <c r="E14" s="2" t="s">
         <v>620</v>
       </c>
-      <c r="E14" s="2" t="s">
+      <c r="F14" s="2" t="s">
         <v>621</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>622</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>5</v>
@@ -6703,19 +6732,19 @@
         <v>12</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C15" s="2" t="s">
+        <v>622</v>
+      </c>
+      <c r="D15" s="2" t="s">
         <v>623</v>
       </c>
-      <c r="D15" s="2" t="s">
+      <c r="E15" s="2" t="s">
         <v>624</v>
       </c>
-      <c r="E15" s="2" t="s">
+      <c r="F15" s="2" t="s">
         <v>625</v>
-      </c>
-      <c r="F15" s="2" t="s">
-        <v>626</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>5</v>
@@ -6732,16 +6761,16 @@
         <v>128</v>
       </c>
       <c r="C16" s="2" t="s">
+        <v>626</v>
+      </c>
+      <c r="D16" s="2" t="s">
         <v>627</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>628</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>159</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>5</v>
@@ -6755,19 +6784,19 @@
         <v>14</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C17" s="2" t="s">
+        <v>629</v>
+      </c>
+      <c r="D17" s="2" t="s">
         <v>630</v>
       </c>
-      <c r="D17" s="2" t="s">
+      <c r="E17" s="2" t="s">
+        <v>578</v>
+      </c>
+      <c r="F17" s="2" t="s">
         <v>631</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>579</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>632</v>
       </c>
       <c r="G17" s="2" t="s">
         <v>5</v>
@@ -6802,7 +6831,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A1" s="4" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="B1" s="4"/>
       <c r="C1" s="4"/>
@@ -6843,19 +6872,19 @@
         <v>1</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C4" s="2" t="s">
+        <v>633</v>
+      </c>
+      <c r="D4" s="2" t="s">
         <v>634</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>635</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>159</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>5</v>
@@ -6869,19 +6898,19 @@
         <v>2</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C5" s="2" t="s">
+        <v>636</v>
+      </c>
+      <c r="D5" s="2" t="s">
         <v>637</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="E5" s="2" t="s">
         <v>638</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="F5" s="2" t="s">
         <v>639</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>640</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>5</v>
@@ -6895,19 +6924,19 @@
         <v>3</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C6" s="2" t="s">
+        <v>640</v>
+      </c>
+      <c r="D6" s="2" t="s">
         <v>641</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>642</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>159</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>5</v>
@@ -6921,19 +6950,19 @@
         <v>4</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C7" s="2" t="s">
+        <v>643</v>
+      </c>
+      <c r="D7" s="2" t="s">
         <v>644</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>645</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>159</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>5</v>
@@ -6947,19 +6976,19 @@
         <v>5</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C8" s="2" t="s">
+        <v>646</v>
+      </c>
+      <c r="D8" s="2" t="s">
         <v>647</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>648</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>159</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>5</v>
@@ -6976,16 +7005,16 @@
         <v>128</v>
       </c>
       <c r="C9" s="2" t="s">
+        <v>649</v>
+      </c>
+      <c r="D9" s="2" t="s">
         <v>650</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>651</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>159</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>5</v>
@@ -7079,7 +7108,7 @@
         <v>5</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="29" x14ac:dyDescent="0.35">
@@ -7105,7 +7134,7 @@
         <v>5</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="29" x14ac:dyDescent="0.35">
@@ -7130,8 +7159,8 @@
       <c r="G6" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="H6" s="2" t="s">
-        <v>5</v>
+      <c r="H6" s="3" t="s">
+        <v>1139</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="29" x14ac:dyDescent="0.35">
@@ -7157,7 +7186,7 @@
         <v>5</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="29" x14ac:dyDescent="0.35">
@@ -7182,8 +7211,8 @@
       <c r="G8" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="H8" s="2" t="s">
-        <v>5</v>
+      <c r="H8" s="3" t="s">
+        <v>1139</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="29" x14ac:dyDescent="0.35">
@@ -7208,8 +7237,8 @@
       <c r="G9" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="H9" s="2" t="s">
-        <v>5</v>
+      <c r="H9" s="3" t="s">
+        <v>1139</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="29" x14ac:dyDescent="0.35">
@@ -7234,8 +7263,8 @@
       <c r="G10" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="H10" s="2" t="s">
-        <v>5</v>
+      <c r="H10" s="3" t="s">
+        <v>1139</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
@@ -7260,8 +7289,8 @@
       <c r="G11" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="H11" s="2" t="s">
-        <v>5</v>
+      <c r="H11" s="3" t="s">
+        <v>1139</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
@@ -7368,7 +7397,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A1" s="4" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="B1" s="4"/>
       <c r="C1" s="4"/>
@@ -7409,19 +7438,19 @@
         <v>1</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C4" s="2" t="s">
+        <v>653</v>
+      </c>
+      <c r="D4" s="2" t="s">
         <v>654</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="E4" s="2" t="s">
         <v>655</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="F4" s="2" t="s">
         <v>656</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>657</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>5</v>
@@ -7435,19 +7464,19 @@
         <v>2</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C5" s="2" t="s">
+        <v>657</v>
+      </c>
+      <c r="D5" s="2" t="s">
         <v>658</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>659</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>159</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>5</v>
@@ -7461,19 +7490,19 @@
         <v>3</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C6" s="2" t="s">
+        <v>660</v>
+      </c>
+      <c r="D6" s="2" t="s">
         <v>661</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>662</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>159</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>5</v>
@@ -7487,19 +7516,19 @@
         <v>4</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C7" s="2" t="s">
+        <v>663</v>
+      </c>
+      <c r="D7" s="2" t="s">
         <v>664</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="E7" s="2" t="s">
         <v>665</v>
       </c>
-      <c r="E7" s="2" t="s">
+      <c r="F7" s="2" t="s">
         <v>666</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>667</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>5</v>
@@ -7513,19 +7542,19 @@
         <v>5</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C8" s="2" t="s">
+        <v>667</v>
+      </c>
+      <c r="D8" s="2" t="s">
         <v>668</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>669</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>159</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>5</v>
@@ -7539,19 +7568,19 @@
         <v>6</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C9" s="2" t="s">
+        <v>670</v>
+      </c>
+      <c r="D9" s="2" t="s">
         <v>671</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>672</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>159</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>5</v>
@@ -7565,19 +7594,19 @@
         <v>7</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C10" s="2" t="s">
+        <v>673</v>
+      </c>
+      <c r="D10" s="2" t="s">
         <v>674</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>675</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>159</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>5</v>
@@ -7591,19 +7620,19 @@
         <v>8</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C11" s="2" t="s">
+        <v>676</v>
+      </c>
+      <c r="D11" s="2" t="s">
         <v>677</v>
       </c>
-      <c r="D11" s="2" t="s">
+      <c r="E11" s="2" t="s">
         <v>678</v>
       </c>
-      <c r="E11" s="2" t="s">
+      <c r="F11" s="2" t="s">
         <v>679</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>680</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>5</v>
@@ -7617,19 +7646,19 @@
         <v>9</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C12" s="2" t="s">
+        <v>680</v>
+      </c>
+      <c r="D12" s="2" t="s">
         <v>681</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>682</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>159</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>5</v>
@@ -7646,16 +7675,16 @@
         <v>128</v>
       </c>
       <c r="C13" s="2" t="s">
+        <v>682</v>
+      </c>
+      <c r="D13" s="2" t="s">
         <v>683</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>684</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>159</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>5</v>
@@ -7690,7 +7719,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A1" s="4" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="B1" s="4"/>
       <c r="C1" s="4"/>
@@ -7731,19 +7760,19 @@
         <v>1</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C4" s="2" t="s">
+        <v>686</v>
+      </c>
+      <c r="D4" s="2" t="s">
         <v>687</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>688</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>159</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>5</v>
@@ -7757,19 +7786,19 @@
         <v>2</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C5" s="2" t="s">
+        <v>689</v>
+      </c>
+      <c r="D5" s="2" t="s">
         <v>690</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>691</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>159</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>5</v>
@@ -7783,19 +7812,19 @@
         <v>3</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C6" s="2" t="s">
+        <v>692</v>
+      </c>
+      <c r="D6" s="2" t="s">
         <v>693</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>694</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>159</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>5</v>
@@ -7809,19 +7838,19 @@
         <v>4</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C7" s="2" t="s">
+        <v>695</v>
+      </c>
+      <c r="D7" s="2" t="s">
         <v>696</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>697</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>159</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>5</v>
@@ -7838,16 +7867,16 @@
         <v>128</v>
       </c>
       <c r="C8" s="2" t="s">
+        <v>698</v>
+      </c>
+      <c r="D8" s="2" t="s">
         <v>699</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>700</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>159</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>5</v>
@@ -7882,7 +7911,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A1" s="4" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="B1" s="4"/>
       <c r="C1" s="4"/>
@@ -7926,16 +7955,16 @@
         <v>132</v>
       </c>
       <c r="C4" s="2" t="s">
+        <v>702</v>
+      </c>
+      <c r="D4" s="2" t="s">
         <v>703</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>704</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>159</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>5</v>
@@ -7949,19 +7978,19 @@
         <v>2</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C5" s="2" t="s">
+        <v>705</v>
+      </c>
+      <c r="D5" s="2" t="s">
         <v>706</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="E5" s="2" t="s">
         <v>707</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="F5" s="2" t="s">
         <v>708</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>709</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>5</v>
@@ -7978,16 +8007,16 @@
         <v>124</v>
       </c>
       <c r="C6" s="2" t="s">
+        <v>709</v>
+      </c>
+      <c r="D6" s="2" t="s">
         <v>710</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>711</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>159</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>5</v>
@@ -8004,16 +8033,16 @@
         <v>119</v>
       </c>
       <c r="C7" s="2" t="s">
+        <v>712</v>
+      </c>
+      <c r="D7" s="2" t="s">
         <v>713</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>714</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>159</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>5</v>
@@ -8027,19 +8056,19 @@
         <v>5</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C8" s="2" t="s">
+        <v>715</v>
+      </c>
+      <c r="D8" s="2" t="s">
         <v>716</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="E8" s="2" t="s">
         <v>717</v>
       </c>
-      <c r="E8" s="2" t="s">
+      <c r="F8" s="2" t="s">
         <v>718</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>719</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>5</v>
@@ -8053,19 +8082,19 @@
         <v>6</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C9" s="2" t="s">
+        <v>719</v>
+      </c>
+      <c r="D9" s="2" t="s">
         <v>720</v>
       </c>
-      <c r="D9" s="2" t="s">
+      <c r="E9" s="2" t="s">
         <v>721</v>
       </c>
-      <c r="E9" s="2" t="s">
+      <c r="F9" s="2" t="s">
         <v>722</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>723</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>5</v>
@@ -8082,16 +8111,16 @@
         <v>128</v>
       </c>
       <c r="C10" s="2" t="s">
+        <v>723</v>
+      </c>
+      <c r="D10" s="2" t="s">
         <v>724</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>725</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>159</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>5</v>
@@ -8126,7 +8155,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A1" s="4" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="B1" s="4"/>
       <c r="C1" s="4"/>
@@ -8167,19 +8196,19 @@
         <v>1</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C4" s="2" t="s">
+        <v>727</v>
+      </c>
+      <c r="D4" s="2" t="s">
         <v>728</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>729</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>159</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>5</v>
@@ -8193,19 +8222,19 @@
         <v>2</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C5" s="2" t="s">
+        <v>730</v>
+      </c>
+      <c r="D5" s="2" t="s">
         <v>731</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>732</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>159</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>5</v>
@@ -8219,19 +8248,19 @@
         <v>3</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C6" s="2" t="s">
+        <v>733</v>
+      </c>
+      <c r="D6" s="2" t="s">
         <v>734</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>735</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>159</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>5</v>
@@ -8248,16 +8277,16 @@
         <v>124</v>
       </c>
       <c r="C7" s="2" t="s">
+        <v>736</v>
+      </c>
+      <c r="D7" s="2" t="s">
         <v>737</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="E7" s="2" t="s">
         <v>738</v>
       </c>
-      <c r="E7" s="2" t="s">
+      <c r="F7" s="2" t="s">
         <v>739</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>740</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>5</v>
@@ -8274,16 +8303,16 @@
         <v>119</v>
       </c>
       <c r="C8" s="2" t="s">
+        <v>740</v>
+      </c>
+      <c r="D8" s="2" t="s">
         <v>741</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>742</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>159</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>5</v>
@@ -8318,7 +8347,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A1" s="4" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="B1" s="4"/>
       <c r="C1" s="4"/>
@@ -8359,19 +8388,19 @@
         <v>1</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C4" s="2" t="s">
+        <v>744</v>
+      </c>
+      <c r="D4" s="2" t="s">
         <v>745</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>746</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>159</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>5</v>
@@ -8385,19 +8414,19 @@
         <v>2</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C5" s="2" t="s">
+        <v>747</v>
+      </c>
+      <c r="D5" s="2" t="s">
         <v>748</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>749</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>159</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>5</v>
@@ -8411,19 +8440,19 @@
         <v>3</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C6" s="2" t="s">
+        <v>750</v>
+      </c>
+      <c r="D6" s="2" t="s">
         <v>751</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="E6" s="2" t="s">
         <v>752</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="F6" s="2" t="s">
         <v>753</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>754</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>5</v>
@@ -8437,19 +8466,19 @@
         <v>4</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C7" s="2" t="s">
+        <v>754</v>
+      </c>
+      <c r="D7" s="2" t="s">
         <v>755</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="E7" s="2" t="s">
         <v>756</v>
       </c>
-      <c r="E7" s="2" t="s">
+      <c r="F7" s="2" t="s">
         <v>757</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>758</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>5</v>
@@ -8463,19 +8492,19 @@
         <v>5</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C8" s="2" t="s">
+        <v>758</v>
+      </c>
+      <c r="D8" s="2" t="s">
         <v>759</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>760</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>159</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>5</v>
@@ -8489,19 +8518,19 @@
         <v>6</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C9" s="2" t="s">
+        <v>761</v>
+      </c>
+      <c r="D9" s="2" t="s">
         <v>762</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>763</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>159</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>5</v>
@@ -8515,19 +8544,19 @@
         <v>7</v>
       </c>
       <c r="B10" s="2" t="s">
+        <v>764</v>
+      </c>
+      <c r="C10" s="2" t="s">
         <v>765</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="D10" s="2" t="s">
         <v>766</v>
       </c>
-      <c r="D10" s="2" t="s">
+      <c r="E10" s="2" t="s">
         <v>767</v>
       </c>
-      <c r="E10" s="2" t="s">
+      <c r="F10" s="2" t="s">
         <v>768</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>769</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>5</v>
@@ -8562,7 +8591,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A1" s="4" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="B1" s="4"/>
       <c r="C1" s="4"/>
@@ -8603,19 +8632,19 @@
         <v>1</v>
       </c>
       <c r="B4" s="2" t="s">
+        <v>770</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>771</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="D4" s="2" t="s">
         <v>772</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>773</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>159</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>5</v>
@@ -8629,19 +8658,19 @@
         <v>2</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C5" s="2" t="s">
+        <v>774</v>
+      </c>
+      <c r="D5" s="2" t="s">
         <v>775</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>776</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>159</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>5</v>
@@ -8655,19 +8684,19 @@
         <v>3</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C6" s="2" t="s">
+        <v>777</v>
+      </c>
+      <c r="D6" s="2" t="s">
         <v>778</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="E6" s="2" t="s">
         <v>779</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="F6" s="2" t="s">
         <v>780</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>781</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>5</v>
@@ -8684,16 +8713,16 @@
         <v>128</v>
       </c>
       <c r="C7" s="2" t="s">
+        <v>781</v>
+      </c>
+      <c r="D7" s="2" t="s">
         <v>782</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>783</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>159</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>5</v>
@@ -8728,7 +8757,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A1" s="4" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="B1" s="4"/>
       <c r="C1" s="4"/>
@@ -8772,16 +8801,16 @@
         <v>128</v>
       </c>
       <c r="C4" s="2" t="s">
+        <v>785</v>
+      </c>
+      <c r="D4" s="2" t="s">
         <v>786</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>787</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>159</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>5</v>
@@ -8798,16 +8827,16 @@
         <v>128</v>
       </c>
       <c r="C5" s="2" t="s">
+        <v>788</v>
+      </c>
+      <c r="D5" s="2" t="s">
         <v>789</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>790</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>159</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>5</v>
@@ -8824,16 +8853,16 @@
         <v>128</v>
       </c>
       <c r="C6" s="2" t="s">
+        <v>790</v>
+      </c>
+      <c r="D6" s="2" t="s">
         <v>791</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>792</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>159</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>5</v>
@@ -8850,16 +8879,16 @@
         <v>128</v>
       </c>
       <c r="C7" s="2" t="s">
+        <v>792</v>
+      </c>
+      <c r="D7" s="2" t="s">
         <v>793</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>794</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>159</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>5</v>
@@ -8876,16 +8905,16 @@
         <v>128</v>
       </c>
       <c r="C8" s="2" t="s">
+        <v>794</v>
+      </c>
+      <c r="D8" s="2" t="s">
         <v>795</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>796</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>159</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>5</v>
@@ -8902,16 +8931,16 @@
         <v>128</v>
       </c>
       <c r="C9" s="2" t="s">
+        <v>797</v>
+      </c>
+      <c r="D9" s="2" t="s">
         <v>798</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>799</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>159</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>5</v>
@@ -8928,16 +8957,16 @@
         <v>124</v>
       </c>
       <c r="C10" s="2" t="s">
+        <v>800</v>
+      </c>
+      <c r="D10" s="2" t="s">
         <v>801</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>802</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>159</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>5</v>
@@ -8954,16 +8983,16 @@
         <v>132</v>
       </c>
       <c r="C11" s="2" t="s">
+        <v>803</v>
+      </c>
+      <c r="D11" s="2" t="s">
         <v>804</v>
       </c>
-      <c r="D11" s="2" t="s">
+      <c r="E11" s="2" t="s">
         <v>805</v>
       </c>
-      <c r="E11" s="2" t="s">
+      <c r="F11" s="2" t="s">
         <v>806</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>807</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>5</v>
@@ -8980,16 +9009,16 @@
         <v>132</v>
       </c>
       <c r="C12" s="2" t="s">
+        <v>807</v>
+      </c>
+      <c r="D12" s="2" t="s">
         <v>808</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>809</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>159</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>5</v>
@@ -9006,16 +9035,16 @@
         <v>132</v>
       </c>
       <c r="C13" s="2" t="s">
+        <v>810</v>
+      </c>
+      <c r="D13" s="2" t="s">
         <v>811</v>
       </c>
-      <c r="D13" s="2" t="s">
+      <c r="E13" s="2" t="s">
         <v>812</v>
       </c>
-      <c r="E13" s="2" t="s">
+      <c r="F13" s="2" t="s">
         <v>813</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>814</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>5</v>
@@ -9047,7 +9076,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A1" s="7" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="B1" s="7"/>
       <c r="C1" s="7"/>
@@ -9057,22 +9086,22 @@
     </row>
     <row r="3" spans="1:6" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
+        <v>815</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>816</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="C3" s="1" t="s">
         <v>817</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="D3" s="1" t="s">
         <v>818</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="E3" s="1" t="s">
         <v>819</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="F3" s="1" t="s">
         <v>820</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>821</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="29" x14ac:dyDescent="0.35">
@@ -9080,19 +9109,19 @@
         <v>119</v>
       </c>
       <c r="B4" s="2" t="s">
+        <v>821</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>822</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="D4" s="2" t="s">
         <v>823</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="E4" s="2" t="s">
         <v>824</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="F4" s="2" t="s">
         <v>825</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>826</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.35">
@@ -9100,19 +9129,19 @@
         <v>124</v>
       </c>
       <c r="B5" s="2" t="s">
+        <v>826</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>827</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="D5" s="2" t="s">
         <v>828</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="E5" s="2" t="s">
+        <v>824</v>
+      </c>
+      <c r="F5" s="2" t="s">
         <v>829</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>825</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>830</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="29" x14ac:dyDescent="0.35">
@@ -9120,19 +9149,19 @@
         <v>128</v>
       </c>
       <c r="B6" s="2" t="s">
+        <v>830</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>831</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="D6" s="2" t="s">
         <v>832</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="E6" s="2" t="s">
+        <v>824</v>
+      </c>
+      <c r="F6" s="2" t="s">
         <v>833</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>825</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>834</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.35">
@@ -9140,59 +9169,59 @@
         <v>128</v>
       </c>
       <c r="B7" s="2" t="s">
+        <v>834</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>831</v>
+      </c>
+      <c r="D7" s="2" t="s">
         <v>835</v>
       </c>
-      <c r="C7" s="2" t="s">
-        <v>832</v>
-      </c>
-      <c r="D7" s="2" t="s">
+      <c r="E7" s="2" t="s">
+        <v>824</v>
+      </c>
+      <c r="F7" s="2" t="s">
         <v>836</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>825</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>837</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
+        <v>837</v>
+      </c>
+      <c r="B8" s="2" t="s">
         <v>838</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="C8" s="2" t="s">
+        <v>831</v>
+      </c>
+      <c r="D8" s="2" t="s">
         <v>839</v>
       </c>
-      <c r="C8" s="2" t="s">
-        <v>832</v>
-      </c>
-      <c r="D8" s="2" t="s">
+      <c r="E8" s="2" t="s">
         <v>840</v>
       </c>
-      <c r="E8" s="2" t="s">
+      <c r="F8" s="2" t="s">
         <v>841</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>842</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A9" s="2" t="s">
+        <v>842</v>
+      </c>
+      <c r="B9" s="2" t="s">
         <v>843</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="C9" s="2" t="s">
         <v>844</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="D9" s="2" t="s">
         <v>845</v>
       </c>
-      <c r="D9" s="2" t="s">
+      <c r="E9" s="2" t="s">
+        <v>824</v>
+      </c>
+      <c r="F9" s="2" t="s">
         <v>846</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>825</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>847</v>
       </c>
     </row>
   </sheetData>
@@ -9218,7 +9247,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A1" s="7" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="B1" s="7"/>
       <c r="C1" s="7"/>
@@ -9228,142 +9257,142 @@
     </row>
     <row r="3" spans="1:6" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
+        <v>848</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>849</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="C3" s="1" t="s">
         <v>850</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="D3" s="1" t="s">
         <v>851</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="E3" s="1" t="s">
         <v>852</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="F3" s="1" t="s">
         <v>853</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>854</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
+        <v>821</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>822</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="C4" s="2" t="s">
         <v>823</v>
       </c>
-      <c r="C4" s="2" t="s">
-        <v>824</v>
-      </c>
       <c r="D4" s="2" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="E4" s="2" t="s">
+        <v>854</v>
+      </c>
+      <c r="F4" s="2" t="s">
         <v>855</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>856</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
+        <v>826</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>827</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="C5" s="2" t="s">
         <v>828</v>
       </c>
-      <c r="C5" s="2" t="s">
-        <v>829</v>
-      </c>
       <c r="D5" s="2" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="E5" s="2" t="s">
+        <v>854</v>
+      </c>
+      <c r="F5" s="2" t="s">
         <v>855</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>856</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
+        <v>830</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>831</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="C6" s="2" t="s">
         <v>832</v>
       </c>
-      <c r="C6" s="2" t="s">
-        <v>833</v>
-      </c>
       <c r="D6" s="2" t="s">
+        <v>856</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>854</v>
+      </c>
+      <c r="F6" s="2" t="s">
         <v>857</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>855</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>858</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
+        <v>834</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>831</v>
+      </c>
+      <c r="C7" s="2" t="s">
         <v>835</v>
       </c>
-      <c r="B7" s="2" t="s">
-        <v>832</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>836</v>
-      </c>
       <c r="D7" s="2" t="s">
+        <v>856</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>854</v>
+      </c>
+      <c r="F7" s="2" t="s">
         <v>857</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>855</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>858</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
+        <v>838</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>831</v>
+      </c>
+      <c r="C8" s="2" t="s">
         <v>839</v>
       </c>
-      <c r="B8" s="2" t="s">
-        <v>832</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>840</v>
-      </c>
       <c r="D8" s="2" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="E8" s="2" t="s">
+        <v>858</v>
+      </c>
+      <c r="F8" s="2" t="s">
         <v>859</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>860</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A9" s="2" t="s">
+        <v>843</v>
+      </c>
+      <c r="B9" s="2" t="s">
         <v>844</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="C9" s="2" t="s">
         <v>845</v>
       </c>
-      <c r="C9" s="2" t="s">
-        <v>846</v>
-      </c>
       <c r="D9" s="2" t="s">
+        <v>860</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>854</v>
+      </c>
+      <c r="F9" s="2" t="s">
         <v>861</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>855</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>862</v>
       </c>
     </row>
   </sheetData>
@@ -9389,7 +9418,7 @@
   <sheetData>
     <row r="1" spans="1:5" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A1" s="7" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="B1" s="7"/>
       <c r="C1" s="7"/>
@@ -9398,189 +9427,189 @@
     </row>
     <row r="3" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
+        <v>863</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>864</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="C3" s="1" t="s">
         <v>865</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="D3" s="1" t="s">
         <v>866</v>
       </c>
-      <c r="D3" s="1" t="s">
-        <v>867</v>
-      </c>
       <c r="E3" s="1" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
+        <v>867</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>868</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="C4" s="2" t="s">
         <v>869</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="D4" s="2" t="s">
         <v>870</v>
       </c>
-      <c r="D4" s="2" t="s">
-        <v>871</v>
-      </c>
       <c r="E4" s="2" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="B5" s="2" t="s">
+        <v>871</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>872</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="D5" s="2" t="s">
         <v>873</v>
       </c>
-      <c r="D5" s="2" t="s">
-        <v>874</v>
-      </c>
       <c r="E5" s="2" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="B6" s="2" t="s">
+        <v>874</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>875</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="D6" s="2" t="s">
         <v>876</v>
       </c>
-      <c r="D6" s="2" t="s">
-        <v>877</v>
-      </c>
       <c r="E6" s="2" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="B7" s="2" t="s">
+        <v>877</v>
+      </c>
+      <c r="C7" s="2" t="s">
         <v>878</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="D7" s="2" t="s">
         <v>879</v>
       </c>
-      <c r="D7" s="2" t="s">
-        <v>880</v>
-      </c>
       <c r="E7" s="2" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="B8" s="2" t="s">
+        <v>880</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>880</v>
+      </c>
+      <c r="D8" s="2" t="s">
         <v>881</v>
       </c>
-      <c r="C8" s="2" t="s">
-        <v>881</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>882</v>
-      </c>
       <c r="E8" s="2" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A9" s="2" t="s">
+        <v>882</v>
+      </c>
+      <c r="B9" s="2" t="s">
         <v>883</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="C9" s="2" t="s">
+        <v>883</v>
+      </c>
+      <c r="D9" s="2" t="s">
         <v>884</v>
       </c>
-      <c r="C9" s="2" t="s">
-        <v>884</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>885</v>
-      </c>
       <c r="E9" s="2" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A10" s="2" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
       <c r="B10" s="2" t="s">
+        <v>885</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>885</v>
+      </c>
+      <c r="D10" s="2" t="s">
         <v>886</v>
       </c>
-      <c r="C10" s="2" t="s">
-        <v>886</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>887</v>
-      </c>
       <c r="E10" s="2" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A11" s="2" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
       <c r="B11" s="2" t="s">
+        <v>887</v>
+      </c>
+      <c r="C11" s="2" t="s">
         <v>888</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="D11" s="2" t="s">
         <v>889</v>
       </c>
-      <c r="D11" s="2" t="s">
-        <v>890</v>
-      </c>
       <c r="E11" s="2" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A12" s="2" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
       <c r="B12" s="2" t="s">
+        <v>890</v>
+      </c>
+      <c r="C12" s="2" t="s">
         <v>891</v>
       </c>
-      <c r="C12" s="2" t="s">
+      <c r="D12" s="2" t="s">
         <v>892</v>
       </c>
-      <c r="D12" s="2" t="s">
-        <v>893</v>
-      </c>
       <c r="E12" s="2" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A13" s="2" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
       <c r="B13" s="2" t="s">
+        <v>893</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>893</v>
+      </c>
+      <c r="D13" s="2" t="s">
         <v>894</v>
       </c>
-      <c r="C13" s="2" t="s">
-        <v>894</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>895</v>
-      </c>
       <c r="E13" s="2" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
     </row>
   </sheetData>
@@ -9827,7 +9856,7 @@
   <sheetData>
     <row r="1" spans="1:10" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A1" s="7" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="B1" s="7"/>
       <c r="C1" s="7"/>
@@ -9841,217 +9870,217 @@
     </row>
     <row r="3" spans="1:10" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
+        <v>896</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>897</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="C3" s="1" t="s">
+        <v>864</v>
+      </c>
+      <c r="D3" s="1" t="s">
         <v>898</v>
       </c>
-      <c r="C3" s="1" t="s">
-        <v>865</v>
-      </c>
-      <c r="D3" s="1" t="s">
+      <c r="E3" s="1" t="s">
         <v>899</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="F3" s="1" t="s">
         <v>900</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="G3" s="1" t="s">
         <v>901</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="H3" s="1" t="s">
         <v>902</v>
       </c>
-      <c r="H3" s="1" t="s">
+      <c r="I3" s="1" t="s">
         <v>903</v>
       </c>
-      <c r="I3" s="1" t="s">
-        <v>904</v>
-      </c>
       <c r="J3" s="1" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
+        <v>904</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>905</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="C4" s="2" t="s">
         <v>906</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="D4" s="2" t="s">
+        <v>868</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>883</v>
+      </c>
+      <c r="F4" s="2" t="s">
         <v>907</v>
       </c>
-      <c r="D4" s="2" t="s">
-        <v>869</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>884</v>
-      </c>
-      <c r="F4" s="2" t="s">
+      <c r="G4" s="2" t="s">
         <v>908</v>
       </c>
-      <c r="G4" s="2" t="s">
+      <c r="H4" s="2" t="s">
         <v>909</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>910</v>
       </c>
       <c r="I4" s="2" t="s">
         <v>63</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
+        <v>910</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>911</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="C5" s="2" t="s">
         <v>912</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="D5" s="2" t="s">
+        <v>871</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>883</v>
+      </c>
+      <c r="F5" s="2" t="s">
         <v>913</v>
       </c>
-      <c r="D5" s="2" t="s">
-        <v>872</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>884</v>
-      </c>
-      <c r="F5" s="2" t="s">
+      <c r="G5" s="2" t="s">
         <v>914</v>
       </c>
-      <c r="G5" s="2" t="s">
+      <c r="H5" s="2" t="s">
         <v>915</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>916</v>
       </c>
       <c r="I5" s="2" t="s">
         <v>48</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
+        <v>916</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>917</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="C6" s="2" t="s">
         <v>918</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="D6" s="2" t="s">
+        <v>871</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>883</v>
+      </c>
+      <c r="F6" s="2" t="s">
         <v>919</v>
       </c>
-      <c r="D6" s="2" t="s">
-        <v>872</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>884</v>
-      </c>
-      <c r="F6" s="2" t="s">
+      <c r="G6" s="2" t="s">
         <v>920</v>
       </c>
-      <c r="G6" s="2" t="s">
+      <c r="H6" s="2" t="s">
         <v>921</v>
       </c>
-      <c r="H6" s="2" t="s">
+      <c r="I6" s="2" t="s">
         <v>922</v>
       </c>
-      <c r="I6" s="2" t="s">
-        <v>923</v>
-      </c>
       <c r="J6" s="2" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
     </row>
     <row r="7" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
+        <v>923</v>
+      </c>
+      <c r="B7" s="2" t="s">
         <v>924</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="C7" s="2" t="s">
         <v>925</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="D7" s="2" t="s">
+        <v>874</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>883</v>
+      </c>
+      <c r="F7" s="2" t="s">
         <v>926</v>
       </c>
-      <c r="D7" s="2" t="s">
-        <v>875</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>884</v>
-      </c>
-      <c r="F7" s="2" t="s">
+      <c r="G7" s="2" t="s">
         <v>927</v>
       </c>
-      <c r="G7" s="2" t="s">
+      <c r="H7" s="2" t="s">
         <v>928</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>929</v>
       </c>
       <c r="I7" s="2" t="s">
         <v>18</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
+        <v>929</v>
+      </c>
+      <c r="B8" s="2" t="s">
         <v>930</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="C8" s="2" t="s">
         <v>931</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="D8" s="2" t="s">
+        <v>877</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>883</v>
+      </c>
+      <c r="F8" s="2" t="s">
         <v>932</v>
       </c>
-      <c r="D8" s="2" t="s">
-        <v>878</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>884</v>
-      </c>
-      <c r="F8" s="2" t="s">
+      <c r="G8" s="2" t="s">
         <v>933</v>
       </c>
-      <c r="G8" s="2" t="s">
+      <c r="H8" s="2" t="s">
         <v>934</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>935</v>
       </c>
       <c r="I8" s="2" t="s">
         <v>33</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
     </row>
     <row r="9" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A9" s="2" t="s">
+        <v>935</v>
+      </c>
+      <c r="B9" s="2" t="s">
         <v>936</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="C9" s="2" t="s">
         <v>937</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="D9" s="2" t="s">
+        <v>868</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>883</v>
+      </c>
+      <c r="F9" s="2" t="s">
         <v>938</v>
       </c>
-      <c r="D9" s="2" t="s">
-        <v>869</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>884</v>
-      </c>
-      <c r="F9" s="2" t="s">
+      <c r="G9" s="2" t="s">
         <v>939</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>940</v>
       </c>
       <c r="H9" s="2" t="s">
         <v>18</v>
@@ -10060,62 +10089,62 @@
         <v>33</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A10" s="2" t="s">
+        <v>941</v>
+      </c>
+      <c r="B10" s="2" t="s">
         <v>942</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="C10" s="2" t="s">
         <v>943</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="D10" s="2" t="s">
+        <v>871</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>883</v>
+      </c>
+      <c r="F10" s="2" t="s">
         <v>944</v>
       </c>
-      <c r="D10" s="2" t="s">
-        <v>872</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>884</v>
-      </c>
-      <c r="F10" s="2" t="s">
+      <c r="G10" s="2" t="s">
         <v>945</v>
       </c>
-      <c r="G10" s="2" t="s">
+      <c r="H10" s="2" t="s">
         <v>946</v>
-      </c>
-      <c r="H10" s="2" t="s">
-        <v>947</v>
       </c>
       <c r="I10" s="2" t="s">
         <v>63</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
     </row>
     <row r="11" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A11" s="2" t="s">
+        <v>948</v>
+      </c>
+      <c r="B11" s="2" t="s">
         <v>949</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="C11" s="2" t="s">
         <v>950</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="D11" s="2" t="s">
+        <v>868</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>883</v>
+      </c>
+      <c r="F11" s="2" t="s">
         <v>951</v>
       </c>
-      <c r="D11" s="2" t="s">
-        <v>869</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>884</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>952</v>
-      </c>
       <c r="G11" s="2" t="s">
-        <v>946</v>
+        <v>945</v>
       </c>
       <c r="H11" s="2" t="s">
         <v>33</v>
@@ -10124,7 +10153,7 @@
         <v>18</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
     </row>
   </sheetData>
@@ -10150,7 +10179,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A1" s="7" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
       <c r="B1" s="7"/>
       <c r="C1" s="7"/>
@@ -10161,117 +10190,117 @@
     </row>
     <row r="3" spans="1:7" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
+        <v>954</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>955</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="C3" s="1" t="s">
+        <v>899</v>
+      </c>
+      <c r="D3" s="1" t="s">
         <v>956</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="E3" s="1" t="s">
+        <v>901</v>
+      </c>
+      <c r="F3" s="1" t="s">
         <v>900</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="G3" s="1" t="s">
         <v>957</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>902</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>901</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>958</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>6</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="B5" s="2" t="s">
+        <v>959</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>887</v>
+      </c>
+      <c r="D5" s="2" t="s">
         <v>960</v>
       </c>
-      <c r="C5" s="2" t="s">
-        <v>888</v>
-      </c>
-      <c r="D5" s="2" t="s">
+      <c r="E5" s="2" t="s">
         <v>961</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="F5" s="2" t="s">
         <v>962</v>
       </c>
-      <c r="F5" s="2" t="s">
-        <v>963</v>
-      </c>
       <c r="G5" s="2" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>6</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>964</v>
+        <v>963</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>75</v>
       </c>
       <c r="E7" s="2" t="s">
+        <v>964</v>
+      </c>
+      <c r="F7" s="2" t="s">
         <v>965</v>
       </c>
-      <c r="F7" s="2" t="s">
-        <v>966</v>
-      </c>
       <c r="G7" s="2" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
     </row>
   </sheetData>
@@ -10294,7 +10323,7 @@
   <sheetData>
     <row r="1" spans="1:4" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A1" s="7" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="B1" s="7"/>
       <c r="C1" s="7"/>
@@ -10302,58 +10331,58 @@
     </row>
     <row r="3" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>967</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>968</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="D3" s="1" t="s">
         <v>969</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>970</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>39</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="B5" s="2" t="s">
+        <v>971</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>960</v>
+      </c>
+      <c r="D5" s="2" t="s">
         <v>972</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>961</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>973</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>974</v>
+        <v>973</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>75</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
     </row>
   </sheetData>
@@ -10381,7 +10410,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A1" s="7" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
       <c r="B1" s="7"/>
       <c r="C1" s="7"/>
@@ -10392,117 +10421,117 @@
     </row>
     <row r="3" spans="1:7" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
+        <v>976</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>864</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>977</v>
       </c>
-      <c r="B3" s="1" t="s">
-        <v>865</v>
-      </c>
-      <c r="C3" s="1" t="s">
+      <c r="D3" s="1" t="s">
         <v>978</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="E3" s="1" t="s">
         <v>979</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="F3" s="1" t="s">
         <v>980</v>
       </c>
-      <c r="F3" s="1" t="s">
-        <v>981</v>
-      </c>
       <c r="G3" s="1" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
+        <v>981</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>982</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="C4" s="2" t="s">
         <v>983</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="D4" s="2" t="s">
         <v>984</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="E4" s="2" t="s">
         <v>985</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="F4" s="2" t="s">
         <v>986</v>
       </c>
-      <c r="F4" s="2" t="s">
-        <v>987</v>
-      </c>
       <c r="G4" s="2" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
+        <v>987</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>988</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="C5" s="2" t="s">
         <v>989</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="D5" s="2" t="s">
         <v>990</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="E5" s="2" t="s">
         <v>991</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="F5" s="2" t="s">
         <v>992</v>
       </c>
-      <c r="F5" s="2" t="s">
-        <v>993</v>
-      </c>
       <c r="G5" s="2" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
+        <v>993</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>994</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="C6" s="2" t="s">
         <v>995</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="D6" s="2" t="s">
         <v>996</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="E6" s="2" t="s">
         <v>997</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="F6" s="2" t="s">
         <v>998</v>
       </c>
-      <c r="F6" s="2" t="s">
-        <v>999</v>
-      </c>
       <c r="G6" s="2" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
+        <v>999</v>
+      </c>
+      <c r="B7" s="2" t="s">
         <v>1000</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="C7" s="2" t="s">
         <v>1001</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="D7" s="2" t="s">
         <v>1002</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="E7" s="2" t="s">
         <v>1003</v>
       </c>
-      <c r="E7" s="2" t="s">
+      <c r="F7" s="2" t="s">
         <v>1004</v>
       </c>
-      <c r="F7" s="2" t="s">
-        <v>1005</v>
-      </c>
       <c r="G7" s="2" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
     </row>
   </sheetData>
@@ -10528,7 +10557,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A1" s="7" t="s">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="B1" s="7"/>
       <c r="C1" s="7"/>
@@ -10540,106 +10569,106 @@
     </row>
     <row r="3" spans="1:8" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
+        <v>1006</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>1007</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="C3" s="1" t="s">
         <v>1008</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="D3" s="1" t="s">
         <v>1009</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="E3" s="1" t="s">
         <v>1010</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="F3" s="1" t="s">
         <v>1011</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="G3" s="1" t="s">
         <v>1012</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="H3" s="1" t="s">
         <v>1013</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>1014</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
+        <v>1014</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>982</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>1015</v>
       </c>
-      <c r="B4" s="2" t="s">
-        <v>983</v>
-      </c>
-      <c r="C4" s="2" t="s">
+      <c r="D4" s="2" t="s">
         <v>1016</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="E4" s="2" t="s">
+        <v>939</v>
+      </c>
+      <c r="F4" s="2" t="s">
         <v>1017</v>
       </c>
-      <c r="E4" s="2" t="s">
-        <v>940</v>
-      </c>
-      <c r="F4" s="2" t="s">
+      <c r="G4" s="2" t="s">
         <v>1018</v>
       </c>
-      <c r="G4" s="2" t="s">
-        <v>1019</v>
-      </c>
       <c r="H4" s="2" t="s">
-        <v>1018</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
+        <v>1019</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>988</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>1020</v>
       </c>
-      <c r="B5" s="2" t="s">
-        <v>989</v>
-      </c>
-      <c r="C5" s="2" t="s">
+      <c r="D5" s="2" t="s">
         <v>1021</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="E5" s="2" t="s">
+        <v>946</v>
+      </c>
+      <c r="F5" s="2" t="s">
         <v>1022</v>
       </c>
-      <c r="E5" s="2" t="s">
-        <v>947</v>
-      </c>
-      <c r="F5" s="2" t="s">
+      <c r="G5" s="2" t="s">
         <v>1023</v>
       </c>
-      <c r="G5" s="2" t="s">
+      <c r="H5" s="2" t="s">
         <v>1024</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>1025</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
+        <v>1025</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>994</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>1026</v>
       </c>
-      <c r="B6" s="2" t="s">
-        <v>995</v>
-      </c>
-      <c r="C6" s="2" t="s">
+      <c r="D6" s="2" t="s">
         <v>1027</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="E6" s="2" t="s">
         <v>1028</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="F6" s="2" t="s">
         <v>1029</v>
       </c>
-      <c r="F6" s="2" t="s">
+      <c r="G6" s="2" t="s">
         <v>1030</v>
       </c>
-      <c r="G6" s="2" t="s">
-        <v>1031</v>
-      </c>
       <c r="H6" s="2" t="s">
-        <v>947</v>
+        <v>946</v>
       </c>
     </row>
   </sheetData>
@@ -10666,7 +10695,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A1" s="7" t="s">
-        <v>1032</v>
+        <v>1031</v>
       </c>
       <c r="B1" s="7"/>
       <c r="C1" s="7"/>
@@ -10676,102 +10705,102 @@
     </row>
     <row r="3" spans="1:6" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
+        <v>1032</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>864</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>978</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>977</v>
+      </c>
+      <c r="E3" s="1" t="s">
         <v>1033</v>
       </c>
-      <c r="B3" s="1" t="s">
-        <v>865</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>979</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>978</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>1034</v>
-      </c>
       <c r="F3" s="1" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
+        <v>1034</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>1035</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="C4" s="2" t="s">
         <v>1036</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="D4" s="2" t="s">
         <v>1037</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="E4" s="2" t="s">
         <v>1038</v>
       </c>
-      <c r="E4" s="2" t="s">
-        <v>1039</v>
-      </c>
       <c r="F4" s="2" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
+        <v>1039</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>1040</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="C5" s="2" t="s">
         <v>1041</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="D5" s="2" t="s">
         <v>1042</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="E5" s="2" t="s">
         <v>1043</v>
       </c>
-      <c r="E5" s="2" t="s">
-        <v>1044</v>
-      </c>
       <c r="F5" s="2" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
+        <v>1044</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>1045</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="C6" s="2" t="s">
         <v>1046</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="D6" s="2" t="s">
         <v>1047</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="E6" s="2" t="s">
         <v>1048</v>
       </c>
-      <c r="E6" s="2" t="s">
-        <v>1049</v>
-      </c>
       <c r="F6" s="2" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
+        <v>1049</v>
+      </c>
+      <c r="B7" s="2" t="s">
         <v>1050</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="C7" s="2" t="s">
         <v>1051</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="D7" s="2" t="s">
         <v>1052</v>
       </c>
-      <c r="D7" s="2" t="s">
-        <v>1053</v>
-      </c>
       <c r="E7" s="2" t="s">
-        <v>947</v>
+        <v>946</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
     </row>
   </sheetData>
@@ -10798,7 +10827,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A1" s="7" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
       <c r="B1" s="7"/>
       <c r="C1" s="7"/>
@@ -10809,94 +10838,94 @@
     </row>
     <row r="3" spans="1:7" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
+        <v>1054</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>1055</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="C3" s="1" t="s">
+        <v>1011</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>1013</v>
+      </c>
+      <c r="E3" s="1" t="s">
         <v>1056</v>
       </c>
-      <c r="C3" s="1" t="s">
-        <v>1012</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>1014</v>
-      </c>
-      <c r="E3" s="1" t="s">
+      <c r="F3" s="1" t="s">
         <v>1057</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="G3" s="1" t="s">
         <v>1058</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>1059</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
       <c r="B4" s="2" t="s">
+        <v>1059</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>1060</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="D4" s="2" t="s">
+        <v>946</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>1060</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>1030</v>
+      </c>
+      <c r="G4" s="2" t="s">
         <v>1061</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>947</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>1061</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>1031</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>1062</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
       <c r="B5" s="2" t="s">
+        <v>1062</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>1038</v>
+      </c>
+      <c r="D5" s="2" t="s">
         <v>1063</v>
       </c>
-      <c r="C5" s="2" t="s">
-        <v>1039</v>
-      </c>
-      <c r="D5" s="2" t="s">
+      <c r="E5" s="2" t="s">
+        <v>1063</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>1023</v>
+      </c>
+      <c r="G5" s="2" t="s">
         <v>1064</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>1064</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>1024</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>1065</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
       <c r="B6" s="2" t="s">
+        <v>1065</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>1066</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="D6" s="2" t="s">
+        <v>1066</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>946</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>1018</v>
+      </c>
+      <c r="G6" s="2" t="s">
         <v>1067</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>1067</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>947</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>1019</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>1068</v>
       </c>
     </row>
   </sheetData>
@@ -10920,7 +10949,7 @@
   <sheetData>
     <row r="1" spans="1:4" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A1" s="7" t="s">
-        <v>1069</v>
+        <v>1068</v>
       </c>
       <c r="B1" s="7"/>
       <c r="C1" s="7"/>
@@ -10928,58 +10957,58 @@
     </row>
     <row r="3" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>1069</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>1070</v>
       </c>
-      <c r="C3" s="1" t="s">
-        <v>1071</v>
-      </c>
       <c r="D3" s="1" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
+        <v>1071</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>1072</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="C4" s="2" t="s">
         <v>1073</v>
       </c>
-      <c r="C4" s="2" t="s">
-        <v>1074</v>
-      </c>
       <c r="D4" s="2" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
+        <v>1074</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>1073</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>1075</v>
       </c>
-      <c r="B5" s="2" t="s">
-        <v>1074</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>1076</v>
-      </c>
       <c r="D5" s="2" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>1073</v>
+        <v>1072</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
     </row>
   </sheetData>
@@ -11006,7 +11035,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A1" s="7" t="s">
-        <v>1078</v>
+        <v>1077</v>
       </c>
       <c r="B1" s="7"/>
       <c r="C1" s="7"/>
@@ -11018,106 +11047,106 @@
     </row>
     <row r="3" spans="1:8" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>1078</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>1079</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="D3" s="1" t="s">
         <v>1080</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="E3" s="1" t="s">
         <v>1081</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="F3" s="1" t="s">
         <v>1082</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="G3" s="1" t="s">
+        <v>1057</v>
+      </c>
+      <c r="H3" s="1" t="s">
         <v>1083</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>1058</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>1084</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>1072</v>
+        <v>1071</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
       <c r="D4" s="2" t="s">
+        <v>1084</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>1084</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>946</v>
+      </c>
+      <c r="G4" s="2" t="s">
         <v>1085</v>
       </c>
-      <c r="E4" s="2" t="s">
-        <v>1085</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>947</v>
-      </c>
-      <c r="G4" s="2" t="s">
+      <c r="H4" s="2" t="s">
         <v>1086</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>1087</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="C5" s="2" t="s">
+        <v>1087</v>
+      </c>
+      <c r="D5" s="2" t="s">
         <v>1088</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="E5" s="2" t="s">
+        <v>1043</v>
+      </c>
+      <c r="F5" s="2" t="s">
         <v>1089</v>
       </c>
-      <c r="E5" s="2" t="s">
-        <v>1044</v>
-      </c>
-      <c r="F5" s="2" t="s">
+      <c r="G5" s="2" t="s">
+        <v>1085</v>
+      </c>
+      <c r="H5" s="2" t="s">
         <v>1090</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>1086</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>1091</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
       <c r="C6" s="2" t="s">
+        <v>1091</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G6" s="2" t="s">
         <v>1092</v>
       </c>
-      <c r="D6" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="G6" s="2" t="s">
+      <c r="H6" s="2" t="s">
         <v>1093</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>1094</v>
       </c>
     </row>
   </sheetData>
@@ -11144,7 +11173,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A1" s="7" t="s">
-        <v>1095</v>
+        <v>1094</v>
       </c>
       <c r="B1" s="7"/>
       <c r="C1" s="7"/>
@@ -11154,102 +11183,102 @@
     </row>
     <row r="3" spans="1:6" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
+        <v>1095</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>898</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>866</v>
+      </c>
+      <c r="D3" s="1" t="s">
         <v>1096</v>
       </c>
-      <c r="B3" s="1" t="s">
-        <v>899</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>867</v>
-      </c>
-      <c r="D3" s="1" t="s">
+      <c r="E3" s="1" t="s">
         <v>1097</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="F3" s="1" t="s">
         <v>1098</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>1099</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
       <c r="B4" s="2" t="s">
+        <v>1099</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>1100</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="D4" s="2" t="s">
         <v>1101</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="E4" s="2" t="s">
         <v>1102</v>
       </c>
-      <c r="E4" s="2" t="s">
-        <v>1103</v>
-      </c>
       <c r="F4" s="2" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
       <c r="B5" s="2" t="s">
+        <v>1103</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>1104</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="D5" s="2" t="s">
         <v>1105</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="E5" s="2" t="s">
         <v>1106</v>
       </c>
-      <c r="E5" s="2" t="s">
-        <v>1107</v>
-      </c>
       <c r="F5" s="2" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
+        <v>1107</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>1108</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="C6" s="2" t="s">
         <v>1109</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="D6" s="2" t="s">
         <v>1110</v>
       </c>
-      <c r="D6" s="2" t="s">
-        <v>1111</v>
-      </c>
       <c r="E6" s="2" t="s">
-        <v>1103</v>
+        <v>1102</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
-        <v>1108</v>
+        <v>1107</v>
       </c>
       <c r="B7" s="2" t="s">
+        <v>1111</v>
+      </c>
+      <c r="C7" s="2" t="s">
         <v>1112</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="D7" s="2" t="s">
         <v>1113</v>
       </c>
-      <c r="D7" s="2" t="s">
-        <v>1114</v>
-      </c>
       <c r="E7" s="2" t="s">
-        <v>1103</v>
+        <v>1102</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
     </row>
   </sheetData>
@@ -11263,7 +11292,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:H13"/>
+  <dimension ref="A1:H14"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
@@ -11337,7 +11366,7 @@
         <v>5</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="29" x14ac:dyDescent="0.35">
@@ -11363,7 +11392,7 @@
         <v>5</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
@@ -11389,7 +11418,7 @@
         <v>5</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="29" x14ac:dyDescent="0.35">
@@ -11414,8 +11443,8 @@
       <c r="G7" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="H7" s="2" t="s">
-        <v>5</v>
+      <c r="H7" s="3" t="s">
+        <v>1139</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="29" x14ac:dyDescent="0.35">
@@ -11441,7 +11470,7 @@
         <v>5</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="29" x14ac:dyDescent="0.35">
@@ -11467,7 +11496,7 @@
         <v>5</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="58" x14ac:dyDescent="0.35">
@@ -11492,8 +11521,8 @@
       <c r="G10" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="H10" s="2" t="s">
-        <v>5</v>
+      <c r="H10" s="3" t="s">
+        <v>1139</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="29" x14ac:dyDescent="0.35">
@@ -11518,8 +11547,8 @@
       <c r="G11" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="H11" s="2" t="s">
-        <v>5</v>
+      <c r="H11" s="3" t="s">
+        <v>1139</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.35">
@@ -11544,11 +11573,11 @@
       <c r="G12" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="H12" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="H12" s="3" t="s">
+        <v>1139</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="58" x14ac:dyDescent="0.35">
       <c r="A13" s="2">
         <v>10</v>
       </c>
@@ -11565,13 +11594,36 @@
         <v>227</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>228</v>
+        <v>1144</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="H13" s="2" t="s">
-        <v>5</v>
+      <c r="H13" s="3" t="s">
+        <v>1139</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" ht="58" x14ac:dyDescent="0.35">
+      <c r="A14" s="8">
+        <v>11</v>
+      </c>
+      <c r="B14" s="8" t="s">
+        <v>119</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>1140</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>1141</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>1142</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>1143</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>1139</v>
       </c>
     </row>
   </sheetData>
@@ -11599,7 +11651,7 @@
   <sheetData>
     <row r="1" spans="1:10" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A1" s="7" t="s">
-        <v>1115</v>
+        <v>1114</v>
       </c>
       <c r="B1" s="7"/>
       <c r="C1" s="7"/>
@@ -11613,226 +11665,226 @@
     </row>
     <row r="3" spans="1:10" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
+        <v>1115</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>856</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>1009</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>1097</v>
+      </c>
+      <c r="E3" s="1" t="s">
         <v>1116</v>
       </c>
-      <c r="B3" s="1" t="s">
-        <v>857</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>1010</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>1098</v>
-      </c>
-      <c r="E3" s="1" t="s">
+      <c r="F3" s="1" t="s">
+        <v>1011</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>1054</v>
+      </c>
+      <c r="H3" s="1" t="s">
         <v>1117</v>
       </c>
-      <c r="F3" s="1" t="s">
-        <v>1012</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>1055</v>
-      </c>
-      <c r="H3" s="1" t="s">
+      <c r="I3" s="1" t="s">
+        <v>1057</v>
+      </c>
+      <c r="J3" s="1" t="s">
         <v>1118</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>1058</v>
-      </c>
-      <c r="J3" s="1" t="s">
-        <v>1119</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
+        <v>1119</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>830</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>1120</v>
       </c>
-      <c r="B4" s="2" t="s">
-        <v>831</v>
-      </c>
-      <c r="C4" s="2" t="s">
+      <c r="D4" s="2" t="s">
+        <v>1102</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>939</v>
+      </c>
+      <c r="F4" s="2" t="s">
         <v>1121</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>1103</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>940</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>1122</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>159</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="I4" s="2" t="s">
+        <v>1122</v>
+      </c>
+      <c r="J4" s="2" t="s">
         <v>1123</v>
-      </c>
-      <c r="J4" s="2" t="s">
-        <v>1124</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
+        <v>1124</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>830</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>1125</v>
       </c>
-      <c r="B5" s="2" t="s">
-        <v>831</v>
-      </c>
-      <c r="C5" s="2" t="s">
+      <c r="D5" s="2" t="s">
         <v>1126</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="E5" s="2" t="s">
         <v>1127</v>
       </c>
-      <c r="E5" s="2" t="s">
-        <v>1128</v>
-      </c>
       <c r="F5" s="2" t="s">
-        <v>1128</v>
+        <v>1127</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>159</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>1129</v>
+        <v>1128</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
+        <v>1129</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>834</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>1130</v>
       </c>
-      <c r="B6" s="2" t="s">
-        <v>835</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>1131</v>
-      </c>
       <c r="D6" s="2" t="s">
-        <v>1107</v>
+        <v>1106</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>159</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>1132</v>
+        <v>1131</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
+        <v>1059</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>830</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>1132</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>1133</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>946</v>
+      </c>
+      <c r="F7" s="2" t="s">
         <v>1060</v>
       </c>
-      <c r="B7" s="2" t="s">
-        <v>831</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>1133</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>1134</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>947</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>1061</v>
-      </c>
       <c r="G7" s="2" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="I7" s="2" t="s">
+        <v>1122</v>
+      </c>
+      <c r="J7" s="2" t="s">
         <v>1123</v>
-      </c>
-      <c r="J7" s="2" t="s">
-        <v>1124</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>1135</v>
+        <v>1134</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>1103</v>
+        <v>1102</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>159</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="I8" s="2" t="s">
+        <v>1122</v>
+      </c>
+      <c r="J8" s="2" t="s">
         <v>1123</v>
-      </c>
-      <c r="J8" s="2" t="s">
-        <v>1124</v>
       </c>
     </row>
     <row r="9" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A9" s="2" t="s">
+        <v>1135</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>830</v>
+      </c>
+      <c r="C9" s="2" t="s">
         <v>1136</v>
       </c>
-      <c r="B9" s="2" t="s">
-        <v>831</v>
-      </c>
-      <c r="C9" s="2" t="s">
+      <c r="D9" s="2" t="s">
+        <v>1102</v>
+      </c>
+      <c r="E9" s="2" t="s">
         <v>1137</v>
       </c>
-      <c r="D9" s="2" t="s">
-        <v>1103</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>1138</v>
-      </c>
       <c r="F9" s="2" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>159</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>1139</v>
+        <v>1138</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
     </row>
   </sheetData>
@@ -11861,7 +11913,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A1" s="4" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B1" s="4"/>
       <c r="C1" s="4"/>
@@ -11902,19 +11954,19 @@
         <v>1</v>
       </c>
       <c r="B4" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>230</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="D4" s="2" t="s">
         <v>231</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>232</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>159</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>5</v>
@@ -11931,16 +11983,16 @@
         <v>128</v>
       </c>
       <c r="C5" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="D5" s="2" t="s">
         <v>234</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>235</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>159</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>5</v>
@@ -11957,16 +12009,16 @@
         <v>119</v>
       </c>
       <c r="C6" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="D6" s="2" t="s">
         <v>237</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="E6" s="2" t="s">
         <v>238</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="F6" s="2" t="s">
         <v>239</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>240</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>5</v>
@@ -11983,16 +12035,16 @@
         <v>124</v>
       </c>
       <c r="C7" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="D7" s="2" t="s">
         <v>241</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>242</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>159</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>5</v>
@@ -12009,16 +12061,16 @@
         <v>119</v>
       </c>
       <c r="C8" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="D8" s="2" t="s">
         <v>244</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="E8" s="2" t="s">
         <v>245</v>
       </c>
-      <c r="E8" s="2" t="s">
+      <c r="F8" s="2" t="s">
         <v>246</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>247</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>5</v>
@@ -12035,16 +12087,16 @@
         <v>119</v>
       </c>
       <c r="C9" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="D9" s="2" t="s">
         <v>248</v>
       </c>
-      <c r="D9" s="2" t="s">
+      <c r="E9" s="2" t="s">
         <v>249</v>
       </c>
-      <c r="E9" s="2" t="s">
+      <c r="F9" s="2" t="s">
         <v>250</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>251</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>5</v>
@@ -12061,16 +12113,16 @@
         <v>119</v>
       </c>
       <c r="C10" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="D10" s="2" t="s">
         <v>252</v>
       </c>
-      <c r="D10" s="2" t="s">
+      <c r="E10" s="2" t="s">
         <v>253</v>
       </c>
-      <c r="E10" s="2" t="s">
+      <c r="F10" s="2" t="s">
         <v>254</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>255</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>5</v>
@@ -12087,16 +12139,16 @@
         <v>119</v>
       </c>
       <c r="C11" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="D11" s="2" t="s">
         <v>256</v>
       </c>
-      <c r="D11" s="2" t="s">
+      <c r="E11" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="F11" s="2" t="s">
         <v>257</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>254</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>258</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>5</v>
@@ -12131,7 +12183,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A1" s="4" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B1" s="4"/>
       <c r="C1" s="4"/>
@@ -12175,16 +12227,16 @@
         <v>132</v>
       </c>
       <c r="C4" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="D4" s="2" t="s">
         <v>260</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="E4" s="2" t="s">
         <v>261</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="F4" s="2" t="s">
         <v>262</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>263</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>5</v>
@@ -12198,19 +12250,19 @@
         <v>2</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C5" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="D5" s="2" t="s">
         <v>264</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>265</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>159</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>5</v>
@@ -12227,16 +12279,16 @@
         <v>119</v>
       </c>
       <c r="C6" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="D6" s="2" t="s">
         <v>267</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="E6" s="2" t="s">
         <v>268</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="F6" s="2" t="s">
         <v>269</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>270</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>5</v>
@@ -12253,16 +12305,16 @@
         <v>119</v>
       </c>
       <c r="C7" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="D7" s="2" t="s">
         <v>271</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="E7" s="2" t="s">
         <v>272</v>
       </c>
-      <c r="E7" s="2" t="s">
+      <c r="F7" s="2" t="s">
         <v>273</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>274</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>5</v>
@@ -12279,16 +12331,16 @@
         <v>124</v>
       </c>
       <c r="C8" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="D8" s="2" t="s">
         <v>275</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>276</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>159</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>5</v>
@@ -12302,19 +12354,19 @@
         <v>6</v>
       </c>
       <c r="B9" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="C9" s="2" t="s">
         <v>277</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="D9" s="2" t="s">
         <v>278</v>
       </c>
-      <c r="D9" s="2" t="s">
+      <c r="E9" s="2" t="s">
         <v>279</v>
       </c>
-      <c r="E9" s="2" t="s">
+      <c r="F9" s="2" t="s">
         <v>280</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>281</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>5</v>
@@ -12349,7 +12401,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A1" s="4" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="B1" s="4"/>
       <c r="C1" s="4"/>
@@ -12390,19 +12442,19 @@
         <v>1</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C4" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="D4" s="2" t="s">
         <v>283</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>284</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>159</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>5</v>
@@ -12416,19 +12468,19 @@
         <v>2</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C5" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="D5" s="2" t="s">
         <v>286</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="E5" s="2" t="s">
         <v>287</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="F5" s="2" t="s">
         <v>288</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>289</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>5</v>
@@ -12442,19 +12494,19 @@
         <v>3</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C6" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="D6" s="2" t="s">
         <v>290</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="E6" s="2" t="s">
         <v>291</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="F6" s="2" t="s">
         <v>292</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>293</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>5</v>
@@ -12468,19 +12520,19 @@
         <v>4</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C7" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="D7" s="2" t="s">
         <v>294</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="E7" s="2" t="s">
         <v>295</v>
       </c>
-      <c r="E7" s="2" t="s">
+      <c r="F7" s="2" t="s">
         <v>296</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>297</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>5</v>
@@ -12494,19 +12546,19 @@
         <v>5</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C8" s="2" t="s">
+        <v>297</v>
+      </c>
+      <c r="D8" s="2" t="s">
         <v>298</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="E8" s="2" t="s">
         <v>299</v>
       </c>
-      <c r="E8" s="2" t="s">
+      <c r="F8" s="2" t="s">
         <v>300</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>301</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>5</v>
@@ -12520,19 +12572,19 @@
         <v>6</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C9" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="D9" s="2" t="s">
         <v>302</v>
       </c>
-      <c r="D9" s="2" t="s">
+      <c r="E9" s="2" t="s">
         <v>303</v>
       </c>
-      <c r="E9" s="2" t="s">
+      <c r="F9" s="2" t="s">
         <v>304</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>305</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>5</v>
@@ -12546,19 +12598,19 @@
         <v>7</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C10" s="2" t="s">
+        <v>305</v>
+      </c>
+      <c r="D10" s="2" t="s">
         <v>306</v>
       </c>
-      <c r="D10" s="2" t="s">
+      <c r="E10" s="2" t="s">
         <v>307</v>
       </c>
-      <c r="E10" s="2" t="s">
+      <c r="F10" s="2" t="s">
         <v>308</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>309</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>5</v>
@@ -12575,16 +12627,16 @@
         <v>128</v>
       </c>
       <c r="C11" s="2" t="s">
+        <v>309</v>
+      </c>
+      <c r="D11" s="2" t="s">
         <v>310</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>311</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>159</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>5</v>
@@ -12619,7 +12671,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A1" s="4" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B1" s="4"/>
       <c r="C1" s="4"/>
@@ -12660,19 +12712,19 @@
         <v>1</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C4" s="2" t="s">
+        <v>313</v>
+      </c>
+      <c r="D4" s="2" t="s">
         <v>314</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>315</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>159</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>5</v>
@@ -12686,19 +12738,19 @@
         <v>2</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C5" s="2" t="s">
+        <v>316</v>
+      </c>
+      <c r="D5" s="2" t="s">
         <v>317</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="E5" s="2" t="s">
         <v>318</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="F5" s="2" t="s">
         <v>319</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>320</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>5</v>
@@ -12712,19 +12764,19 @@
         <v>3</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C6" s="2" t="s">
+        <v>320</v>
+      </c>
+      <c r="D6" s="2" t="s">
         <v>321</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="E6" s="2" t="s">
         <v>322</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="F6" s="2" t="s">
         <v>323</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>324</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>5</v>
@@ -12738,19 +12790,19 @@
         <v>4</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C7" s="2" t="s">
+        <v>324</v>
+      </c>
+      <c r="D7" s="2" t="s">
         <v>325</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="E7" s="2" t="s">
         <v>326</v>
       </c>
-      <c r="E7" s="2" t="s">
-        <v>327</v>
-      </c>
       <c r="F7" s="2" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>5</v>
@@ -12764,19 +12816,19 @@
         <v>5</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C8" s="2" t="s">
+        <v>327</v>
+      </c>
+      <c r="D8" s="2" t="s">
         <v>328</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="E8" s="2" t="s">
         <v>329</v>
       </c>
-      <c r="E8" s="2" t="s">
+      <c r="F8" s="2" t="s">
         <v>330</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>331</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>5</v>
@@ -12811,7 +12863,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A1" s="4" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B1" s="4"/>
       <c r="C1" s="4"/>
@@ -12852,19 +12904,19 @@
         <v>1</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C4" s="2" t="s">
+        <v>332</v>
+      </c>
+      <c r="D4" s="2" t="s">
         <v>333</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="E4" s="2" t="s">
         <v>334</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="F4" s="2" t="s">
         <v>335</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>336</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>5</v>
@@ -12878,19 +12930,19 @@
         <v>2</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C5" s="2" t="s">
+        <v>336</v>
+      </c>
+      <c r="D5" s="2" t="s">
         <v>337</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="E5" s="2" t="s">
         <v>338</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="F5" s="2" t="s">
         <v>339</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>340</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>5</v>
@@ -12904,19 +12956,19 @@
         <v>3</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C6" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="D6" s="2" t="s">
         <v>341</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="E6" s="2" t="s">
         <v>342</v>
       </c>
-      <c r="E6" s="2" t="s">
-        <v>343</v>
-      </c>
       <c r="F6" s="2" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>5</v>
@@ -12930,19 +12982,19 @@
         <v>4</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C7" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="D7" s="2" t="s">
         <v>344</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="E7" s="2" t="s">
         <v>345</v>
       </c>
-      <c r="E7" s="2" t="s">
+      <c r="F7" s="2" t="s">
         <v>346</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>347</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>5</v>
@@ -12956,19 +13008,19 @@
         <v>5</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C8" s="2" t="s">
+        <v>347</v>
+      </c>
+      <c r="D8" s="2" t="s">
         <v>348</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="E8" s="2" t="s">
         <v>349</v>
       </c>
-      <c r="E8" s="2" t="s">
+      <c r="F8" s="2" t="s">
         <v>350</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>351</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>5</v>
@@ -12982,19 +13034,19 @@
         <v>6</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C9" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="D9" s="2" t="s">
         <v>352</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>353</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>159</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>5</v>
@@ -13008,19 +13060,19 @@
         <v>7</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C10" s="2" t="s">
+        <v>354</v>
+      </c>
+      <c r="D10" s="2" t="s">
         <v>355</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>356</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>159</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>5</v>
@@ -13034,19 +13086,19 @@
         <v>8</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C11" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="D11" s="2" t="s">
         <v>358</v>
       </c>
-      <c r="D11" s="2" t="s">
+      <c r="E11" s="2" t="s">
         <v>359</v>
       </c>
-      <c r="E11" s="2" t="s">
+      <c r="F11" s="2" t="s">
         <v>360</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>361</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>5</v>
@@ -13060,19 +13112,19 @@
         <v>9</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C12" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="D12" s="2" t="s">
         <v>362</v>
       </c>
-      <c r="D12" s="2" t="s">
+      <c r="E12" s="2" t="s">
         <v>363</v>
       </c>
-      <c r="E12" s="2" t="s">
+      <c r="F12" s="2" t="s">
         <v>364</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>365</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>5</v>
@@ -13086,19 +13138,19 @@
         <v>10</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C13" s="2" t="s">
+        <v>365</v>
+      </c>
+      <c r="D13" s="2" t="s">
         <v>366</v>
       </c>
-      <c r="D13" s="2" t="s">
+      <c r="E13" s="2" t="s">
         <v>367</v>
       </c>
-      <c r="E13" s="2" t="s">
+      <c r="F13" s="2" t="s">
         <v>368</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>369</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>5</v>
@@ -13112,19 +13164,19 @@
         <v>11</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C14" s="2" t="s">
+        <v>369</v>
+      </c>
+      <c r="D14" s="2" t="s">
         <v>370</v>
       </c>
-      <c r="D14" s="2" t="s">
+      <c r="E14" s="2" t="s">
         <v>371</v>
       </c>
-      <c r="E14" s="2" t="s">
+      <c r="F14" s="2" t="s">
         <v>372</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>373</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>5</v>
@@ -13138,19 +13190,19 @@
         <v>12</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C15" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="D15" s="2" t="s">
         <v>374</v>
       </c>
-      <c r="D15" s="2" t="s">
+      <c r="E15" s="2" t="s">
         <v>375</v>
       </c>
-      <c r="E15" s="2" t="s">
+      <c r="F15" s="2" t="s">
         <v>376</v>
-      </c>
-      <c r="F15" s="2" t="s">
-        <v>377</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>5</v>
@@ -13164,19 +13216,19 @@
         <v>13</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C16" s="2" t="s">
+        <v>377</v>
+      </c>
+      <c r="D16" s="2" t="s">
         <v>378</v>
       </c>
-      <c r="D16" s="2" t="s">
+      <c r="E16" s="2" t="s">
         <v>379</v>
       </c>
-      <c r="E16" s="2" t="s">
+      <c r="F16" s="2" t="s">
         <v>380</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>381</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>5</v>
@@ -13190,19 +13242,19 @@
         <v>14</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C17" s="2" t="s">
+        <v>381</v>
+      </c>
+      <c r="D17" s="2" t="s">
         <v>382</v>
       </c>
-      <c r="D17" s="2" t="s">
+      <c r="E17" s="2" t="s">
         <v>383</v>
       </c>
-      <c r="E17" s="2" t="s">
+      <c r="F17" s="2" t="s">
         <v>384</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>385</v>
       </c>
       <c r="G17" s="2" t="s">
         <v>5</v>
@@ -13216,19 +13268,19 @@
         <v>15</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C18" s="2" t="s">
+        <v>385</v>
+      </c>
+      <c r="D18" s="2" t="s">
         <v>386</v>
       </c>
-      <c r="D18" s="2" t="s">
+      <c r="E18" s="2" t="s">
         <v>387</v>
       </c>
-      <c r="E18" s="2" t="s">
+      <c r="F18" s="2" t="s">
         <v>388</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>389</v>
       </c>
       <c r="G18" s="2" t="s">
         <v>5</v>
@@ -13242,19 +13294,19 @@
         <v>16</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C19" s="2" t="s">
+        <v>389</v>
+      </c>
+      <c r="D19" s="2" t="s">
         <v>390</v>
       </c>
-      <c r="D19" s="2" t="s">
+      <c r="E19" s="2" t="s">
         <v>391</v>
       </c>
-      <c r="E19" s="2" t="s">
+      <c r="F19" s="2" t="s">
         <v>392</v>
-      </c>
-      <c r="F19" s="2" t="s">
-        <v>393</v>
       </c>
       <c r="G19" s="2" t="s">
         <v>5</v>
@@ -13271,16 +13323,16 @@
         <v>128</v>
       </c>
       <c r="C20" s="2" t="s">
+        <v>393</v>
+      </c>
+      <c r="D20" s="2" t="s">
         <v>394</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>395</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>159</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>5</v>

--- a/docs/Dokumen_Testing_POS.xlsx
+++ b/docs/Dokumen_Testing_POS.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B622D1D-8511-4DA0-99AB-06F5CBF0DC2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A30E675-21F9-472F-BA0C-A7384CDF5442}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="867" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="867" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Daftar Isi" sheetId="1" r:id="rId1"/>
@@ -54,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2248" uniqueCount="1145">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2262" uniqueCount="1149">
   <si>
     <t>DOKUMEN TESTING APLIKASI POS</t>
   </si>
@@ -3631,6 +3631,18 @@
   </si>
   <si>
     <t>Button hapus/nonaktifkan owner yang sedang digunakan disabled. Jadi karena button disabled tidak bisa di klik.</t>
+  </si>
+  <si>
+    <t>Tambah unit dengan name duplikat</t>
+  </si>
+  <si>
+    <t>1. Isi name yang sudah ada</t>
+  </si>
+  <si>
+    <t>name: Box</t>
+  </si>
+  <si>
+    <t>Tambah kategori tanpa nama (required)</t>
   </si>
 </sst>
 </file>
@@ -7341,8 +7353,8 @@
       <c r="G13" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="H13" s="2" t="s">
-        <v>5</v>
+      <c r="H13" s="3" t="s">
+        <v>1139</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
@@ -12386,7 +12398,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
@@ -12459,8 +12471,8 @@
       <c r="G4" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="2" t="s">
-        <v>5</v>
+      <c r="H4" s="3" t="s">
+        <v>1139</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
@@ -12485,8 +12497,8 @@
       <c r="G5" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="H5" s="2" t="s">
-        <v>5</v>
+      <c r="H5" s="3" t="s">
+        <v>1139</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="29" x14ac:dyDescent="0.35">
@@ -12511,8 +12523,8 @@
       <c r="G6" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="H6" s="2" t="s">
-        <v>5</v>
+      <c r="H6" s="3" t="s">
+        <v>1139</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="29" x14ac:dyDescent="0.35">
@@ -12643,6 +12655,32 @@
       </c>
       <c r="H11" s="2" t="s">
         <v>5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="29" x14ac:dyDescent="0.35">
+      <c r="A12" s="2">
+        <v>3</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>1148</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>322</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>1139</v>
       </c>
     </row>
   </sheetData>
@@ -12656,7 +12694,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
-  <dimension ref="A1:H8"/>
+  <dimension ref="A1:H9"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
@@ -12729,8 +12767,8 @@
       <c r="G4" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="2" t="s">
-        <v>5</v>
+      <c r="H4" s="3" t="s">
+        <v>1139</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
@@ -12755,8 +12793,8 @@
       <c r="G5" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="H5" s="2" t="s">
-        <v>5</v>
+      <c r="H5" s="3" t="s">
+        <v>1139</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="29" x14ac:dyDescent="0.35">
@@ -12781,8 +12819,8 @@
       <c r="G6" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="H6" s="2" t="s">
-        <v>5</v>
+      <c r="H6" s="3" t="s">
+        <v>1139</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
@@ -12835,6 +12873,32 @@
       </c>
       <c r="H8" s="2" t="s">
         <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A9" s="2">
+        <v>3</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>1145</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>1146</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>1147</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>1139</v>
       </c>
     </row>
   </sheetData>

--- a/docs/Dokumen_Testing_POS.xlsx
+++ b/docs/Dokumen_Testing_POS.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A30E675-21F9-472F-BA0C-A7384CDF5442}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4393C7C9-49DA-405F-A7C9-082D32B48FFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="867" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="867" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Daftar Isi" sheetId="1" r:id="rId1"/>
@@ -54,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2262" uniqueCount="1149">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2290" uniqueCount="1159">
   <si>
     <t>DOKUMEN TESTING APLIKASI POS</t>
   </si>
@@ -976,18 +976,6 @@
   </si>
   <si>
     <t>Validasi gagal unique code</t>
-  </si>
-  <si>
-    <t>Tambah kategori dengan kode &gt; 10 karakter</t>
-  </si>
-  <si>
-    <t>1. Isi kode terlalu panjang</t>
-  </si>
-  <si>
-    <t>code: KATEGORIPANJANGSEKALI</t>
-  </si>
-  <si>
-    <t>Validasi gagal max length</t>
   </si>
   <si>
     <t>Edit kategori</t>
@@ -3643,6 +3631,48 @@
   </si>
   <si>
     <t>Tambah kategori tanpa nama (required)</t>
+  </si>
+  <si>
+    <t>Nonaktifkan satuan (toggle status)</t>
+  </si>
+  <si>
+    <t>1. Toggle status satuan</t>
+  </si>
+  <si>
+    <t>kategori: ATK</t>
+  </si>
+  <si>
+    <t>Kasir mengakses list satuan (tanpa permission middleware)</t>
+  </si>
+  <si>
+    <t>Hapus kategori</t>
+  </si>
+  <si>
+    <t>1. Klik hapus pada kaegori test</t>
+  </si>
+  <si>
+    <t>Kategori terhapus dari list</t>
+  </si>
+  <si>
+    <t>Hapus Unit</t>
+  </si>
+  <si>
+    <t>1. Klik hapus pada Unit test</t>
+  </si>
+  <si>
+    <t>Unit terhapus dari list</t>
+  </si>
+  <si>
+    <t>Hapus Produk</t>
+  </si>
+  <si>
+    <t>1. Klik hapus pada Produk test</t>
+  </si>
+  <si>
+    <t>Produk terhapus dari list</t>
+  </si>
+  <si>
+    <t>unit: ATK</t>
   </si>
 </sst>
 </file>
@@ -3764,15 +3794,15 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4122,20 +4152,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5"/>
-      <c r="C1" s="5"/>
-      <c r="D1" s="5"/>
+      <c r="B1" s="6"/>
+      <c r="C1" s="6"/>
+      <c r="D1" s="6"/>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A2" s="6" t="s">
+      <c r="A2" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="6"/>
-      <c r="C2" s="6"/>
-      <c r="D2" s="6"/>
+      <c r="B2" s="7"/>
+      <c r="C2" s="7"/>
+      <c r="D2" s="7"/>
     </row>
     <row r="4" spans="1:4" ht="18.649999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
@@ -4620,16 +4650,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="A1" s="4" t="s">
-        <v>396</v>
-      </c>
-      <c r="B1" s="4"/>
-      <c r="C1" s="4"/>
-      <c r="D1" s="4"/>
-      <c r="E1" s="4"/>
-      <c r="F1" s="4"/>
-      <c r="G1" s="4"/>
-      <c r="H1" s="4"/>
+      <c r="A1" s="5" t="s">
+        <v>392</v>
+      </c>
+      <c r="B1" s="5"/>
+      <c r="C1" s="5"/>
+      <c r="D1" s="5"/>
+      <c r="E1" s="5"/>
+      <c r="F1" s="5"/>
+      <c r="G1" s="5"/>
+      <c r="H1" s="5"/>
     </row>
     <row r="3" spans="1:8" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
@@ -4665,16 +4695,16 @@
         <v>229</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>397</v>
+        <v>393</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>159</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>399</v>
+        <v>395</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>5</v>
@@ -4691,16 +4721,16 @@
         <v>229</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>400</v>
+        <v>396</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>401</v>
+        <v>397</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>403</v>
+        <v>399</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>5</v>
@@ -4717,13 +4747,13 @@
         <v>229</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>404</v>
+        <v>400</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>405</v>
+        <v>401</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>246</v>
@@ -4743,16 +4773,16 @@
         <v>229</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>409</v>
+        <v>405</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>5</v>
@@ -4769,16 +4799,16 @@
         <v>229</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>411</v>
+        <v>407</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>413</v>
+        <v>409</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>5</v>
@@ -4795,16 +4825,16 @@
         <v>229</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>415</v>
+        <v>411</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>416</v>
+        <v>412</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>417</v>
+        <v>413</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>5</v>
@@ -4838,16 +4868,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="A1" s="4" t="s">
-        <v>418</v>
-      </c>
-      <c r="B1" s="4"/>
-      <c r="C1" s="4"/>
-      <c r="D1" s="4"/>
-      <c r="E1" s="4"/>
-      <c r="F1" s="4"/>
-      <c r="G1" s="4"/>
-      <c r="H1" s="4"/>
+      <c r="A1" s="5" t="s">
+        <v>414</v>
+      </c>
+      <c r="B1" s="5"/>
+      <c r="C1" s="5"/>
+      <c r="D1" s="5"/>
+      <c r="E1" s="5"/>
+      <c r="F1" s="5"/>
+      <c r="G1" s="5"/>
+      <c r="H1" s="5"/>
     </row>
     <row r="3" spans="1:8" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
@@ -4883,16 +4913,16 @@
         <v>229</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>419</v>
+        <v>415</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>420</v>
+        <v>416</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>159</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>421</v>
+        <v>417</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>5</v>
@@ -4909,16 +4939,16 @@
         <v>229</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>422</v>
+        <v>418</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>423</v>
+        <v>419</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>424</v>
+        <v>420</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>425</v>
+        <v>421</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>5</v>
@@ -4935,16 +4965,16 @@
         <v>229</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>426</v>
+        <v>422</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>427</v>
+        <v>423</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>428</v>
+        <v>424</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>429</v>
+        <v>425</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>5</v>
@@ -4961,16 +4991,16 @@
         <v>229</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>430</v>
+        <v>426</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>433</v>
+        <v>429</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>5</v>
@@ -4987,16 +5017,16 @@
         <v>229</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>434</v>
+        <v>430</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>435</v>
+        <v>431</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>436</v>
+        <v>432</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>437</v>
+        <v>433</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>5</v>
@@ -5013,16 +5043,16 @@
         <v>229</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>438</v>
+        <v>434</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>439</v>
+        <v>435</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>159</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>440</v>
+        <v>436</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>5</v>
@@ -5039,16 +5069,16 @@
         <v>229</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>441</v>
+        <v>437</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>442</v>
+        <v>438</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>443</v>
+        <v>439</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>444</v>
+        <v>440</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>5</v>
@@ -5065,16 +5095,16 @@
         <v>229</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>445</v>
+        <v>441</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>446</v>
+        <v>442</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>159</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>447</v>
+        <v>443</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>5</v>
@@ -5091,16 +5121,16 @@
         <v>229</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>448</v>
+        <v>444</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>449</v>
+        <v>445</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>159</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>450</v>
+        <v>446</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>5</v>
@@ -5134,16 +5164,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="A1" s="4" t="s">
-        <v>451</v>
-      </c>
-      <c r="B1" s="4"/>
-      <c r="C1" s="4"/>
-      <c r="D1" s="4"/>
-      <c r="E1" s="4"/>
-      <c r="F1" s="4"/>
-      <c r="G1" s="4"/>
-      <c r="H1" s="4"/>
+      <c r="A1" s="5" t="s">
+        <v>447</v>
+      </c>
+      <c r="B1" s="5"/>
+      <c r="C1" s="5"/>
+      <c r="D1" s="5"/>
+      <c r="E1" s="5"/>
+      <c r="F1" s="5"/>
+      <c r="G1" s="5"/>
+      <c r="H1" s="5"/>
     </row>
     <row r="3" spans="1:8" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
@@ -5179,16 +5209,16 @@
         <v>229</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>452</v>
+        <v>448</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>453</v>
+        <v>449</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>454</v>
+        <v>450</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>455</v>
+        <v>451</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>5</v>
@@ -5205,16 +5235,16 @@
         <v>229</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>456</v>
+        <v>452</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>457</v>
+        <v>453</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>458</v>
+        <v>454</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>5</v>
@@ -5231,16 +5261,16 @@
         <v>229</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>459</v>
+        <v>455</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>460</v>
+        <v>456</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>461</v>
+        <v>457</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>462</v>
+        <v>458</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>5</v>
@@ -5257,16 +5287,16 @@
         <v>229</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>463</v>
+        <v>459</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>464</v>
+        <v>460</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>465</v>
+        <v>461</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>466</v>
+        <v>462</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>5</v>
@@ -5283,16 +5313,16 @@
         <v>229</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>467</v>
+        <v>463</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>468</v>
+        <v>464</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>159</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>469</v>
+        <v>465</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>5</v>
@@ -5326,16 +5356,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="A1" s="4" t="s">
-        <v>470</v>
-      </c>
-      <c r="B1" s="4"/>
-      <c r="C1" s="4"/>
-      <c r="D1" s="4"/>
-      <c r="E1" s="4"/>
-      <c r="F1" s="4"/>
-      <c r="G1" s="4"/>
-      <c r="H1" s="4"/>
+      <c r="A1" s="5" t="s">
+        <v>466</v>
+      </c>
+      <c r="B1" s="5"/>
+      <c r="C1" s="5"/>
+      <c r="D1" s="5"/>
+      <c r="E1" s="5"/>
+      <c r="F1" s="5"/>
+      <c r="G1" s="5"/>
+      <c r="H1" s="5"/>
     </row>
     <row r="3" spans="1:8" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
@@ -5371,16 +5401,16 @@
         <v>229</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>471</v>
+        <v>467</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>472</v>
+        <v>468</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>159</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>473</v>
+        <v>469</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>5</v>
@@ -5397,16 +5427,16 @@
         <v>229</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>474</v>
+        <v>470</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>401</v>
+        <v>397</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>475</v>
+        <v>471</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>476</v>
+        <v>472</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>5</v>
@@ -5423,13 +5453,13 @@
         <v>229</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>477</v>
+        <v>473</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>290</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>478</v>
+        <v>474</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>246</v>
@@ -5449,16 +5479,16 @@
         <v>229</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>479</v>
+        <v>475</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>480</v>
+        <v>476</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>481</v>
+        <v>477</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>5</v>
@@ -5475,16 +5505,16 @@
         <v>229</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>482</v>
+        <v>478</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>483</v>
+        <v>479</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>484</v>
+        <v>480</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>485</v>
+        <v>481</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>5</v>
@@ -5501,16 +5531,16 @@
         <v>229</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>486</v>
+        <v>482</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>487</v>
+        <v>483</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>488</v>
+        <v>484</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>489</v>
+        <v>485</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>5</v>
@@ -5544,16 +5574,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="A1" s="4" t="s">
-        <v>490</v>
-      </c>
-      <c r="B1" s="4"/>
-      <c r="C1" s="4"/>
-      <c r="D1" s="4"/>
-      <c r="E1" s="4"/>
-      <c r="F1" s="4"/>
-      <c r="G1" s="4"/>
-      <c r="H1" s="4"/>
+      <c r="A1" s="5" t="s">
+        <v>486</v>
+      </c>
+      <c r="B1" s="5"/>
+      <c r="C1" s="5"/>
+      <c r="D1" s="5"/>
+      <c r="E1" s="5"/>
+      <c r="F1" s="5"/>
+      <c r="G1" s="5"/>
+      <c r="H1" s="5"/>
     </row>
     <row r="3" spans="1:8" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
@@ -5589,16 +5619,16 @@
         <v>229</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>491</v>
+        <v>487</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>493</v>
+        <v>489</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>494</v>
+        <v>490</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>5</v>
@@ -5615,16 +5645,16 @@
         <v>229</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>495</v>
+        <v>491</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>496</v>
+        <v>492</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>159</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>497</v>
+        <v>493</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>5</v>
@@ -5641,16 +5671,16 @@
         <v>229</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>498</v>
+        <v>494</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>499</v>
+        <v>495</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>500</v>
+        <v>496</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>501</v>
+        <v>497</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>5</v>
@@ -5667,16 +5697,16 @@
         <v>229</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>502</v>
+        <v>498</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>503</v>
+        <v>499</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>436</v>
+        <v>432</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>504</v>
+        <v>500</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>5</v>
@@ -5693,16 +5723,16 @@
         <v>229</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>505</v>
+        <v>501</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>506</v>
+        <v>502</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>159</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>507</v>
+        <v>503</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>5</v>
@@ -5719,16 +5749,16 @@
         <v>229</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>508</v>
+        <v>504</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>509</v>
+        <v>505</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>510</v>
+        <v>506</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>511</v>
+        <v>507</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>5</v>
@@ -5762,16 +5792,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="A1" s="4" t="s">
-        <v>512</v>
-      </c>
-      <c r="B1" s="4"/>
-      <c r="C1" s="4"/>
-      <c r="D1" s="4"/>
-      <c r="E1" s="4"/>
-      <c r="F1" s="4"/>
-      <c r="G1" s="4"/>
-      <c r="H1" s="4"/>
+      <c r="A1" s="5" t="s">
+        <v>508</v>
+      </c>
+      <c r="B1" s="5"/>
+      <c r="C1" s="5"/>
+      <c r="D1" s="5"/>
+      <c r="E1" s="5"/>
+      <c r="F1" s="5"/>
+      <c r="G1" s="5"/>
+      <c r="H1" s="5"/>
     </row>
     <row r="3" spans="1:8" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
@@ -5807,16 +5837,16 @@
         <v>229</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>513</v>
+        <v>509</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>514</v>
+        <v>510</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>159</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>515</v>
+        <v>511</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>5</v>
@@ -5833,16 +5863,16 @@
         <v>229</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>516</v>
+        <v>512</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>517</v>
+        <v>513</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>518</v>
+        <v>514</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>519</v>
+        <v>515</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>5</v>
@@ -5859,16 +5889,16 @@
         <v>229</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>520</v>
+        <v>516</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>521</v>
+        <v>517</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>522</v>
+        <v>518</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>523</v>
+        <v>519</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>5</v>
@@ -5885,16 +5915,16 @@
         <v>229</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>524</v>
+        <v>520</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>525</v>
+        <v>521</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>526</v>
+        <v>522</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>5</v>
@@ -5911,16 +5941,16 @@
         <v>229</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>527</v>
+        <v>523</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>528</v>
+        <v>524</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>159</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>529</v>
+        <v>525</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>5</v>
@@ -5937,16 +5967,16 @@
         <v>229</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>530</v>
+        <v>526</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>531</v>
+        <v>527</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>532</v>
+        <v>528</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>533</v>
+        <v>529</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>5</v>
@@ -5980,16 +6010,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="A1" s="4" t="s">
-        <v>534</v>
-      </c>
-      <c r="B1" s="4"/>
-      <c r="C1" s="4"/>
-      <c r="D1" s="4"/>
-      <c r="E1" s="4"/>
-      <c r="F1" s="4"/>
-      <c r="G1" s="4"/>
-      <c r="H1" s="4"/>
+      <c r="A1" s="5" t="s">
+        <v>530</v>
+      </c>
+      <c r="B1" s="5"/>
+      <c r="C1" s="5"/>
+      <c r="D1" s="5"/>
+      <c r="E1" s="5"/>
+      <c r="F1" s="5"/>
+      <c r="G1" s="5"/>
+      <c r="H1" s="5"/>
     </row>
     <row r="3" spans="1:8" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
@@ -6025,16 +6055,16 @@
         <v>128</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>535</v>
+        <v>531</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>536</v>
+        <v>532</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>537</v>
+        <v>533</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>538</v>
+        <v>534</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>5</v>
@@ -6051,16 +6081,16 @@
         <v>128</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>539</v>
+        <v>535</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>540</v>
+        <v>536</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>159</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>541</v>
+        <v>537</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>5</v>
@@ -6077,16 +6107,16 @@
         <v>128</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>542</v>
+        <v>538</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>543</v>
+        <v>539</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>544</v>
+        <v>540</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>545</v>
+        <v>541</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>5</v>
@@ -6103,16 +6133,16 @@
         <v>128</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>546</v>
+        <v>542</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>547</v>
+        <v>543</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>548</v>
+        <v>544</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>549</v>
+        <v>545</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>5</v>
@@ -6129,16 +6159,16 @@
         <v>128</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>550</v>
+        <v>546</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>551</v>
+        <v>547</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>553</v>
+        <v>549</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>5</v>
@@ -6155,16 +6185,16 @@
         <v>229</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>554</v>
+        <v>550</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>555</v>
+        <v>551</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>159</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>556</v>
+        <v>552</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>5</v>
@@ -6181,16 +6211,16 @@
         <v>229</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>557</v>
+        <v>553</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>558</v>
+        <v>554</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>159</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>559</v>
+        <v>555</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>5</v>
@@ -6224,16 +6254,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="A1" s="4" t="s">
-        <v>560</v>
-      </c>
-      <c r="B1" s="4"/>
-      <c r="C1" s="4"/>
-      <c r="D1" s="4"/>
-      <c r="E1" s="4"/>
-      <c r="F1" s="4"/>
-      <c r="G1" s="4"/>
-      <c r="H1" s="4"/>
+      <c r="A1" s="5" t="s">
+        <v>556</v>
+      </c>
+      <c r="B1" s="5"/>
+      <c r="C1" s="5"/>
+      <c r="D1" s="5"/>
+      <c r="E1" s="5"/>
+      <c r="F1" s="5"/>
+      <c r="G1" s="5"/>
+      <c r="H1" s="5"/>
     </row>
     <row r="3" spans="1:8" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
@@ -6266,19 +6296,19 @@
         <v>1</v>
       </c>
       <c r="B4" s="2" t="s">
+        <v>557</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>558</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>559</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>560</v>
+      </c>
+      <c r="F4" s="2" t="s">
         <v>561</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>562</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>563</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>564</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>565</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>5</v>
@@ -6295,16 +6325,16 @@
         <v>132</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>566</v>
+        <v>562</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>567</v>
+        <v>563</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>568</v>
+        <v>564</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>5</v>
@@ -6321,16 +6351,16 @@
         <v>229</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>569</v>
+        <v>565</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>570</v>
+        <v>566</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>571</v>
+        <v>567</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>572</v>
+        <v>568</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>5</v>
@@ -6347,16 +6377,16 @@
         <v>229</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>573</v>
+        <v>569</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>574</v>
+        <v>570</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>159</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>575</v>
+        <v>571</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>5</v>
@@ -6373,16 +6403,16 @@
         <v>229</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>576</v>
+        <v>572</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>577</v>
+        <v>573</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>578</v>
+        <v>574</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>579</v>
+        <v>575</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>5</v>
@@ -6416,16 +6446,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="A1" s="4" t="s">
-        <v>580</v>
-      </c>
-      <c r="B1" s="4"/>
-      <c r="C1" s="4"/>
-      <c r="D1" s="4"/>
-      <c r="E1" s="4"/>
-      <c r="F1" s="4"/>
-      <c r="G1" s="4"/>
-      <c r="H1" s="4"/>
+      <c r="A1" s="5" t="s">
+        <v>576</v>
+      </c>
+      <c r="B1" s="5"/>
+      <c r="C1" s="5"/>
+      <c r="D1" s="5"/>
+      <c r="E1" s="5"/>
+      <c r="F1" s="5"/>
+      <c r="G1" s="5"/>
+      <c r="H1" s="5"/>
     </row>
     <row r="3" spans="1:8" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
@@ -6461,16 +6491,16 @@
         <v>128</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>581</v>
+        <v>577</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>582</v>
+        <v>578</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>583</v>
+        <v>579</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>584</v>
+        <v>580</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>5</v>
@@ -6487,16 +6517,16 @@
         <v>128</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>585</v>
+        <v>581</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>586</v>
+        <v>582</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>587</v>
+        <v>583</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>588</v>
+        <v>584</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>5</v>
@@ -6513,16 +6543,16 @@
         <v>128</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>589</v>
+        <v>585</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>590</v>
+        <v>586</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>591</v>
+        <v>587</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>592</v>
+        <v>588</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>5</v>
@@ -6539,16 +6569,16 @@
         <v>128</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>593</v>
+        <v>589</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>594</v>
+        <v>590</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>595</v>
+        <v>591</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>596</v>
+        <v>592</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>5</v>
@@ -6565,16 +6595,16 @@
         <v>128</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>597</v>
+        <v>593</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>598</v>
+        <v>594</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>599</v>
+        <v>595</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>600</v>
+        <v>596</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>5</v>
@@ -6591,16 +6621,16 @@
         <v>128</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>601</v>
+        <v>597</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>602</v>
+        <v>598</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>603</v>
+        <v>599</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>5</v>
@@ -6617,16 +6647,16 @@
         <v>128</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>605</v>
+        <v>601</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>606</v>
+        <v>602</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>428</v>
+        <v>424</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>429</v>
+        <v>425</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>5</v>
@@ -6643,16 +6673,16 @@
         <v>128</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>608</v>
+        <v>604</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>609</v>
+        <v>605</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>372</v>
+        <v>368</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>5</v>
@@ -6669,16 +6699,16 @@
         <v>128</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>610</v>
+        <v>606</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>611</v>
+        <v>607</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>612</v>
+        <v>608</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>613</v>
+        <v>609</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>5</v>
@@ -6695,16 +6725,16 @@
         <v>128</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>614</v>
+        <v>610</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>615</v>
+        <v>611</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>616</v>
+        <v>612</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>617</v>
+        <v>613</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>5</v>
@@ -6721,16 +6751,16 @@
         <v>128</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>618</v>
+        <v>614</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>619</v>
+        <v>615</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>620</v>
+        <v>616</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>621</v>
+        <v>617</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>5</v>
@@ -6747,16 +6777,16 @@
         <v>229</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>622</v>
+        <v>618</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>623</v>
+        <v>619</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>624</v>
+        <v>620</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>5</v>
@@ -6773,16 +6803,16 @@
         <v>128</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>627</v>
+        <v>623</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>159</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>628</v>
+        <v>624</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>5</v>
@@ -6799,16 +6829,16 @@
         <v>229</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>629</v>
+        <v>625</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>630</v>
+        <v>626</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>578</v>
+        <v>574</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>631</v>
+        <v>627</v>
       </c>
       <c r="G17" s="2" t="s">
         <v>5</v>
@@ -6842,16 +6872,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="A1" s="4" t="s">
-        <v>632</v>
-      </c>
-      <c r="B1" s="4"/>
-      <c r="C1" s="4"/>
-      <c r="D1" s="4"/>
-      <c r="E1" s="4"/>
-      <c r="F1" s="4"/>
-      <c r="G1" s="4"/>
-      <c r="H1" s="4"/>
+      <c r="A1" s="5" t="s">
+        <v>628</v>
+      </c>
+      <c r="B1" s="5"/>
+      <c r="C1" s="5"/>
+      <c r="D1" s="5"/>
+      <c r="E1" s="5"/>
+      <c r="F1" s="5"/>
+      <c r="G1" s="5"/>
+      <c r="H1" s="5"/>
     </row>
     <row r="3" spans="1:8" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
@@ -6887,16 +6917,16 @@
         <v>229</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>633</v>
+        <v>629</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>634</v>
+        <v>630</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>159</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>635</v>
+        <v>631</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>5</v>
@@ -6913,16 +6943,16 @@
         <v>229</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>636</v>
+        <v>632</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>637</v>
+        <v>633</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>638</v>
+        <v>634</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>639</v>
+        <v>635</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>5</v>
@@ -6939,16 +6969,16 @@
         <v>229</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>640</v>
+        <v>636</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>641</v>
+        <v>637</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>159</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>642</v>
+        <v>638</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>5</v>
@@ -6965,16 +6995,16 @@
         <v>229</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>643</v>
+        <v>639</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>644</v>
+        <v>640</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>159</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>645</v>
+        <v>641</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>5</v>
@@ -6991,16 +7021,16 @@
         <v>229</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>646</v>
+        <v>642</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>647</v>
+        <v>643</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>159</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>648</v>
+        <v>644</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>5</v>
@@ -7017,16 +7047,16 @@
         <v>128</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>649</v>
+        <v>645</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>650</v>
+        <v>646</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>159</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>651</v>
+        <v>647</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>5</v>
@@ -7060,16 +7090,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="5" t="s">
         <v>111</v>
       </c>
-      <c r="B1" s="4"/>
-      <c r="C1" s="4"/>
-      <c r="D1" s="4"/>
-      <c r="E1" s="4"/>
-      <c r="F1" s="4"/>
-      <c r="G1" s="4"/>
-      <c r="H1" s="4"/>
+      <c r="B1" s="5"/>
+      <c r="C1" s="5"/>
+      <c r="D1" s="5"/>
+      <c r="E1" s="5"/>
+      <c r="F1" s="5"/>
+      <c r="G1" s="5"/>
+      <c r="H1" s="5"/>
     </row>
     <row r="3" spans="1:8" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
@@ -7120,7 +7150,7 @@
         <v>5</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>1139</v>
+        <v>1135</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="29" x14ac:dyDescent="0.35">
@@ -7146,7 +7176,7 @@
         <v>5</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>1139</v>
+        <v>1135</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="29" x14ac:dyDescent="0.35">
@@ -7172,7 +7202,7 @@
         <v>5</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>1139</v>
+        <v>1135</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="29" x14ac:dyDescent="0.35">
@@ -7198,7 +7228,7 @@
         <v>5</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>1139</v>
+        <v>1135</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="29" x14ac:dyDescent="0.35">
@@ -7224,7 +7254,7 @@
         <v>5</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>1139</v>
+        <v>1135</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="29" x14ac:dyDescent="0.35">
@@ -7250,7 +7280,7 @@
         <v>5</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>1139</v>
+        <v>1135</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="29" x14ac:dyDescent="0.35">
@@ -7276,7 +7306,7 @@
         <v>5</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>1139</v>
+        <v>1135</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
@@ -7302,7 +7332,7 @@
         <v>5</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>1139</v>
+        <v>1135</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
@@ -7354,7 +7384,7 @@
         <v>5</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>1139</v>
+        <v>1135</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
@@ -7408,16 +7438,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="A1" s="4" t="s">
-        <v>652</v>
-      </c>
-      <c r="B1" s="4"/>
-      <c r="C1" s="4"/>
-      <c r="D1" s="4"/>
-      <c r="E1" s="4"/>
-      <c r="F1" s="4"/>
-      <c r="G1" s="4"/>
-      <c r="H1" s="4"/>
+      <c r="A1" s="5" t="s">
+        <v>648</v>
+      </c>
+      <c r="B1" s="5"/>
+      <c r="C1" s="5"/>
+      <c r="D1" s="5"/>
+      <c r="E1" s="5"/>
+      <c r="F1" s="5"/>
+      <c r="G1" s="5"/>
+      <c r="H1" s="5"/>
     </row>
     <row r="3" spans="1:8" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
@@ -7453,16 +7483,16 @@
         <v>229</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>653</v>
+        <v>649</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>654</v>
+        <v>650</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>655</v>
+        <v>651</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>656</v>
+        <v>652</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>5</v>
@@ -7479,16 +7509,16 @@
         <v>229</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>657</v>
+        <v>653</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>658</v>
+        <v>654</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>159</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>659</v>
+        <v>655</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>5</v>
@@ -7505,16 +7535,16 @@
         <v>229</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>660</v>
+        <v>656</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>661</v>
+        <v>657</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>159</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>662</v>
+        <v>658</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>5</v>
@@ -7531,16 +7561,16 @@
         <v>229</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>663</v>
+        <v>659</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>664</v>
+        <v>660</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>665</v>
+        <v>661</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>666</v>
+        <v>662</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>5</v>
@@ -7557,16 +7587,16 @@
         <v>229</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>667</v>
+        <v>663</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>668</v>
+        <v>664</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>159</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>669</v>
+        <v>665</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>5</v>
@@ -7583,16 +7613,16 @@
         <v>229</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>670</v>
+        <v>666</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>671</v>
+        <v>667</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>159</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>672</v>
+        <v>668</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>5</v>
@@ -7609,16 +7639,16 @@
         <v>229</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>673</v>
+        <v>669</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>674</v>
+        <v>670</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>159</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>675</v>
+        <v>671</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>5</v>
@@ -7635,16 +7665,16 @@
         <v>229</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>676</v>
+        <v>672</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>677</v>
+        <v>673</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>678</v>
+        <v>674</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>679</v>
+        <v>675</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>5</v>
@@ -7661,16 +7691,16 @@
         <v>229</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>680</v>
+        <v>676</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>681</v>
+        <v>677</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>159</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>669</v>
+        <v>665</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>5</v>
@@ -7687,16 +7717,16 @@
         <v>128</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>682</v>
+        <v>678</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>683</v>
+        <v>679</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>159</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>684</v>
+        <v>680</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>5</v>
@@ -7730,16 +7760,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="A1" s="4" t="s">
-        <v>685</v>
-      </c>
-      <c r="B1" s="4"/>
-      <c r="C1" s="4"/>
-      <c r="D1" s="4"/>
-      <c r="E1" s="4"/>
-      <c r="F1" s="4"/>
-      <c r="G1" s="4"/>
-      <c r="H1" s="4"/>
+      <c r="A1" s="5" t="s">
+        <v>681</v>
+      </c>
+      <c r="B1" s="5"/>
+      <c r="C1" s="5"/>
+      <c r="D1" s="5"/>
+      <c r="E1" s="5"/>
+      <c r="F1" s="5"/>
+      <c r="G1" s="5"/>
+      <c r="H1" s="5"/>
     </row>
     <row r="3" spans="1:8" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
@@ -7775,16 +7805,16 @@
         <v>229</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>686</v>
+        <v>682</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>687</v>
+        <v>683</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>159</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>688</v>
+        <v>684</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>5</v>
@@ -7801,16 +7831,16 @@
         <v>229</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>689</v>
+        <v>685</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>690</v>
+        <v>686</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>159</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>691</v>
+        <v>687</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>5</v>
@@ -7827,16 +7857,16 @@
         <v>229</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>692</v>
+        <v>688</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>693</v>
+        <v>689</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>159</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>694</v>
+        <v>690</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>5</v>
@@ -7853,16 +7883,16 @@
         <v>229</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>695</v>
+        <v>691</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>696</v>
+        <v>692</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>159</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>697</v>
+        <v>693</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>5</v>
@@ -7879,16 +7909,16 @@
         <v>128</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>698</v>
+        <v>694</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>699</v>
+        <v>695</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>159</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>700</v>
+        <v>696</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>5</v>
@@ -7922,16 +7952,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="A1" s="4" t="s">
-        <v>701</v>
-      </c>
-      <c r="B1" s="4"/>
-      <c r="C1" s="4"/>
-      <c r="D1" s="4"/>
-      <c r="E1" s="4"/>
-      <c r="F1" s="4"/>
-      <c r="G1" s="4"/>
-      <c r="H1" s="4"/>
+      <c r="A1" s="5" t="s">
+        <v>697</v>
+      </c>
+      <c r="B1" s="5"/>
+      <c r="C1" s="5"/>
+      <c r="D1" s="5"/>
+      <c r="E1" s="5"/>
+      <c r="F1" s="5"/>
+      <c r="G1" s="5"/>
+      <c r="H1" s="5"/>
     </row>
     <row r="3" spans="1:8" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
@@ -7967,16 +7997,16 @@
         <v>132</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>702</v>
+        <v>698</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>703</v>
+        <v>699</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>159</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>704</v>
+        <v>700</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>5</v>
@@ -7993,16 +8023,16 @@
         <v>229</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>705</v>
+        <v>701</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>706</v>
+        <v>702</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>707</v>
+        <v>703</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>708</v>
+        <v>704</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>5</v>
@@ -8019,16 +8049,16 @@
         <v>124</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>709</v>
+        <v>705</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>710</v>
+        <v>706</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>159</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>711</v>
+        <v>707</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>5</v>
@@ -8045,16 +8075,16 @@
         <v>119</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>712</v>
+        <v>708</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>713</v>
+        <v>709</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>159</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>714</v>
+        <v>710</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>5</v>
@@ -8071,16 +8101,16 @@
         <v>229</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>715</v>
+        <v>711</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>716</v>
+        <v>712</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>717</v>
+        <v>713</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>718</v>
+        <v>714</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>5</v>
@@ -8097,16 +8127,16 @@
         <v>229</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>719</v>
+        <v>715</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>720</v>
+        <v>716</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>721</v>
+        <v>717</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>722</v>
+        <v>718</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>5</v>
@@ -8123,16 +8153,16 @@
         <v>128</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>723</v>
+        <v>719</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>724</v>
+        <v>720</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>159</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>725</v>
+        <v>721</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>5</v>
@@ -8166,16 +8196,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="A1" s="4" t="s">
-        <v>726</v>
-      </c>
-      <c r="B1" s="4"/>
-      <c r="C1" s="4"/>
-      <c r="D1" s="4"/>
-      <c r="E1" s="4"/>
-      <c r="F1" s="4"/>
-      <c r="G1" s="4"/>
-      <c r="H1" s="4"/>
+      <c r="A1" s="5" t="s">
+        <v>722</v>
+      </c>
+      <c r="B1" s="5"/>
+      <c r="C1" s="5"/>
+      <c r="D1" s="5"/>
+      <c r="E1" s="5"/>
+      <c r="F1" s="5"/>
+      <c r="G1" s="5"/>
+      <c r="H1" s="5"/>
     </row>
     <row r="3" spans="1:8" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
@@ -8211,16 +8241,16 @@
         <v>229</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>727</v>
+        <v>723</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>728</v>
+        <v>724</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>159</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>729</v>
+        <v>725</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>5</v>
@@ -8237,16 +8267,16 @@
         <v>229</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>730</v>
+        <v>726</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>731</v>
+        <v>727</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>159</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>732</v>
+        <v>728</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>5</v>
@@ -8263,16 +8293,16 @@
         <v>229</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>733</v>
+        <v>729</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>734</v>
+        <v>730</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>159</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>735</v>
+        <v>731</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>5</v>
@@ -8289,16 +8319,16 @@
         <v>124</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>736</v>
+        <v>732</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>737</v>
+        <v>733</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>738</v>
+        <v>734</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>739</v>
+        <v>735</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>5</v>
@@ -8315,16 +8345,16 @@
         <v>119</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>740</v>
+        <v>736</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>741</v>
+        <v>737</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>159</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>742</v>
+        <v>738</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>5</v>
@@ -8358,16 +8388,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="A1" s="4" t="s">
-        <v>743</v>
-      </c>
-      <c r="B1" s="4"/>
-      <c r="C1" s="4"/>
-      <c r="D1" s="4"/>
-      <c r="E1" s="4"/>
-      <c r="F1" s="4"/>
-      <c r="G1" s="4"/>
-      <c r="H1" s="4"/>
+      <c r="A1" s="5" t="s">
+        <v>739</v>
+      </c>
+      <c r="B1" s="5"/>
+      <c r="C1" s="5"/>
+      <c r="D1" s="5"/>
+      <c r="E1" s="5"/>
+      <c r="F1" s="5"/>
+      <c r="G1" s="5"/>
+      <c r="H1" s="5"/>
     </row>
     <row r="3" spans="1:8" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
@@ -8403,16 +8433,16 @@
         <v>229</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>744</v>
+        <v>740</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>745</v>
+        <v>741</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>159</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>746</v>
+        <v>742</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>5</v>
@@ -8429,16 +8459,16 @@
         <v>229</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>747</v>
+        <v>743</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>748</v>
+        <v>744</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>159</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>749</v>
+        <v>745</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>5</v>
@@ -8455,16 +8485,16 @@
         <v>229</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>750</v>
+        <v>746</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>751</v>
+        <v>747</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>752</v>
+        <v>748</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>753</v>
+        <v>749</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>5</v>
@@ -8481,16 +8511,16 @@
         <v>229</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>754</v>
+        <v>750</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>755</v>
+        <v>751</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>756</v>
+        <v>752</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>757</v>
+        <v>753</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>5</v>
@@ -8507,16 +8537,16 @@
         <v>229</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>758</v>
+        <v>754</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>759</v>
+        <v>755</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>159</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>760</v>
+        <v>756</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>5</v>
@@ -8533,16 +8563,16 @@
         <v>229</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>761</v>
+        <v>757</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>762</v>
+        <v>758</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>159</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>763</v>
+        <v>759</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>5</v>
@@ -8556,19 +8586,19 @@
         <v>7</v>
       </c>
       <c r="B10" s="2" t="s">
+        <v>760</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>761</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>762</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>763</v>
+      </c>
+      <c r="F10" s="2" t="s">
         <v>764</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>765</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>766</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>767</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>768</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>5</v>
@@ -8602,16 +8632,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="A1" s="4" t="s">
-        <v>769</v>
-      </c>
-      <c r="B1" s="4"/>
-      <c r="C1" s="4"/>
-      <c r="D1" s="4"/>
-      <c r="E1" s="4"/>
-      <c r="F1" s="4"/>
-      <c r="G1" s="4"/>
-      <c r="H1" s="4"/>
+      <c r="A1" s="5" t="s">
+        <v>765</v>
+      </c>
+      <c r="B1" s="5"/>
+      <c r="C1" s="5"/>
+      <c r="D1" s="5"/>
+      <c r="E1" s="5"/>
+      <c r="F1" s="5"/>
+      <c r="G1" s="5"/>
+      <c r="H1" s="5"/>
     </row>
     <row r="3" spans="1:8" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
@@ -8644,19 +8674,19 @@
         <v>1</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>770</v>
+        <v>766</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>771</v>
+        <v>767</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>772</v>
+        <v>768</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>159</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>773</v>
+        <v>769</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>5</v>
@@ -8673,16 +8703,16 @@
         <v>229</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>774</v>
+        <v>770</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>775</v>
+        <v>771</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>159</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>776</v>
+        <v>772</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>5</v>
@@ -8699,16 +8729,16 @@
         <v>229</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>777</v>
+        <v>773</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>778</v>
+        <v>774</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>779</v>
+        <v>775</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>780</v>
+        <v>776</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>5</v>
@@ -8725,16 +8755,16 @@
         <v>128</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>781</v>
+        <v>777</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>782</v>
+        <v>778</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>159</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>783</v>
+        <v>779</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>5</v>
@@ -8768,16 +8798,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="A1" s="4" t="s">
-        <v>784</v>
-      </c>
-      <c r="B1" s="4"/>
-      <c r="C1" s="4"/>
-      <c r="D1" s="4"/>
-      <c r="E1" s="4"/>
-      <c r="F1" s="4"/>
-      <c r="G1" s="4"/>
-      <c r="H1" s="4"/>
+      <c r="A1" s="5" t="s">
+        <v>780</v>
+      </c>
+      <c r="B1" s="5"/>
+      <c r="C1" s="5"/>
+      <c r="D1" s="5"/>
+      <c r="E1" s="5"/>
+      <c r="F1" s="5"/>
+      <c r="G1" s="5"/>
+      <c r="H1" s="5"/>
     </row>
     <row r="3" spans="1:8" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
@@ -8813,16 +8843,16 @@
         <v>128</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>785</v>
+        <v>781</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>786</v>
+        <v>782</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>159</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>787</v>
+        <v>783</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>5</v>
@@ -8839,16 +8869,16 @@
         <v>128</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>788</v>
+        <v>784</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>789</v>
+        <v>785</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>159</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>783</v>
+        <v>779</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>5</v>
@@ -8865,16 +8895,16 @@
         <v>128</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>790</v>
+        <v>786</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>791</v>
+        <v>787</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>159</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>783</v>
+        <v>779</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>5</v>
@@ -8891,16 +8921,16 @@
         <v>128</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>792</v>
+        <v>788</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>793</v>
+        <v>789</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>159</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>783</v>
+        <v>779</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>5</v>
@@ -8917,16 +8947,16 @@
         <v>128</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>794</v>
+        <v>790</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>795</v>
+        <v>791</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>159</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>796</v>
+        <v>792</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>5</v>
@@ -8943,16 +8973,16 @@
         <v>128</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>797</v>
+        <v>793</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>798</v>
+        <v>794</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>159</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>799</v>
+        <v>795</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>5</v>
@@ -8969,16 +8999,16 @@
         <v>124</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>800</v>
+        <v>796</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>801</v>
+        <v>797</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>159</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>802</v>
+        <v>798</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>5</v>
@@ -8995,16 +9025,16 @@
         <v>132</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>803</v>
+        <v>799</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>804</v>
+        <v>800</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>805</v>
+        <v>801</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>806</v>
+        <v>802</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>5</v>
@@ -9021,16 +9051,16 @@
         <v>132</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>807</v>
+        <v>803</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>808</v>
+        <v>804</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>159</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>809</v>
+        <v>805</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>5</v>
@@ -9047,16 +9077,16 @@
         <v>132</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>810</v>
+        <v>806</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>812</v>
+        <v>808</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>813</v>
+        <v>809</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>5</v>
@@ -9087,33 +9117,33 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="A1" s="7" t="s">
-        <v>814</v>
-      </c>
-      <c r="B1" s="7"/>
-      <c r="C1" s="7"/>
-      <c r="D1" s="7"/>
-      <c r="E1" s="7"/>
-      <c r="F1" s="7"/>
+      <c r="A1" s="8" t="s">
+        <v>810</v>
+      </c>
+      <c r="B1" s="8"/>
+      <c r="C1" s="8"/>
+      <c r="D1" s="8"/>
+      <c r="E1" s="8"/>
+      <c r="F1" s="8"/>
     </row>
     <row r="3" spans="1:6" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
+        <v>811</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>812</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>813</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>814</v>
+      </c>
+      <c r="E3" s="1" t="s">
         <v>815</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="F3" s="1" t="s">
         <v>816</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>817</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>818</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>819</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>820</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="29" x14ac:dyDescent="0.35">
@@ -9121,19 +9151,19 @@
         <v>119</v>
       </c>
       <c r="B4" s="2" t="s">
+        <v>817</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>818</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>819</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>820</v>
+      </c>
+      <c r="F4" s="2" t="s">
         <v>821</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>822</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>823</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>824</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>825</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.35">
@@ -9141,19 +9171,19 @@
         <v>124</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>826</v>
+        <v>822</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>827</v>
+        <v>823</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>828</v>
+        <v>824</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>824</v>
+        <v>820</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>829</v>
+        <v>825</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="29" x14ac:dyDescent="0.35">
@@ -9161,19 +9191,19 @@
         <v>128</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>830</v>
+        <v>826</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>831</v>
+        <v>827</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>832</v>
+        <v>828</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>824</v>
+        <v>820</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>833</v>
+        <v>829</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.35">
@@ -9181,59 +9211,59 @@
         <v>128</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>834</v>
+        <v>830</v>
       </c>
       <c r="C7" s="2" t="s">
+        <v>827</v>
+      </c>
+      <c r="D7" s="2" t="s">
         <v>831</v>
       </c>
-      <c r="D7" s="2" t="s">
-        <v>835</v>
-      </c>
       <c r="E7" s="2" t="s">
-        <v>824</v>
+        <v>820</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>836</v>
+        <v>832</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
+        <v>833</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>834</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>827</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>835</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>836</v>
+      </c>
+      <c r="F8" s="2" t="s">
         <v>837</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>838</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>831</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>839</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>840</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>841</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A9" s="2" t="s">
+        <v>838</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>839</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>840</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>841</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>820</v>
+      </c>
+      <c r="F9" s="2" t="s">
         <v>842</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>843</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>844</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>845</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>824</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>846</v>
       </c>
     </row>
   </sheetData>
@@ -9258,153 +9288,153 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="A1" s="7" t="s">
-        <v>847</v>
-      </c>
-      <c r="B1" s="7"/>
-      <c r="C1" s="7"/>
-      <c r="D1" s="7"/>
-      <c r="E1" s="7"/>
-      <c r="F1" s="7"/>
+      <c r="A1" s="8" t="s">
+        <v>843</v>
+      </c>
+      <c r="B1" s="8"/>
+      <c r="C1" s="8"/>
+      <c r="D1" s="8"/>
+      <c r="E1" s="8"/>
+      <c r="F1" s="8"/>
     </row>
     <row r="3" spans="1:6" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
+        <v>844</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>845</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>846</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>847</v>
+      </c>
+      <c r="E3" s="1" t="s">
         <v>848</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="F3" s="1" t="s">
         <v>849</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>850</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>851</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>852</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>853</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
-        <v>821</v>
+        <v>817</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>822</v>
+        <v>818</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>823</v>
+        <v>819</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>821</v>
+        <v>817</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>854</v>
+        <v>850</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>855</v>
+        <v>851</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
-        <v>826</v>
+        <v>822</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>827</v>
+        <v>823</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>828</v>
+        <v>824</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>826</v>
+        <v>822</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>854</v>
+        <v>850</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>855</v>
+        <v>851</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
-        <v>830</v>
+        <v>826</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>831</v>
+        <v>827</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>832</v>
+        <v>828</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>856</v>
+        <v>852</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>854</v>
+        <v>850</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>857</v>
+        <v>853</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
-        <v>834</v>
+        <v>830</v>
       </c>
       <c r="B7" s="2" t="s">
+        <v>827</v>
+      </c>
+      <c r="C7" s="2" t="s">
         <v>831</v>
       </c>
-      <c r="C7" s="2" t="s">
-        <v>835</v>
-      </c>
       <c r="D7" s="2" t="s">
-        <v>856</v>
+        <v>852</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>854</v>
+        <v>850</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>857</v>
+        <v>853</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
-        <v>838</v>
+        <v>834</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>831</v>
+        <v>827</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>839</v>
+        <v>835</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>856</v>
+        <v>852</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>858</v>
+        <v>854</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>859</v>
+        <v>855</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A9" s="2" t="s">
-        <v>843</v>
+        <v>839</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>844</v>
+        <v>840</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>845</v>
+        <v>841</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>860</v>
+        <v>856</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>854</v>
+        <v>850</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>861</v>
+        <v>857</v>
       </c>
     </row>
   </sheetData>
@@ -9429,199 +9459,199 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="A1" s="7" t="s">
-        <v>862</v>
-      </c>
-      <c r="B1" s="7"/>
-      <c r="C1" s="7"/>
-      <c r="D1" s="7"/>
-      <c r="E1" s="7"/>
+      <c r="A1" s="8" t="s">
+        <v>858</v>
+      </c>
+      <c r="B1" s="8"/>
+      <c r="C1" s="8"/>
+      <c r="D1" s="8"/>
+      <c r="E1" s="8"/>
     </row>
     <row r="3" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
-        <v>863</v>
+        <v>859</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>864</v>
+        <v>860</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>865</v>
+        <v>861</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>866</v>
+        <v>862</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>852</v>
+        <v>848</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
-        <v>867</v>
+        <v>863</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>868</v>
+        <v>864</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>869</v>
+        <v>865</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>870</v>
+        <v>866</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>854</v>
+        <v>850</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
+        <v>863</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>867</v>
       </c>
-      <c r="B5" s="2" t="s">
-        <v>871</v>
-      </c>
       <c r="C5" s="2" t="s">
-        <v>872</v>
+        <v>868</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>873</v>
+        <v>869</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>854</v>
+        <v>850</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
-        <v>867</v>
+        <v>863</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>874</v>
+        <v>870</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>875</v>
+        <v>871</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>876</v>
+        <v>872</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>854</v>
+        <v>850</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
-        <v>867</v>
+        <v>863</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>877</v>
+        <v>873</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>878</v>
+        <v>874</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>879</v>
+        <v>875</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>854</v>
+        <v>850</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
-        <v>867</v>
+        <v>863</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>880</v>
+        <v>876</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>880</v>
+        <v>876</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>881</v>
+        <v>877</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>858</v>
+        <v>854</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A9" s="2" t="s">
-        <v>882</v>
+        <v>878</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>883</v>
+        <v>879</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>883</v>
+        <v>879</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>884</v>
+        <v>880</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>854</v>
+        <v>850</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A10" s="2" t="s">
+        <v>878</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>881</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>881</v>
+      </c>
+      <c r="D10" s="2" t="s">
         <v>882</v>
       </c>
-      <c r="B10" s="2" t="s">
-        <v>885</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>885</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>886</v>
-      </c>
       <c r="E10" s="2" t="s">
-        <v>854</v>
+        <v>850</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A11" s="2" t="s">
-        <v>882</v>
+        <v>878</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>887</v>
+        <v>883</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>888</v>
+        <v>884</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>889</v>
+        <v>885</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>854</v>
+        <v>850</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A12" s="2" t="s">
-        <v>882</v>
+        <v>878</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>890</v>
+        <v>886</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>891</v>
+        <v>887</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>892</v>
+        <v>888</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>854</v>
+        <v>850</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A13" s="2" t="s">
-        <v>882</v>
+        <v>878</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>893</v>
+        <v>889</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>893</v>
+        <v>889</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>894</v>
+        <v>890</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>854</v>
+        <v>850</v>
       </c>
     </row>
   </sheetData>
@@ -9649,16 +9679,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="5" t="s">
         <v>165</v>
       </c>
-      <c r="B1" s="4"/>
-      <c r="C1" s="4"/>
-      <c r="D1" s="4"/>
-      <c r="E1" s="4"/>
-      <c r="F1" s="4"/>
-      <c r="G1" s="4"/>
-      <c r="H1" s="4"/>
+      <c r="B1" s="5"/>
+      <c r="C1" s="5"/>
+      <c r="D1" s="5"/>
+      <c r="E1" s="5"/>
+      <c r="F1" s="5"/>
+      <c r="G1" s="5"/>
+      <c r="H1" s="5"/>
     </row>
     <row r="3" spans="1:8" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
@@ -9867,232 +9897,232 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="A1" s="7" t="s">
-        <v>895</v>
-      </c>
-      <c r="B1" s="7"/>
-      <c r="C1" s="7"/>
-      <c r="D1" s="7"/>
-      <c r="E1" s="7"/>
-      <c r="F1" s="7"/>
-      <c r="G1" s="7"/>
-      <c r="H1" s="7"/>
-      <c r="I1" s="7"/>
-      <c r="J1" s="7"/>
+      <c r="A1" s="8" t="s">
+        <v>891</v>
+      </c>
+      <c r="B1" s="8"/>
+      <c r="C1" s="8"/>
+      <c r="D1" s="8"/>
+      <c r="E1" s="8"/>
+      <c r="F1" s="8"/>
+      <c r="G1" s="8"/>
+      <c r="H1" s="8"/>
+      <c r="I1" s="8"/>
+      <c r="J1" s="8"/>
     </row>
     <row r="3" spans="1:10" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
+        <v>892</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>893</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>860</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>894</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>895</v>
+      </c>
+      <c r="F3" s="1" t="s">
         <v>896</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="G3" s="1" t="s">
         <v>897</v>
       </c>
-      <c r="C3" s="1" t="s">
-        <v>864</v>
-      </c>
-      <c r="D3" s="1" t="s">
+      <c r="H3" s="1" t="s">
         <v>898</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="I3" s="1" t="s">
         <v>899</v>
       </c>
-      <c r="F3" s="1" t="s">
-        <v>900</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>901</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>902</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>903</v>
-      </c>
       <c r="J3" s="1" t="s">
-        <v>852</v>
+        <v>848</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
+        <v>900</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>901</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>902</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>864</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>879</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>903</v>
+      </c>
+      <c r="G4" s="2" t="s">
         <v>904</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="H4" s="2" t="s">
         <v>905</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>906</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>868</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>883</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>907</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>908</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>909</v>
       </c>
       <c r="I4" s="2" t="s">
         <v>63</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>854</v>
+        <v>850</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
+        <v>906</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>907</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>908</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>867</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>879</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>909</v>
+      </c>
+      <c r="G5" s="2" t="s">
         <v>910</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="H5" s="2" t="s">
         <v>911</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>912</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>871</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>883</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>913</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>914</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>915</v>
       </c>
       <c r="I5" s="2" t="s">
         <v>48</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>854</v>
+        <v>850</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
+        <v>912</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>913</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>914</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>867</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>879</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>915</v>
+      </c>
+      <c r="G6" s="2" t="s">
         <v>916</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="H6" s="2" t="s">
         <v>917</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="I6" s="2" t="s">
         <v>918</v>
       </c>
-      <c r="D6" s="2" t="s">
-        <v>871</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>883</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>919</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>920</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>921</v>
-      </c>
-      <c r="I6" s="2" t="s">
-        <v>922</v>
-      </c>
       <c r="J6" s="2" t="s">
-        <v>854</v>
+        <v>850</v>
       </c>
     </row>
     <row r="7" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
+        <v>919</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>920</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>921</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>870</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>879</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>922</v>
+      </c>
+      <c r="G7" s="2" t="s">
         <v>923</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="H7" s="2" t="s">
         <v>924</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>925</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>874</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>883</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>926</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>927</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>928</v>
       </c>
       <c r="I7" s="2" t="s">
         <v>18</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>854</v>
+        <v>850</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
+        <v>925</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>926</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>927</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>873</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>879</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>928</v>
+      </c>
+      <c r="G8" s="2" t="s">
         <v>929</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="H8" s="2" t="s">
         <v>930</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>931</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>877</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>883</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>932</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>933</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>934</v>
       </c>
       <c r="I8" s="2" t="s">
         <v>33</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>854</v>
+        <v>850</v>
       </c>
     </row>
     <row r="9" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A9" s="2" t="s">
+        <v>931</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>932</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>933</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>864</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>879</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>934</v>
+      </c>
+      <c r="G9" s="2" t="s">
         <v>935</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>936</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>937</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>868</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>883</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>938</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>939</v>
       </c>
       <c r="H9" s="2" t="s">
         <v>18</v>
@@ -10101,62 +10131,62 @@
         <v>33</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>940</v>
+        <v>936</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A10" s="2" t="s">
+        <v>937</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>938</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>939</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>867</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>879</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>940</v>
+      </c>
+      <c r="G10" s="2" t="s">
         <v>941</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="H10" s="2" t="s">
         <v>942</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>943</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>871</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>883</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>944</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>945</v>
-      </c>
-      <c r="H10" s="2" t="s">
-        <v>946</v>
       </c>
       <c r="I10" s="2" t="s">
         <v>63</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>947</v>
+        <v>943</v>
       </c>
     </row>
     <row r="11" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A11" s="2" t="s">
-        <v>948</v>
+        <v>944</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>949</v>
+        <v>945</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>950</v>
+        <v>946</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>868</v>
+        <v>864</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>883</v>
+        <v>879</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>951</v>
+        <v>947</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>945</v>
+        <v>941</v>
       </c>
       <c r="H11" s="2" t="s">
         <v>33</v>
@@ -10165,7 +10195,7 @@
         <v>18</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>952</v>
+        <v>948</v>
       </c>
     </row>
   </sheetData>
@@ -10190,129 +10220,129 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="A1" s="7" t="s">
-        <v>953</v>
-      </c>
-      <c r="B1" s="7"/>
-      <c r="C1" s="7"/>
-      <c r="D1" s="7"/>
-      <c r="E1" s="7"/>
-      <c r="F1" s="7"/>
-      <c r="G1" s="7"/>
+      <c r="A1" s="8" t="s">
+        <v>949</v>
+      </c>
+      <c r="B1" s="8"/>
+      <c r="C1" s="8"/>
+      <c r="D1" s="8"/>
+      <c r="E1" s="8"/>
+      <c r="F1" s="8"/>
+      <c r="G1" s="8"/>
     </row>
     <row r="3" spans="1:7" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
-        <v>954</v>
+        <v>950</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>955</v>
+        <v>951</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>899</v>
+        <v>895</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>956</v>
+        <v>952</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>901</v>
+        <v>897</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>900</v>
+        <v>896</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>957</v>
+        <v>953</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
-        <v>906</v>
+        <v>902</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>958</v>
+        <v>954</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>883</v>
+        <v>879</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>6</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>908</v>
+        <v>904</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>907</v>
+        <v>903</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>854</v>
+        <v>850</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
-        <v>906</v>
+        <v>902</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>959</v>
+        <v>955</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>887</v>
+        <v>883</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>960</v>
+        <v>956</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>961</v>
+        <v>957</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>962</v>
+        <v>958</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>858</v>
+        <v>854</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
-        <v>918</v>
+        <v>914</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>958</v>
+        <v>954</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>883</v>
+        <v>879</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>6</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>920</v>
+        <v>916</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>919</v>
+        <v>915</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>854</v>
+        <v>850</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
-        <v>918</v>
+        <v>914</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>963</v>
+        <v>959</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>887</v>
+        <v>883</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>75</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>964</v>
+        <v>960</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>965</v>
+        <v>961</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>858</v>
+        <v>854</v>
       </c>
     </row>
   </sheetData>
@@ -10334,67 +10364,67 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="A1" s="7" t="s">
-        <v>966</v>
-      </c>
-      <c r="B1" s="7"/>
-      <c r="C1" s="7"/>
-      <c r="D1" s="7"/>
+      <c r="A1" s="8" t="s">
+        <v>962</v>
+      </c>
+      <c r="B1" s="8"/>
+      <c r="C1" s="8"/>
+      <c r="D1" s="8"/>
     </row>
     <row r="3" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
-        <v>954</v>
+        <v>950</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>967</v>
+        <v>963</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>968</v>
+        <v>964</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>969</v>
+        <v>965</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
-        <v>906</v>
+        <v>902</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>970</v>
+        <v>966</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>39</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>919</v>
+        <v>915</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
-        <v>906</v>
+        <v>902</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>960</v>
+        <v>956</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>972</v>
+        <v>968</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
-        <v>918</v>
+        <v>914</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>973</v>
+        <v>969</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>75</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>974</v>
+        <v>970</v>
       </c>
     </row>
   </sheetData>
@@ -10421,129 +10451,129 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="A1" s="7" t="s">
-        <v>975</v>
-      </c>
-      <c r="B1" s="7"/>
-      <c r="C1" s="7"/>
-      <c r="D1" s="7"/>
-      <c r="E1" s="7"/>
-      <c r="F1" s="7"/>
-      <c r="G1" s="7"/>
+      <c r="A1" s="8" t="s">
+        <v>971</v>
+      </c>
+      <c r="B1" s="8"/>
+      <c r="C1" s="8"/>
+      <c r="D1" s="8"/>
+      <c r="E1" s="8"/>
+      <c r="F1" s="8"/>
+      <c r="G1" s="8"/>
     </row>
     <row r="3" spans="1:7" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
+        <v>972</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>860</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>973</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>974</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>975</v>
+      </c>
+      <c r="F3" s="1" t="s">
         <v>976</v>
       </c>
-      <c r="B3" s="1" t="s">
-        <v>864</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>977</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>978</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>979</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>980</v>
-      </c>
       <c r="G3" s="1" t="s">
-        <v>852</v>
+        <v>848</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
+        <v>977</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>978</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>979</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>980</v>
+      </c>
+      <c r="E4" s="2" t="s">
         <v>981</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="F4" s="2" t="s">
         <v>982</v>
       </c>
-      <c r="C4" s="2" t="s">
-        <v>983</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>984</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>985</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>986</v>
-      </c>
       <c r="G4" s="2" t="s">
-        <v>854</v>
+        <v>850</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
+        <v>983</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>984</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>985</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>986</v>
+      </c>
+      <c r="E5" s="2" t="s">
         <v>987</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="F5" s="2" t="s">
         <v>988</v>
       </c>
-      <c r="C5" s="2" t="s">
-        <v>989</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>990</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>991</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>992</v>
-      </c>
       <c r="G5" s="2" t="s">
-        <v>854</v>
+        <v>850</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
+        <v>989</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>990</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>991</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>992</v>
+      </c>
+      <c r="E6" s="2" t="s">
         <v>993</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="F6" s="2" t="s">
         <v>994</v>
       </c>
-      <c r="C6" s="2" t="s">
-        <v>995</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>996</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>997</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>998</v>
-      </c>
       <c r="G6" s="2" t="s">
-        <v>854</v>
+        <v>850</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
+        <v>995</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>996</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>997</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>998</v>
+      </c>
+      <c r="E7" s="2" t="s">
         <v>999</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="F7" s="2" t="s">
         <v>1000</v>
       </c>
-      <c r="C7" s="2" t="s">
-        <v>1001</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>1002</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>1003</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>1004</v>
-      </c>
       <c r="G7" s="2" t="s">
-        <v>858</v>
+        <v>854</v>
       </c>
     </row>
   </sheetData>
@@ -10568,119 +10598,119 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="A1" s="7" t="s">
-        <v>1005</v>
-      </c>
-      <c r="B1" s="7"/>
-      <c r="C1" s="7"/>
-      <c r="D1" s="7"/>
-      <c r="E1" s="7"/>
-      <c r="F1" s="7"/>
-      <c r="G1" s="7"/>
-      <c r="H1" s="7"/>
+      <c r="A1" s="8" t="s">
+        <v>1001</v>
+      </c>
+      <c r="B1" s="8"/>
+      <c r="C1" s="8"/>
+      <c r="D1" s="8"/>
+      <c r="E1" s="8"/>
+      <c r="F1" s="8"/>
+      <c r="G1" s="8"/>
+      <c r="H1" s="8"/>
     </row>
     <row r="3" spans="1:8" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
+        <v>1002</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>1003</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>1004</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>1005</v>
+      </c>
+      <c r="E3" s="1" t="s">
         <v>1006</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="F3" s="1" t="s">
         <v>1007</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="G3" s="1" t="s">
         <v>1008</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="H3" s="1" t="s">
         <v>1009</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>1010</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>1011</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>1012</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>1013</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
+        <v>1010</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>978</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>1011</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>1012</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>935</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>1013</v>
+      </c>
+      <c r="G4" s="2" t="s">
         <v>1014</v>
       </c>
-      <c r="B4" s="2" t="s">
-        <v>982</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>1015</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>1016</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>939</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>1017</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>1018</v>
-      </c>
       <c r="H4" s="2" t="s">
-        <v>1017</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
+        <v>1015</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>984</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>1016</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>1017</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>942</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>1018</v>
+      </c>
+      <c r="G5" s="2" t="s">
         <v>1019</v>
       </c>
-      <c r="B5" s="2" t="s">
-        <v>988</v>
-      </c>
-      <c r="C5" s="2" t="s">
+      <c r="H5" s="2" t="s">
         <v>1020</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>1021</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>946</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>1022</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>1023</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>1024</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
+        <v>1021</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>990</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>1022</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>1023</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>1024</v>
+      </c>
+      <c r="F6" s="2" t="s">
         <v>1025</v>
       </c>
-      <c r="B6" s="2" t="s">
-        <v>994</v>
-      </c>
-      <c r="C6" s="2" t="s">
+      <c r="G6" s="2" t="s">
         <v>1026</v>
       </c>
-      <c r="D6" s="2" t="s">
-        <v>1027</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>1028</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>1029</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>1030</v>
-      </c>
       <c r="H6" s="2" t="s">
-        <v>946</v>
+        <v>942</v>
       </c>
     </row>
   </sheetData>
@@ -10706,113 +10736,113 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="A1" s="7" t="s">
-        <v>1031</v>
-      </c>
-      <c r="B1" s="7"/>
-      <c r="C1" s="7"/>
-      <c r="D1" s="7"/>
-      <c r="E1" s="7"/>
-      <c r="F1" s="7"/>
+      <c r="A1" s="8" t="s">
+        <v>1027</v>
+      </c>
+      <c r="B1" s="8"/>
+      <c r="C1" s="8"/>
+      <c r="D1" s="8"/>
+      <c r="E1" s="8"/>
+      <c r="F1" s="8"/>
     </row>
     <row r="3" spans="1:6" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
-        <v>1032</v>
+        <v>1028</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>864</v>
+        <v>860</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>978</v>
+        <v>974</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>977</v>
+        <v>973</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>1033</v>
+        <v>1029</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>852</v>
+        <v>848</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
+        <v>1030</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>1031</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>1032</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>1033</v>
+      </c>
+      <c r="E4" s="2" t="s">
         <v>1034</v>
       </c>
-      <c r="B4" s="2" t="s">
-        <v>1035</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>1036</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>1037</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>1038</v>
-      </c>
       <c r="F4" s="2" t="s">
-        <v>854</v>
+        <v>850</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
+        <v>1035</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>1036</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>1037</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>1038</v>
+      </c>
+      <c r="E5" s="2" t="s">
         <v>1039</v>
       </c>
-      <c r="B5" s="2" t="s">
-        <v>1040</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>1041</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>1042</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>1043</v>
-      </c>
       <c r="F5" s="2" t="s">
-        <v>854</v>
+        <v>850</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
+        <v>1040</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>1041</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>1042</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>1043</v>
+      </c>
+      <c r="E6" s="2" t="s">
         <v>1044</v>
       </c>
-      <c r="B6" s="2" t="s">
-        <v>1045</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>1046</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>1047</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>1048</v>
-      </c>
       <c r="F6" s="2" t="s">
-        <v>854</v>
+        <v>850</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
-        <v>1049</v>
+        <v>1045</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>1050</v>
+        <v>1046</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>1051</v>
+        <v>1047</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>1052</v>
+        <v>1048</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>946</v>
+        <v>942</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>858</v>
+        <v>854</v>
       </c>
     </row>
   </sheetData>
@@ -10838,106 +10868,106 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="A1" s="7" t="s">
-        <v>1053</v>
-      </c>
-      <c r="B1" s="7"/>
-      <c r="C1" s="7"/>
-      <c r="D1" s="7"/>
-      <c r="E1" s="7"/>
-      <c r="F1" s="7"/>
-      <c r="G1" s="7"/>
+      <c r="A1" s="8" t="s">
+        <v>1049</v>
+      </c>
+      <c r="B1" s="8"/>
+      <c r="C1" s="8"/>
+      <c r="D1" s="8"/>
+      <c r="E1" s="8"/>
+      <c r="F1" s="8"/>
+      <c r="G1" s="8"/>
     </row>
     <row r="3" spans="1:7" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
+        <v>1050</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>1051</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>1007</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>1009</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>1052</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>1053</v>
+      </c>
+      <c r="G3" s="1" t="s">
         <v>1054</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>1055</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>1011</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>1013</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>1056</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>1057</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>1058</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
-        <v>1035</v>
+        <v>1031</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>1059</v>
+        <v>1055</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>1060</v>
+        <v>1056</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>946</v>
+        <v>942</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>1060</v>
+        <v>1056</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>1030</v>
+        <v>1026</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>1061</v>
+        <v>1057</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
-        <v>1040</v>
+        <v>1036</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>1062</v>
+        <v>1058</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>1038</v>
+        <v>1034</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>1063</v>
+        <v>1059</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>1063</v>
+        <v>1059</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>1023</v>
+        <v>1019</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>1064</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
-        <v>1045</v>
+        <v>1041</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>1065</v>
+        <v>1061</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>1066</v>
+        <v>1062</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>1066</v>
+        <v>1062</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>946</v>
+        <v>942</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>1018</v>
+        <v>1014</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>1067</v>
+        <v>1063</v>
       </c>
     </row>
   </sheetData>
@@ -10960,67 +10990,67 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="A1" s="7" t="s">
-        <v>1068</v>
-      </c>
-      <c r="B1" s="7"/>
-      <c r="C1" s="7"/>
-      <c r="D1" s="7"/>
+      <c r="A1" s="8" t="s">
+        <v>1064</v>
+      </c>
+      <c r="B1" s="8"/>
+      <c r="C1" s="8"/>
+      <c r="D1" s="8"/>
     </row>
     <row r="3" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
-        <v>864</v>
+        <v>860</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>1069</v>
+        <v>1065</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>1070</v>
+        <v>1066</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>852</v>
+        <v>848</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
-        <v>1071</v>
+        <v>1067</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>1072</v>
+        <v>1068</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>1073</v>
+        <v>1069</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>854</v>
+        <v>850</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
-        <v>1074</v>
+        <v>1070</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>1073</v>
+        <v>1069</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>1075</v>
+        <v>1071</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>854</v>
+        <v>850</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
-        <v>1076</v>
+        <v>1072</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>1075</v>
+        <v>1071</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>1072</v>
+        <v>1068</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>854</v>
+        <v>850</v>
       </c>
     </row>
   </sheetData>
@@ -11046,104 +11076,104 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="A1" s="7" t="s">
-        <v>1077</v>
-      </c>
-      <c r="B1" s="7"/>
-      <c r="C1" s="7"/>
-      <c r="D1" s="7"/>
-      <c r="E1" s="7"/>
-      <c r="F1" s="7"/>
-      <c r="G1" s="7"/>
-      <c r="H1" s="7"/>
+      <c r="A1" s="8" t="s">
+        <v>1073</v>
+      </c>
+      <c r="B1" s="8"/>
+      <c r="C1" s="8"/>
+      <c r="D1" s="8"/>
+      <c r="E1" s="8"/>
+      <c r="F1" s="8"/>
+      <c r="G1" s="8"/>
+      <c r="H1" s="8"/>
     </row>
     <row r="3" spans="1:8" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
-        <v>856</v>
+        <v>852</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>1074</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>1075</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>1076</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>1077</v>
+      </c>
+      <c r="F3" s="1" t="s">
         <v>1078</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="G3" s="1" t="s">
+        <v>1053</v>
+      </c>
+      <c r="H3" s="1" t="s">
         <v>1079</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>1080</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>1081</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>1082</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>1057</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>1083</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
-        <v>830</v>
+        <v>826</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>1071</v>
+        <v>1067</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>1038</v>
+        <v>1034</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>1084</v>
+        <v>1080</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>1084</v>
+        <v>1080</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>946</v>
+        <v>942</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>1085</v>
+        <v>1081</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>1086</v>
+        <v>1082</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
-        <v>834</v>
+        <v>830</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>1074</v>
+        <v>1070</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>1087</v>
+        <v>1083</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>1088</v>
+        <v>1084</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>1043</v>
+        <v>1039</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>1089</v>
+        <v>1085</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>1085</v>
+        <v>1081</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>1090</v>
+        <v>1086</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
-        <v>830</v>
+        <v>826</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>1076</v>
+        <v>1072</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>1091</v>
+        <v>1087</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>5</v>
@@ -11155,10 +11185,10 @@
         <v>5</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>1092</v>
+        <v>1088</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>1093</v>
+        <v>1089</v>
       </c>
     </row>
   </sheetData>
@@ -11184,113 +11214,113 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="A1" s="7" t="s">
-        <v>1094</v>
-      </c>
-      <c r="B1" s="7"/>
-      <c r="C1" s="7"/>
-      <c r="D1" s="7"/>
-      <c r="E1" s="7"/>
-      <c r="F1" s="7"/>
+      <c r="A1" s="8" t="s">
+        <v>1090</v>
+      </c>
+      <c r="B1" s="8"/>
+      <c r="C1" s="8"/>
+      <c r="D1" s="8"/>
+      <c r="E1" s="8"/>
+      <c r="F1" s="8"/>
     </row>
     <row r="3" spans="1:6" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
-        <v>1095</v>
+        <v>1091</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>898</v>
+        <v>894</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>866</v>
+        <v>862</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>1096</v>
+        <v>1092</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>1097</v>
+        <v>1093</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>1098</v>
+        <v>1094</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
-        <v>1026</v>
+        <v>1022</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>1099</v>
+        <v>1095</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>1100</v>
+        <v>1096</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>1101</v>
+        <v>1097</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>1102</v>
+        <v>1098</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>830</v>
+        <v>826</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
-        <v>1026</v>
+        <v>1022</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>1103</v>
+        <v>1099</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>1104</v>
+        <v>1100</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>1105</v>
+        <v>1101</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>1106</v>
+        <v>1102</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>826</v>
+        <v>822</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
-        <v>1107</v>
+        <v>1103</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>1108</v>
+        <v>1104</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>1109</v>
+        <v>1105</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>1110</v>
+        <v>1106</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>1102</v>
+        <v>1098</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>834</v>
+        <v>830</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
+        <v>1103</v>
+      </c>
+      <c r="B7" s="2" t="s">
         <v>1107</v>
       </c>
-      <c r="B7" s="2" t="s">
-        <v>1111</v>
-      </c>
       <c r="C7" s="2" t="s">
-        <v>1112</v>
+        <v>1108</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>1113</v>
+        <v>1109</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>1102</v>
+        <v>1098</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>821</v>
+        <v>817</v>
       </c>
     </row>
   </sheetData>
@@ -11318,16 +11348,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="5" t="s">
         <v>190</v>
       </c>
-      <c r="B1" s="4"/>
-      <c r="C1" s="4"/>
-      <c r="D1" s="4"/>
-      <c r="E1" s="4"/>
-      <c r="F1" s="4"/>
-      <c r="G1" s="4"/>
-      <c r="H1" s="4"/>
+      <c r="B1" s="5"/>
+      <c r="C1" s="5"/>
+      <c r="D1" s="5"/>
+      <c r="E1" s="5"/>
+      <c r="F1" s="5"/>
+      <c r="G1" s="5"/>
+      <c r="H1" s="5"/>
     </row>
     <row r="3" spans="1:8" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
@@ -11378,7 +11408,7 @@
         <v>5</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>1139</v>
+        <v>1135</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="29" x14ac:dyDescent="0.35">
@@ -11404,7 +11434,7 @@
         <v>5</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>1139</v>
+        <v>1135</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
@@ -11430,7 +11460,7 @@
         <v>5</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>1139</v>
+        <v>1135</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="29" x14ac:dyDescent="0.35">
@@ -11456,7 +11486,7 @@
         <v>5</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>1139</v>
+        <v>1135</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="29" x14ac:dyDescent="0.35">
@@ -11482,7 +11512,7 @@
         <v>5</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>1139</v>
+        <v>1135</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="29" x14ac:dyDescent="0.35">
@@ -11508,7 +11538,7 @@
         <v>5</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>1139</v>
+        <v>1135</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="58" x14ac:dyDescent="0.35">
@@ -11534,7 +11564,7 @@
         <v>5</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>1139</v>
+        <v>1135</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="29" x14ac:dyDescent="0.35">
@@ -11560,7 +11590,7 @@
         <v>5</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>1139</v>
+        <v>1135</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.35">
@@ -11586,7 +11616,7 @@
         <v>5</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>1139</v>
+        <v>1135</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="58" x14ac:dyDescent="0.35">
@@ -11606,36 +11636,36 @@
         <v>227</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>1144</v>
+        <v>1140</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>5</v>
       </c>
       <c r="H13" s="3" t="s">
+        <v>1135</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" ht="58" x14ac:dyDescent="0.35">
+      <c r="A14" s="4">
+        <v>11</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>1136</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>1137</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>1138</v>
+      </c>
+      <c r="F14" s="2" t="s">
         <v>1139</v>
       </c>
-    </row>
-    <row r="14" spans="1:8" ht="58" x14ac:dyDescent="0.35">
-      <c r="A14" s="8">
-        <v>11</v>
-      </c>
-      <c r="B14" s="8" t="s">
-        <v>119</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>1140</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>1141</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>1142</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>1143</v>
-      </c>
       <c r="H14" s="3" t="s">
-        <v>1139</v>
+        <v>1135</v>
       </c>
     </row>
   </sheetData>
@@ -11662,241 +11692,241 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="A1" s="7" t="s">
-        <v>1114</v>
-      </c>
-      <c r="B1" s="7"/>
-      <c r="C1" s="7"/>
-      <c r="D1" s="7"/>
-      <c r="E1" s="7"/>
-      <c r="F1" s="7"/>
-      <c r="G1" s="7"/>
-      <c r="H1" s="7"/>
-      <c r="I1" s="7"/>
-      <c r="J1" s="7"/>
+      <c r="A1" s="8" t="s">
+        <v>1110</v>
+      </c>
+      <c r="B1" s="8"/>
+      <c r="C1" s="8"/>
+      <c r="D1" s="8"/>
+      <c r="E1" s="8"/>
+      <c r="F1" s="8"/>
+      <c r="G1" s="8"/>
+      <c r="H1" s="8"/>
+      <c r="I1" s="8"/>
+      <c r="J1" s="8"/>
     </row>
     <row r="3" spans="1:10" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
-        <v>1115</v>
+        <v>1111</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>856</v>
+        <v>852</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>1009</v>
+        <v>1005</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>1097</v>
+        <v>1093</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>1116</v>
+        <v>1112</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>1011</v>
+        <v>1007</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>1054</v>
+        <v>1050</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>1117</v>
+        <v>1113</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>1057</v>
+        <v>1053</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>1118</v>
+        <v>1114</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
-        <v>1119</v>
+        <v>1115</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>830</v>
+        <v>826</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>1120</v>
+        <v>1116</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>1102</v>
+        <v>1098</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>939</v>
+        <v>935</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>1121</v>
+        <v>1117</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>159</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>858</v>
+        <v>854</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>1122</v>
+        <v>1118</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>1123</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
-        <v>1124</v>
+        <v>1120</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>830</v>
+        <v>826</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>1125</v>
+        <v>1121</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>1126</v>
+        <v>1122</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>1127</v>
+        <v>1123</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>1127</v>
+        <v>1123</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>159</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>858</v>
+        <v>854</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>1122</v>
+        <v>1118</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>1128</v>
+        <v>1124</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
-        <v>1129</v>
+        <v>1125</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>834</v>
+        <v>830</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>1130</v>
+        <v>1126</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>1106</v>
+        <v>1102</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>927</v>
+        <v>923</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>927</v>
+        <v>923</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>159</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>858</v>
+        <v>854</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>1122</v>
+        <v>1118</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>1131</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
-        <v>1059</v>
+        <v>1055</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>830</v>
+        <v>826</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>1132</v>
+        <v>1128</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>1133</v>
+        <v>1129</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>946</v>
+        <v>942</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>1060</v>
+        <v>1056</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>1035</v>
+        <v>1031</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>854</v>
+        <v>850</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>1122</v>
+        <v>1118</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>1123</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
-        <v>1065</v>
+        <v>1061</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>834</v>
+        <v>830</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>1134</v>
+        <v>1130</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>1102</v>
+        <v>1098</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>961</v>
+        <v>957</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>961</v>
+        <v>957</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>159</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>858</v>
+        <v>854</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>1122</v>
+        <v>1118</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>1123</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="9" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A9" s="2" t="s">
-        <v>1135</v>
+        <v>1131</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>830</v>
+        <v>826</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>1136</v>
+        <v>1132</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>1102</v>
+        <v>1098</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>1137</v>
+        <v>1133</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>1137</v>
+        <v>1133</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>159</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>858</v>
+        <v>854</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>1138</v>
+        <v>1134</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>1123</v>
+        <v>1119</v>
       </c>
     </row>
   </sheetData>
@@ -11924,16 +11954,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="5" t="s">
         <v>228</v>
       </c>
-      <c r="B1" s="4"/>
-      <c r="C1" s="4"/>
-      <c r="D1" s="4"/>
-      <c r="E1" s="4"/>
-      <c r="F1" s="4"/>
-      <c r="G1" s="4"/>
-      <c r="H1" s="4"/>
+      <c r="B1" s="5"/>
+      <c r="C1" s="5"/>
+      <c r="D1" s="5"/>
+      <c r="E1" s="5"/>
+      <c r="F1" s="5"/>
+      <c r="G1" s="5"/>
+      <c r="H1" s="5"/>
     </row>
     <row r="3" spans="1:8" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
@@ -12194,16 +12224,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="5" t="s">
         <v>258</v>
       </c>
-      <c r="B1" s="4"/>
-      <c r="C1" s="4"/>
-      <c r="D1" s="4"/>
-      <c r="E1" s="4"/>
-      <c r="F1" s="4"/>
-      <c r="G1" s="4"/>
-      <c r="H1" s="4"/>
+      <c r="B1" s="5"/>
+      <c r="C1" s="5"/>
+      <c r="D1" s="5"/>
+      <c r="E1" s="5"/>
+      <c r="F1" s="5"/>
+      <c r="G1" s="5"/>
+      <c r="H1" s="5"/>
     </row>
     <row r="3" spans="1:8" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
@@ -12412,16 +12442,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="5" t="s">
         <v>281</v>
       </c>
-      <c r="B1" s="4"/>
-      <c r="C1" s="4"/>
-      <c r="D1" s="4"/>
-      <c r="E1" s="4"/>
-      <c r="F1" s="4"/>
-      <c r="G1" s="4"/>
-      <c r="H1" s="4"/>
+      <c r="B1" s="5"/>
+      <c r="C1" s="5"/>
+      <c r="D1" s="5"/>
+      <c r="E1" s="5"/>
+      <c r="F1" s="5"/>
+      <c r="G1" s="5"/>
+      <c r="H1" s="5"/>
     </row>
     <row r="3" spans="1:8" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
@@ -12472,7 +12502,7 @@
         <v>5</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>1139</v>
+        <v>1135</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
@@ -12498,7 +12528,7 @@
         <v>5</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>1139</v>
+        <v>1135</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="29" x14ac:dyDescent="0.35">
@@ -12509,22 +12539,22 @@
         <v>229</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>289</v>
+        <v>1144</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>290</v>
+        <v>317</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>291</v>
+        <v>318</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>292</v>
+        <v>319</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>5</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>1139</v>
+        <v>1135</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="29" x14ac:dyDescent="0.35">
@@ -12535,22 +12565,22 @@
         <v>229</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>294</v>
+        <v>290</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="H7" s="2" t="s">
-        <v>5</v>
+      <c r="H7" s="3" t="s">
+        <v>1135</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
@@ -12561,22 +12591,22 @@
         <v>229</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>299</v>
+        <v>295</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="H8" s="2" t="s">
-        <v>5</v>
+      <c r="H8" s="3" t="s">
+        <v>1135</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="29" x14ac:dyDescent="0.35">
@@ -12587,22 +12617,22 @@
         <v>229</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="H9" s="2" t="s">
-        <v>5</v>
+      <c r="H9" s="3" t="s">
+        <v>1135</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
@@ -12613,22 +12643,22 @@
         <v>229</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>306</v>
+        <v>302</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="H10" s="2" t="s">
-        <v>5</v>
+      <c r="H10" s="3" t="s">
+        <v>1135</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="58" x14ac:dyDescent="0.35">
@@ -12639,48 +12669,48 @@
         <v>128</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>159</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="H11" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" ht="29" x14ac:dyDescent="0.35">
+      <c r="H11" s="3" t="s">
+        <v>1135</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A12" s="2">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>229</v>
+        <v>119</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>1148</v>
+        <v>1149</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>321</v>
+        <v>1150</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>322</v>
+        <v>299</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>323</v>
+        <v>1151</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>5</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>1139</v>
+        <v>1135</v>
       </c>
     </row>
   </sheetData>
@@ -12694,7 +12724,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
@@ -12708,16 +12738,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="A1" s="4" t="s">
-        <v>312</v>
-      </c>
-      <c r="B1" s="4"/>
-      <c r="C1" s="4"/>
-      <c r="D1" s="4"/>
-      <c r="E1" s="4"/>
-      <c r="F1" s="4"/>
-      <c r="G1" s="4"/>
-      <c r="H1" s="4"/>
+      <c r="A1" s="5" t="s">
+        <v>308</v>
+      </c>
+      <c r="B1" s="5"/>
+      <c r="C1" s="5"/>
+      <c r="D1" s="5"/>
+      <c r="E1" s="5"/>
+      <c r="F1" s="5"/>
+      <c r="G1" s="5"/>
+      <c r="H1" s="5"/>
     </row>
     <row r="3" spans="1:8" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
@@ -12753,22 +12783,22 @@
         <v>229</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>159</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>5</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>1139</v>
+        <v>1135</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
@@ -12779,22 +12809,22 @@
         <v>229</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>5</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>1139</v>
+        <v>1135</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="29" x14ac:dyDescent="0.35">
@@ -12805,25 +12835,25 @@
         <v>229</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>5</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>1139</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
+        <v>1135</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A7" s="2">
         <v>4</v>
       </c>
@@ -12831,25 +12861,25 @@
         <v>229</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>324</v>
+        <v>1141</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>325</v>
+        <v>1142</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>326</v>
+        <v>1143</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>300</v>
+        <v>292</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="H7" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" ht="29" x14ac:dyDescent="0.35">
+      <c r="H7" s="3" t="s">
+        <v>1135</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A8" s="2">
         <v>5</v>
       </c>
@@ -12857,27 +12887,27 @@
         <v>229</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>327</v>
+        <v>320</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>328</v>
+        <v>321</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>329</v>
+        <v>322</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>330</v>
+        <v>296</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="H8" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="H8" s="3" t="s">
+        <v>1135</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A9" s="2">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>229</v>
@@ -12892,13 +12922,91 @@
         <v>1147</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>292</v>
+        <v>300</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>5</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>1139</v>
+        <v>1135</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="29" x14ac:dyDescent="0.35">
+      <c r="A10" s="2">
+        <v>7</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>324</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>326</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>1135</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="58" x14ac:dyDescent="0.35">
+      <c r="A11" s="2">
+        <v>8</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>1148</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>306</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>307</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="H11" s="3" t="s">
+        <v>1135</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A12" s="2">
+        <v>9</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>1152</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>1153</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>1158</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>1154</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>1135</v>
       </c>
     </row>
   </sheetData>
@@ -12912,7 +13020,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
-  <dimension ref="A1:H20"/>
+  <dimension ref="A1:H21"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
@@ -12926,16 +13034,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="A1" s="4" t="s">
-        <v>331</v>
-      </c>
-      <c r="B1" s="4"/>
-      <c r="C1" s="4"/>
-      <c r="D1" s="4"/>
-      <c r="E1" s="4"/>
-      <c r="F1" s="4"/>
-      <c r="G1" s="4"/>
-      <c r="H1" s="4"/>
+      <c r="A1" s="5" t="s">
+        <v>327</v>
+      </c>
+      <c r="B1" s="5"/>
+      <c r="C1" s="5"/>
+      <c r="D1" s="5"/>
+      <c r="E1" s="5"/>
+      <c r="F1" s="5"/>
+      <c r="G1" s="5"/>
+      <c r="H1" s="5"/>
     </row>
     <row r="3" spans="1:8" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
@@ -12971,22 +13079,22 @@
         <v>229</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="2" t="s">
-        <v>5</v>
+      <c r="H4" s="3" t="s">
+        <v>1135</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="87" x14ac:dyDescent="0.35">
@@ -12997,22 +13105,22 @@
         <v>229</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>337</v>
+        <v>333</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>339</v>
+        <v>335</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="H5" s="2" t="s">
-        <v>5</v>
+      <c r="H5" s="3" t="s">
+        <v>1135</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="29" x14ac:dyDescent="0.35">
@@ -13023,13 +13131,13 @@
         <v>229</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>342</v>
+        <v>338</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>246</v>
@@ -13037,8 +13145,8 @@
       <c r="G6" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="H6" s="2" t="s">
-        <v>5</v>
+      <c r="H6" s="3" t="s">
+        <v>1135</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="29" x14ac:dyDescent="0.35">
@@ -13049,22 +13157,22 @@
         <v>229</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>343</v>
+        <v>339</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>346</v>
+        <v>342</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="H7" s="2" t="s">
-        <v>5</v>
+      <c r="H7" s="3" t="s">
+        <v>1135</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="29" x14ac:dyDescent="0.35">
@@ -13075,22 +13183,22 @@
         <v>229</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>347</v>
+        <v>343</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>348</v>
+        <v>344</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="H8" s="2" t="s">
-        <v>5</v>
+      <c r="H8" s="3" t="s">
+        <v>1135</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="29" x14ac:dyDescent="0.35">
@@ -13101,22 +13209,22 @@
         <v>229</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>159</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>353</v>
+        <v>349</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="H9" s="2" t="s">
-        <v>5</v>
+      <c r="H9" s="3" t="s">
+        <v>1135</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.35">
@@ -13127,22 +13235,22 @@
         <v>229</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>354</v>
+        <v>350</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>355</v>
+        <v>351</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>159</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>356</v>
+        <v>352</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="H10" s="2" t="s">
-        <v>5</v>
+      <c r="H10" s="3" t="s">
+        <v>1135</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="29" x14ac:dyDescent="0.35">
@@ -13153,22 +13261,22 @@
         <v>229</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>357</v>
+        <v>353</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>358</v>
+        <v>354</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>359</v>
+        <v>355</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="H11" s="2" t="s">
-        <v>5</v>
+      <c r="H11" s="3" t="s">
+        <v>1135</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="29" x14ac:dyDescent="0.35">
@@ -13179,22 +13287,22 @@
         <v>229</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>361</v>
+        <v>357</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>362</v>
+        <v>358</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>363</v>
+        <v>359</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="H12" s="2" t="s">
-        <v>5</v>
+      <c r="H12" s="3" t="s">
+        <v>1135</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="58" x14ac:dyDescent="0.35">
@@ -13205,16 +13313,16 @@
         <v>229</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>365</v>
+        <v>361</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>366</v>
+        <v>362</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>367</v>
+        <v>363</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>368</v>
+        <v>364</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>5</v>
@@ -13231,16 +13339,16 @@
         <v>229</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>369</v>
+        <v>365</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>371</v>
+        <v>367</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>372</v>
+        <v>368</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>5</v>
@@ -13257,16 +13365,16 @@
         <v>229</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>373</v>
+        <v>369</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>376</v>
+        <v>372</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>5</v>
@@ -13283,16 +13391,16 @@
         <v>229</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>378</v>
+        <v>374</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>379</v>
+        <v>375</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>380</v>
+        <v>376</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>5</v>
@@ -13309,16 +13417,16 @@
         <v>229</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="G17" s="2" t="s">
         <v>5</v>
@@ -13335,16 +13443,16 @@
         <v>229</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>385</v>
+        <v>381</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>386</v>
+        <v>382</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>387</v>
+        <v>383</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>388</v>
+        <v>384</v>
       </c>
       <c r="G18" s="2" t="s">
         <v>5</v>
@@ -13361,16 +13469,16 @@
         <v>229</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>389</v>
+        <v>385</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>390</v>
+        <v>386</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>391</v>
+        <v>387</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>392</v>
+        <v>388</v>
       </c>
       <c r="G19" s="2" t="s">
         <v>5</v>
@@ -13387,22 +13495,48 @@
         <v>128</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>393</v>
+        <v>389</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>394</v>
+        <v>390</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>159</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>395</v>
+        <v>391</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>5</v>
       </c>
       <c r="H20" s="2" t="s">
         <v>5</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A21" s="2">
+        <v>9</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>1155</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>1156</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>1157</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="H21" s="3" t="s">
+        <v>1135</v>
       </c>
     </row>
   </sheetData>

--- a/docs/Dokumen_Testing_POS.xlsx
+++ b/docs/Dokumen_Testing_POS.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4393C7C9-49DA-405F-A7C9-082D32B48FFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{032A6B41-4582-4003-B580-8B77DCAC5697}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="867" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="867" firstSheet="6" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Daftar Isi" sheetId="1" r:id="rId1"/>
@@ -49,12 +49,23 @@
     <sheet name="Dummy - Pengeluaran" sheetId="39" r:id="rId39"/>
     <sheet name="Dummy - Transaksi" sheetId="40" r:id="rId40"/>
   </sheets>
-  <calcPr calcId="171027"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2290" uniqueCount="1159">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2270" uniqueCount="1145">
   <si>
     <t>DOKUMEN TESTING APLIKASI POS</t>
   </si>
@@ -2895,9 +2906,6 @@
     <t>min_stock</t>
   </si>
   <si>
-    <t>8991002100016</t>
-  </si>
-  <si>
     <t>SKU-0001</t>
   </si>
   <si>
@@ -2913,27 +2921,15 @@
     <t>200</t>
   </si>
   <si>
-    <t>8992388123456</t>
-  </si>
-  <si>
     <t>SKU-0002</t>
   </si>
   <si>
     <t>Teh Botol Sosro 450ml</t>
   </si>
   <si>
-    <t>4000</t>
-  </si>
-  <si>
-    <t>5000</t>
-  </si>
-  <si>
     <t>150</t>
   </si>
   <si>
-    <t>8996001600028</t>
-  </si>
-  <si>
     <t>SKU-0003</t>
   </si>
   <si>
@@ -2970,54 +2966,33 @@
     <t>50</t>
   </si>
   <si>
-    <t>8991234567890</t>
-  </si>
-  <si>
     <t>SKU-0005</t>
   </si>
   <si>
     <t>Sampoerna A Mild 16</t>
   </si>
   <si>
-    <t>22000</t>
-  </si>
-  <si>
-    <t>24000</t>
-  </si>
-  <si>
     <t>80</t>
   </si>
   <si>
-    <t>8990001112223</t>
-  </si>
-  <si>
     <t>SKU-0006</t>
   </si>
   <si>
     <t>Chitato Sapi Panggang 68g</t>
   </si>
   <si>
-    <t>8500</t>
-  </si>
-  <si>
     <t>10000</t>
   </si>
   <si>
     <t>true - stok di bawah min_stock (untuk uji notifikasi stok)</t>
   </si>
   <si>
-    <t>8990004445556</t>
-  </si>
-  <si>
     <t>SKU-0007</t>
   </si>
   <si>
     <t>Kopi Kapal Api Sachet</t>
   </si>
   <si>
-    <t>1200</t>
-  </si>
-  <si>
     <t>1500</t>
   </si>
   <si>
@@ -3073,12 +3048,6 @@
   </si>
   <si>
     <t>Dus (isi 24)</t>
-  </si>
-  <si>
-    <t>78000</t>
-  </si>
-  <si>
-    <t>65000</t>
   </si>
   <si>
     <t>DUMMY DATA - DATA HARGA GROSIR (TIER PRICE) - lanjutan sheet Produk</t>
@@ -7150,7 +7119,7 @@
         <v>5</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>1135</v>
+        <v>1121</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="29" x14ac:dyDescent="0.35">
@@ -7176,7 +7145,7 @@
         <v>5</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>1135</v>
+        <v>1121</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="29" x14ac:dyDescent="0.35">
@@ -7202,7 +7171,7 @@
         <v>5</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>1135</v>
+        <v>1121</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="29" x14ac:dyDescent="0.35">
@@ -7228,7 +7197,7 @@
         <v>5</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>1135</v>
+        <v>1121</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="29" x14ac:dyDescent="0.35">
@@ -7254,7 +7223,7 @@
         <v>5</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>1135</v>
+        <v>1121</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="29" x14ac:dyDescent="0.35">
@@ -7280,7 +7249,7 @@
         <v>5</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>1135</v>
+        <v>1121</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="29" x14ac:dyDescent="0.35">
@@ -7306,7 +7275,7 @@
         <v>5</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>1135</v>
+        <v>1121</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
@@ -7332,7 +7301,7 @@
         <v>5</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>1135</v>
+        <v>1121</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
@@ -7384,7 +7353,7 @@
         <v>5</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>1135</v>
+        <v>1121</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
@@ -9943,14 +9912,14 @@
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A4" s="2" t="s">
+      <c r="A4" s="2">
+        <v>8991002100016</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>900</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="C4" s="2" t="s">
         <v>901</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>902</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>864</v>
@@ -9958,14 +9927,14 @@
       <c r="E4" s="2" t="s">
         <v>879</v>
       </c>
-      <c r="F4" s="2" t="s">
-        <v>903</v>
-      </c>
-      <c r="G4" s="2" t="s">
+      <c r="F4" s="2">
+        <v>2500</v>
+      </c>
+      <c r="G4" s="2">
+        <v>3000</v>
+      </c>
+      <c r="H4" s="2" t="s">
         <v>904</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>905</v>
       </c>
       <c r="I4" s="2" t="s">
         <v>63</v>
@@ -9975,14 +9944,14 @@
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A5" s="2" t="s">
+      <c r="A5" s="2">
+        <v>8992388123456</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>905</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>906</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>907</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>908</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>867</v>
@@ -9990,14 +9959,14 @@
       <c r="E5" s="2" t="s">
         <v>879</v>
       </c>
-      <c r="F5" s="2" t="s">
-        <v>909</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>910</v>
+      <c r="F5" s="2">
+        <v>4000</v>
+      </c>
+      <c r="G5" s="2">
+        <v>5000</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>911</v>
+        <v>907</v>
       </c>
       <c r="I5" s="2" t="s">
         <v>48</v>
@@ -10007,14 +9976,14 @@
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A6" s="2" t="s">
-        <v>912</v>
+      <c r="A6" s="2">
+        <v>8996001600028</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>913</v>
+        <v>908</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>914</v>
+        <v>909</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>867</v>
@@ -10022,17 +9991,17 @@
       <c r="E6" s="2" t="s">
         <v>879</v>
       </c>
-      <c r="F6" s="2" t="s">
-        <v>915</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>916</v>
+      <c r="F6" s="2">
+        <v>2800</v>
+      </c>
+      <c r="G6" s="2">
+        <v>3500</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>917</v>
+        <v>912</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>918</v>
+        <v>913</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>850</v>
@@ -10040,13 +10009,13 @@
     </row>
     <row r="7" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
-        <v>919</v>
+        <v>914</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>920</v>
+        <v>915</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>921</v>
+        <v>916</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>870</v>
@@ -10055,13 +10024,13 @@
         <v>879</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>922</v>
+        <v>917</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>923</v>
+        <v>918</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>924</v>
+        <v>919</v>
       </c>
       <c r="I7" s="2" t="s">
         <v>18</v>
@@ -10071,14 +10040,14 @@
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A8" s="2" t="s">
-        <v>925</v>
+      <c r="A8" s="2">
+        <v>8991234567890</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>926</v>
+        <v>920</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>927</v>
+        <v>921</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>873</v>
@@ -10086,14 +10055,14 @@
       <c r="E8" s="2" t="s">
         <v>879</v>
       </c>
-      <c r="F8" s="2" t="s">
-        <v>928</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>929</v>
+      <c r="F8" s="2">
+        <v>22000</v>
+      </c>
+      <c r="G8" s="2">
+        <v>24000</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>930</v>
+        <v>922</v>
       </c>
       <c r="I8" s="2" t="s">
         <v>33</v>
@@ -10103,14 +10072,14 @@
       </c>
     </row>
     <row r="9" spans="1:10" ht="29" x14ac:dyDescent="0.35">
-      <c r="A9" s="2" t="s">
-        <v>931</v>
+      <c r="A9" s="2">
+        <v>8990001112223</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>932</v>
+        <v>923</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>933</v>
+        <v>924</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>864</v>
@@ -10118,11 +10087,11 @@
       <c r="E9" s="2" t="s">
         <v>879</v>
       </c>
-      <c r="F9" s="2" t="s">
-        <v>934</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>935</v>
+      <c r="F9" s="2">
+        <v>8500</v>
+      </c>
+      <c r="G9" s="2">
+        <v>10000</v>
       </c>
       <c r="H9" s="2" t="s">
         <v>18</v>
@@ -10131,18 +10100,18 @@
         <v>33</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>936</v>
+        <v>926</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A10" s="2" t="s">
-        <v>937</v>
+      <c r="A10" s="2">
+        <v>8990004445556</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>938</v>
+        <v>927</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>939</v>
+        <v>928</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>867</v>
@@ -10150,31 +10119,31 @@
       <c r="E10" s="2" t="s">
         <v>879</v>
       </c>
-      <c r="F10" s="2" t="s">
-        <v>940</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>941</v>
+      <c r="F10" s="2">
+        <v>1200</v>
+      </c>
+      <c r="G10" s="2">
+        <v>1500</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>942</v>
+        <v>930</v>
       </c>
       <c r="I10" s="2" t="s">
         <v>63</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>943</v>
+        <v>931</v>
       </c>
     </row>
     <row r="11" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A11" s="2" t="s">
-        <v>944</v>
+        <v>932</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>945</v>
+        <v>933</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>946</v>
+        <v>934</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>864</v>
@@ -10183,10 +10152,10 @@
         <v>879</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>947</v>
+        <v>935</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>941</v>
+        <v>929</v>
       </c>
       <c r="H11" s="2" t="s">
         <v>33</v>
@@ -10195,7 +10164,7 @@
         <v>18</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>948</v>
+        <v>936</v>
       </c>
     </row>
   </sheetData>
@@ -10221,7 +10190,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A1" s="8" t="s">
-        <v>949</v>
+        <v>937</v>
       </c>
       <c r="B1" s="8"/>
       <c r="C1" s="8"/>
@@ -10232,16 +10201,16 @@
     </row>
     <row r="3" spans="1:7" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
-        <v>950</v>
+        <v>938</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>951</v>
+        <v>939</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>895</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>952</v>
+        <v>940</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>897</v>
@@ -10250,15 +10219,15 @@
         <v>896</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>953</v>
+        <v>941</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>954</v>
+        <v>942</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>879</v>
@@ -10267,10 +10236,10 @@
         <v>6</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>850</v>
@@ -10278,22 +10247,22 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>955</v>
+        <v>943</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>883</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>956</v>
+        <v>944</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>957</v>
+        <v>945</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>958</v>
+        <v>946</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>854</v>
@@ -10301,10 +10270,10 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
-        <v>914</v>
+        <v>909</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>954</v>
+        <v>942</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>879</v>
@@ -10313,10 +10282,10 @@
         <v>6</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>916</v>
+        <v>911</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>915</v>
+        <v>910</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>850</v>
@@ -10324,10 +10293,10 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
-        <v>914</v>
+        <v>909</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>959</v>
+        <v>947</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>883</v>
@@ -10335,11 +10304,11 @@
       <c r="D7" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="E7" s="2" t="s">
-        <v>960</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>961</v>
+      <c r="E7" s="2">
+        <v>78000</v>
+      </c>
+      <c r="F7" s="2">
+        <v>65000</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>854</v>
@@ -10365,7 +10334,7 @@
   <sheetData>
     <row r="1" spans="1:4" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A1" s="8" t="s">
-        <v>962</v>
+        <v>948</v>
       </c>
       <c r="B1" s="8"/>
       <c r="C1" s="8"/>
@@ -10373,58 +10342,58 @@
     </row>
     <row r="3" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
+        <v>938</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>949</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>950</v>
       </c>
-      <c r="B3" s="1" t="s">
-        <v>963</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>964</v>
-      </c>
       <c r="D3" s="1" t="s">
-        <v>965</v>
+        <v>951</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>966</v>
+        <v>952</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>39</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>915</v>
+        <v>910</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>967</v>
+        <v>953</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>956</v>
+        <v>944</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>968</v>
+        <v>954</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
-        <v>914</v>
+        <v>909</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>969</v>
+        <v>955</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>75</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>970</v>
+        <v>956</v>
       </c>
     </row>
   </sheetData>
@@ -10452,7 +10421,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A1" s="8" t="s">
-        <v>971</v>
+        <v>957</v>
       </c>
       <c r="B1" s="8"/>
       <c r="C1" s="8"/>
@@ -10463,22 +10432,22 @@
     </row>
     <row r="3" spans="1:7" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
-        <v>972</v>
+        <v>958</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>860</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>973</v>
+        <v>959</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>974</v>
+        <v>960</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>975</v>
+        <v>961</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>976</v>
+        <v>962</v>
       </c>
       <c r="G3" s="1" t="s">
         <v>848</v>
@@ -10486,22 +10455,22 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
-        <v>977</v>
+        <v>963</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>978</v>
+        <v>964</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>979</v>
+        <v>965</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>980</v>
+        <v>966</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>981</v>
+        <v>967</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>982</v>
+        <v>968</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>850</v>
@@ -10509,22 +10478,22 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
-        <v>983</v>
+        <v>969</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>984</v>
+        <v>970</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>985</v>
+        <v>971</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>986</v>
+        <v>972</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>987</v>
+        <v>973</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>988</v>
+        <v>974</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>850</v>
@@ -10532,22 +10501,22 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
-        <v>989</v>
+        <v>975</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>990</v>
+        <v>976</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>991</v>
+        <v>977</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>992</v>
+        <v>978</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>993</v>
+        <v>979</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>994</v>
+        <v>980</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>850</v>
@@ -10555,22 +10524,22 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
-        <v>995</v>
+        <v>981</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>996</v>
+        <v>982</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>997</v>
+        <v>983</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>998</v>
+        <v>984</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>999</v>
+        <v>985</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>1000</v>
+        <v>986</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>854</v>
@@ -10599,7 +10568,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A1" s="8" t="s">
-        <v>1001</v>
+        <v>987</v>
       </c>
       <c r="B1" s="8"/>
       <c r="C1" s="8"/>
@@ -10611,106 +10580,106 @@
     </row>
     <row r="3" spans="1:8" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
-        <v>1002</v>
+        <v>988</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>1003</v>
+        <v>989</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>1004</v>
+        <v>990</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>1005</v>
+        <v>991</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>1006</v>
+        <v>992</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>1007</v>
+        <v>993</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>1008</v>
+        <v>994</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>1009</v>
+        <v>995</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
-        <v>1010</v>
+        <v>996</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>978</v>
+        <v>964</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>1011</v>
+        <v>997</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>1012</v>
+        <v>998</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>935</v>
+        <v>925</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>1013</v>
+        <v>999</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>1014</v>
+        <v>1000</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>1013</v>
+        <v>999</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
-        <v>1015</v>
+        <v>1001</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>984</v>
+        <v>970</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>1016</v>
+        <v>1002</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>1017</v>
+        <v>1003</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>942</v>
+        <v>930</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>1018</v>
+        <v>1004</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>1019</v>
+        <v>1005</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>1020</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
-        <v>1021</v>
+        <v>1007</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>990</v>
+        <v>976</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>1022</v>
+        <v>1008</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>1023</v>
+        <v>1009</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>1024</v>
+        <v>1010</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>1025</v>
+        <v>1011</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>1026</v>
+        <v>1012</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>942</v>
+        <v>930</v>
       </c>
     </row>
   </sheetData>
@@ -10737,7 +10706,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A1" s="8" t="s">
-        <v>1027</v>
+        <v>1013</v>
       </c>
       <c r="B1" s="8"/>
       <c r="C1" s="8"/>
@@ -10747,19 +10716,19 @@
     </row>
     <row r="3" spans="1:6" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
-        <v>1028</v>
+        <v>1014</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>860</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>974</v>
+        <v>960</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>973</v>
+        <v>959</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>1029</v>
+        <v>1015</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>848</v>
@@ -10767,19 +10736,19 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
-        <v>1030</v>
+        <v>1016</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>1031</v>
+        <v>1017</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>1032</v>
+        <v>1018</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>1033</v>
+        <v>1019</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>1034</v>
+        <v>1020</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>850</v>
@@ -10787,19 +10756,19 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
-        <v>1035</v>
+        <v>1021</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>1036</v>
+        <v>1022</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>1037</v>
+        <v>1023</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>1038</v>
+        <v>1024</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>1039</v>
+        <v>1025</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>850</v>
@@ -10807,19 +10776,19 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
-        <v>1040</v>
+        <v>1026</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>1041</v>
+        <v>1027</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>1042</v>
+        <v>1028</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>1043</v>
+        <v>1029</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>1044</v>
+        <v>1030</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>850</v>
@@ -10827,19 +10796,19 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
-        <v>1045</v>
+        <v>1031</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>1046</v>
+        <v>1032</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>1047</v>
+        <v>1033</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>1048</v>
+        <v>1034</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>942</v>
+        <v>930</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>854</v>
@@ -10869,7 +10838,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A1" s="8" t="s">
-        <v>1049</v>
+        <v>1035</v>
       </c>
       <c r="B1" s="8"/>
       <c r="C1" s="8"/>
@@ -10880,94 +10849,94 @@
     </row>
     <row r="3" spans="1:7" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
-        <v>1050</v>
+        <v>1036</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>1051</v>
+        <v>1037</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>1007</v>
+        <v>993</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>1009</v>
+        <v>995</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>1052</v>
+        <v>1038</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>1053</v>
+        <v>1039</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>1054</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
-        <v>1031</v>
+        <v>1017</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>1055</v>
+        <v>1041</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>1056</v>
+        <v>1042</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>942</v>
+        <v>930</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>1056</v>
+        <v>1042</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>1026</v>
+        <v>1012</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>1057</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
-        <v>1036</v>
+        <v>1022</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>1058</v>
+        <v>1044</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>1034</v>
+        <v>1020</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>1059</v>
+        <v>1045</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>1059</v>
+        <v>1045</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>1019</v>
+        <v>1005</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>1060</v>
+        <v>1046</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
-        <v>1041</v>
+        <v>1027</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>1061</v>
+        <v>1047</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>1062</v>
+        <v>1048</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>1062</v>
+        <v>1048</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>942</v>
+        <v>930</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>1014</v>
+        <v>1000</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>1063</v>
+        <v>1049</v>
       </c>
     </row>
   </sheetData>
@@ -10991,7 +10960,7 @@
   <sheetData>
     <row r="1" spans="1:4" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A1" s="8" t="s">
-        <v>1064</v>
+        <v>1050</v>
       </c>
       <c r="B1" s="8"/>
       <c r="C1" s="8"/>
@@ -11002,10 +10971,10 @@
         <v>860</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>1065</v>
+        <v>1051</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>1066</v>
+        <v>1052</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>848</v>
@@ -11013,13 +10982,13 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
-        <v>1067</v>
+        <v>1053</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>1068</v>
+        <v>1054</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>1069</v>
+        <v>1055</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>850</v>
@@ -11027,13 +10996,13 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
-        <v>1070</v>
+        <v>1056</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>1069</v>
+        <v>1055</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>1071</v>
+        <v>1057</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>850</v>
@@ -11041,13 +11010,13 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
-        <v>1072</v>
+        <v>1058</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>1071</v>
+        <v>1057</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>1068</v>
+        <v>1054</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>850</v>
@@ -11077,7 +11046,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A1" s="8" t="s">
-        <v>1073</v>
+        <v>1059</v>
       </c>
       <c r="B1" s="8"/>
       <c r="C1" s="8"/>
@@ -11092,25 +11061,25 @@
         <v>852</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>1074</v>
+        <v>1060</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>1075</v>
+        <v>1061</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>1076</v>
+        <v>1062</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>1077</v>
+        <v>1063</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>1078</v>
+        <v>1064</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>1053</v>
+        <v>1039</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>1079</v>
+        <v>1065</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.35">
@@ -11118,25 +11087,25 @@
         <v>826</v>
       </c>
       <c r="B4" s="2" t="s">
+        <v>1053</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>1020</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>1066</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>1066</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>930</v>
+      </c>
+      <c r="G4" s="2" t="s">
         <v>1067</v>
       </c>
-      <c r="C4" s="2" t="s">
-        <v>1034</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>1080</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>1080</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>942</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>1081</v>
-      </c>
       <c r="H4" s="2" t="s">
-        <v>1082</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.35">
@@ -11144,25 +11113,25 @@
         <v>830</v>
       </c>
       <c r="B5" s="2" t="s">
+        <v>1056</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>1069</v>
+      </c>
+      <c r="D5" s="2" t="s">
         <v>1070</v>
       </c>
-      <c r="C5" s="2" t="s">
-        <v>1083</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>1084</v>
-      </c>
       <c r="E5" s="2" t="s">
-        <v>1039</v>
+        <v>1025</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>1085</v>
+        <v>1071</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>1081</v>
+        <v>1067</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>1086</v>
+        <v>1072</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.35">
@@ -11170,10 +11139,10 @@
         <v>826</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>1072</v>
+        <v>1058</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>1087</v>
+        <v>1073</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>5</v>
@@ -11185,10 +11154,10 @@
         <v>5</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>1088</v>
+        <v>1074</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>1089</v>
+        <v>1075</v>
       </c>
     </row>
   </sheetData>
@@ -11215,7 +11184,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A1" s="8" t="s">
-        <v>1090</v>
+        <v>1076</v>
       </c>
       <c r="B1" s="8"/>
       <c r="C1" s="8"/>
@@ -11225,7 +11194,7 @@
     </row>
     <row r="3" spans="1:6" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
-        <v>1091</v>
+        <v>1077</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>894</v>
@@ -11234,30 +11203,30 @@
         <v>862</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>1092</v>
+        <v>1078</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>1093</v>
+        <v>1079</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>1094</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
-        <v>1022</v>
+        <v>1008</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>1095</v>
+        <v>1081</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>1096</v>
+        <v>1082</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>1097</v>
+        <v>1083</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>1098</v>
+        <v>1084</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>826</v>
@@ -11265,19 +11234,19 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
-        <v>1022</v>
+        <v>1008</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>1099</v>
+        <v>1085</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>1100</v>
+        <v>1086</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>1101</v>
+        <v>1087</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>1102</v>
+        <v>1088</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>822</v>
@@ -11285,19 +11254,19 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
-        <v>1103</v>
+        <v>1089</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>1104</v>
+        <v>1090</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>1105</v>
+        <v>1091</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>1106</v>
+        <v>1092</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>1098</v>
+        <v>1084</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>830</v>
@@ -11305,19 +11274,19 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
-        <v>1103</v>
+        <v>1089</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>1107</v>
+        <v>1093</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>1108</v>
+        <v>1094</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>1109</v>
+        <v>1095</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>1098</v>
+        <v>1084</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>817</v>
@@ -11408,7 +11377,7 @@
         <v>5</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>1135</v>
+        <v>1121</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="29" x14ac:dyDescent="0.35">
@@ -11434,7 +11403,7 @@
         <v>5</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>1135</v>
+        <v>1121</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
@@ -11460,7 +11429,7 @@
         <v>5</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>1135</v>
+        <v>1121</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="29" x14ac:dyDescent="0.35">
@@ -11486,7 +11455,7 @@
         <v>5</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>1135</v>
+        <v>1121</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="29" x14ac:dyDescent="0.35">
@@ -11512,7 +11481,7 @@
         <v>5</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>1135</v>
+        <v>1121</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="29" x14ac:dyDescent="0.35">
@@ -11538,7 +11507,7 @@
         <v>5</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>1135</v>
+        <v>1121</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="58" x14ac:dyDescent="0.35">
@@ -11564,7 +11533,7 @@
         <v>5</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>1135</v>
+        <v>1121</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="29" x14ac:dyDescent="0.35">
@@ -11590,7 +11559,7 @@
         <v>5</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>1135</v>
+        <v>1121</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.35">
@@ -11616,7 +11585,7 @@
         <v>5</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>1135</v>
+        <v>1121</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="58" x14ac:dyDescent="0.35">
@@ -11636,13 +11605,13 @@
         <v>227</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>1140</v>
+        <v>1126</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>5</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>1135</v>
+        <v>1121</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="58" x14ac:dyDescent="0.35">
@@ -11653,19 +11622,19 @@
         <v>119</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>1136</v>
+        <v>1122</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>1137</v>
+        <v>1123</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>1138</v>
+        <v>1124</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>1139</v>
+        <v>1125</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>1135</v>
+        <v>1121</v>
       </c>
     </row>
   </sheetData>
@@ -11693,7 +11662,7 @@
   <sheetData>
     <row r="1" spans="1:10" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A1" s="8" t="s">
-        <v>1110</v>
+        <v>1096</v>
       </c>
       <c r="B1" s="8"/>
       <c r="C1" s="8"/>
@@ -11707,54 +11676,54 @@
     </row>
     <row r="3" spans="1:10" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
-        <v>1111</v>
+        <v>1097</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>852</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>1005</v>
+        <v>991</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>1093</v>
+        <v>1079</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>1112</v>
+        <v>1098</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>1007</v>
+        <v>993</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>1050</v>
+        <v>1036</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>1113</v>
+        <v>1099</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>1053</v>
+        <v>1039</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>1114</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
-        <v>1115</v>
+        <v>1101</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>826</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>1116</v>
+        <v>1102</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>1098</v>
+        <v>1084</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>935</v>
+        <v>925</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>1117</v>
+        <v>1103</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>159</v>
@@ -11763,30 +11732,30 @@
         <v>854</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>1118</v>
+        <v>1104</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>1119</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
-        <v>1120</v>
+        <v>1106</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>826</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>1121</v>
+        <v>1107</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>1122</v>
+        <v>1108</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>1123</v>
+        <v>1109</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>1123</v>
+        <v>1109</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>159</v>
@@ -11795,30 +11764,30 @@
         <v>854</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>1118</v>
+        <v>1104</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>1124</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
-        <v>1125</v>
+        <v>1111</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>830</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>1126</v>
+        <v>1112</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>1102</v>
+        <v>1088</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>923</v>
+        <v>918</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>923</v>
+        <v>918</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>159</v>
@@ -11827,62 +11796,62 @@
         <v>854</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>1118</v>
+        <v>1104</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>1127</v>
+        <v>1113</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
-        <v>1055</v>
+        <v>1041</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>826</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>1128</v>
+        <v>1114</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>1129</v>
+        <v>1115</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>942</v>
+        <v>930</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>1056</v>
+        <v>1042</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>1031</v>
+        <v>1017</v>
       </c>
       <c r="H7" s="2" t="s">
         <v>850</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>1118</v>
+        <v>1104</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>1119</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
-        <v>1061</v>
+        <v>1047</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>830</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>1130</v>
+        <v>1116</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>1098</v>
+        <v>1084</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>957</v>
+        <v>945</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>957</v>
+        <v>945</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>159</v>
@@ -11891,30 +11860,30 @@
         <v>854</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>1118</v>
+        <v>1104</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>1119</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="9" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A9" s="2" t="s">
-        <v>1131</v>
+        <v>1117</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>826</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>1132</v>
+        <v>1118</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>1098</v>
+        <v>1084</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>1133</v>
+        <v>1119</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>1133</v>
+        <v>1119</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>159</v>
@@ -11923,10 +11892,10 @@
         <v>854</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>1134</v>
+        <v>1120</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>1119</v>
+        <v>1105</v>
       </c>
     </row>
   </sheetData>
@@ -12502,7 +12471,7 @@
         <v>5</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>1135</v>
+        <v>1121</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
@@ -12528,7 +12497,7 @@
         <v>5</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>1135</v>
+        <v>1121</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="29" x14ac:dyDescent="0.35">
@@ -12539,7 +12508,7 @@
         <v>229</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>1144</v>
+        <v>1130</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>317</v>
@@ -12554,7 +12523,7 @@
         <v>5</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>1135</v>
+        <v>1121</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="29" x14ac:dyDescent="0.35">
@@ -12580,7 +12549,7 @@
         <v>5</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>1135</v>
+        <v>1121</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
@@ -12606,7 +12575,7 @@
         <v>5</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>1135</v>
+        <v>1121</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="29" x14ac:dyDescent="0.35">
@@ -12632,7 +12601,7 @@
         <v>5</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>1135</v>
+        <v>1121</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
@@ -12658,7 +12627,7 @@
         <v>5</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>1135</v>
+        <v>1121</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="58" x14ac:dyDescent="0.35">
@@ -12684,7 +12653,7 @@
         <v>5</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>1135</v>
+        <v>1121</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.35">
@@ -12695,22 +12664,22 @@
         <v>119</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>1149</v>
+        <v>1135</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>1150</v>
+        <v>1136</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>299</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>1151</v>
+        <v>1137</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>5</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>1135</v>
+        <v>1121</v>
       </c>
     </row>
   </sheetData>
@@ -12798,7 +12767,7 @@
         <v>5</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>1135</v>
+        <v>1121</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
@@ -12824,7 +12793,7 @@
         <v>5</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>1135</v>
+        <v>1121</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="29" x14ac:dyDescent="0.35">
@@ -12850,7 +12819,7 @@
         <v>5</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>1135</v>
+        <v>1121</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.35">
@@ -12861,13 +12830,13 @@
         <v>229</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>1141</v>
+        <v>1127</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>1142</v>
+        <v>1128</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>1143</v>
+        <v>1129</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>292</v>
@@ -12876,7 +12845,7 @@
         <v>5</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>1135</v>
+        <v>1121</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
@@ -12902,7 +12871,7 @@
         <v>5</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>1135</v>
+        <v>1121</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="29" x14ac:dyDescent="0.35">
@@ -12913,13 +12882,13 @@
         <v>229</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>1145</v>
+        <v>1131</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>1146</v>
+        <v>1132</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>1147</v>
+        <v>1133</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>300</v>
@@ -12928,7 +12897,7 @@
         <v>5</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>1135</v>
+        <v>1121</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="29" x14ac:dyDescent="0.35">
@@ -12954,7 +12923,7 @@
         <v>5</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>1135</v>
+        <v>1121</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="58" x14ac:dyDescent="0.35">
@@ -12965,7 +12934,7 @@
         <v>128</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>1148</v>
+        <v>1134</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>306</v>
@@ -12980,7 +12949,7 @@
         <v>5</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>1135</v>
+        <v>1121</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.35">
@@ -12991,22 +12960,22 @@
         <v>119</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>1152</v>
+        <v>1138</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>1153</v>
+        <v>1139</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>1158</v>
+        <v>1144</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>1154</v>
+        <v>1140</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>5</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>1135</v>
+        <v>1121</v>
       </c>
     </row>
   </sheetData>
@@ -13094,7 +13063,7 @@
         <v>5</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>1135</v>
+        <v>1121</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="87" x14ac:dyDescent="0.35">
@@ -13120,7 +13089,7 @@
         <v>5</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>1135</v>
+        <v>1121</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="29" x14ac:dyDescent="0.35">
@@ -13146,7 +13115,7 @@
         <v>5</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>1135</v>
+        <v>1121</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="29" x14ac:dyDescent="0.35">
@@ -13172,7 +13141,7 @@
         <v>5</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>1135</v>
+        <v>1121</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="29" x14ac:dyDescent="0.35">
@@ -13198,7 +13167,7 @@
         <v>5</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>1135</v>
+        <v>1121</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="29" x14ac:dyDescent="0.35">
@@ -13224,7 +13193,7 @@
         <v>5</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>1135</v>
+        <v>1121</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.35">
@@ -13250,7 +13219,7 @@
         <v>5</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>1135</v>
+        <v>1121</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="29" x14ac:dyDescent="0.35">
@@ -13276,7 +13245,7 @@
         <v>5</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>1135</v>
+        <v>1121</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="29" x14ac:dyDescent="0.35">
@@ -13302,7 +13271,7 @@
         <v>5</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>1135</v>
+        <v>1121</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="58" x14ac:dyDescent="0.35">
@@ -13327,8 +13296,8 @@
       <c r="G13" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="H13" s="2" t="s">
-        <v>5</v>
+      <c r="H13" s="3" t="s">
+        <v>1121</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="29" x14ac:dyDescent="0.35">
@@ -13353,8 +13322,8 @@
       <c r="G14" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="H14" s="2" t="s">
-        <v>5</v>
+      <c r="H14" s="3" t="s">
+        <v>1121</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="29" x14ac:dyDescent="0.35">
@@ -13379,8 +13348,8 @@
       <c r="G15" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="H15" s="2" t="s">
-        <v>5</v>
+      <c r="H15" s="3" t="s">
+        <v>1121</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="72.5" x14ac:dyDescent="0.35">
@@ -13405,8 +13374,8 @@
       <c r="G16" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="H16" s="2" t="s">
-        <v>5</v>
+      <c r="H16" s="3" t="s">
+        <v>1121</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
@@ -13431,8 +13400,8 @@
       <c r="G17" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="H17" s="2" t="s">
-        <v>5</v>
+      <c r="H17" s="3" t="s">
+        <v>1121</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="72.5" x14ac:dyDescent="0.35">
@@ -13457,8 +13426,8 @@
       <c r="G18" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="H18" s="2" t="s">
-        <v>5</v>
+      <c r="H18" s="3" t="s">
+        <v>1121</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="29" x14ac:dyDescent="0.35">
@@ -13509,34 +13478,34 @@
       <c r="G20" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="H20" s="2" t="s">
-        <v>5</v>
+      <c r="H20" s="3" t="s">
+        <v>1121</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A21" s="2">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>119</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>1155</v>
+        <v>1141</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>1156</v>
+        <v>1142</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>387</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>1157</v>
+        <v>1143</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>5</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>1135</v>
+        <v>1121</v>
       </c>
     </row>
   </sheetData>

--- a/docs/Dokumen_Testing_POS.xlsx
+++ b/docs/Dokumen_Testing_POS.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{032A6B41-4582-4003-B580-8B77DCAC5697}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4B60EC1-4659-461B-AB88-52572FAE72D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="867" firstSheet="6" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="867" firstSheet="8" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Daftar Isi" sheetId="1" r:id="rId1"/>
@@ -65,7 +65,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2270" uniqueCount="1145">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2288" uniqueCount="1152">
   <si>
     <t>DOKUMEN TESTING APLIKASI POS</t>
   </si>
@@ -3104,9 +3104,6 @@
     <t>Jl. Industri No.10, Jakarta</t>
   </si>
   <si>
-    <t>081234567890</t>
-  </si>
-  <si>
     <t>sumber@makmur.co.id</t>
   </si>
   <si>
@@ -3642,13 +3639,43 @@
   </si>
   <si>
     <t>unit: ATK</t>
+  </si>
+  <si>
+    <t>Stok Produk Habis</t>
+  </si>
+  <si>
+    <t>1. Login kasir
+2. Menu Kasir
+3. Cari Produk yang stok nya habis</t>
+  </si>
+  <si>
+    <t>Produk yang stok habis muncul di pencarian tapi terdapat peringatan stok habis</t>
+  </si>
+  <si>
+    <t>Stok Produk Dibawah minimum stok</t>
+  </si>
+  <si>
+    <t>1. Login kasir
+2. Menu Kasir
+3. Cari Produk yang stok nya dibawah minimum</t>
+  </si>
+  <si>
+    <t>Produk yang stok dibawah minimum muncul di pencarian tapi terdapat peringatan stok minipis</t>
+  </si>
+  <si>
+    <t>Edit data produk</t>
+  </si>
+  <si>
+    <t>1. Pilih produk
+2. Ubah nama produk
+3. Simpan</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3678,6 +3705,14 @@
       <sz val="14"/>
       <color rgb="FF2F5496"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="4">
@@ -3749,10 +3784,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -3772,8 +3808,18 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -4678,8 +4724,8 @@
       <c r="G4" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="2" t="s">
-        <v>5</v>
+      <c r="H4" s="3" t="s">
+        <v>1120</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="72.5" x14ac:dyDescent="0.35">
@@ -4704,8 +4750,8 @@
       <c r="G5" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="H5" s="2" t="s">
-        <v>5</v>
+      <c r="H5" s="3" t="s">
+        <v>1120</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="29" x14ac:dyDescent="0.35">
@@ -4756,8 +4802,8 @@
       <c r="G7" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="H7" s="2" t="s">
-        <v>5</v>
+      <c r="H7" s="3" t="s">
+        <v>1120</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="29" x14ac:dyDescent="0.35">
@@ -7119,7 +7165,7 @@
         <v>5</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>1121</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="29" x14ac:dyDescent="0.35">
@@ -7145,7 +7191,7 @@
         <v>5</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>1121</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="29" x14ac:dyDescent="0.35">
@@ -7171,7 +7217,7 @@
         <v>5</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>1121</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="29" x14ac:dyDescent="0.35">
@@ -7197,7 +7243,7 @@
         <v>5</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>1121</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="29" x14ac:dyDescent="0.35">
@@ -7223,7 +7269,7 @@
         <v>5</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>1121</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="29" x14ac:dyDescent="0.35">
@@ -7249,7 +7295,7 @@
         <v>5</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>1121</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="29" x14ac:dyDescent="0.35">
@@ -7275,7 +7321,7 @@
         <v>5</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>1121</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
@@ -7301,7 +7347,7 @@
         <v>5</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>1121</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
@@ -7353,7 +7399,7 @@
         <v>5</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>1121</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
@@ -10463,14 +10509,14 @@
       <c r="C4" s="2" t="s">
         <v>965</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="D4" s="2">
+        <v>81234567890</v>
+      </c>
+      <c r="E4" s="11" t="s">
         <v>966</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="F4" s="2" t="s">
         <v>967</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>968</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>850</v>
@@ -10478,22 +10524,22 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
+        <v>968</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>969</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="C5" s="2" t="s">
         <v>970</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="D5" s="2" t="s">
         <v>971</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="E5" s="2" t="s">
         <v>972</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="F5" s="2" t="s">
         <v>973</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>974</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>850</v>
@@ -10501,22 +10547,22 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
+        <v>974</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>975</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="C6" s="2" t="s">
         <v>976</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="D6" s="2" t="s">
         <v>977</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="E6" s="2" t="s">
         <v>978</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="F6" s="2" t="s">
         <v>979</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>980</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>850</v>
@@ -10524,22 +10570,22 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
+        <v>980</v>
+      </c>
+      <c r="B7" s="2" t="s">
         <v>981</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="C7" s="2" t="s">
         <v>982</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="D7" s="2" t="s">
         <v>983</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="E7" s="2" t="s">
         <v>984</v>
       </c>
-      <c r="E7" s="2" t="s">
+      <c r="F7" s="2" t="s">
         <v>985</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>986</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>854</v>
@@ -10549,6 +10595,9 @@
   <mergeCells count="1">
     <mergeCell ref="A1:G1"/>
   </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="E4" r:id="rId1" xr:uid="{FB2289E2-792D-435C-810A-6E2EA67335A0}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
@@ -10568,7 +10617,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A1" s="8" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="B1" s="8"/>
       <c r="C1" s="8"/>
@@ -10580,103 +10629,103 @@
     </row>
     <row r="3" spans="1:8" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
+        <v>987</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>988</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="C3" s="1" t="s">
         <v>989</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="D3" s="1" t="s">
         <v>990</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="E3" s="1" t="s">
         <v>991</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="F3" s="1" t="s">
         <v>992</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="G3" s="1" t="s">
         <v>993</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="H3" s="1" t="s">
         <v>994</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>995</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
-        <v>996</v>
+        <v>995</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>964</v>
       </c>
       <c r="C4" s="2" t="s">
+        <v>996</v>
+      </c>
+      <c r="D4" s="2" t="s">
         <v>997</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>998</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>925</v>
       </c>
       <c r="F4" s="2" t="s">
+        <v>998</v>
+      </c>
+      <c r="G4" s="2" t="s">
         <v>999</v>
       </c>
-      <c r="G4" s="2" t="s">
-        <v>1000</v>
-      </c>
       <c r="H4" s="2" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
+        <v>1000</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>969</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>1001</v>
       </c>
-      <c r="B5" s="2" t="s">
-        <v>970</v>
-      </c>
-      <c r="C5" s="2" t="s">
+      <c r="D5" s="2" t="s">
         <v>1002</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>1003</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>930</v>
       </c>
       <c r="F5" s="2" t="s">
+        <v>1003</v>
+      </c>
+      <c r="G5" s="2" t="s">
         <v>1004</v>
       </c>
-      <c r="G5" s="2" t="s">
+      <c r="H5" s="2" t="s">
         <v>1005</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>1006</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
+        <v>1006</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>975</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>1007</v>
       </c>
-      <c r="B6" s="2" t="s">
-        <v>976</v>
-      </c>
-      <c r="C6" s="2" t="s">
+      <c r="D6" s="2" t="s">
         <v>1008</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="E6" s="2" t="s">
         <v>1009</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="F6" s="2" t="s">
         <v>1010</v>
       </c>
-      <c r="F6" s="2" t="s">
+      <c r="G6" s="2" t="s">
         <v>1011</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>1012</v>
       </c>
       <c r="H6" s="2" t="s">
         <v>930</v>
@@ -10706,7 +10755,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A1" s="8" t="s">
-        <v>1013</v>
+        <v>1012</v>
       </c>
       <c r="B1" s="8"/>
       <c r="C1" s="8"/>
@@ -10716,7 +10765,7 @@
     </row>
     <row r="3" spans="1:6" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>860</v>
@@ -10728,7 +10777,7 @@
         <v>959</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>848</v>
@@ -10736,19 +10785,19 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
+        <v>1015</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>1016</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="C4" s="2" t="s">
         <v>1017</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="D4" s="2" t="s">
         <v>1018</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="E4" s="2" t="s">
         <v>1019</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>1020</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>850</v>
@@ -10756,19 +10805,19 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
+        <v>1020</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>1021</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="C5" s="2" t="s">
         <v>1022</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="D5" s="2" t="s">
         <v>1023</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="E5" s="2" t="s">
         <v>1024</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>1025</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>850</v>
@@ -10776,19 +10825,19 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
+        <v>1025</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>1026</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="C6" s="2" t="s">
         <v>1027</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="D6" s="2" t="s">
         <v>1028</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="E6" s="2" t="s">
         <v>1029</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>1030</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>850</v>
@@ -10796,16 +10845,16 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
+        <v>1030</v>
+      </c>
+      <c r="B7" s="2" t="s">
         <v>1031</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="C7" s="2" t="s">
         <v>1032</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="D7" s="2" t="s">
         <v>1033</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>1034</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>930</v>
@@ -10838,7 +10887,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A1" s="8" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="B1" s="8"/>
       <c r="C1" s="8"/>
@@ -10849,94 +10898,94 @@
     </row>
     <row r="3" spans="1:7" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
+        <v>1035</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>1036</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="C3" s="1" t="s">
+        <v>992</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>994</v>
+      </c>
+      <c r="E3" s="1" t="s">
         <v>1037</v>
       </c>
-      <c r="C3" s="1" t="s">
-        <v>993</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>995</v>
-      </c>
-      <c r="E3" s="1" t="s">
+      <c r="F3" s="1" t="s">
         <v>1038</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="G3" s="1" t="s">
         <v>1039</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>1040</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
       <c r="B4" s="2" t="s">
+        <v>1040</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>1041</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>1042</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>930</v>
       </c>
       <c r="E4" s="2" t="s">
+        <v>1041</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>1011</v>
+      </c>
+      <c r="G4" s="2" t="s">
         <v>1042</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>1012</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>1043</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
-        <v>1022</v>
+        <v>1021</v>
       </c>
       <c r="B5" s="2" t="s">
+        <v>1043</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>1019</v>
+      </c>
+      <c r="D5" s="2" t="s">
         <v>1044</v>
       </c>
-      <c r="C5" s="2" t="s">
-        <v>1020</v>
-      </c>
-      <c r="D5" s="2" t="s">
+      <c r="E5" s="2" t="s">
+        <v>1044</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>1004</v>
+      </c>
+      <c r="G5" s="2" t="s">
         <v>1045</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>1045</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>1005</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>1046</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
       <c r="B6" s="2" t="s">
+        <v>1046</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>1047</v>
       </c>
-      <c r="C6" s="2" t="s">
-        <v>1048</v>
-      </c>
       <c r="D6" s="2" t="s">
-        <v>1048</v>
+        <v>1047</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>930</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>1000</v>
+        <v>999</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
     </row>
   </sheetData>
@@ -10960,7 +11009,7 @@
   <sheetData>
     <row r="1" spans="1:4" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A1" s="8" t="s">
-        <v>1050</v>
+        <v>1049</v>
       </c>
       <c r="B1" s="8"/>
       <c r="C1" s="8"/>
@@ -10971,10 +11020,10 @@
         <v>860</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>1050</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>1051</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>1052</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>848</v>
@@ -10982,13 +11031,13 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
+        <v>1052</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>1053</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="C4" s="2" t="s">
         <v>1054</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>1055</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>850</v>
@@ -10996,13 +11045,13 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
+        <v>1055</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>1054</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>1056</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>1055</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>1057</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>850</v>
@@ -11010,13 +11059,13 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
-        <v>1058</v>
+        <v>1057</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>1057</v>
+        <v>1056</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>850</v>
@@ -11046,7 +11095,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A1" s="8" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="B1" s="8"/>
       <c r="C1" s="8"/>
@@ -11061,25 +11110,25 @@
         <v>852</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>1059</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>1060</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="D3" s="1" t="s">
         <v>1061</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="E3" s="1" t="s">
         <v>1062</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="F3" s="1" t="s">
         <v>1063</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="G3" s="1" t="s">
+        <v>1038</v>
+      </c>
+      <c r="H3" s="1" t="s">
         <v>1064</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>1039</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>1065</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.35">
@@ -11087,25 +11136,25 @@
         <v>826</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>1053</v>
+        <v>1052</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>930</v>
       </c>
       <c r="G4" s="2" t="s">
+        <v>1066</v>
+      </c>
+      <c r="H4" s="2" t="s">
         <v>1067</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>1068</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.35">
@@ -11113,25 +11162,25 @@
         <v>830</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>1056</v>
+        <v>1055</v>
       </c>
       <c r="C5" s="2" t="s">
+        <v>1068</v>
+      </c>
+      <c r="D5" s="2" t="s">
         <v>1069</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="E5" s="2" t="s">
+        <v>1024</v>
+      </c>
+      <c r="F5" s="2" t="s">
         <v>1070</v>
       </c>
-      <c r="E5" s="2" t="s">
-        <v>1025</v>
-      </c>
-      <c r="F5" s="2" t="s">
+      <c r="G5" s="2" t="s">
+        <v>1066</v>
+      </c>
+      <c r="H5" s="2" t="s">
         <v>1071</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>1067</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>1072</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.35">
@@ -11139,25 +11188,25 @@
         <v>826</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>1058</v>
+        <v>1057</v>
       </c>
       <c r="C6" s="2" t="s">
+        <v>1072</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G6" s="2" t="s">
         <v>1073</v>
       </c>
-      <c r="D6" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="G6" s="2" t="s">
+      <c r="H6" s="2" t="s">
         <v>1074</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>1075</v>
       </c>
     </row>
   </sheetData>
@@ -11184,7 +11233,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A1" s="8" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="B1" s="8"/>
       <c r="C1" s="8"/>
@@ -11194,7 +11243,7 @@
     </row>
     <row r="3" spans="1:6" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>894</v>
@@ -11203,30 +11252,30 @@
         <v>862</v>
       </c>
       <c r="D3" s="1" t="s">
+        <v>1077</v>
+      </c>
+      <c r="E3" s="1" t="s">
         <v>1078</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="F3" s="1" t="s">
         <v>1079</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>1080</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
-        <v>1008</v>
+        <v>1007</v>
       </c>
       <c r="B4" s="2" t="s">
+        <v>1080</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>1081</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="D4" s="2" t="s">
         <v>1082</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="E4" s="2" t="s">
         <v>1083</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>1084</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>826</v>
@@ -11234,19 +11283,19 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
-        <v>1008</v>
+        <v>1007</v>
       </c>
       <c r="B5" s="2" t="s">
+        <v>1084</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>1085</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="D5" s="2" t="s">
         <v>1086</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="E5" s="2" t="s">
         <v>1087</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>1088</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>822</v>
@@ -11254,19 +11303,19 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
+        <v>1088</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>1089</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="C6" s="2" t="s">
         <v>1090</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="D6" s="2" t="s">
         <v>1091</v>
       </c>
-      <c r="D6" s="2" t="s">
-        <v>1092</v>
-      </c>
       <c r="E6" s="2" t="s">
-        <v>1084</v>
+        <v>1083</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>830</v>
@@ -11274,19 +11323,19 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
-        <v>1089</v>
+        <v>1088</v>
       </c>
       <c r="B7" s="2" t="s">
+        <v>1092</v>
+      </c>
+      <c r="C7" s="2" t="s">
         <v>1093</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="D7" s="2" t="s">
         <v>1094</v>
       </c>
-      <c r="D7" s="2" t="s">
-        <v>1095</v>
-      </c>
       <c r="E7" s="2" t="s">
-        <v>1084</v>
+        <v>1083</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>817</v>
@@ -11377,7 +11426,7 @@
         <v>5</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>1121</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="29" x14ac:dyDescent="0.35">
@@ -11403,7 +11452,7 @@
         <v>5</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>1121</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
@@ -11429,7 +11478,7 @@
         <v>5</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>1121</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="29" x14ac:dyDescent="0.35">
@@ -11455,7 +11504,7 @@
         <v>5</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>1121</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="29" x14ac:dyDescent="0.35">
@@ -11481,7 +11530,7 @@
         <v>5</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>1121</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="29" x14ac:dyDescent="0.35">
@@ -11507,7 +11556,7 @@
         <v>5</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>1121</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="58" x14ac:dyDescent="0.35">
@@ -11533,7 +11582,7 @@
         <v>5</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>1121</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="29" x14ac:dyDescent="0.35">
@@ -11559,7 +11608,7 @@
         <v>5</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>1121</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.35">
@@ -11585,7 +11634,7 @@
         <v>5</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>1121</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="58" x14ac:dyDescent="0.35">
@@ -11605,13 +11654,13 @@
         <v>227</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>1126</v>
+        <v>1125</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>5</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>1121</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="58" x14ac:dyDescent="0.35">
@@ -11622,19 +11671,19 @@
         <v>119</v>
       </c>
       <c r="C14" s="2" t="s">
+        <v>1121</v>
+      </c>
+      <c r="D14" s="2" t="s">
         <v>1122</v>
       </c>
-      <c r="D14" s="2" t="s">
+      <c r="E14" s="2" t="s">
         <v>1123</v>
       </c>
-      <c r="E14" s="2" t="s">
+      <c r="F14" s="2" t="s">
         <v>1124</v>
       </c>
-      <c r="F14" s="2" t="s">
-        <v>1125</v>
-      </c>
       <c r="H14" s="3" t="s">
-        <v>1121</v>
+        <v>1120</v>
       </c>
     </row>
   </sheetData>
@@ -11662,7 +11711,7 @@
   <sheetData>
     <row r="1" spans="1:10" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A1" s="8" t="s">
-        <v>1096</v>
+        <v>1095</v>
       </c>
       <c r="B1" s="8"/>
       <c r="C1" s="8"/>
@@ -11676,54 +11725,54 @@
     </row>
     <row r="3" spans="1:10" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
-        <v>1097</v>
+        <v>1096</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>852</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="E3" s="1" t="s">
+        <v>1097</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>992</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>1035</v>
+      </c>
+      <c r="H3" s="1" t="s">
         <v>1098</v>
       </c>
-      <c r="F3" s="1" t="s">
-        <v>993</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>1036</v>
-      </c>
-      <c r="H3" s="1" t="s">
+      <c r="I3" s="1" t="s">
+        <v>1038</v>
+      </c>
+      <c r="J3" s="1" t="s">
         <v>1099</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>1039</v>
-      </c>
-      <c r="J3" s="1" t="s">
-        <v>1100</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
-        <v>1101</v>
+        <v>1100</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>826</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>1102</v>
+        <v>1101</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>1084</v>
+        <v>1083</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>925</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>1103</v>
+        <v>1102</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>159</v>
@@ -11732,30 +11781,30 @@
         <v>854</v>
       </c>
       <c r="I4" s="2" t="s">
+        <v>1103</v>
+      </c>
+      <c r="J4" s="2" t="s">
         <v>1104</v>
-      </c>
-      <c r="J4" s="2" t="s">
-        <v>1105</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
-        <v>1106</v>
+        <v>1105</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>826</v>
       </c>
       <c r="C5" s="2" t="s">
+        <v>1106</v>
+      </c>
+      <c r="D5" s="2" t="s">
         <v>1107</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="E5" s="2" t="s">
         <v>1108</v>
       </c>
-      <c r="E5" s="2" t="s">
-        <v>1109</v>
-      </c>
       <c r="F5" s="2" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>159</v>
@@ -11764,24 +11813,24 @@
         <v>854</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>1104</v>
+        <v>1103</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>1110</v>
+        <v>1109</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>830</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>1112</v>
+        <v>1111</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>918</v>
@@ -11796,56 +11845,56 @@
         <v>854</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>1104</v>
+        <v>1103</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>1113</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>826</v>
       </c>
       <c r="C7" s="2" t="s">
+        <v>1113</v>
+      </c>
+      <c r="D7" s="2" t="s">
         <v>1114</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>1115</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>930</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
       <c r="H7" s="2" t="s">
         <v>850</v>
       </c>
       <c r="I7" s="2" t="s">
+        <v>1103</v>
+      </c>
+      <c r="J7" s="2" t="s">
         <v>1104</v>
-      </c>
-      <c r="J7" s="2" t="s">
-        <v>1105</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>830</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>1084</v>
+        <v>1083</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>945</v>
@@ -11860,30 +11909,30 @@
         <v>854</v>
       </c>
       <c r="I8" s="2" t="s">
+        <v>1103</v>
+      </c>
+      <c r="J8" s="2" t="s">
         <v>1104</v>
-      </c>
-      <c r="J8" s="2" t="s">
-        <v>1105</v>
       </c>
     </row>
     <row r="9" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A9" s="2" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>826</v>
       </c>
       <c r="C9" s="2" t="s">
+        <v>1117</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="E9" s="2" t="s">
         <v>1118</v>
       </c>
-      <c r="D9" s="2" t="s">
-        <v>1084</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>1119</v>
-      </c>
       <c r="F9" s="2" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>159</v>
@@ -11892,10 +11941,10 @@
         <v>854</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>1105</v>
+        <v>1104</v>
       </c>
     </row>
   </sheetData>
@@ -12471,7 +12520,7 @@
         <v>5</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>1121</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
@@ -12497,7 +12546,7 @@
         <v>5</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>1121</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="29" x14ac:dyDescent="0.35">
@@ -12508,7 +12557,7 @@
         <v>229</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>317</v>
@@ -12523,7 +12572,7 @@
         <v>5</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>1121</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="29" x14ac:dyDescent="0.35">
@@ -12549,7 +12598,7 @@
         <v>5</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>1121</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
@@ -12575,7 +12624,7 @@
         <v>5</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>1121</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="29" x14ac:dyDescent="0.35">
@@ -12601,7 +12650,7 @@
         <v>5</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>1121</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
@@ -12627,7 +12676,7 @@
         <v>5</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>1121</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="58" x14ac:dyDescent="0.35">
@@ -12653,7 +12702,7 @@
         <v>5</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>1121</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.35">
@@ -12664,22 +12713,22 @@
         <v>119</v>
       </c>
       <c r="C12" s="2" t="s">
+        <v>1134</v>
+      </c>
+      <c r="D12" s="2" t="s">
         <v>1135</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>1136</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>299</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>5</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>1121</v>
+        <v>1120</v>
       </c>
     </row>
   </sheetData>
@@ -12767,7 +12816,7 @@
         <v>5</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>1121</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
@@ -12793,7 +12842,7 @@
         <v>5</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>1121</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="29" x14ac:dyDescent="0.35">
@@ -12819,7 +12868,7 @@
         <v>5</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>1121</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.35">
@@ -12830,13 +12879,13 @@
         <v>229</v>
       </c>
       <c r="C7" s="2" t="s">
+        <v>1126</v>
+      </c>
+      <c r="D7" s="2" t="s">
         <v>1127</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="E7" s="2" t="s">
         <v>1128</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>1129</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>292</v>
@@ -12845,7 +12894,7 @@
         <v>5</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>1121</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
@@ -12871,7 +12920,7 @@
         <v>5</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>1121</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="29" x14ac:dyDescent="0.35">
@@ -12882,13 +12931,13 @@
         <v>229</v>
       </c>
       <c r="C9" s="2" t="s">
+        <v>1130</v>
+      </c>
+      <c r="D9" s="2" t="s">
         <v>1131</v>
       </c>
-      <c r="D9" s="2" t="s">
+      <c r="E9" s="2" t="s">
         <v>1132</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>1133</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>300</v>
@@ -12897,7 +12946,7 @@
         <v>5</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>1121</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="29" x14ac:dyDescent="0.35">
@@ -12923,7 +12972,7 @@
         <v>5</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>1121</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="58" x14ac:dyDescent="0.35">
@@ -12934,7 +12983,7 @@
         <v>128</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>1134</v>
+        <v>1133</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>306</v>
@@ -12949,7 +12998,7 @@
         <v>5</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>1121</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.35">
@@ -12960,22 +13009,22 @@
         <v>119</v>
       </c>
       <c r="C12" s="2" t="s">
+        <v>1137</v>
+      </c>
+      <c r="D12" s="2" t="s">
         <v>1138</v>
       </c>
-      <c r="D12" s="2" t="s">
+      <c r="E12" s="2" t="s">
+        <v>1143</v>
+      </c>
+      <c r="F12" s="2" t="s">
         <v>1139</v>
       </c>
-      <c r="E12" s="2" t="s">
-        <v>1144</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>1140</v>
-      </c>
       <c r="G12" s="2" t="s">
         <v>5</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>1121</v>
+        <v>1120</v>
       </c>
     </row>
   </sheetData>
@@ -12989,7 +13038,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
-  <dimension ref="A1:H21"/>
+  <dimension ref="A1:H24"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
@@ -13063,7 +13112,7 @@
         <v>5</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>1121</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="87" x14ac:dyDescent="0.35">
@@ -13089,7 +13138,7 @@
         <v>5</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>1121</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="29" x14ac:dyDescent="0.35">
@@ -13115,7 +13164,7 @@
         <v>5</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>1121</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="29" x14ac:dyDescent="0.35">
@@ -13141,7 +13190,7 @@
         <v>5</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>1121</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="29" x14ac:dyDescent="0.35">
@@ -13167,7 +13216,7 @@
         <v>5</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>1121</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="29" x14ac:dyDescent="0.35">
@@ -13193,7 +13242,7 @@
         <v>5</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>1121</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.35">
@@ -13219,7 +13268,7 @@
         <v>5</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>1121</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="29" x14ac:dyDescent="0.35">
@@ -13245,7 +13294,7 @@
         <v>5</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>1121</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="29" x14ac:dyDescent="0.35">
@@ -13271,7 +13320,7 @@
         <v>5</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>1121</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="58" x14ac:dyDescent="0.35">
@@ -13297,7 +13346,7 @@
         <v>5</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>1121</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="29" x14ac:dyDescent="0.35">
@@ -13323,10 +13372,10 @@
         <v>5</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>1121</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" ht="29" x14ac:dyDescent="0.35">
+        <v>1120</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A15" s="2">
         <v>12</v>
       </c>
@@ -13334,25 +13383,25 @@
         <v>229</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>369</v>
+        <v>1150</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>370</v>
+        <v>1151</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>371</v>
+        <v>387</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>372</v>
+        <v>296</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>5</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>1121</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" ht="72.5" x14ac:dyDescent="0.35">
+        <v>1120</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A16" s="2">
         <v>13</v>
       </c>
@@ -13360,25 +13409,25 @@
         <v>229</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>373</v>
+        <v>369</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>376</v>
+        <v>372</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>5</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>1121</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
+        <v>1120</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A17" s="2">
         <v>14</v>
       </c>
@@ -13386,25 +13435,25 @@
         <v>229</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>378</v>
+        <v>374</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>379</v>
+        <v>375</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>380</v>
+        <v>376</v>
       </c>
       <c r="G17" s="2" t="s">
         <v>5</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>1121</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" ht="72.5" x14ac:dyDescent="0.35">
+        <v>1120</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A18" s="2">
         <v>15</v>
       </c>
@@ -13412,25 +13461,25 @@
         <v>229</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="G18" s="2" t="s">
         <v>5</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>1121</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" ht="29" x14ac:dyDescent="0.35">
+        <v>1120</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A19" s="2">
         <v>16</v>
       </c>
@@ -13438,22 +13487,22 @@
         <v>229</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>385</v>
+        <v>381</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>386</v>
+        <v>382</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>387</v>
+        <v>383</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>388</v>
+        <v>384</v>
       </c>
       <c r="G19" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="H19" s="2" t="s">
-        <v>5</v>
+      <c r="H19" s="3" t="s">
+        <v>1120</v>
       </c>
     </row>
     <row r="20" spans="1:8" ht="29" x14ac:dyDescent="0.35">
@@ -13461,51 +13510,123 @@
         <v>17</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>128</v>
+        <v>229</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>389</v>
+        <v>385</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>390</v>
+        <v>386</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>159</v>
+        <v>387</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>5</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>1121</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.35">
+        <v>1120</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A21" s="2">
         <v>18</v>
       </c>
       <c r="B21" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>389</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>390</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="H21" s="3" t="s">
+        <v>1120</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A22" s="2">
+        <v>19</v>
+      </c>
+      <c r="B22" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="C21" s="2" t="s">
+      <c r="C22" s="2" t="s">
+        <v>1140</v>
+      </c>
+      <c r="D22" s="2" t="s">
         <v>1141</v>
       </c>
-      <c r="D21" s="2" t="s">
+      <c r="E22" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="F22" s="2" t="s">
         <v>1142</v>
       </c>
-      <c r="E21" s="2" t="s">
+      <c r="G22" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>1120</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A23" s="2">
+        <v>20</v>
+      </c>
+      <c r="B23" s="9" t="s">
+        <v>128</v>
+      </c>
+      <c r="C23" s="9" t="s">
+        <v>1144</v>
+      </c>
+      <c r="D23" s="10" t="s">
+        <v>1145</v>
+      </c>
+      <c r="E23" s="2" t="s">
         <v>387</v>
       </c>
-      <c r="F21" s="2" t="s">
-        <v>1143</v>
-      </c>
-      <c r="G21" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="H21" s="3" t="s">
-        <v>1121</v>
+      <c r="F23" s="9" t="s">
+        <v>1146</v>
+      </c>
+      <c r="H23" s="3" t="s">
+        <v>1120</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A24" s="2">
+        <v>21</v>
+      </c>
+      <c r="B24" s="9" t="s">
+        <v>128</v>
+      </c>
+      <c r="C24" s="9" t="s">
+        <v>1147</v>
+      </c>
+      <c r="D24" s="10" t="s">
+        <v>1148</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="F24" s="9" t="s">
+        <v>1149</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>1120</v>
       </c>
     </row>
   </sheetData>

--- a/docs/Dokumen_Testing_POS.xlsx
+++ b/docs/Dokumen_Testing_POS.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4B60EC1-4659-461B-AB88-52572FAE72D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EFE79627-EFB9-4C75-A84D-378629CA5AEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="867" firstSheet="8" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="867" firstSheet="6" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Daftar Isi" sheetId="1" r:id="rId1"/>
@@ -65,7 +65,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2288" uniqueCount="1152">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2289" uniqueCount="1152">
   <si>
     <t>DOKUMEN TESTING APLIKASI POS</t>
   </si>
@@ -3119,9 +3119,6 @@
     <t>Jl. Raya Bogor No.25</t>
   </si>
   <si>
-    <t>082198765432</t>
-  </si>
-  <si>
     <t>berkat@jaya.co.id</t>
   </si>
   <si>
@@ -3669,6 +3666,9 @@
     <t>1. Pilih produk
 2. Ubah nama produk
 3. Simpan</t>
+  </si>
+  <si>
+    <t>Buat retur baru tapi faktur pembelian belum ada</t>
   </si>
 </sst>
 </file>
@@ -4725,7 +4725,7 @@
         <v>5</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="72.5" x14ac:dyDescent="0.35">
@@ -4751,7 +4751,7 @@
         <v>5</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="29" x14ac:dyDescent="0.35">
@@ -4803,7 +4803,7 @@
         <v>5</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="29" x14ac:dyDescent="0.35">
@@ -5165,7 +5165,7 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
-  <dimension ref="A1:H8"/>
+  <dimension ref="A1:H9"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
@@ -5344,6 +5344,17 @@
       </c>
       <c r="H8" s="2" t="s">
         <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="29" x14ac:dyDescent="0.35">
+      <c r="A9" s="9">
+        <v>6</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>1151</v>
       </c>
     </row>
   </sheetData>
@@ -7165,7 +7176,7 @@
         <v>5</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="29" x14ac:dyDescent="0.35">
@@ -7191,7 +7202,7 @@
         <v>5</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="29" x14ac:dyDescent="0.35">
@@ -7217,7 +7228,7 @@
         <v>5</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="29" x14ac:dyDescent="0.35">
@@ -7243,7 +7254,7 @@
         <v>5</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="29" x14ac:dyDescent="0.35">
@@ -7269,7 +7280,7 @@
         <v>5</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="29" x14ac:dyDescent="0.35">
@@ -7295,7 +7306,7 @@
         <v>5</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="29" x14ac:dyDescent="0.35">
@@ -7321,7 +7332,7 @@
         <v>5</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
@@ -7347,7 +7358,7 @@
         <v>5</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
@@ -7399,7 +7410,7 @@
         <v>5</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
@@ -10532,14 +10543,14 @@
       <c r="C5" s="2" t="s">
         <v>970</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="D5" s="2">
+        <v>82198765432</v>
+      </c>
+      <c r="E5" s="11" t="s">
         <v>971</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="F5" s="2" t="s">
         <v>972</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>973</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>850</v>
@@ -10547,22 +10558,22 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
+        <v>973</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>974</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="C6" s="2" t="s">
         <v>975</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="D6" s="2" t="s">
         <v>976</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="E6" s="2" t="s">
         <v>977</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="F6" s="2" t="s">
         <v>978</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>979</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>850</v>
@@ -10570,22 +10581,22 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
+        <v>979</v>
+      </c>
+      <c r="B7" s="2" t="s">
         <v>980</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="C7" s="2" t="s">
         <v>981</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="D7" s="2" t="s">
         <v>982</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="E7" s="2" t="s">
         <v>983</v>
       </c>
-      <c r="E7" s="2" t="s">
+      <c r="F7" s="2" t="s">
         <v>984</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>985</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>854</v>
@@ -10597,6 +10608,7 @@
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="E4" r:id="rId1" xr:uid="{FB2289E2-792D-435C-810A-6E2EA67335A0}"/>
+    <hyperlink ref="E5" r:id="rId2" xr:uid="{1B3B372F-6FE5-4902-9C2B-F70D87A1F496}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
@@ -10617,7 +10629,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A1" s="8" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
       <c r="B1" s="8"/>
       <c r="C1" s="8"/>
@@ -10629,103 +10641,103 @@
     </row>
     <row r="3" spans="1:8" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
+        <v>986</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>987</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="C3" s="1" t="s">
         <v>988</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="D3" s="1" t="s">
         <v>989</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="E3" s="1" t="s">
         <v>990</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="F3" s="1" t="s">
         <v>991</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="G3" s="1" t="s">
         <v>992</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="H3" s="1" t="s">
         <v>993</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>994</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>964</v>
       </c>
       <c r="C4" s="2" t="s">
+        <v>995</v>
+      </c>
+      <c r="D4" s="2" t="s">
         <v>996</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>997</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>925</v>
       </c>
       <c r="F4" s="2" t="s">
+        <v>997</v>
+      </c>
+      <c r="G4" s="2" t="s">
         <v>998</v>
       </c>
-      <c r="G4" s="2" t="s">
-        <v>999</v>
-      </c>
       <c r="H4" s="2" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
-        <v>1000</v>
+        <v>999</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>969</v>
       </c>
       <c r="C5" s="2" t="s">
+        <v>1000</v>
+      </c>
+      <c r="D5" s="2" t="s">
         <v>1001</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>1002</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>930</v>
       </c>
       <c r="F5" s="2" t="s">
+        <v>1002</v>
+      </c>
+      <c r="G5" s="2" t="s">
         <v>1003</v>
       </c>
-      <c r="G5" s="2" t="s">
+      <c r="H5" s="2" t="s">
         <v>1004</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>1005</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
+        <v>1005</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>974</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>1006</v>
       </c>
-      <c r="B6" s="2" t="s">
-        <v>975</v>
-      </c>
-      <c r="C6" s="2" t="s">
+      <c r="D6" s="2" t="s">
         <v>1007</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="E6" s="2" t="s">
         <v>1008</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="F6" s="2" t="s">
         <v>1009</v>
       </c>
-      <c r="F6" s="2" t="s">
+      <c r="G6" s="2" t="s">
         <v>1010</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>1011</v>
       </c>
       <c r="H6" s="2" t="s">
         <v>930</v>
@@ -10755,7 +10767,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A1" s="8" t="s">
-        <v>1012</v>
+        <v>1011</v>
       </c>
       <c r="B1" s="8"/>
       <c r="C1" s="8"/>
@@ -10765,7 +10777,7 @@
     </row>
     <row r="3" spans="1:6" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
-        <v>1013</v>
+        <v>1012</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>860</v>
@@ -10777,7 +10789,7 @@
         <v>959</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>848</v>
@@ -10785,19 +10797,19 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
+        <v>1014</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>1015</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="C4" s="2" t="s">
         <v>1016</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="D4" s="2" t="s">
         <v>1017</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="E4" s="2" t="s">
         <v>1018</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>1019</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>850</v>
@@ -10805,19 +10817,19 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
+        <v>1019</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>1020</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="C5" s="2" t="s">
         <v>1021</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="D5" s="2" t="s">
         <v>1022</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="E5" s="2" t="s">
         <v>1023</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>1024</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>850</v>
@@ -10825,19 +10837,19 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
+        <v>1024</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>1025</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="C6" s="2" t="s">
         <v>1026</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="D6" s="2" t="s">
         <v>1027</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="E6" s="2" t="s">
         <v>1028</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>1029</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>850</v>
@@ -10845,16 +10857,16 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
+        <v>1029</v>
+      </c>
+      <c r="B7" s="2" t="s">
         <v>1030</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="C7" s="2" t="s">
         <v>1031</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="D7" s="2" t="s">
         <v>1032</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>1033</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>930</v>
@@ -10887,7 +10899,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A1" s="8" t="s">
-        <v>1034</v>
+        <v>1033</v>
       </c>
       <c r="B1" s="8"/>
       <c r="C1" s="8"/>
@@ -10898,94 +10910,94 @@
     </row>
     <row r="3" spans="1:7" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
+        <v>1034</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>1035</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="C3" s="1" t="s">
+        <v>991</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>993</v>
+      </c>
+      <c r="E3" s="1" t="s">
         <v>1036</v>
       </c>
-      <c r="C3" s="1" t="s">
-        <v>992</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>994</v>
-      </c>
-      <c r="E3" s="1" t="s">
+      <c r="F3" s="1" t="s">
         <v>1037</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="G3" s="1" t="s">
         <v>1038</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>1039</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
-        <v>1016</v>
+        <v>1015</v>
       </c>
       <c r="B4" s="2" t="s">
+        <v>1039</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>1040</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>1041</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>930</v>
       </c>
       <c r="E4" s="2" t="s">
+        <v>1040</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>1010</v>
+      </c>
+      <c r="G4" s="2" t="s">
         <v>1041</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>1011</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>1042</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
-        <v>1021</v>
+        <v>1020</v>
       </c>
       <c r="B5" s="2" t="s">
+        <v>1042</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>1018</v>
+      </c>
+      <c r="D5" s="2" t="s">
         <v>1043</v>
       </c>
-      <c r="C5" s="2" t="s">
-        <v>1019</v>
-      </c>
-      <c r="D5" s="2" t="s">
+      <c r="E5" s="2" t="s">
+        <v>1043</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>1003</v>
+      </c>
+      <c r="G5" s="2" t="s">
         <v>1044</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>1044</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>1004</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>1045</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
-        <v>1026</v>
+        <v>1025</v>
       </c>
       <c r="B6" s="2" t="s">
+        <v>1045</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>1046</v>
       </c>
-      <c r="C6" s="2" t="s">
-        <v>1047</v>
-      </c>
       <c r="D6" s="2" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>930</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>1048</v>
+        <v>1047</v>
       </c>
     </row>
   </sheetData>
@@ -11009,7 +11021,7 @@
   <sheetData>
     <row r="1" spans="1:4" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A1" s="8" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
       <c r="B1" s="8"/>
       <c r="C1" s="8"/>
@@ -11020,10 +11032,10 @@
         <v>860</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>1049</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>1050</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>1051</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>848</v>
@@ -11031,13 +11043,13 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
+        <v>1051</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>1052</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="C4" s="2" t="s">
         <v>1053</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>1054</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>850</v>
@@ -11045,13 +11057,13 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
+        <v>1054</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>1053</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>1055</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>1054</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>1056</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>850</v>
@@ -11059,13 +11071,13 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
-        <v>1057</v>
+        <v>1056</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>1056</v>
+        <v>1055</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>1053</v>
+        <v>1052</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>850</v>
@@ -11095,7 +11107,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A1" s="8" t="s">
-        <v>1058</v>
+        <v>1057</v>
       </c>
       <c r="B1" s="8"/>
       <c r="C1" s="8"/>
@@ -11110,25 +11122,25 @@
         <v>852</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>1058</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>1059</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="D3" s="1" t="s">
         <v>1060</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="E3" s="1" t="s">
         <v>1061</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="F3" s="1" t="s">
         <v>1062</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="G3" s="1" t="s">
+        <v>1037</v>
+      </c>
+      <c r="H3" s="1" t="s">
         <v>1063</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>1038</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>1064</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.35">
@@ -11136,25 +11148,25 @@
         <v>826</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>1052</v>
+        <v>1051</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>1019</v>
+        <v>1018</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>930</v>
       </c>
       <c r="G4" s="2" t="s">
+        <v>1065</v>
+      </c>
+      <c r="H4" s="2" t="s">
         <v>1066</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>1067</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.35">
@@ -11162,25 +11174,25 @@
         <v>830</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>1055</v>
+        <v>1054</v>
       </c>
       <c r="C5" s="2" t="s">
+        <v>1067</v>
+      </c>
+      <c r="D5" s="2" t="s">
         <v>1068</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="E5" s="2" t="s">
+        <v>1023</v>
+      </c>
+      <c r="F5" s="2" t="s">
         <v>1069</v>
       </c>
-      <c r="E5" s="2" t="s">
-        <v>1024</v>
-      </c>
-      <c r="F5" s="2" t="s">
+      <c r="G5" s="2" t="s">
+        <v>1065</v>
+      </c>
+      <c r="H5" s="2" t="s">
         <v>1070</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>1066</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>1071</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.35">
@@ -11188,25 +11200,25 @@
         <v>826</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>1057</v>
+        <v>1056</v>
       </c>
       <c r="C6" s="2" t="s">
+        <v>1071</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G6" s="2" t="s">
         <v>1072</v>
       </c>
-      <c r="D6" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="G6" s="2" t="s">
+      <c r="H6" s="2" t="s">
         <v>1073</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>1074</v>
       </c>
     </row>
   </sheetData>
@@ -11233,7 +11245,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A1" s="8" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="B1" s="8"/>
       <c r="C1" s="8"/>
@@ -11243,7 +11255,7 @@
     </row>
     <row r="3" spans="1:6" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>894</v>
@@ -11252,30 +11264,30 @@
         <v>862</v>
       </c>
       <c r="D3" s="1" t="s">
+        <v>1076</v>
+      </c>
+      <c r="E3" s="1" t="s">
         <v>1077</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="F3" s="1" t="s">
         <v>1078</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>1079</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="B4" s="2" t="s">
+        <v>1079</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>1080</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="D4" s="2" t="s">
         <v>1081</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="E4" s="2" t="s">
         <v>1082</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>1083</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>826</v>
@@ -11283,19 +11295,19 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="B5" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>1084</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="D5" s="2" t="s">
         <v>1085</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="E5" s="2" t="s">
         <v>1086</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>1087</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>822</v>
@@ -11303,19 +11315,19 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
+        <v>1087</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>1088</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="C6" s="2" t="s">
         <v>1089</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="D6" s="2" t="s">
         <v>1090</v>
       </c>
-      <c r="D6" s="2" t="s">
-        <v>1091</v>
-      </c>
       <c r="E6" s="2" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>830</v>
@@ -11323,19 +11335,19 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="B7" s="2" t="s">
+        <v>1091</v>
+      </c>
+      <c r="C7" s="2" t="s">
         <v>1092</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="D7" s="2" t="s">
         <v>1093</v>
       </c>
-      <c r="D7" s="2" t="s">
-        <v>1094</v>
-      </c>
       <c r="E7" s="2" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>817</v>
@@ -11426,7 +11438,7 @@
         <v>5</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="29" x14ac:dyDescent="0.35">
@@ -11452,7 +11464,7 @@
         <v>5</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
@@ -11478,7 +11490,7 @@
         <v>5</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="29" x14ac:dyDescent="0.35">
@@ -11504,7 +11516,7 @@
         <v>5</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="29" x14ac:dyDescent="0.35">
@@ -11530,7 +11542,7 @@
         <v>5</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="29" x14ac:dyDescent="0.35">
@@ -11556,7 +11568,7 @@
         <v>5</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="58" x14ac:dyDescent="0.35">
@@ -11582,7 +11594,7 @@
         <v>5</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="29" x14ac:dyDescent="0.35">
@@ -11608,7 +11620,7 @@
         <v>5</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.35">
@@ -11634,7 +11646,7 @@
         <v>5</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="58" x14ac:dyDescent="0.35">
@@ -11654,13 +11666,13 @@
         <v>227</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>1125</v>
+        <v>1124</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>5</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="58" x14ac:dyDescent="0.35">
@@ -11671,19 +11683,19 @@
         <v>119</v>
       </c>
       <c r="C14" s="2" t="s">
+        <v>1120</v>
+      </c>
+      <c r="D14" s="2" t="s">
         <v>1121</v>
       </c>
-      <c r="D14" s="2" t="s">
+      <c r="E14" s="2" t="s">
         <v>1122</v>
       </c>
-      <c r="E14" s="2" t="s">
+      <c r="F14" s="2" t="s">
         <v>1123</v>
       </c>
-      <c r="F14" s="2" t="s">
-        <v>1124</v>
-      </c>
       <c r="H14" s="3" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
     </row>
   </sheetData>
@@ -11711,7 +11723,7 @@
   <sheetData>
     <row r="1" spans="1:10" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A1" s="8" t="s">
-        <v>1095</v>
+        <v>1094</v>
       </c>
       <c r="B1" s="8"/>
       <c r="C1" s="8"/>
@@ -11725,54 +11737,54 @@
     </row>
     <row r="3" spans="1:10" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
-        <v>1096</v>
+        <v>1095</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>852</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>1078</v>
+        <v>1077</v>
       </c>
       <c r="E3" s="1" t="s">
+        <v>1096</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>991</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>1034</v>
+      </c>
+      <c r="H3" s="1" t="s">
         <v>1097</v>
       </c>
-      <c r="F3" s="1" t="s">
-        <v>992</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>1035</v>
-      </c>
-      <c r="H3" s="1" t="s">
+      <c r="I3" s="1" t="s">
+        <v>1037</v>
+      </c>
+      <c r="J3" s="1" t="s">
         <v>1098</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>1038</v>
-      </c>
-      <c r="J3" s="1" t="s">
-        <v>1099</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
-        <v>1100</v>
+        <v>1099</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>826</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>1101</v>
+        <v>1100</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>925</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>1102</v>
+        <v>1101</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>159</v>
@@ -11781,30 +11793,30 @@
         <v>854</v>
       </c>
       <c r="I4" s="2" t="s">
+        <v>1102</v>
+      </c>
+      <c r="J4" s="2" t="s">
         <v>1103</v>
-      </c>
-      <c r="J4" s="2" t="s">
-        <v>1104</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
-        <v>1105</v>
+        <v>1104</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>826</v>
       </c>
       <c r="C5" s="2" t="s">
+        <v>1105</v>
+      </c>
+      <c r="D5" s="2" t="s">
         <v>1106</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="E5" s="2" t="s">
         <v>1107</v>
       </c>
-      <c r="E5" s="2" t="s">
-        <v>1108</v>
-      </c>
       <c r="F5" s="2" t="s">
-        <v>1108</v>
+        <v>1107</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>159</v>
@@ -11813,24 +11825,24 @@
         <v>854</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>1103</v>
+        <v>1102</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
-        <v>1110</v>
+        <v>1109</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>830</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>918</v>
@@ -11845,56 +11857,56 @@
         <v>854</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>1103</v>
+        <v>1102</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>1112</v>
+        <v>1111</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>826</v>
       </c>
       <c r="C7" s="2" t="s">
+        <v>1112</v>
+      </c>
+      <c r="D7" s="2" t="s">
         <v>1113</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>1114</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>930</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>1016</v>
+        <v>1015</v>
       </c>
       <c r="H7" s="2" t="s">
         <v>850</v>
       </c>
       <c r="I7" s="2" t="s">
+        <v>1102</v>
+      </c>
+      <c r="J7" s="2" t="s">
         <v>1103</v>
-      </c>
-      <c r="J7" s="2" t="s">
-        <v>1104</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>830</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>1115</v>
+        <v>1114</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>945</v>
@@ -11909,30 +11921,30 @@
         <v>854</v>
       </c>
       <c r="I8" s="2" t="s">
+        <v>1102</v>
+      </c>
+      <c r="J8" s="2" t="s">
         <v>1103</v>
-      </c>
-      <c r="J8" s="2" t="s">
-        <v>1104</v>
       </c>
     </row>
     <row r="9" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A9" s="2" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>826</v>
       </c>
       <c r="C9" s="2" t="s">
+        <v>1116</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>1082</v>
+      </c>
+      <c r="E9" s="2" t="s">
         <v>1117</v>
       </c>
-      <c r="D9" s="2" t="s">
-        <v>1083</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>1118</v>
-      </c>
       <c r="F9" s="2" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>159</v>
@@ -11941,10 +11953,10 @@
         <v>854</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>1104</v>
+        <v>1103</v>
       </c>
     </row>
   </sheetData>
@@ -12520,7 +12532,7 @@
         <v>5</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
@@ -12546,7 +12558,7 @@
         <v>5</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="29" x14ac:dyDescent="0.35">
@@ -12557,7 +12569,7 @@
         <v>229</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>1129</v>
+        <v>1128</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>317</v>
@@ -12572,7 +12584,7 @@
         <v>5</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="29" x14ac:dyDescent="0.35">
@@ -12598,7 +12610,7 @@
         <v>5</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
@@ -12624,7 +12636,7 @@
         <v>5</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="29" x14ac:dyDescent="0.35">
@@ -12650,7 +12662,7 @@
         <v>5</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
@@ -12676,7 +12688,7 @@
         <v>5</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="58" x14ac:dyDescent="0.35">
@@ -12702,7 +12714,7 @@
         <v>5</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.35">
@@ -12713,22 +12725,22 @@
         <v>119</v>
       </c>
       <c r="C12" s="2" t="s">
+        <v>1133</v>
+      </c>
+      <c r="D12" s="2" t="s">
         <v>1134</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>1135</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>299</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>1136</v>
+        <v>1135</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>5</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
     </row>
   </sheetData>
@@ -12816,7 +12828,7 @@
         <v>5</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
@@ -12842,7 +12854,7 @@
         <v>5</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="29" x14ac:dyDescent="0.35">
@@ -12868,7 +12880,7 @@
         <v>5</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.35">
@@ -12879,13 +12891,13 @@
         <v>229</v>
       </c>
       <c r="C7" s="2" t="s">
+        <v>1125</v>
+      </c>
+      <c r="D7" s="2" t="s">
         <v>1126</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="E7" s="2" t="s">
         <v>1127</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>1128</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>292</v>
@@ -12894,7 +12906,7 @@
         <v>5</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
@@ -12920,7 +12932,7 @@
         <v>5</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="29" x14ac:dyDescent="0.35">
@@ -12931,13 +12943,13 @@
         <v>229</v>
       </c>
       <c r="C9" s="2" t="s">
+        <v>1129</v>
+      </c>
+      <c r="D9" s="2" t="s">
         <v>1130</v>
       </c>
-      <c r="D9" s="2" t="s">
+      <c r="E9" s="2" t="s">
         <v>1131</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>1132</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>300</v>
@@ -12946,7 +12958,7 @@
         <v>5</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="29" x14ac:dyDescent="0.35">
@@ -12972,7 +12984,7 @@
         <v>5</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="58" x14ac:dyDescent="0.35">
@@ -12983,7 +12995,7 @@
         <v>128</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>1133</v>
+        <v>1132</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>306</v>
@@ -12998,7 +13010,7 @@
         <v>5</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.35">
@@ -13009,22 +13021,22 @@
         <v>119</v>
       </c>
       <c r="C12" s="2" t="s">
+        <v>1136</v>
+      </c>
+      <c r="D12" s="2" t="s">
         <v>1137</v>
       </c>
-      <c r="D12" s="2" t="s">
+      <c r="E12" s="2" t="s">
+        <v>1142</v>
+      </c>
+      <c r="F12" s="2" t="s">
         <v>1138</v>
       </c>
-      <c r="E12" s="2" t="s">
-        <v>1143</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>1139</v>
-      </c>
       <c r="G12" s="2" t="s">
         <v>5</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
     </row>
   </sheetData>
@@ -13112,7 +13124,7 @@
         <v>5</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="87" x14ac:dyDescent="0.35">
@@ -13138,7 +13150,7 @@
         <v>5</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="29" x14ac:dyDescent="0.35">
@@ -13164,7 +13176,7 @@
         <v>5</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="29" x14ac:dyDescent="0.35">
@@ -13190,7 +13202,7 @@
         <v>5</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="29" x14ac:dyDescent="0.35">
@@ -13216,7 +13228,7 @@
         <v>5</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="29" x14ac:dyDescent="0.35">
@@ -13242,7 +13254,7 @@
         <v>5</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.35">
@@ -13268,7 +13280,7 @@
         <v>5</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="29" x14ac:dyDescent="0.35">
@@ -13294,7 +13306,7 @@
         <v>5</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="29" x14ac:dyDescent="0.35">
@@ -13320,7 +13332,7 @@
         <v>5</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="58" x14ac:dyDescent="0.35">
@@ -13346,7 +13358,7 @@
         <v>5</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="29" x14ac:dyDescent="0.35">
@@ -13372,7 +13384,7 @@
         <v>5</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
@@ -13383,10 +13395,10 @@
         <v>229</v>
       </c>
       <c r="C15" s="2" t="s">
+        <v>1149</v>
+      </c>
+      <c r="D15" s="2" t="s">
         <v>1150</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>1151</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>387</v>
@@ -13398,7 +13410,7 @@
         <v>5</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="29" x14ac:dyDescent="0.35">
@@ -13424,7 +13436,7 @@
         <v>5</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="72.5" x14ac:dyDescent="0.35">
@@ -13450,7 +13462,7 @@
         <v>5</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
@@ -13476,7 +13488,7 @@
         <v>5</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="72.5" x14ac:dyDescent="0.35">
@@ -13502,7 +13514,7 @@
         <v>5</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="20" spans="1:8" ht="29" x14ac:dyDescent="0.35">
@@ -13528,7 +13540,7 @@
         <v>5</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="21" spans="1:8" ht="29" x14ac:dyDescent="0.35">
@@ -13554,7 +13566,7 @@
         <v>5</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.35">
@@ -13565,22 +13577,22 @@
         <v>119</v>
       </c>
       <c r="C22" s="2" t="s">
+        <v>1139</v>
+      </c>
+      <c r="D22" s="2" t="s">
         <v>1140</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>1141</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>387</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>1142</v>
+        <v>1141</v>
       </c>
       <c r="G22" s="2" t="s">
         <v>5</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="23" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
@@ -13591,19 +13603,19 @@
         <v>128</v>
       </c>
       <c r="C23" s="9" t="s">
+        <v>1143</v>
+      </c>
+      <c r="D23" s="10" t="s">
         <v>1144</v>
-      </c>
-      <c r="D23" s="10" t="s">
-        <v>1145</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>387</v>
       </c>
       <c r="F23" s="9" t="s">
-        <v>1146</v>
+        <v>1145</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="24" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
@@ -13614,19 +13626,19 @@
         <v>128</v>
       </c>
       <c r="C24" s="9" t="s">
+        <v>1146</v>
+      </c>
+      <c r="D24" s="10" t="s">
         <v>1147</v>
-      </c>
-      <c r="D24" s="10" t="s">
-        <v>1148</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>387</v>
       </c>
       <c r="F24" s="9" t="s">
-        <v>1149</v>
+        <v>1148</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
     </row>
   </sheetData>

--- a/docs/Dokumen_Testing_POS.xlsx
+++ b/docs/Dokumen_Testing_POS.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EFE79627-EFB9-4C75-A84D-378629CA5AEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74A9D204-5E9E-4379-B1A5-E2CE022C5639}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="867" firstSheet="6" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="867" firstSheet="6" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Daftar Isi" sheetId="1" r:id="rId1"/>
@@ -65,7 +65,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2289" uniqueCount="1152">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2296" uniqueCount="1153">
   <si>
     <t>DOKUMEN TESTING APLIKASI POS</t>
   </si>
@@ -3669,6 +3669,9 @@
   </si>
   <si>
     <t>Buat retur baru tapi faktur pembelian belum ada</t>
+  </si>
+  <si>
+    <t>Hapus Produk tapi stok masih ada</t>
   </si>
 </sst>
 </file>
@@ -3788,7 +3791,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -3802,21 +3805,18 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -4167,20 +4167,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="6"/>
-      <c r="C1" s="6"/>
-      <c r="D1" s="6"/>
+      <c r="B1" s="8"/>
+      <c r="C1" s="8"/>
+      <c r="D1" s="8"/>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A2" s="7" t="s">
+      <c r="A2" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="7"/>
-      <c r="C2" s="7"/>
-      <c r="D2" s="7"/>
+      <c r="B2" s="9"/>
+      <c r="C2" s="9"/>
+      <c r="D2" s="9"/>
     </row>
     <row r="4" spans="1:4" ht="18.649999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
@@ -4665,16 +4665,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="7" t="s">
         <v>392</v>
       </c>
-      <c r="B1" s="5"/>
-      <c r="C1" s="5"/>
-      <c r="D1" s="5"/>
-      <c r="E1" s="5"/>
-      <c r="F1" s="5"/>
-      <c r="G1" s="5"/>
-      <c r="H1" s="5"/>
+      <c r="B1" s="7"/>
+      <c r="C1" s="7"/>
+      <c r="D1" s="7"/>
+      <c r="E1" s="7"/>
+      <c r="F1" s="7"/>
+      <c r="G1" s="7"/>
+      <c r="H1" s="7"/>
     </row>
     <row r="3" spans="1:8" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
@@ -4883,16 +4883,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="7" t="s">
         <v>414</v>
       </c>
-      <c r="B1" s="5"/>
-      <c r="C1" s="5"/>
-      <c r="D1" s="5"/>
-      <c r="E1" s="5"/>
-      <c r="F1" s="5"/>
-      <c r="G1" s="5"/>
-      <c r="H1" s="5"/>
+      <c r="B1" s="7"/>
+      <c r="C1" s="7"/>
+      <c r="D1" s="7"/>
+      <c r="E1" s="7"/>
+      <c r="F1" s="7"/>
+      <c r="G1" s="7"/>
+      <c r="H1" s="7"/>
     </row>
     <row r="3" spans="1:8" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
@@ -5179,16 +5179,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="7" t="s">
         <v>447</v>
       </c>
-      <c r="B1" s="5"/>
-      <c r="C1" s="5"/>
-      <c r="D1" s="5"/>
-      <c r="E1" s="5"/>
-      <c r="F1" s="5"/>
-      <c r="G1" s="5"/>
-      <c r="H1" s="5"/>
+      <c r="B1" s="7"/>
+      <c r="C1" s="7"/>
+      <c r="D1" s="7"/>
+      <c r="E1" s="7"/>
+      <c r="F1" s="7"/>
+      <c r="G1" s="7"/>
+      <c r="H1" s="7"/>
     </row>
     <row r="3" spans="1:8" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
@@ -5347,7 +5347,7 @@
       </c>
     </row>
     <row r="9" spans="1:8" ht="29" x14ac:dyDescent="0.35">
-      <c r="A9" s="9">
+      <c r="A9" s="4">
         <v>6</v>
       </c>
       <c r="B9" s="2" t="s">
@@ -5382,16 +5382,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="7" t="s">
         <v>466</v>
       </c>
-      <c r="B1" s="5"/>
-      <c r="C1" s="5"/>
-      <c r="D1" s="5"/>
-      <c r="E1" s="5"/>
-      <c r="F1" s="5"/>
-      <c r="G1" s="5"/>
-      <c r="H1" s="5"/>
+      <c r="B1" s="7"/>
+      <c r="C1" s="7"/>
+      <c r="D1" s="7"/>
+      <c r="E1" s="7"/>
+      <c r="F1" s="7"/>
+      <c r="G1" s="7"/>
+      <c r="H1" s="7"/>
     </row>
     <row r="3" spans="1:8" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
@@ -5600,16 +5600,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="7" t="s">
         <v>486</v>
       </c>
-      <c r="B1" s="5"/>
-      <c r="C1" s="5"/>
-      <c r="D1" s="5"/>
-      <c r="E1" s="5"/>
-      <c r="F1" s="5"/>
-      <c r="G1" s="5"/>
-      <c r="H1" s="5"/>
+      <c r="B1" s="7"/>
+      <c r="C1" s="7"/>
+      <c r="D1" s="7"/>
+      <c r="E1" s="7"/>
+      <c r="F1" s="7"/>
+      <c r="G1" s="7"/>
+      <c r="H1" s="7"/>
     </row>
     <row r="3" spans="1:8" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
@@ -5818,16 +5818,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="7" t="s">
         <v>508</v>
       </c>
-      <c r="B1" s="5"/>
-      <c r="C1" s="5"/>
-      <c r="D1" s="5"/>
-      <c r="E1" s="5"/>
-      <c r="F1" s="5"/>
-      <c r="G1" s="5"/>
-      <c r="H1" s="5"/>
+      <c r="B1" s="7"/>
+      <c r="C1" s="7"/>
+      <c r="D1" s="7"/>
+      <c r="E1" s="7"/>
+      <c r="F1" s="7"/>
+      <c r="G1" s="7"/>
+      <c r="H1" s="7"/>
     </row>
     <row r="3" spans="1:8" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
@@ -6036,16 +6036,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="7" t="s">
         <v>530</v>
       </c>
-      <c r="B1" s="5"/>
-      <c r="C1" s="5"/>
-      <c r="D1" s="5"/>
-      <c r="E1" s="5"/>
-      <c r="F1" s="5"/>
-      <c r="G1" s="5"/>
-      <c r="H1" s="5"/>
+      <c r="B1" s="7"/>
+      <c r="C1" s="7"/>
+      <c r="D1" s="7"/>
+      <c r="E1" s="7"/>
+      <c r="F1" s="7"/>
+      <c r="G1" s="7"/>
+      <c r="H1" s="7"/>
     </row>
     <row r="3" spans="1:8" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
@@ -6280,16 +6280,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="7" t="s">
         <v>556</v>
       </c>
-      <c r="B1" s="5"/>
-      <c r="C1" s="5"/>
-      <c r="D1" s="5"/>
-      <c r="E1" s="5"/>
-      <c r="F1" s="5"/>
-      <c r="G1" s="5"/>
-      <c r="H1" s="5"/>
+      <c r="B1" s="7"/>
+      <c r="C1" s="7"/>
+      <c r="D1" s="7"/>
+      <c r="E1" s="7"/>
+      <c r="F1" s="7"/>
+      <c r="G1" s="7"/>
+      <c r="H1" s="7"/>
     </row>
     <row r="3" spans="1:8" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
@@ -6472,16 +6472,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="7" t="s">
         <v>576</v>
       </c>
-      <c r="B1" s="5"/>
-      <c r="C1" s="5"/>
-      <c r="D1" s="5"/>
-      <c r="E1" s="5"/>
-      <c r="F1" s="5"/>
-      <c r="G1" s="5"/>
-      <c r="H1" s="5"/>
+      <c r="B1" s="7"/>
+      <c r="C1" s="7"/>
+      <c r="D1" s="7"/>
+      <c r="E1" s="7"/>
+      <c r="F1" s="7"/>
+      <c r="G1" s="7"/>
+      <c r="H1" s="7"/>
     </row>
     <row r="3" spans="1:8" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
@@ -6898,16 +6898,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="7" t="s">
         <v>628</v>
       </c>
-      <c r="B1" s="5"/>
-      <c r="C1" s="5"/>
-      <c r="D1" s="5"/>
-      <c r="E1" s="5"/>
-      <c r="F1" s="5"/>
-      <c r="G1" s="5"/>
-      <c r="H1" s="5"/>
+      <c r="B1" s="7"/>
+      <c r="C1" s="7"/>
+      <c r="D1" s="7"/>
+      <c r="E1" s="7"/>
+      <c r="F1" s="7"/>
+      <c r="G1" s="7"/>
+      <c r="H1" s="7"/>
     </row>
     <row r="3" spans="1:8" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
@@ -7116,16 +7116,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="7" t="s">
         <v>111</v>
       </c>
-      <c r="B1" s="5"/>
-      <c r="C1" s="5"/>
-      <c r="D1" s="5"/>
-      <c r="E1" s="5"/>
-      <c r="F1" s="5"/>
-      <c r="G1" s="5"/>
-      <c r="H1" s="5"/>
+      <c r="B1" s="7"/>
+      <c r="C1" s="7"/>
+      <c r="D1" s="7"/>
+      <c r="E1" s="7"/>
+      <c r="F1" s="7"/>
+      <c r="G1" s="7"/>
+      <c r="H1" s="7"/>
     </row>
     <row r="3" spans="1:8" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
@@ -7464,16 +7464,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="7" t="s">
         <v>648</v>
       </c>
-      <c r="B1" s="5"/>
-      <c r="C1" s="5"/>
-      <c r="D1" s="5"/>
-      <c r="E1" s="5"/>
-      <c r="F1" s="5"/>
-      <c r="G1" s="5"/>
-      <c r="H1" s="5"/>
+      <c r="B1" s="7"/>
+      <c r="C1" s="7"/>
+      <c r="D1" s="7"/>
+      <c r="E1" s="7"/>
+      <c r="F1" s="7"/>
+      <c r="G1" s="7"/>
+      <c r="H1" s="7"/>
     </row>
     <row r="3" spans="1:8" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
@@ -7786,16 +7786,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="7" t="s">
         <v>681</v>
       </c>
-      <c r="B1" s="5"/>
-      <c r="C1" s="5"/>
-      <c r="D1" s="5"/>
-      <c r="E1" s="5"/>
-      <c r="F1" s="5"/>
-      <c r="G1" s="5"/>
-      <c r="H1" s="5"/>
+      <c r="B1" s="7"/>
+      <c r="C1" s="7"/>
+      <c r="D1" s="7"/>
+      <c r="E1" s="7"/>
+      <c r="F1" s="7"/>
+      <c r="G1" s="7"/>
+      <c r="H1" s="7"/>
     </row>
     <row r="3" spans="1:8" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
@@ -7978,16 +7978,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="7" t="s">
         <v>697</v>
       </c>
-      <c r="B1" s="5"/>
-      <c r="C1" s="5"/>
-      <c r="D1" s="5"/>
-      <c r="E1" s="5"/>
-      <c r="F1" s="5"/>
-      <c r="G1" s="5"/>
-      <c r="H1" s="5"/>
+      <c r="B1" s="7"/>
+      <c r="C1" s="7"/>
+      <c r="D1" s="7"/>
+      <c r="E1" s="7"/>
+      <c r="F1" s="7"/>
+      <c r="G1" s="7"/>
+      <c r="H1" s="7"/>
     </row>
     <row r="3" spans="1:8" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
@@ -8222,16 +8222,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="7" t="s">
         <v>722</v>
       </c>
-      <c r="B1" s="5"/>
-      <c r="C1" s="5"/>
-      <c r="D1" s="5"/>
-      <c r="E1" s="5"/>
-      <c r="F1" s="5"/>
-      <c r="G1" s="5"/>
-      <c r="H1" s="5"/>
+      <c r="B1" s="7"/>
+      <c r="C1" s="7"/>
+      <c r="D1" s="7"/>
+      <c r="E1" s="7"/>
+      <c r="F1" s="7"/>
+      <c r="G1" s="7"/>
+      <c r="H1" s="7"/>
     </row>
     <row r="3" spans="1:8" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
@@ -8414,16 +8414,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="7" t="s">
         <v>739</v>
       </c>
-      <c r="B1" s="5"/>
-      <c r="C1" s="5"/>
-      <c r="D1" s="5"/>
-      <c r="E1" s="5"/>
-      <c r="F1" s="5"/>
-      <c r="G1" s="5"/>
-      <c r="H1" s="5"/>
+      <c r="B1" s="7"/>
+      <c r="C1" s="7"/>
+      <c r="D1" s="7"/>
+      <c r="E1" s="7"/>
+      <c r="F1" s="7"/>
+      <c r="G1" s="7"/>
+      <c r="H1" s="7"/>
     </row>
     <row r="3" spans="1:8" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
@@ -8658,16 +8658,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="7" t="s">
         <v>765</v>
       </c>
-      <c r="B1" s="5"/>
-      <c r="C1" s="5"/>
-      <c r="D1" s="5"/>
-      <c r="E1" s="5"/>
-      <c r="F1" s="5"/>
-      <c r="G1" s="5"/>
-      <c r="H1" s="5"/>
+      <c r="B1" s="7"/>
+      <c r="C1" s="7"/>
+      <c r="D1" s="7"/>
+      <c r="E1" s="7"/>
+      <c r="F1" s="7"/>
+      <c r="G1" s="7"/>
+      <c r="H1" s="7"/>
     </row>
     <row r="3" spans="1:8" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
@@ -8824,16 +8824,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="7" t="s">
         <v>780</v>
       </c>
-      <c r="B1" s="5"/>
-      <c r="C1" s="5"/>
-      <c r="D1" s="5"/>
-      <c r="E1" s="5"/>
-      <c r="F1" s="5"/>
-      <c r="G1" s="5"/>
-      <c r="H1" s="5"/>
+      <c r="B1" s="7"/>
+      <c r="C1" s="7"/>
+      <c r="D1" s="7"/>
+      <c r="E1" s="7"/>
+      <c r="F1" s="7"/>
+      <c r="G1" s="7"/>
+      <c r="H1" s="7"/>
     </row>
     <row r="3" spans="1:8" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
@@ -9143,14 +9143,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="10" t="s">
         <v>810</v>
       </c>
-      <c r="B1" s="8"/>
-      <c r="C1" s="8"/>
-      <c r="D1" s="8"/>
-      <c r="E1" s="8"/>
-      <c r="F1" s="8"/>
+      <c r="B1" s="10"/>
+      <c r="C1" s="10"/>
+      <c r="D1" s="10"/>
+      <c r="E1" s="10"/>
+      <c r="F1" s="10"/>
     </row>
     <row r="3" spans="1:6" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
@@ -9314,14 +9314,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="10" t="s">
         <v>843</v>
       </c>
-      <c r="B1" s="8"/>
-      <c r="C1" s="8"/>
-      <c r="D1" s="8"/>
-      <c r="E1" s="8"/>
-      <c r="F1" s="8"/>
+      <c r="B1" s="10"/>
+      <c r="C1" s="10"/>
+      <c r="D1" s="10"/>
+      <c r="E1" s="10"/>
+      <c r="F1" s="10"/>
     </row>
     <row r="3" spans="1:6" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
@@ -9485,13 +9485,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="10" t="s">
         <v>858</v>
       </c>
-      <c r="B1" s="8"/>
-      <c r="C1" s="8"/>
-      <c r="D1" s="8"/>
-      <c r="E1" s="8"/>
+      <c r="B1" s="10"/>
+      <c r="C1" s="10"/>
+      <c r="D1" s="10"/>
+      <c r="E1" s="10"/>
     </row>
     <row r="3" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
@@ -9705,16 +9705,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="7" t="s">
         <v>165</v>
       </c>
-      <c r="B1" s="5"/>
-      <c r="C1" s="5"/>
-      <c r="D1" s="5"/>
-      <c r="E1" s="5"/>
-      <c r="F1" s="5"/>
-      <c r="G1" s="5"/>
-      <c r="H1" s="5"/>
+      <c r="B1" s="7"/>
+      <c r="C1" s="7"/>
+      <c r="D1" s="7"/>
+      <c r="E1" s="7"/>
+      <c r="F1" s="7"/>
+      <c r="G1" s="7"/>
+      <c r="H1" s="7"/>
     </row>
     <row r="3" spans="1:8" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
@@ -9923,18 +9923,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="10" t="s">
         <v>891</v>
       </c>
-      <c r="B1" s="8"/>
-      <c r="C1" s="8"/>
-      <c r="D1" s="8"/>
-      <c r="E1" s="8"/>
-      <c r="F1" s="8"/>
-      <c r="G1" s="8"/>
-      <c r="H1" s="8"/>
-      <c r="I1" s="8"/>
-      <c r="J1" s="8"/>
+      <c r="B1" s="10"/>
+      <c r="C1" s="10"/>
+      <c r="D1" s="10"/>
+      <c r="E1" s="10"/>
+      <c r="F1" s="10"/>
+      <c r="G1" s="10"/>
+      <c r="H1" s="10"/>
+      <c r="I1" s="10"/>
+      <c r="J1" s="10"/>
     </row>
     <row r="3" spans="1:10" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
@@ -10246,15 +10246,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="10" t="s">
         <v>937</v>
       </c>
-      <c r="B1" s="8"/>
-      <c r="C1" s="8"/>
-      <c r="D1" s="8"/>
-      <c r="E1" s="8"/>
-      <c r="F1" s="8"/>
-      <c r="G1" s="8"/>
+      <c r="B1" s="10"/>
+      <c r="C1" s="10"/>
+      <c r="D1" s="10"/>
+      <c r="E1" s="10"/>
+      <c r="F1" s="10"/>
+      <c r="G1" s="10"/>
     </row>
     <row r="3" spans="1:7" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
@@ -10390,12 +10390,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="10" t="s">
         <v>948</v>
       </c>
-      <c r="B1" s="8"/>
-      <c r="C1" s="8"/>
-      <c r="D1" s="8"/>
+      <c r="B1" s="10"/>
+      <c r="C1" s="10"/>
+      <c r="D1" s="10"/>
     </row>
     <row r="3" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
@@ -10477,15 +10477,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="10" t="s">
         <v>957</v>
       </c>
-      <c r="B1" s="8"/>
-      <c r="C1" s="8"/>
-      <c r="D1" s="8"/>
-      <c r="E1" s="8"/>
-      <c r="F1" s="8"/>
-      <c r="G1" s="8"/>
+      <c r="B1" s="10"/>
+      <c r="C1" s="10"/>
+      <c r="D1" s="10"/>
+      <c r="E1" s="10"/>
+      <c r="F1" s="10"/>
+      <c r="G1" s="10"/>
     </row>
     <row r="3" spans="1:7" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
@@ -10523,7 +10523,7 @@
       <c r="D4" s="2">
         <v>81234567890</v>
       </c>
-      <c r="E4" s="11" t="s">
+      <c r="E4" s="6" t="s">
         <v>966</v>
       </c>
       <c r="F4" s="2" t="s">
@@ -10546,7 +10546,7 @@
       <c r="D5" s="2">
         <v>82198765432</v>
       </c>
-      <c r="E5" s="11" t="s">
+      <c r="E5" s="6" t="s">
         <v>971</v>
       </c>
       <c r="F5" s="2" t="s">
@@ -10628,16 +10628,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="10" t="s">
         <v>985</v>
       </c>
-      <c r="B1" s="8"/>
-      <c r="C1" s="8"/>
-      <c r="D1" s="8"/>
-      <c r="E1" s="8"/>
-      <c r="F1" s="8"/>
-      <c r="G1" s="8"/>
-      <c r="H1" s="8"/>
+      <c r="B1" s="10"/>
+      <c r="C1" s="10"/>
+      <c r="D1" s="10"/>
+      <c r="E1" s="10"/>
+      <c r="F1" s="10"/>
+      <c r="G1" s="10"/>
+      <c r="H1" s="10"/>
     </row>
     <row r="3" spans="1:8" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
@@ -10766,14 +10766,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="10" t="s">
         <v>1011</v>
       </c>
-      <c r="B1" s="8"/>
-      <c r="C1" s="8"/>
-      <c r="D1" s="8"/>
-      <c r="E1" s="8"/>
-      <c r="F1" s="8"/>
+      <c r="B1" s="10"/>
+      <c r="C1" s="10"/>
+      <c r="D1" s="10"/>
+      <c r="E1" s="10"/>
+      <c r="F1" s="10"/>
     </row>
     <row r="3" spans="1:6" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
@@ -10898,15 +10898,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="10" t="s">
         <v>1033</v>
       </c>
-      <c r="B1" s="8"/>
-      <c r="C1" s="8"/>
-      <c r="D1" s="8"/>
-      <c r="E1" s="8"/>
-      <c r="F1" s="8"/>
-      <c r="G1" s="8"/>
+      <c r="B1" s="10"/>
+      <c r="C1" s="10"/>
+      <c r="D1" s="10"/>
+      <c r="E1" s="10"/>
+      <c r="F1" s="10"/>
+      <c r="G1" s="10"/>
     </row>
     <row r="3" spans="1:7" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
@@ -11020,12 +11020,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="10" t="s">
         <v>1048</v>
       </c>
-      <c r="B1" s="8"/>
-      <c r="C1" s="8"/>
-      <c r="D1" s="8"/>
+      <c r="B1" s="10"/>
+      <c r="C1" s="10"/>
+      <c r="D1" s="10"/>
     </row>
     <row r="3" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
@@ -11106,16 +11106,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="10" t="s">
         <v>1057</v>
       </c>
-      <c r="B1" s="8"/>
-      <c r="C1" s="8"/>
-      <c r="D1" s="8"/>
-      <c r="E1" s="8"/>
-      <c r="F1" s="8"/>
-      <c r="G1" s="8"/>
-      <c r="H1" s="8"/>
+      <c r="B1" s="10"/>
+      <c r="C1" s="10"/>
+      <c r="D1" s="10"/>
+      <c r="E1" s="10"/>
+      <c r="F1" s="10"/>
+      <c r="G1" s="10"/>
+      <c r="H1" s="10"/>
     </row>
     <row r="3" spans="1:8" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
@@ -11244,14 +11244,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="10" t="s">
         <v>1074</v>
       </c>
-      <c r="B1" s="8"/>
-      <c r="C1" s="8"/>
-      <c r="D1" s="8"/>
-      <c r="E1" s="8"/>
-      <c r="F1" s="8"/>
+      <c r="B1" s="10"/>
+      <c r="C1" s="10"/>
+      <c r="D1" s="10"/>
+      <c r="E1" s="10"/>
+      <c r="F1" s="10"/>
     </row>
     <row r="3" spans="1:6" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
@@ -11378,16 +11378,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="7" t="s">
         <v>190</v>
       </c>
-      <c r="B1" s="5"/>
-      <c r="C1" s="5"/>
-      <c r="D1" s="5"/>
-      <c r="E1" s="5"/>
-      <c r="F1" s="5"/>
-      <c r="G1" s="5"/>
-      <c r="H1" s="5"/>
+      <c r="B1" s="7"/>
+      <c r="C1" s="7"/>
+      <c r="D1" s="7"/>
+      <c r="E1" s="7"/>
+      <c r="F1" s="7"/>
+      <c r="G1" s="7"/>
+      <c r="H1" s="7"/>
     </row>
     <row r="3" spans="1:8" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
@@ -11722,18 +11722,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="10" t="s">
         <v>1094</v>
       </c>
-      <c r="B1" s="8"/>
-      <c r="C1" s="8"/>
-      <c r="D1" s="8"/>
-      <c r="E1" s="8"/>
-      <c r="F1" s="8"/>
-      <c r="G1" s="8"/>
-      <c r="H1" s="8"/>
-      <c r="I1" s="8"/>
-      <c r="J1" s="8"/>
+      <c r="B1" s="10"/>
+      <c r="C1" s="10"/>
+      <c r="D1" s="10"/>
+      <c r="E1" s="10"/>
+      <c r="F1" s="10"/>
+      <c r="G1" s="10"/>
+      <c r="H1" s="10"/>
+      <c r="I1" s="10"/>
+      <c r="J1" s="10"/>
     </row>
     <row r="3" spans="1:10" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
@@ -11984,16 +11984,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="7" t="s">
         <v>228</v>
       </c>
-      <c r="B1" s="5"/>
-      <c r="C1" s="5"/>
-      <c r="D1" s="5"/>
-      <c r="E1" s="5"/>
-      <c r="F1" s="5"/>
-      <c r="G1" s="5"/>
-      <c r="H1" s="5"/>
+      <c r="B1" s="7"/>
+      <c r="C1" s="7"/>
+      <c r="D1" s="7"/>
+      <c r="E1" s="7"/>
+      <c r="F1" s="7"/>
+      <c r="G1" s="7"/>
+      <c r="H1" s="7"/>
     </row>
     <row r="3" spans="1:8" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
@@ -12254,16 +12254,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="7" t="s">
         <v>258</v>
       </c>
-      <c r="B1" s="5"/>
-      <c r="C1" s="5"/>
-      <c r="D1" s="5"/>
-      <c r="E1" s="5"/>
-      <c r="F1" s="5"/>
-      <c r="G1" s="5"/>
-      <c r="H1" s="5"/>
+      <c r="B1" s="7"/>
+      <c r="C1" s="7"/>
+      <c r="D1" s="7"/>
+      <c r="E1" s="7"/>
+      <c r="F1" s="7"/>
+      <c r="G1" s="7"/>
+      <c r="H1" s="7"/>
     </row>
     <row r="3" spans="1:8" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
@@ -12472,16 +12472,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="7" t="s">
         <v>281</v>
       </c>
-      <c r="B1" s="5"/>
-      <c r="C1" s="5"/>
-      <c r="D1" s="5"/>
-      <c r="E1" s="5"/>
-      <c r="F1" s="5"/>
-      <c r="G1" s="5"/>
-      <c r="H1" s="5"/>
+      <c r="B1" s="7"/>
+      <c r="C1" s="7"/>
+      <c r="D1" s="7"/>
+      <c r="E1" s="7"/>
+      <c r="F1" s="7"/>
+      <c r="G1" s="7"/>
+      <c r="H1" s="7"/>
     </row>
     <row r="3" spans="1:8" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
@@ -12768,16 +12768,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="7" t="s">
         <v>308</v>
       </c>
-      <c r="B1" s="5"/>
-      <c r="C1" s="5"/>
-      <c r="D1" s="5"/>
-      <c r="E1" s="5"/>
-      <c r="F1" s="5"/>
-      <c r="G1" s="5"/>
-      <c r="H1" s="5"/>
+      <c r="B1" s="7"/>
+      <c r="C1" s="7"/>
+      <c r="D1" s="7"/>
+      <c r="E1" s="7"/>
+      <c r="F1" s="7"/>
+      <c r="G1" s="7"/>
+      <c r="H1" s="7"/>
     </row>
     <row r="3" spans="1:8" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
@@ -13050,7 +13050,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
-  <dimension ref="A1:H24"/>
+  <dimension ref="A1:H25"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
@@ -13064,16 +13064,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="7" t="s">
         <v>327</v>
       </c>
-      <c r="B1" s="5"/>
-      <c r="C1" s="5"/>
-      <c r="D1" s="5"/>
-      <c r="E1" s="5"/>
-      <c r="F1" s="5"/>
-      <c r="G1" s="5"/>
-      <c r="H1" s="5"/>
+      <c r="B1" s="7"/>
+      <c r="C1" s="7"/>
+      <c r="D1" s="7"/>
+      <c r="E1" s="7"/>
+      <c r="F1" s="7"/>
+      <c r="G1" s="7"/>
+      <c r="H1" s="7"/>
     </row>
     <row r="3" spans="1:8" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
@@ -13599,19 +13599,19 @@
       <c r="A23" s="2">
         <v>20</v>
       </c>
-      <c r="B23" s="9" t="s">
+      <c r="B23" s="4" t="s">
         <v>128</v>
       </c>
-      <c r="C23" s="9" t="s">
+      <c r="C23" s="4" t="s">
         <v>1143</v>
       </c>
-      <c r="D23" s="10" t="s">
+      <c r="D23" s="5" t="s">
         <v>1144</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>387</v>
       </c>
-      <c r="F23" s="9" t="s">
+      <c r="F23" s="4" t="s">
         <v>1145</v>
       </c>
       <c r="H23" s="3" t="s">
@@ -13622,22 +13622,48 @@
       <c r="A24" s="2">
         <v>21</v>
       </c>
-      <c r="B24" s="9" t="s">
+      <c r="B24" s="4" t="s">
         <v>128</v>
       </c>
-      <c r="C24" s="9" t="s">
+      <c r="C24" s="4" t="s">
         <v>1146</v>
       </c>
-      <c r="D24" s="10" t="s">
+      <c r="D24" s="5" t="s">
         <v>1147</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>387</v>
       </c>
-      <c r="F24" s="9" t="s">
+      <c r="F24" s="4" t="s">
         <v>1148</v>
       </c>
       <c r="H24" s="3" t="s">
+        <v>1119</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A25" s="2">
+        <v>22</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>1152</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>1140</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>1141</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="H25" s="3" t="s">
         <v>1119</v>
       </c>
     </row>

--- a/docs/Dokumen_Testing_POS.xlsx
+++ b/docs/Dokumen_Testing_POS.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74A9D204-5E9E-4379-B1A5-E2CE022C5639}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{382AFBE5-5776-4C77-AC99-F7AE9F037E43}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="867" firstSheet="6" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="867" firstSheet="6" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Daftar Isi" sheetId="1" r:id="rId1"/>
@@ -65,7 +65,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2296" uniqueCount="1153">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2309" uniqueCount="1158">
   <si>
     <t>DOKUMEN TESTING APLIKASI POS</t>
   </si>
@@ -1334,9 +1334,6 @@
   </si>
   <si>
     <t>1. Isi kode yang sudah dipakai</t>
-  </si>
-  <si>
-    <t>supplier_code: SUP-001 (duplikat)</t>
   </si>
   <si>
     <t>Edit data supplier</t>
@@ -3672,6 +3669,24 @@
   </si>
   <si>
     <t>Hapus Produk tapi stok masih ada</t>
+  </si>
+  <si>
+    <t>Produk nonaktif tidak muncul di pembelian pengadaan</t>
+  </si>
+  <si>
+    <t>Produk yang tidak dapat dihapus, karena stok masih ada</t>
+  </si>
+  <si>
+    <t>Hapus Supplier</t>
+  </si>
+  <si>
+    <t>1. Klik hapus pada Supplier test</t>
+  </si>
+  <si>
+    <t>Supplier terhapus dari list</t>
+  </si>
+  <si>
+    <t>name: PT Sumber Makmur (duplikat)</t>
   </si>
 </sst>
 </file>
@@ -4651,7 +4666,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:H10"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
@@ -4725,7 +4740,7 @@
         <v>5</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="72.5" x14ac:dyDescent="0.35">
@@ -4751,7 +4766,7 @@
         <v>5</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="29" x14ac:dyDescent="0.35">
@@ -4768,7 +4783,7 @@
         <v>401</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>402</v>
+        <v>1157</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>246</v>
@@ -4776,8 +4791,8 @@
       <c r="G6" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="H6" s="2" t="s">
-        <v>5</v>
+      <c r="H6" s="3" t="s">
+        <v>1118</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
@@ -4788,13 +4803,13 @@
         <v>229</v>
       </c>
       <c r="C7" s="2" t="s">
+        <v>402</v>
+      </c>
+      <c r="D7" s="2" t="s">
         <v>403</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="E7" s="2" t="s">
         <v>404</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>405</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>296</v>
@@ -4803,7 +4818,7 @@
         <v>5</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="29" x14ac:dyDescent="0.35">
@@ -4814,22 +4829,22 @@
         <v>229</v>
       </c>
       <c r="C8" s="2" t="s">
+        <v>405</v>
+      </c>
+      <c r="D8" s="2" t="s">
         <v>406</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="E8" s="2" t="s">
         <v>407</v>
       </c>
-      <c r="E8" s="2" t="s">
+      <c r="F8" s="2" t="s">
         <v>408</v>
       </c>
-      <c r="F8" s="2" t="s">
-        <v>409</v>
-      </c>
       <c r="G8" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="H8" s="2" t="s">
-        <v>5</v>
+      <c r="H8" s="3" t="s">
+        <v>1118</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
@@ -4840,21 +4855,44 @@
         <v>229</v>
       </c>
       <c r="C9" s="2" t="s">
+        <v>409</v>
+      </c>
+      <c r="D9" s="2" t="s">
         <v>410</v>
       </c>
-      <c r="D9" s="2" t="s">
+      <c r="E9" s="2" t="s">
         <v>411</v>
       </c>
-      <c r="E9" s="2" t="s">
+      <c r="F9" s="2" t="s">
         <v>412</v>
       </c>
-      <c r="F9" s="2" t="s">
-        <v>413</v>
-      </c>
       <c r="G9" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="H9" s="2" t="s">
+      <c r="H9" s="3" t="s">
+        <v>1118</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A10" s="2">
+        <v>7</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>1154</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>1155</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>407</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>1156</v>
+      </c>
+      <c r="G10" s="2" t="s">
         <v>5</v>
       </c>
     </row>
@@ -4884,7 +4922,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A1" s="7" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B1" s="7"/>
       <c r="C1" s="7"/>
@@ -4928,16 +4966,16 @@
         <v>229</v>
       </c>
       <c r="C4" s="2" t="s">
+        <v>414</v>
+      </c>
+      <c r="D4" s="2" t="s">
         <v>415</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>416</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>159</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>5</v>
@@ -4954,16 +4992,16 @@
         <v>229</v>
       </c>
       <c r="C5" s="2" t="s">
+        <v>417</v>
+      </c>
+      <c r="D5" s="2" t="s">
         <v>418</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="E5" s="2" t="s">
         <v>419</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="F5" s="2" t="s">
         <v>420</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>421</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>5</v>
@@ -4980,16 +5018,16 @@
         <v>229</v>
       </c>
       <c r="C6" s="2" t="s">
+        <v>421</v>
+      </c>
+      <c r="D6" s="2" t="s">
         <v>422</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="E6" s="2" t="s">
         <v>423</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="F6" s="2" t="s">
         <v>424</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>425</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>5</v>
@@ -5006,16 +5044,16 @@
         <v>229</v>
       </c>
       <c r="C7" s="2" t="s">
+        <v>425</v>
+      </c>
+      <c r="D7" s="2" t="s">
         <v>426</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="E7" s="2" t="s">
         <v>427</v>
       </c>
-      <c r="E7" s="2" t="s">
+      <c r="F7" s="2" t="s">
         <v>428</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>429</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>5</v>
@@ -5032,16 +5070,16 @@
         <v>229</v>
       </c>
       <c r="C8" s="2" t="s">
+        <v>429</v>
+      </c>
+      <c r="D8" s="2" t="s">
         <v>430</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="E8" s="2" t="s">
         <v>431</v>
       </c>
-      <c r="E8" s="2" t="s">
+      <c r="F8" s="2" t="s">
         <v>432</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>433</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>5</v>
@@ -5058,16 +5096,16 @@
         <v>229</v>
       </c>
       <c r="C9" s="2" t="s">
+        <v>433</v>
+      </c>
+      <c r="D9" s="2" t="s">
         <v>434</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>435</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>159</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>5</v>
@@ -5084,16 +5122,16 @@
         <v>229</v>
       </c>
       <c r="C10" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="D10" s="2" t="s">
         <v>437</v>
       </c>
-      <c r="D10" s="2" t="s">
+      <c r="E10" s="2" t="s">
         <v>438</v>
       </c>
-      <c r="E10" s="2" t="s">
+      <c r="F10" s="2" t="s">
         <v>439</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>440</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>5</v>
@@ -5110,16 +5148,16 @@
         <v>229</v>
       </c>
       <c r="C11" s="2" t="s">
+        <v>440</v>
+      </c>
+      <c r="D11" s="2" t="s">
         <v>441</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>442</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>159</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>5</v>
@@ -5136,16 +5174,16 @@
         <v>229</v>
       </c>
       <c r="C12" s="2" t="s">
+        <v>443</v>
+      </c>
+      <c r="D12" s="2" t="s">
         <v>444</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>445</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>159</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>5</v>
@@ -5180,7 +5218,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A1" s="7" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="B1" s="7"/>
       <c r="C1" s="7"/>
@@ -5224,16 +5262,16 @@
         <v>229</v>
       </c>
       <c r="C4" s="2" t="s">
+        <v>447</v>
+      </c>
+      <c r="D4" s="2" t="s">
         <v>448</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="E4" s="2" t="s">
         <v>449</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="F4" s="2" t="s">
         <v>450</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>451</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>5</v>
@@ -5250,13 +5288,13 @@
         <v>229</v>
       </c>
       <c r="C5" s="2" t="s">
+        <v>451</v>
+      </c>
+      <c r="D5" s="2" t="s">
         <v>452</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="E5" s="2" t="s">
         <v>453</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>454</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>319</v>
@@ -5276,16 +5314,16 @@
         <v>229</v>
       </c>
       <c r="C6" s="2" t="s">
+        <v>454</v>
+      </c>
+      <c r="D6" s="2" t="s">
         <v>455</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="E6" s="2" t="s">
         <v>456</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="F6" s="2" t="s">
         <v>457</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>458</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>5</v>
@@ -5302,16 +5340,16 @@
         <v>229</v>
       </c>
       <c r="C7" s="2" t="s">
+        <v>458</v>
+      </c>
+      <c r="D7" s="2" t="s">
         <v>459</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="E7" s="2" t="s">
         <v>460</v>
       </c>
-      <c r="E7" s="2" t="s">
+      <c r="F7" s="2" t="s">
         <v>461</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>462</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>5</v>
@@ -5328,16 +5366,16 @@
         <v>229</v>
       </c>
       <c r="C8" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="D8" s="2" t="s">
         <v>463</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>464</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>159</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>5</v>
@@ -5354,7 +5392,7 @@
         <v>229</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>1151</v>
+        <v>1150</v>
       </c>
     </row>
   </sheetData>
@@ -5383,7 +5421,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A1" s="7" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="B1" s="7"/>
       <c r="C1" s="7"/>
@@ -5427,16 +5465,16 @@
         <v>229</v>
       </c>
       <c r="C4" s="2" t="s">
+        <v>466</v>
+      </c>
+      <c r="D4" s="2" t="s">
         <v>467</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>468</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>159</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>5</v>
@@ -5453,16 +5491,16 @@
         <v>229</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>397</v>
       </c>
       <c r="E5" s="2" t="s">
+        <v>470</v>
+      </c>
+      <c r="F5" s="2" t="s">
         <v>471</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>472</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>5</v>
@@ -5479,13 +5517,13 @@
         <v>229</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>290</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>246</v>
@@ -5505,13 +5543,13 @@
         <v>229</v>
       </c>
       <c r="C7" s="2" t="s">
+        <v>474</v>
+      </c>
+      <c r="D7" s="2" t="s">
         <v>475</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="E7" s="2" t="s">
         <v>476</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>477</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>296</v>
@@ -5531,16 +5569,16 @@
         <v>229</v>
       </c>
       <c r="C8" s="2" t="s">
+        <v>477</v>
+      </c>
+      <c r="D8" s="2" t="s">
         <v>478</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="E8" s="2" t="s">
         <v>479</v>
       </c>
-      <c r="E8" s="2" t="s">
+      <c r="F8" s="2" t="s">
         <v>480</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>481</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>5</v>
@@ -5557,16 +5595,16 @@
         <v>229</v>
       </c>
       <c r="C9" s="2" t="s">
+        <v>481</v>
+      </c>
+      <c r="D9" s="2" t="s">
         <v>482</v>
       </c>
-      <c r="D9" s="2" t="s">
+      <c r="E9" s="2" t="s">
         <v>483</v>
       </c>
-      <c r="E9" s="2" t="s">
+      <c r="F9" s="2" t="s">
         <v>484</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>485</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>5</v>
@@ -5601,7 +5639,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A1" s="7" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="B1" s="7"/>
       <c r="C1" s="7"/>
@@ -5645,16 +5683,16 @@
         <v>229</v>
       </c>
       <c r="C4" s="2" t="s">
+        <v>486</v>
+      </c>
+      <c r="D4" s="2" t="s">
         <v>487</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="E4" s="2" t="s">
         <v>488</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="F4" s="2" t="s">
         <v>489</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>490</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>5</v>
@@ -5671,16 +5709,16 @@
         <v>229</v>
       </c>
       <c r="C5" s="2" t="s">
+        <v>490</v>
+      </c>
+      <c r="D5" s="2" t="s">
         <v>491</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>492</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>159</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>5</v>
@@ -5697,16 +5735,16 @@
         <v>229</v>
       </c>
       <c r="C6" s="2" t="s">
+        <v>493</v>
+      </c>
+      <c r="D6" s="2" t="s">
         <v>494</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="E6" s="2" t="s">
         <v>495</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="F6" s="2" t="s">
         <v>496</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>497</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>5</v>
@@ -5723,16 +5761,16 @@
         <v>229</v>
       </c>
       <c r="C7" s="2" t="s">
+        <v>497</v>
+      </c>
+      <c r="D7" s="2" t="s">
         <v>498</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="E7" s="2" t="s">
+        <v>431</v>
+      </c>
+      <c r="F7" s="2" t="s">
         <v>499</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>432</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>500</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>5</v>
@@ -5749,16 +5787,16 @@
         <v>229</v>
       </c>
       <c r="C8" s="2" t="s">
+        <v>500</v>
+      </c>
+      <c r="D8" s="2" t="s">
         <v>501</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>502</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>159</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>5</v>
@@ -5775,16 +5813,16 @@
         <v>229</v>
       </c>
       <c r="C9" s="2" t="s">
+        <v>503</v>
+      </c>
+      <c r="D9" s="2" t="s">
         <v>504</v>
       </c>
-      <c r="D9" s="2" t="s">
+      <c r="E9" s="2" t="s">
         <v>505</v>
       </c>
-      <c r="E9" s="2" t="s">
+      <c r="F9" s="2" t="s">
         <v>506</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>507</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>5</v>
@@ -5819,7 +5857,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A1" s="7" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B1" s="7"/>
       <c r="C1" s="7"/>
@@ -5863,16 +5901,16 @@
         <v>229</v>
       </c>
       <c r="C4" s="2" t="s">
+        <v>508</v>
+      </c>
+      <c r="D4" s="2" t="s">
         <v>509</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>510</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>159</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>5</v>
@@ -5889,16 +5927,16 @@
         <v>229</v>
       </c>
       <c r="C5" s="2" t="s">
+        <v>511</v>
+      </c>
+      <c r="D5" s="2" t="s">
         <v>512</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="E5" s="2" t="s">
         <v>513</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="F5" s="2" t="s">
         <v>514</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>515</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>5</v>
@@ -5915,16 +5953,16 @@
         <v>229</v>
       </c>
       <c r="C6" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="D6" s="2" t="s">
         <v>516</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="E6" s="2" t="s">
         <v>517</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="F6" s="2" t="s">
         <v>518</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>519</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>5</v>
@@ -5941,13 +5979,13 @@
         <v>229</v>
       </c>
       <c r="C7" s="2" t="s">
+        <v>519</v>
+      </c>
+      <c r="D7" s="2" t="s">
         <v>520</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="E7" s="2" t="s">
         <v>521</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>522</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>296</v>
@@ -5967,16 +6005,16 @@
         <v>229</v>
       </c>
       <c r="C8" s="2" t="s">
+        <v>522</v>
+      </c>
+      <c r="D8" s="2" t="s">
         <v>523</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>524</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>159</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>5</v>
@@ -5993,16 +6031,16 @@
         <v>229</v>
       </c>
       <c r="C9" s="2" t="s">
+        <v>525</v>
+      </c>
+      <c r="D9" s="2" t="s">
         <v>526</v>
       </c>
-      <c r="D9" s="2" t="s">
+      <c r="E9" s="2" t="s">
         <v>527</v>
       </c>
-      <c r="E9" s="2" t="s">
+      <c r="F9" s="2" t="s">
         <v>528</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>529</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>5</v>
@@ -6037,7 +6075,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A1" s="7" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="B1" s="7"/>
       <c r="C1" s="7"/>
@@ -6081,16 +6119,16 @@
         <v>128</v>
       </c>
       <c r="C4" s="2" t="s">
+        <v>530</v>
+      </c>
+      <c r="D4" s="2" t="s">
         <v>531</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="E4" s="2" t="s">
         <v>532</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="F4" s="2" t="s">
         <v>533</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>534</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>5</v>
@@ -6107,16 +6145,16 @@
         <v>128</v>
       </c>
       <c r="C5" s="2" t="s">
+        <v>534</v>
+      </c>
+      <c r="D5" s="2" t="s">
         <v>535</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>536</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>159</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>5</v>
@@ -6133,16 +6171,16 @@
         <v>128</v>
       </c>
       <c r="C6" s="2" t="s">
+        <v>537</v>
+      </c>
+      <c r="D6" s="2" t="s">
         <v>538</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="E6" s="2" t="s">
         <v>539</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="F6" s="2" t="s">
         <v>540</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>541</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>5</v>
@@ -6159,16 +6197,16 @@
         <v>128</v>
       </c>
       <c r="C7" s="2" t="s">
+        <v>541</v>
+      </c>
+      <c r="D7" s="2" t="s">
         <v>542</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="E7" s="2" t="s">
         <v>543</v>
       </c>
-      <c r="E7" s="2" t="s">
+      <c r="F7" s="2" t="s">
         <v>544</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>545</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>5</v>
@@ -6185,16 +6223,16 @@
         <v>128</v>
       </c>
       <c r="C8" s="2" t="s">
+        <v>545</v>
+      </c>
+      <c r="D8" s="2" t="s">
         <v>546</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="E8" s="2" t="s">
         <v>547</v>
       </c>
-      <c r="E8" s="2" t="s">
+      <c r="F8" s="2" t="s">
         <v>548</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>549</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>5</v>
@@ -6211,16 +6249,16 @@
         <v>229</v>
       </c>
       <c r="C9" s="2" t="s">
+        <v>549</v>
+      </c>
+      <c r="D9" s="2" t="s">
         <v>550</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>551</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>159</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>5</v>
@@ -6237,16 +6275,16 @@
         <v>229</v>
       </c>
       <c r="C10" s="2" t="s">
+        <v>552</v>
+      </c>
+      <c r="D10" s="2" t="s">
         <v>553</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>554</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>159</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>5</v>
@@ -6281,7 +6319,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A1" s="7" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="B1" s="7"/>
       <c r="C1" s="7"/>
@@ -6322,19 +6360,19 @@
         <v>1</v>
       </c>
       <c r="B4" s="2" t="s">
+        <v>556</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>557</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="D4" s="2" t="s">
         <v>558</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="E4" s="2" t="s">
         <v>559</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="F4" s="2" t="s">
         <v>560</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>561</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>5</v>
@@ -6351,13 +6389,13 @@
         <v>132</v>
       </c>
       <c r="C5" s="2" t="s">
+        <v>561</v>
+      </c>
+      <c r="D5" s="2" t="s">
         <v>562</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="E5" s="2" t="s">
         <v>563</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>564</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>319</v>
@@ -6377,16 +6415,16 @@
         <v>229</v>
       </c>
       <c r="C6" s="2" t="s">
+        <v>564</v>
+      </c>
+      <c r="D6" s="2" t="s">
         <v>565</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="E6" s="2" t="s">
         <v>566</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="F6" s="2" t="s">
         <v>567</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>568</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>5</v>
@@ -6403,16 +6441,16 @@
         <v>229</v>
       </c>
       <c r="C7" s="2" t="s">
+        <v>568</v>
+      </c>
+      <c r="D7" s="2" t="s">
         <v>569</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>570</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>159</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>5</v>
@@ -6429,16 +6467,16 @@
         <v>229</v>
       </c>
       <c r="C8" s="2" t="s">
+        <v>571</v>
+      </c>
+      <c r="D8" s="2" t="s">
         <v>572</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="E8" s="2" t="s">
         <v>573</v>
       </c>
-      <c r="E8" s="2" t="s">
+      <c r="F8" s="2" t="s">
         <v>574</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>575</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>5</v>
@@ -6473,7 +6511,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A1" s="7" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="B1" s="7"/>
       <c r="C1" s="7"/>
@@ -6517,16 +6555,16 @@
         <v>128</v>
       </c>
       <c r="C4" s="2" t="s">
+        <v>576</v>
+      </c>
+      <c r="D4" s="2" t="s">
         <v>577</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="E4" s="2" t="s">
         <v>578</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="F4" s="2" t="s">
         <v>579</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>580</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>5</v>
@@ -6543,16 +6581,16 @@
         <v>128</v>
       </c>
       <c r="C5" s="2" t="s">
+        <v>580</v>
+      </c>
+      <c r="D5" s="2" t="s">
         <v>581</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="E5" s="2" t="s">
         <v>582</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="F5" s="2" t="s">
         <v>583</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>584</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>5</v>
@@ -6569,16 +6607,16 @@
         <v>128</v>
       </c>
       <c r="C6" s="2" t="s">
+        <v>584</v>
+      </c>
+      <c r="D6" s="2" t="s">
         <v>585</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="E6" s="2" t="s">
         <v>586</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="F6" s="2" t="s">
         <v>587</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>588</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>5</v>
@@ -6595,16 +6633,16 @@
         <v>128</v>
       </c>
       <c r="C7" s="2" t="s">
+        <v>588</v>
+      </c>
+      <c r="D7" s="2" t="s">
         <v>589</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="E7" s="2" t="s">
         <v>590</v>
       </c>
-      <c r="E7" s="2" t="s">
+      <c r="F7" s="2" t="s">
         <v>591</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>592</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>5</v>
@@ -6621,16 +6659,16 @@
         <v>128</v>
       </c>
       <c r="C8" s="2" t="s">
+        <v>592</v>
+      </c>
+      <c r="D8" s="2" t="s">
         <v>593</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="E8" s="2" t="s">
         <v>594</v>
       </c>
-      <c r="E8" s="2" t="s">
+      <c r="F8" s="2" t="s">
         <v>595</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>596</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>5</v>
@@ -6647,16 +6685,16 @@
         <v>128</v>
       </c>
       <c r="C9" s="2" t="s">
+        <v>596</v>
+      </c>
+      <c r="D9" s="2" t="s">
         <v>597</v>
       </c>
-      <c r="D9" s="2" t="s">
+      <c r="E9" s="2" t="s">
         <v>598</v>
       </c>
-      <c r="E9" s="2" t="s">
+      <c r="F9" s="2" t="s">
         <v>599</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>600</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>5</v>
@@ -6673,16 +6711,16 @@
         <v>128</v>
       </c>
       <c r="C10" s="2" t="s">
+        <v>600</v>
+      </c>
+      <c r="D10" s="2" t="s">
         <v>601</v>
       </c>
-      <c r="D10" s="2" t="s">
-        <v>602</v>
-      </c>
       <c r="E10" s="2" t="s">
+        <v>423</v>
+      </c>
+      <c r="F10" s="2" t="s">
         <v>424</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>425</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>5</v>
@@ -6699,13 +6737,13 @@
         <v>128</v>
       </c>
       <c r="C11" s="2" t="s">
+        <v>602</v>
+      </c>
+      <c r="D11" s="2" t="s">
         <v>603</v>
       </c>
-      <c r="D11" s="2" t="s">
+      <c r="E11" s="2" t="s">
         <v>604</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>605</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>368</v>
@@ -6725,16 +6763,16 @@
         <v>128</v>
       </c>
       <c r="C12" s="2" t="s">
+        <v>605</v>
+      </c>
+      <c r="D12" s="2" t="s">
         <v>606</v>
       </c>
-      <c r="D12" s="2" t="s">
+      <c r="E12" s="2" t="s">
         <v>607</v>
       </c>
-      <c r="E12" s="2" t="s">
+      <c r="F12" s="2" t="s">
         <v>608</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>609</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>5</v>
@@ -6751,16 +6789,16 @@
         <v>128</v>
       </c>
       <c r="C13" s="2" t="s">
+        <v>609</v>
+      </c>
+      <c r="D13" s="2" t="s">
         <v>610</v>
       </c>
-      <c r="D13" s="2" t="s">
+      <c r="E13" s="2" t="s">
         <v>611</v>
       </c>
-      <c r="E13" s="2" t="s">
+      <c r="F13" s="2" t="s">
         <v>612</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>613</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>5</v>
@@ -6777,16 +6815,16 @@
         <v>128</v>
       </c>
       <c r="C14" s="2" t="s">
+        <v>613</v>
+      </c>
+      <c r="D14" s="2" t="s">
         <v>614</v>
       </c>
-      <c r="D14" s="2" t="s">
+      <c r="E14" s="2" t="s">
         <v>615</v>
       </c>
-      <c r="E14" s="2" t="s">
+      <c r="F14" s="2" t="s">
         <v>616</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>617</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>5</v>
@@ -6803,16 +6841,16 @@
         <v>229</v>
       </c>
       <c r="C15" s="2" t="s">
+        <v>617</v>
+      </c>
+      <c r="D15" s="2" t="s">
         <v>618</v>
       </c>
-      <c r="D15" s="2" t="s">
+      <c r="E15" s="2" t="s">
         <v>619</v>
       </c>
-      <c r="E15" s="2" t="s">
+      <c r="F15" s="2" t="s">
         <v>620</v>
-      </c>
-      <c r="F15" s="2" t="s">
-        <v>621</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>5</v>
@@ -6829,16 +6867,16 @@
         <v>128</v>
       </c>
       <c r="C16" s="2" t="s">
+        <v>621</v>
+      </c>
+      <c r="D16" s="2" t="s">
         <v>622</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>623</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>159</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>5</v>
@@ -6855,16 +6893,16 @@
         <v>229</v>
       </c>
       <c r="C17" s="2" t="s">
+        <v>624</v>
+      </c>
+      <c r="D17" s="2" t="s">
         <v>625</v>
       </c>
-      <c r="D17" s="2" t="s">
+      <c r="E17" s="2" t="s">
+        <v>573</v>
+      </c>
+      <c r="F17" s="2" t="s">
         <v>626</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>574</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>627</v>
       </c>
       <c r="G17" s="2" t="s">
         <v>5</v>
@@ -6899,7 +6937,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A1" s="7" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="B1" s="7"/>
       <c r="C1" s="7"/>
@@ -6943,16 +6981,16 @@
         <v>229</v>
       </c>
       <c r="C4" s="2" t="s">
+        <v>628</v>
+      </c>
+      <c r="D4" s="2" t="s">
         <v>629</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>630</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>159</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>5</v>
@@ -6969,16 +7007,16 @@
         <v>229</v>
       </c>
       <c r="C5" s="2" t="s">
+        <v>631</v>
+      </c>
+      <c r="D5" s="2" t="s">
         <v>632</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="E5" s="2" t="s">
         <v>633</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="F5" s="2" t="s">
         <v>634</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>635</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>5</v>
@@ -6995,16 +7033,16 @@
         <v>229</v>
       </c>
       <c r="C6" s="2" t="s">
+        <v>635</v>
+      </c>
+      <c r="D6" s="2" t="s">
         <v>636</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>637</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>159</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>5</v>
@@ -7021,16 +7059,16 @@
         <v>229</v>
       </c>
       <c r="C7" s="2" t="s">
+        <v>638</v>
+      </c>
+      <c r="D7" s="2" t="s">
         <v>639</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>640</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>159</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>5</v>
@@ -7047,16 +7085,16 @@
         <v>229</v>
       </c>
       <c r="C8" s="2" t="s">
+        <v>641</v>
+      </c>
+      <c r="D8" s="2" t="s">
         <v>642</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>643</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>159</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>5</v>
@@ -7073,16 +7111,16 @@
         <v>128</v>
       </c>
       <c r="C9" s="2" t="s">
+        <v>644</v>
+      </c>
+      <c r="D9" s="2" t="s">
         <v>645</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>646</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>159</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>5</v>
@@ -7176,7 +7214,7 @@
         <v>5</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="29" x14ac:dyDescent="0.35">
@@ -7202,7 +7240,7 @@
         <v>5</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="29" x14ac:dyDescent="0.35">
@@ -7228,7 +7266,7 @@
         <v>5</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="29" x14ac:dyDescent="0.35">
@@ -7254,7 +7292,7 @@
         <v>5</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="29" x14ac:dyDescent="0.35">
@@ -7280,7 +7318,7 @@
         <v>5</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="29" x14ac:dyDescent="0.35">
@@ -7306,7 +7344,7 @@
         <v>5</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="29" x14ac:dyDescent="0.35">
@@ -7332,7 +7370,7 @@
         <v>5</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
@@ -7358,7 +7396,7 @@
         <v>5</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
@@ -7410,7 +7448,7 @@
         <v>5</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
@@ -7465,7 +7503,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A1" s="7" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="B1" s="7"/>
       <c r="C1" s="7"/>
@@ -7509,16 +7547,16 @@
         <v>229</v>
       </c>
       <c r="C4" s="2" t="s">
+        <v>648</v>
+      </c>
+      <c r="D4" s="2" t="s">
         <v>649</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="E4" s="2" t="s">
         <v>650</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="F4" s="2" t="s">
         <v>651</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>652</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>5</v>
@@ -7535,16 +7573,16 @@
         <v>229</v>
       </c>
       <c r="C5" s="2" t="s">
+        <v>652</v>
+      </c>
+      <c r="D5" s="2" t="s">
         <v>653</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>654</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>159</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>5</v>
@@ -7561,16 +7599,16 @@
         <v>229</v>
       </c>
       <c r="C6" s="2" t="s">
+        <v>655</v>
+      </c>
+      <c r="D6" s="2" t="s">
         <v>656</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>657</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>159</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>5</v>
@@ -7587,16 +7625,16 @@
         <v>229</v>
       </c>
       <c r="C7" s="2" t="s">
+        <v>658</v>
+      </c>
+      <c r="D7" s="2" t="s">
         <v>659</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="E7" s="2" t="s">
         <v>660</v>
       </c>
-      <c r="E7" s="2" t="s">
+      <c r="F7" s="2" t="s">
         <v>661</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>662</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>5</v>
@@ -7613,16 +7651,16 @@
         <v>229</v>
       </c>
       <c r="C8" s="2" t="s">
+        <v>662</v>
+      </c>
+      <c r="D8" s="2" t="s">
         <v>663</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>664</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>159</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>5</v>
@@ -7639,16 +7677,16 @@
         <v>229</v>
       </c>
       <c r="C9" s="2" t="s">
+        <v>665</v>
+      </c>
+      <c r="D9" s="2" t="s">
         <v>666</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>667</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>159</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>5</v>
@@ -7665,16 +7703,16 @@
         <v>229</v>
       </c>
       <c r="C10" s="2" t="s">
+        <v>668</v>
+      </c>
+      <c r="D10" s="2" t="s">
         <v>669</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>670</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>159</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>5</v>
@@ -7691,16 +7729,16 @@
         <v>229</v>
       </c>
       <c r="C11" s="2" t="s">
+        <v>671</v>
+      </c>
+      <c r="D11" s="2" t="s">
         <v>672</v>
       </c>
-      <c r="D11" s="2" t="s">
+      <c r="E11" s="2" t="s">
         <v>673</v>
       </c>
-      <c r="E11" s="2" t="s">
+      <c r="F11" s="2" t="s">
         <v>674</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>675</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>5</v>
@@ -7717,16 +7755,16 @@
         <v>229</v>
       </c>
       <c r="C12" s="2" t="s">
+        <v>675</v>
+      </c>
+      <c r="D12" s="2" t="s">
         <v>676</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>677</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>159</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>5</v>
@@ -7743,16 +7781,16 @@
         <v>128</v>
       </c>
       <c r="C13" s="2" t="s">
+        <v>677</v>
+      </c>
+      <c r="D13" s="2" t="s">
         <v>678</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>679</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>159</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>5</v>
@@ -7787,7 +7825,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A1" s="7" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="B1" s="7"/>
       <c r="C1" s="7"/>
@@ -7831,16 +7869,16 @@
         <v>229</v>
       </c>
       <c r="C4" s="2" t="s">
+        <v>681</v>
+      </c>
+      <c r="D4" s="2" t="s">
         <v>682</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>683</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>159</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>5</v>
@@ -7857,16 +7895,16 @@
         <v>229</v>
       </c>
       <c r="C5" s="2" t="s">
+        <v>684</v>
+      </c>
+      <c r="D5" s="2" t="s">
         <v>685</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>686</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>159</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>5</v>
@@ -7883,16 +7921,16 @@
         <v>229</v>
       </c>
       <c r="C6" s="2" t="s">
+        <v>687</v>
+      </c>
+      <c r="D6" s="2" t="s">
         <v>688</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>689</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>159</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>5</v>
@@ -7909,16 +7947,16 @@
         <v>229</v>
       </c>
       <c r="C7" s="2" t="s">
+        <v>690</v>
+      </c>
+      <c r="D7" s="2" t="s">
         <v>691</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>692</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>159</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>5</v>
@@ -7935,16 +7973,16 @@
         <v>128</v>
       </c>
       <c r="C8" s="2" t="s">
+        <v>693</v>
+      </c>
+      <c r="D8" s="2" t="s">
         <v>694</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>695</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>159</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>5</v>
@@ -7979,7 +8017,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A1" s="7" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="B1" s="7"/>
       <c r="C1" s="7"/>
@@ -8023,16 +8061,16 @@
         <v>132</v>
       </c>
       <c r="C4" s="2" t="s">
+        <v>697</v>
+      </c>
+      <c r="D4" s="2" t="s">
         <v>698</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>699</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>159</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>5</v>
@@ -8049,16 +8087,16 @@
         <v>229</v>
       </c>
       <c r="C5" s="2" t="s">
+        <v>700</v>
+      </c>
+      <c r="D5" s="2" t="s">
         <v>701</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="E5" s="2" t="s">
         <v>702</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="F5" s="2" t="s">
         <v>703</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>704</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>5</v>
@@ -8075,16 +8113,16 @@
         <v>124</v>
       </c>
       <c r="C6" s="2" t="s">
+        <v>704</v>
+      </c>
+      <c r="D6" s="2" t="s">
         <v>705</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>706</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>159</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>5</v>
@@ -8101,16 +8139,16 @@
         <v>119</v>
       </c>
       <c r="C7" s="2" t="s">
+        <v>707</v>
+      </c>
+      <c r="D7" s="2" t="s">
         <v>708</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>709</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>159</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>5</v>
@@ -8127,16 +8165,16 @@
         <v>229</v>
       </c>
       <c r="C8" s="2" t="s">
+        <v>710</v>
+      </c>
+      <c r="D8" s="2" t="s">
         <v>711</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="E8" s="2" t="s">
         <v>712</v>
       </c>
-      <c r="E8" s="2" t="s">
+      <c r="F8" s="2" t="s">
         <v>713</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>714</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>5</v>
@@ -8153,16 +8191,16 @@
         <v>229</v>
       </c>
       <c r="C9" s="2" t="s">
+        <v>714</v>
+      </c>
+      <c r="D9" s="2" t="s">
         <v>715</v>
       </c>
-      <c r="D9" s="2" t="s">
+      <c r="E9" s="2" t="s">
         <v>716</v>
       </c>
-      <c r="E9" s="2" t="s">
+      <c r="F9" s="2" t="s">
         <v>717</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>718</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>5</v>
@@ -8179,16 +8217,16 @@
         <v>128</v>
       </c>
       <c r="C10" s="2" t="s">
+        <v>718</v>
+      </c>
+      <c r="D10" s="2" t="s">
         <v>719</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>720</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>159</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>5</v>
@@ -8223,7 +8261,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A1" s="7" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="B1" s="7"/>
       <c r="C1" s="7"/>
@@ -8267,16 +8305,16 @@
         <v>229</v>
       </c>
       <c r="C4" s="2" t="s">
+        <v>722</v>
+      </c>
+      <c r="D4" s="2" t="s">
         <v>723</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>724</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>159</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>5</v>
@@ -8293,16 +8331,16 @@
         <v>229</v>
       </c>
       <c r="C5" s="2" t="s">
+        <v>725</v>
+      </c>
+      <c r="D5" s="2" t="s">
         <v>726</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>727</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>159</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>5</v>
@@ -8319,16 +8357,16 @@
         <v>229</v>
       </c>
       <c r="C6" s="2" t="s">
+        <v>728</v>
+      </c>
+      <c r="D6" s="2" t="s">
         <v>729</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>730</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>159</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>5</v>
@@ -8345,16 +8383,16 @@
         <v>124</v>
       </c>
       <c r="C7" s="2" t="s">
+        <v>731</v>
+      </c>
+      <c r="D7" s="2" t="s">
         <v>732</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="E7" s="2" t="s">
         <v>733</v>
       </c>
-      <c r="E7" s="2" t="s">
+      <c r="F7" s="2" t="s">
         <v>734</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>735</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>5</v>
@@ -8371,16 +8409,16 @@
         <v>119</v>
       </c>
       <c r="C8" s="2" t="s">
+        <v>735</v>
+      </c>
+      <c r="D8" s="2" t="s">
         <v>736</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>737</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>159</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>5</v>
@@ -8415,7 +8453,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A1" s="7" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="B1" s="7"/>
       <c r="C1" s="7"/>
@@ -8459,16 +8497,16 @@
         <v>229</v>
       </c>
       <c r="C4" s="2" t="s">
+        <v>739</v>
+      </c>
+      <c r="D4" s="2" t="s">
         <v>740</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>741</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>159</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>5</v>
@@ -8485,16 +8523,16 @@
         <v>229</v>
       </c>
       <c r="C5" s="2" t="s">
+        <v>742</v>
+      </c>
+      <c r="D5" s="2" t="s">
         <v>743</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>744</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>159</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>5</v>
@@ -8511,16 +8549,16 @@
         <v>229</v>
       </c>
       <c r="C6" s="2" t="s">
+        <v>745</v>
+      </c>
+      <c r="D6" s="2" t="s">
         <v>746</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="E6" s="2" t="s">
         <v>747</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="F6" s="2" t="s">
         <v>748</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>749</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>5</v>
@@ -8537,16 +8575,16 @@
         <v>229</v>
       </c>
       <c r="C7" s="2" t="s">
+        <v>749</v>
+      </c>
+      <c r="D7" s="2" t="s">
         <v>750</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="E7" s="2" t="s">
         <v>751</v>
       </c>
-      <c r="E7" s="2" t="s">
+      <c r="F7" s="2" t="s">
         <v>752</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>753</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>5</v>
@@ -8563,16 +8601,16 @@
         <v>229</v>
       </c>
       <c r="C8" s="2" t="s">
+        <v>753</v>
+      </c>
+      <c r="D8" s="2" t="s">
         <v>754</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>755</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>159</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>5</v>
@@ -8589,16 +8627,16 @@
         <v>229</v>
       </c>
       <c r="C9" s="2" t="s">
+        <v>756</v>
+      </c>
+      <c r="D9" s="2" t="s">
         <v>757</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>758</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>159</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>5</v>
@@ -8612,19 +8650,19 @@
         <v>7</v>
       </c>
       <c r="B10" s="2" t="s">
+        <v>759</v>
+      </c>
+      <c r="C10" s="2" t="s">
         <v>760</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="D10" s="2" t="s">
         <v>761</v>
       </c>
-      <c r="D10" s="2" t="s">
+      <c r="E10" s="2" t="s">
         <v>762</v>
       </c>
-      <c r="E10" s="2" t="s">
+      <c r="F10" s="2" t="s">
         <v>763</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>764</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>5</v>
@@ -8659,7 +8697,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A1" s="7" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="B1" s="7"/>
       <c r="C1" s="7"/>
@@ -8700,19 +8738,19 @@
         <v>1</v>
       </c>
       <c r="B4" s="2" t="s">
+        <v>765</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>766</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="D4" s="2" t="s">
         <v>767</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>768</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>159</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>5</v>
@@ -8729,16 +8767,16 @@
         <v>229</v>
       </c>
       <c r="C5" s="2" t="s">
+        <v>769</v>
+      </c>
+      <c r="D5" s="2" t="s">
         <v>770</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>771</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>159</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>5</v>
@@ -8755,16 +8793,16 @@
         <v>229</v>
       </c>
       <c r="C6" s="2" t="s">
+        <v>772</v>
+      </c>
+      <c r="D6" s="2" t="s">
         <v>773</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="E6" s="2" t="s">
         <v>774</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="F6" s="2" t="s">
         <v>775</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>776</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>5</v>
@@ -8781,16 +8819,16 @@
         <v>128</v>
       </c>
       <c r="C7" s="2" t="s">
+        <v>776</v>
+      </c>
+      <c r="D7" s="2" t="s">
         <v>777</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>778</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>159</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>5</v>
@@ -8825,7 +8863,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A1" s="7" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="B1" s="7"/>
       <c r="C1" s="7"/>
@@ -8869,16 +8907,16 @@
         <v>128</v>
       </c>
       <c r="C4" s="2" t="s">
+        <v>780</v>
+      </c>
+      <c r="D4" s="2" t="s">
         <v>781</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>782</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>159</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>5</v>
@@ -8895,16 +8933,16 @@
         <v>128</v>
       </c>
       <c r="C5" s="2" t="s">
+        <v>783</v>
+      </c>
+      <c r="D5" s="2" t="s">
         <v>784</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>785</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>159</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>5</v>
@@ -8921,16 +8959,16 @@
         <v>128</v>
       </c>
       <c r="C6" s="2" t="s">
+        <v>785</v>
+      </c>
+      <c r="D6" s="2" t="s">
         <v>786</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>787</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>159</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>5</v>
@@ -8947,16 +8985,16 @@
         <v>128</v>
       </c>
       <c r="C7" s="2" t="s">
+        <v>787</v>
+      </c>
+      <c r="D7" s="2" t="s">
         <v>788</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>789</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>159</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>5</v>
@@ -8973,16 +9011,16 @@
         <v>128</v>
       </c>
       <c r="C8" s="2" t="s">
+        <v>789</v>
+      </c>
+      <c r="D8" s="2" t="s">
         <v>790</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>791</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>159</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>5</v>
@@ -8999,16 +9037,16 @@
         <v>128</v>
       </c>
       <c r="C9" s="2" t="s">
+        <v>792</v>
+      </c>
+      <c r="D9" s="2" t="s">
         <v>793</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>794</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>159</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>5</v>
@@ -9025,16 +9063,16 @@
         <v>124</v>
       </c>
       <c r="C10" s="2" t="s">
+        <v>795</v>
+      </c>
+      <c r="D10" s="2" t="s">
         <v>796</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>797</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>159</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>5</v>
@@ -9051,16 +9089,16 @@
         <v>132</v>
       </c>
       <c r="C11" s="2" t="s">
+        <v>798</v>
+      </c>
+      <c r="D11" s="2" t="s">
         <v>799</v>
       </c>
-      <c r="D11" s="2" t="s">
+      <c r="E11" s="2" t="s">
         <v>800</v>
       </c>
-      <c r="E11" s="2" t="s">
+      <c r="F11" s="2" t="s">
         <v>801</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>802</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>5</v>
@@ -9077,16 +9115,16 @@
         <v>132</v>
       </c>
       <c r="C12" s="2" t="s">
+        <v>802</v>
+      </c>
+      <c r="D12" s="2" t="s">
         <v>803</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>804</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>159</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>5</v>
@@ -9103,16 +9141,16 @@
         <v>132</v>
       </c>
       <c r="C13" s="2" t="s">
+        <v>805</v>
+      </c>
+      <c r="D13" s="2" t="s">
         <v>806</v>
       </c>
-      <c r="D13" s="2" t="s">
+      <c r="E13" s="2" t="s">
         <v>807</v>
       </c>
-      <c r="E13" s="2" t="s">
+      <c r="F13" s="2" t="s">
         <v>808</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>809</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>5</v>
@@ -9144,7 +9182,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A1" s="10" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="B1" s="10"/>
       <c r="C1" s="10"/>
@@ -9154,22 +9192,22 @@
     </row>
     <row r="3" spans="1:6" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
+        <v>810</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>811</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="C3" s="1" t="s">
         <v>812</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="D3" s="1" t="s">
         <v>813</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="E3" s="1" t="s">
         <v>814</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="F3" s="1" t="s">
         <v>815</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>816</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="29" x14ac:dyDescent="0.35">
@@ -9177,19 +9215,19 @@
         <v>119</v>
       </c>
       <c r="B4" s="2" t="s">
+        <v>816</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>817</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="D4" s="2" t="s">
         <v>818</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="E4" s="2" t="s">
         <v>819</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="F4" s="2" t="s">
         <v>820</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>821</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.35">
@@ -9197,19 +9235,19 @@
         <v>124</v>
       </c>
       <c r="B5" s="2" t="s">
+        <v>821</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>822</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="D5" s="2" t="s">
         <v>823</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="E5" s="2" t="s">
+        <v>819</v>
+      </c>
+      <c r="F5" s="2" t="s">
         <v>824</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>820</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>825</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="29" x14ac:dyDescent="0.35">
@@ -9217,19 +9255,19 @@
         <v>128</v>
       </c>
       <c r="B6" s="2" t="s">
+        <v>825</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>826</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="D6" s="2" t="s">
         <v>827</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="E6" s="2" t="s">
+        <v>819</v>
+      </c>
+      <c r="F6" s="2" t="s">
         <v>828</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>820</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>829</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.35">
@@ -9237,59 +9275,59 @@
         <v>128</v>
       </c>
       <c r="B7" s="2" t="s">
+        <v>829</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>826</v>
+      </c>
+      <c r="D7" s="2" t="s">
         <v>830</v>
       </c>
-      <c r="C7" s="2" t="s">
-        <v>827</v>
-      </c>
-      <c r="D7" s="2" t="s">
+      <c r="E7" s="2" t="s">
+        <v>819</v>
+      </c>
+      <c r="F7" s="2" t="s">
         <v>831</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>820</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>832</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
+        <v>832</v>
+      </c>
+      <c r="B8" s="2" t="s">
         <v>833</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="C8" s="2" t="s">
+        <v>826</v>
+      </c>
+      <c r="D8" s="2" t="s">
         <v>834</v>
       </c>
-      <c r="C8" s="2" t="s">
-        <v>827</v>
-      </c>
-      <c r="D8" s="2" t="s">
+      <c r="E8" s="2" t="s">
         <v>835</v>
       </c>
-      <c r="E8" s="2" t="s">
+      <c r="F8" s="2" t="s">
         <v>836</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>837</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A9" s="2" t="s">
+        <v>837</v>
+      </c>
+      <c r="B9" s="2" t="s">
         <v>838</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="C9" s="2" t="s">
         <v>839</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="D9" s="2" t="s">
         <v>840</v>
       </c>
-      <c r="D9" s="2" t="s">
+      <c r="E9" s="2" t="s">
+        <v>819</v>
+      </c>
+      <c r="F9" s="2" t="s">
         <v>841</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>820</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>842</v>
       </c>
     </row>
   </sheetData>
@@ -9315,7 +9353,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A1" s="10" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="B1" s="10"/>
       <c r="C1" s="10"/>
@@ -9325,142 +9363,142 @@
     </row>
     <row r="3" spans="1:6" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
+        <v>843</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>844</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="C3" s="1" t="s">
         <v>845</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="D3" s="1" t="s">
         <v>846</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="E3" s="1" t="s">
         <v>847</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="F3" s="1" t="s">
         <v>848</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>849</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
+        <v>816</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>817</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="C4" s="2" t="s">
         <v>818</v>
       </c>
-      <c r="C4" s="2" t="s">
-        <v>819</v>
-      </c>
       <c r="D4" s="2" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="E4" s="2" t="s">
+        <v>849</v>
+      </c>
+      <c r="F4" s="2" t="s">
         <v>850</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>851</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
+        <v>821</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>822</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="C5" s="2" t="s">
         <v>823</v>
       </c>
-      <c r="C5" s="2" t="s">
-        <v>824</v>
-      </c>
       <c r="D5" s="2" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="E5" s="2" t="s">
+        <v>849</v>
+      </c>
+      <c r="F5" s="2" t="s">
         <v>850</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>851</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
+        <v>825</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>826</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="C6" s="2" t="s">
         <v>827</v>
       </c>
-      <c r="C6" s="2" t="s">
-        <v>828</v>
-      </c>
       <c r="D6" s="2" t="s">
+        <v>851</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>849</v>
+      </c>
+      <c r="F6" s="2" t="s">
         <v>852</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>850</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>853</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
+        <v>829</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>826</v>
+      </c>
+      <c r="C7" s="2" t="s">
         <v>830</v>
       </c>
-      <c r="B7" s="2" t="s">
-        <v>827</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>831</v>
-      </c>
       <c r="D7" s="2" t="s">
+        <v>851</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>849</v>
+      </c>
+      <c r="F7" s="2" t="s">
         <v>852</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>850</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>853</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
+        <v>833</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>826</v>
+      </c>
+      <c r="C8" s="2" t="s">
         <v>834</v>
       </c>
-      <c r="B8" s="2" t="s">
-        <v>827</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>835</v>
-      </c>
       <c r="D8" s="2" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="E8" s="2" t="s">
+        <v>853</v>
+      </c>
+      <c r="F8" s="2" t="s">
         <v>854</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>855</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A9" s="2" t="s">
+        <v>838</v>
+      </c>
+      <c r="B9" s="2" t="s">
         <v>839</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="C9" s="2" t="s">
         <v>840</v>
       </c>
-      <c r="C9" s="2" t="s">
-        <v>841</v>
-      </c>
       <c r="D9" s="2" t="s">
+        <v>855</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>849</v>
+      </c>
+      <c r="F9" s="2" t="s">
         <v>856</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>850</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>857</v>
       </c>
     </row>
   </sheetData>
@@ -9486,7 +9524,7 @@
   <sheetData>
     <row r="1" spans="1:5" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A1" s="10" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="B1" s="10"/>
       <c r="C1" s="10"/>
@@ -9495,189 +9533,189 @@
     </row>
     <row r="3" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
+        <v>858</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>859</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="C3" s="1" t="s">
         <v>860</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="D3" s="1" t="s">
         <v>861</v>
       </c>
-      <c r="D3" s="1" t="s">
-        <v>862</v>
-      </c>
       <c r="E3" s="1" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
+        <v>862</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>863</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="C4" s="2" t="s">
         <v>864</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="D4" s="2" t="s">
         <v>865</v>
       </c>
-      <c r="D4" s="2" t="s">
-        <v>866</v>
-      </c>
       <c r="E4" s="2" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="B5" s="2" t="s">
+        <v>866</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>867</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="D5" s="2" t="s">
         <v>868</v>
       </c>
-      <c r="D5" s="2" t="s">
-        <v>869</v>
-      </c>
       <c r="E5" s="2" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="B6" s="2" t="s">
+        <v>869</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>870</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="D6" s="2" t="s">
         <v>871</v>
       </c>
-      <c r="D6" s="2" t="s">
-        <v>872</v>
-      </c>
       <c r="E6" s="2" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="B7" s="2" t="s">
+        <v>872</v>
+      </c>
+      <c r="C7" s="2" t="s">
         <v>873</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="D7" s="2" t="s">
         <v>874</v>
       </c>
-      <c r="D7" s="2" t="s">
-        <v>875</v>
-      </c>
       <c r="E7" s="2" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="B8" s="2" t="s">
+        <v>875</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>875</v>
+      </c>
+      <c r="D8" s="2" t="s">
         <v>876</v>
       </c>
-      <c r="C8" s="2" t="s">
-        <v>876</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>877</v>
-      </c>
       <c r="E8" s="2" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A9" s="2" t="s">
+        <v>877</v>
+      </c>
+      <c r="B9" s="2" t="s">
         <v>878</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="C9" s="2" t="s">
+        <v>878</v>
+      </c>
+      <c r="D9" s="2" t="s">
         <v>879</v>
       </c>
-      <c r="C9" s="2" t="s">
-        <v>879</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>880</v>
-      </c>
       <c r="E9" s="2" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A10" s="2" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="B10" s="2" t="s">
+        <v>880</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>880</v>
+      </c>
+      <c r="D10" s="2" t="s">
         <v>881</v>
       </c>
-      <c r="C10" s="2" t="s">
-        <v>881</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>882</v>
-      </c>
       <c r="E10" s="2" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A11" s="2" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="B11" s="2" t="s">
+        <v>882</v>
+      </c>
+      <c r="C11" s="2" t="s">
         <v>883</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="D11" s="2" t="s">
         <v>884</v>
       </c>
-      <c r="D11" s="2" t="s">
-        <v>885</v>
-      </c>
       <c r="E11" s="2" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A12" s="2" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="B12" s="2" t="s">
+        <v>885</v>
+      </c>
+      <c r="C12" s="2" t="s">
         <v>886</v>
       </c>
-      <c r="C12" s="2" t="s">
+      <c r="D12" s="2" t="s">
         <v>887</v>
       </c>
-      <c r="D12" s="2" t="s">
-        <v>888</v>
-      </c>
       <c r="E12" s="2" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A13" s="2" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="B13" s="2" t="s">
+        <v>888</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>888</v>
+      </c>
+      <c r="D13" s="2" t="s">
         <v>889</v>
       </c>
-      <c r="C13" s="2" t="s">
-        <v>889</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>890</v>
-      </c>
       <c r="E13" s="2" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
     </row>
   </sheetData>
@@ -9924,7 +9962,7 @@
   <sheetData>
     <row r="1" spans="1:10" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A1" s="10" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="B1" s="10"/>
       <c r="C1" s="10"/>
@@ -9938,34 +9976,34 @@
     </row>
     <row r="3" spans="1:10" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
+        <v>891</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>892</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="C3" s="1" t="s">
+        <v>859</v>
+      </c>
+      <c r="D3" s="1" t="s">
         <v>893</v>
       </c>
-      <c r="C3" s="1" t="s">
-        <v>860</v>
-      </c>
-      <c r="D3" s="1" t="s">
+      <c r="E3" s="1" t="s">
         <v>894</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="F3" s="1" t="s">
         <v>895</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="G3" s="1" t="s">
         <v>896</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="H3" s="1" t="s">
         <v>897</v>
       </c>
-      <c r="H3" s="1" t="s">
+      <c r="I3" s="1" t="s">
         <v>898</v>
       </c>
-      <c r="I3" s="1" t="s">
-        <v>899</v>
-      </c>
       <c r="J3" s="1" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.35">
@@ -9973,16 +10011,16 @@
         <v>8991002100016</v>
       </c>
       <c r="B4" s="2" t="s">
+        <v>899</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>900</v>
       </c>
-      <c r="C4" s="2" t="s">
-        <v>901</v>
-      </c>
       <c r="D4" s="2" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="F4" s="2">
         <v>2500</v>
@@ -9991,13 +10029,13 @@
         <v>3000</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="I4" s="2" t="s">
         <v>63</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.35">
@@ -10005,16 +10043,16 @@
         <v>8992388123456</v>
       </c>
       <c r="B5" s="2" t="s">
+        <v>904</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>905</v>
       </c>
-      <c r="C5" s="2" t="s">
-        <v>906</v>
-      </c>
       <c r="D5" s="2" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="F5" s="2">
         <v>4000</v>
@@ -10023,13 +10061,13 @@
         <v>5000</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="I5" s="2" t="s">
         <v>48</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.35">
@@ -10037,16 +10075,16 @@
         <v>8996001600028</v>
       </c>
       <c r="B6" s="2" t="s">
+        <v>907</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>908</v>
       </c>
-      <c r="C6" s="2" t="s">
-        <v>909</v>
-      </c>
       <c r="D6" s="2" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="F6" s="2">
         <v>2800</v>
@@ -10055,45 +10093,45 @@
         <v>3500</v>
       </c>
       <c r="H6" s="2" t="s">
+        <v>911</v>
+      </c>
+      <c r="I6" s="2" t="s">
         <v>912</v>
       </c>
-      <c r="I6" s="2" t="s">
-        <v>913</v>
-      </c>
       <c r="J6" s="2" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
     </row>
     <row r="7" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
+        <v>913</v>
+      </c>
+      <c r="B7" s="2" t="s">
         <v>914</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="C7" s="2" t="s">
         <v>915</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="D7" s="2" t="s">
+        <v>869</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>878</v>
+      </c>
+      <c r="F7" s="2" t="s">
         <v>916</v>
       </c>
-      <c r="D7" s="2" t="s">
-        <v>870</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>879</v>
-      </c>
-      <c r="F7" s="2" t="s">
+      <c r="G7" s="2" t="s">
         <v>917</v>
       </c>
-      <c r="G7" s="2" t="s">
+      <c r="H7" s="2" t="s">
         <v>918</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>919</v>
       </c>
       <c r="I7" s="2" t="s">
         <v>18</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.35">
@@ -10101,16 +10139,16 @@
         <v>8991234567890</v>
       </c>
       <c r="B8" s="2" t="s">
+        <v>919</v>
+      </c>
+      <c r="C8" s="2" t="s">
         <v>920</v>
       </c>
-      <c r="C8" s="2" t="s">
-        <v>921</v>
-      </c>
       <c r="D8" s="2" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="F8" s="2">
         <v>22000</v>
@@ -10119,13 +10157,13 @@
         <v>24000</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
       <c r="I8" s="2" t="s">
         <v>33</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
     </row>
     <row r="9" spans="1:10" ht="29" x14ac:dyDescent="0.35">
@@ -10133,16 +10171,16 @@
         <v>8990001112223</v>
       </c>
       <c r="B9" s="2" t="s">
+        <v>922</v>
+      </c>
+      <c r="C9" s="2" t="s">
         <v>923</v>
       </c>
-      <c r="C9" s="2" t="s">
-        <v>924</v>
-      </c>
       <c r="D9" s="2" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="F9" s="2">
         <v>8500</v>
@@ -10157,7 +10195,7 @@
         <v>33</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.35">
@@ -10165,16 +10203,16 @@
         <v>8990004445556</v>
       </c>
       <c r="B10" s="2" t="s">
+        <v>926</v>
+      </c>
+      <c r="C10" s="2" t="s">
         <v>927</v>
       </c>
-      <c r="C10" s="2" t="s">
-        <v>928</v>
-      </c>
       <c r="D10" s="2" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="F10" s="2">
         <v>1200</v>
@@ -10183,36 +10221,36 @@
         <v>1500</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="I10" s="2" t="s">
         <v>63</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
     </row>
     <row r="11" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A11" s="2" t="s">
+        <v>931</v>
+      </c>
+      <c r="B11" s="2" t="s">
         <v>932</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="C11" s="2" t="s">
         <v>933</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="D11" s="2" t="s">
+        <v>863</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>878</v>
+      </c>
+      <c r="F11" s="2" t="s">
         <v>934</v>
       </c>
-      <c r="D11" s="2" t="s">
-        <v>864</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>879</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>935</v>
-      </c>
       <c r="G11" s="2" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="H11" s="2" t="s">
         <v>33</v>
@@ -10221,7 +10259,7 @@
         <v>18</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>936</v>
+        <v>935</v>
       </c>
     </row>
   </sheetData>
@@ -10247,7 +10285,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A1" s="10" t="s">
-        <v>937</v>
+        <v>936</v>
       </c>
       <c r="B1" s="10"/>
       <c r="C1" s="10"/>
@@ -10258,105 +10296,105 @@
     </row>
     <row r="3" spans="1:7" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
+        <v>937</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>938</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="C3" s="1" t="s">
+        <v>894</v>
+      </c>
+      <c r="D3" s="1" t="s">
         <v>939</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="E3" s="1" t="s">
+        <v>896</v>
+      </c>
+      <c r="F3" s="1" t="s">
         <v>895</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="G3" s="1" t="s">
         <v>940</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>897</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>896</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>941</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>6</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="B5" s="2" t="s">
+        <v>942</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>882</v>
+      </c>
+      <c r="D5" s="2" t="s">
         <v>943</v>
       </c>
-      <c r="C5" s="2" t="s">
-        <v>883</v>
-      </c>
-      <c r="D5" s="2" t="s">
+      <c r="E5" s="2" t="s">
         <v>944</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="F5" s="2" t="s">
         <v>945</v>
       </c>
-      <c r="F5" s="2" t="s">
-        <v>946</v>
-      </c>
       <c r="G5" s="2" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>6</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>947</v>
+        <v>946</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>75</v>
@@ -10368,7 +10406,7 @@
         <v>65000</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
     </row>
   </sheetData>
@@ -10391,7 +10429,7 @@
   <sheetData>
     <row r="1" spans="1:4" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A1" s="10" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="B1" s="10"/>
       <c r="C1" s="10"/>
@@ -10399,58 +10437,58 @@
     </row>
     <row r="3" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>948</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>949</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="D3" s="1" t="s">
         <v>950</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>951</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>39</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="B5" s="2" t="s">
+        <v>952</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>943</v>
+      </c>
+      <c r="D5" s="2" t="s">
         <v>953</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>944</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>954</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>75</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>956</v>
+        <v>955</v>
       </c>
     </row>
   </sheetData>
@@ -10478,7 +10516,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A1" s="10" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
       <c r="B1" s="10"/>
       <c r="C1" s="10"/>
@@ -10489,117 +10527,117 @@
     </row>
     <row r="3" spans="1:7" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
+        <v>957</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>859</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>958</v>
       </c>
-      <c r="B3" s="1" t="s">
-        <v>860</v>
-      </c>
-      <c r="C3" s="1" t="s">
+      <c r="D3" s="1" t="s">
         <v>959</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="E3" s="1" t="s">
         <v>960</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="F3" s="1" t="s">
         <v>961</v>
       </c>
-      <c r="F3" s="1" t="s">
-        <v>962</v>
-      </c>
       <c r="G3" s="1" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
+        <v>962</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>963</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="C4" s="2" t="s">
         <v>964</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>965</v>
       </c>
       <c r="D4" s="2">
         <v>81234567890</v>
       </c>
       <c r="E4" s="6" t="s">
+        <v>965</v>
+      </c>
+      <c r="F4" s="2" t="s">
         <v>966</v>
       </c>
-      <c r="F4" s="2" t="s">
-        <v>967</v>
-      </c>
       <c r="G4" s="2" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
+        <v>967</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>968</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="C5" s="2" t="s">
         <v>969</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>970</v>
       </c>
       <c r="D5" s="2">
         <v>82198765432</v>
       </c>
       <c r="E5" s="6" t="s">
+        <v>970</v>
+      </c>
+      <c r="F5" s="2" t="s">
         <v>971</v>
       </c>
-      <c r="F5" s="2" t="s">
-        <v>972</v>
-      </c>
       <c r="G5" s="2" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
+        <v>972</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>973</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="C6" s="2" t="s">
         <v>974</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="D6" s="2" t="s">
         <v>975</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="E6" s="2" t="s">
         <v>976</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="F6" s="2" t="s">
         <v>977</v>
       </c>
-      <c r="F6" s="2" t="s">
-        <v>978</v>
-      </c>
       <c r="G6" s="2" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
+        <v>978</v>
+      </c>
+      <c r="B7" s="2" t="s">
         <v>979</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="C7" s="2" t="s">
         <v>980</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="D7" s="2" t="s">
         <v>981</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="E7" s="2" t="s">
         <v>982</v>
       </c>
-      <c r="E7" s="2" t="s">
+      <c r="F7" s="2" t="s">
         <v>983</v>
       </c>
-      <c r="F7" s="2" t="s">
-        <v>984</v>
-      </c>
       <c r="G7" s="2" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
     </row>
   </sheetData>
@@ -10629,7 +10667,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A1" s="10" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
       <c r="B1" s="10"/>
       <c r="C1" s="10"/>
@@ -10641,106 +10679,106 @@
     </row>
     <row r="3" spans="1:8" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
+        <v>985</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>986</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="C3" s="1" t="s">
         <v>987</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="D3" s="1" t="s">
         <v>988</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="E3" s="1" t="s">
         <v>989</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="F3" s="1" t="s">
         <v>990</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="G3" s="1" t="s">
         <v>991</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="H3" s="1" t="s">
         <v>992</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>993</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
+        <v>993</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>963</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>994</v>
       </c>
-      <c r="B4" s="2" t="s">
-        <v>964</v>
-      </c>
-      <c r="C4" s="2" t="s">
+      <c r="D4" s="2" t="s">
         <v>995</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="E4" s="2" t="s">
+        <v>924</v>
+      </c>
+      <c r="F4" s="2" t="s">
         <v>996</v>
       </c>
-      <c r="E4" s="2" t="s">
-        <v>925</v>
-      </c>
-      <c r="F4" s="2" t="s">
+      <c r="G4" s="2" t="s">
         <v>997</v>
       </c>
-      <c r="G4" s="2" t="s">
-        <v>998</v>
-      </c>
       <c r="H4" s="2" t="s">
-        <v>997</v>
+        <v>996</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
+        <v>998</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>968</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>999</v>
       </c>
-      <c r="B5" s="2" t="s">
-        <v>969</v>
-      </c>
-      <c r="C5" s="2" t="s">
+      <c r="D5" s="2" t="s">
         <v>1000</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="E5" s="2" t="s">
+        <v>929</v>
+      </c>
+      <c r="F5" s="2" t="s">
         <v>1001</v>
       </c>
-      <c r="E5" s="2" t="s">
-        <v>930</v>
-      </c>
-      <c r="F5" s="2" t="s">
+      <c r="G5" s="2" t="s">
         <v>1002</v>
       </c>
-      <c r="G5" s="2" t="s">
+      <c r="H5" s="2" t="s">
         <v>1003</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>1004</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
+        <v>1004</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>973</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>1005</v>
       </c>
-      <c r="B6" s="2" t="s">
-        <v>974</v>
-      </c>
-      <c r="C6" s="2" t="s">
+      <c r="D6" s="2" t="s">
         <v>1006</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="E6" s="2" t="s">
         <v>1007</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="F6" s="2" t="s">
         <v>1008</v>
       </c>
-      <c r="F6" s="2" t="s">
+      <c r="G6" s="2" t="s">
         <v>1009</v>
       </c>
-      <c r="G6" s="2" t="s">
-        <v>1010</v>
-      </c>
       <c r="H6" s="2" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
     </row>
   </sheetData>
@@ -10767,7 +10805,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A1" s="10" t="s">
-        <v>1011</v>
+        <v>1010</v>
       </c>
       <c r="B1" s="10"/>
       <c r="C1" s="10"/>
@@ -10777,102 +10815,102 @@
     </row>
     <row r="3" spans="1:6" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
+        <v>1011</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>859</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>959</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>958</v>
+      </c>
+      <c r="E3" s="1" t="s">
         <v>1012</v>
       </c>
-      <c r="B3" s="1" t="s">
-        <v>860</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>960</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>959</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>1013</v>
-      </c>
       <c r="F3" s="1" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
+        <v>1013</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>1014</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="C4" s="2" t="s">
         <v>1015</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="D4" s="2" t="s">
         <v>1016</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="E4" s="2" t="s">
         <v>1017</v>
       </c>
-      <c r="E4" s="2" t="s">
-        <v>1018</v>
-      </c>
       <c r="F4" s="2" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
+        <v>1018</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>1019</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="C5" s="2" t="s">
         <v>1020</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="D5" s="2" t="s">
         <v>1021</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="E5" s="2" t="s">
         <v>1022</v>
       </c>
-      <c r="E5" s="2" t="s">
-        <v>1023</v>
-      </c>
       <c r="F5" s="2" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
+        <v>1023</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>1024</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="C6" s="2" t="s">
         <v>1025</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="D6" s="2" t="s">
         <v>1026</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="E6" s="2" t="s">
         <v>1027</v>
       </c>
-      <c r="E6" s="2" t="s">
-        <v>1028</v>
-      </c>
       <c r="F6" s="2" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
+        <v>1028</v>
+      </c>
+      <c r="B7" s="2" t="s">
         <v>1029</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="C7" s="2" t="s">
         <v>1030</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="D7" s="2" t="s">
         <v>1031</v>
       </c>
-      <c r="D7" s="2" t="s">
-        <v>1032</v>
-      </c>
       <c r="E7" s="2" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
     </row>
   </sheetData>
@@ -10899,7 +10937,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A1" s="10" t="s">
-        <v>1033</v>
+        <v>1032</v>
       </c>
       <c r="B1" s="10"/>
       <c r="C1" s="10"/>
@@ -10910,94 +10948,94 @@
     </row>
     <row r="3" spans="1:7" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
+        <v>1033</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>1034</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="C3" s="1" t="s">
+        <v>990</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>992</v>
+      </c>
+      <c r="E3" s="1" t="s">
         <v>1035</v>
       </c>
-      <c r="C3" s="1" t="s">
-        <v>991</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>993</v>
-      </c>
-      <c r="E3" s="1" t="s">
+      <c r="F3" s="1" t="s">
         <v>1036</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="G3" s="1" t="s">
         <v>1037</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>1038</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="B4" s="2" t="s">
+        <v>1038</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>1039</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="D4" s="2" t="s">
+        <v>929</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>1039</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>1009</v>
+      </c>
+      <c r="G4" s="2" t="s">
         <v>1040</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>930</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>1040</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>1010</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>1041</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
       <c r="B5" s="2" t="s">
+        <v>1041</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>1017</v>
+      </c>
+      <c r="D5" s="2" t="s">
         <v>1042</v>
       </c>
-      <c r="C5" s="2" t="s">
-        <v>1018</v>
-      </c>
-      <c r="D5" s="2" t="s">
+      <c r="E5" s="2" t="s">
+        <v>1042</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>1002</v>
+      </c>
+      <c r="G5" s="2" t="s">
         <v>1043</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>1043</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>1003</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>1044</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
-        <v>1025</v>
+        <v>1024</v>
       </c>
       <c r="B6" s="2" t="s">
+        <v>1044</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>1045</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="D6" s="2" t="s">
+        <v>1045</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>929</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>997</v>
+      </c>
+      <c r="G6" s="2" t="s">
         <v>1046</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>1046</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>930</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>998</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>1047</v>
       </c>
     </row>
   </sheetData>
@@ -11021,7 +11059,7 @@
   <sheetData>
     <row r="1" spans="1:4" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A1" s="10" t="s">
-        <v>1048</v>
+        <v>1047</v>
       </c>
       <c r="B1" s="10"/>
       <c r="C1" s="10"/>
@@ -11029,58 +11067,58 @@
     </row>
     <row r="3" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>1048</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>1049</v>
       </c>
-      <c r="C3" s="1" t="s">
-        <v>1050</v>
-      </c>
       <c r="D3" s="1" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
+        <v>1050</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>1051</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="C4" s="2" t="s">
         <v>1052</v>
       </c>
-      <c r="C4" s="2" t="s">
-        <v>1053</v>
-      </c>
       <c r="D4" s="2" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
+        <v>1053</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>1052</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>1054</v>
       </c>
-      <c r="B5" s="2" t="s">
-        <v>1053</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>1055</v>
-      </c>
       <c r="D5" s="2" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
-        <v>1056</v>
+        <v>1055</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>1055</v>
+        <v>1054</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>1052</v>
+        <v>1051</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
     </row>
   </sheetData>
@@ -11107,7 +11145,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A1" s="10" t="s">
-        <v>1057</v>
+        <v>1056</v>
       </c>
       <c r="B1" s="10"/>
       <c r="C1" s="10"/>
@@ -11119,106 +11157,106 @@
     </row>
     <row r="3" spans="1:8" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>1057</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>1058</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="D3" s="1" t="s">
         <v>1059</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="E3" s="1" t="s">
         <v>1060</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="F3" s="1" t="s">
         <v>1061</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="G3" s="1" t="s">
+        <v>1036</v>
+      </c>
+      <c r="H3" s="1" t="s">
         <v>1062</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>1037</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>1063</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>1051</v>
+        <v>1050</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>1018</v>
+        <v>1017</v>
       </c>
       <c r="D4" s="2" t="s">
+        <v>1063</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>1063</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>929</v>
+      </c>
+      <c r="G4" s="2" t="s">
         <v>1064</v>
       </c>
-      <c r="E4" s="2" t="s">
-        <v>1064</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>930</v>
-      </c>
-      <c r="G4" s="2" t="s">
+      <c r="H4" s="2" t="s">
         <v>1065</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>1066</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
       <c r="C5" s="2" t="s">
+        <v>1066</v>
+      </c>
+      <c r="D5" s="2" t="s">
         <v>1067</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="E5" s="2" t="s">
+        <v>1022</v>
+      </c>
+      <c r="F5" s="2" t="s">
         <v>1068</v>
       </c>
-      <c r="E5" s="2" t="s">
-        <v>1023</v>
-      </c>
-      <c r="F5" s="2" t="s">
+      <c r="G5" s="2" t="s">
+        <v>1064</v>
+      </c>
+      <c r="H5" s="2" t="s">
         <v>1069</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>1065</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>1070</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>1056</v>
+        <v>1055</v>
       </c>
       <c r="C6" s="2" t="s">
+        <v>1070</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G6" s="2" t="s">
         <v>1071</v>
       </c>
-      <c r="D6" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="G6" s="2" t="s">
+      <c r="H6" s="2" t="s">
         <v>1072</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>1073</v>
       </c>
     </row>
   </sheetData>
@@ -11245,7 +11283,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A1" s="10" t="s">
-        <v>1074</v>
+        <v>1073</v>
       </c>
       <c r="B1" s="10"/>
       <c r="C1" s="10"/>
@@ -11255,102 +11293,102 @@
     </row>
     <row r="3" spans="1:6" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
+        <v>1074</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>893</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>861</v>
+      </c>
+      <c r="D3" s="1" t="s">
         <v>1075</v>
       </c>
-      <c r="B3" s="1" t="s">
-        <v>894</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>862</v>
-      </c>
-      <c r="D3" s="1" t="s">
+      <c r="E3" s="1" t="s">
         <v>1076</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="F3" s="1" t="s">
         <v>1077</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>1078</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="B4" s="2" t="s">
+        <v>1078</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>1079</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="D4" s="2" t="s">
         <v>1080</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="E4" s="2" t="s">
         <v>1081</v>
       </c>
-      <c r="E4" s="2" t="s">
-        <v>1082</v>
-      </c>
       <c r="F4" s="2" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="B5" s="2" t="s">
+        <v>1082</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>1083</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="D5" s="2" t="s">
         <v>1084</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="E5" s="2" t="s">
         <v>1085</v>
       </c>
-      <c r="E5" s="2" t="s">
-        <v>1086</v>
-      </c>
       <c r="F5" s="2" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
+        <v>1086</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>1087</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="C6" s="2" t="s">
         <v>1088</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="D6" s="2" t="s">
         <v>1089</v>
       </c>
-      <c r="D6" s="2" t="s">
-        <v>1090</v>
-      </c>
       <c r="E6" s="2" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="B7" s="2" t="s">
+        <v>1090</v>
+      </c>
+      <c r="C7" s="2" t="s">
         <v>1091</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="D7" s="2" t="s">
         <v>1092</v>
       </c>
-      <c r="D7" s="2" t="s">
-        <v>1093</v>
-      </c>
       <c r="E7" s="2" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
     </row>
   </sheetData>
@@ -11438,7 +11476,7 @@
         <v>5</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="29" x14ac:dyDescent="0.35">
@@ -11464,7 +11502,7 @@
         <v>5</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
@@ -11490,7 +11528,7 @@
         <v>5</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="29" x14ac:dyDescent="0.35">
@@ -11516,7 +11554,7 @@
         <v>5</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="29" x14ac:dyDescent="0.35">
@@ -11542,7 +11580,7 @@
         <v>5</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="29" x14ac:dyDescent="0.35">
@@ -11568,7 +11606,7 @@
         <v>5</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="58" x14ac:dyDescent="0.35">
@@ -11594,7 +11632,7 @@
         <v>5</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="29" x14ac:dyDescent="0.35">
@@ -11620,7 +11658,7 @@
         <v>5</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.35">
@@ -11646,7 +11684,7 @@
         <v>5</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="58" x14ac:dyDescent="0.35">
@@ -11666,13 +11704,13 @@
         <v>227</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>5</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="58" x14ac:dyDescent="0.35">
@@ -11683,19 +11721,19 @@
         <v>119</v>
       </c>
       <c r="C14" s="2" t="s">
+        <v>1119</v>
+      </c>
+      <c r="D14" s="2" t="s">
         <v>1120</v>
       </c>
-      <c r="D14" s="2" t="s">
+      <c r="E14" s="2" t="s">
         <v>1121</v>
       </c>
-      <c r="E14" s="2" t="s">
+      <c r="F14" s="2" t="s">
         <v>1122</v>
       </c>
-      <c r="F14" s="2" t="s">
-        <v>1123</v>
-      </c>
       <c r="H14" s="3" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
     </row>
   </sheetData>
@@ -11723,7 +11761,7 @@
   <sheetData>
     <row r="1" spans="1:10" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A1" s="10" t="s">
-        <v>1094</v>
+        <v>1093</v>
       </c>
       <c r="B1" s="10"/>
       <c r="C1" s="10"/>
@@ -11737,226 +11775,226 @@
     </row>
     <row r="3" spans="1:10" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
+        <v>1094</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>851</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>988</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>1076</v>
+      </c>
+      <c r="E3" s="1" t="s">
         <v>1095</v>
       </c>
-      <c r="B3" s="1" t="s">
-        <v>852</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>989</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>1077</v>
-      </c>
-      <c r="E3" s="1" t="s">
+      <c r="F3" s="1" t="s">
+        <v>990</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>1033</v>
+      </c>
+      <c r="H3" s="1" t="s">
         <v>1096</v>
       </c>
-      <c r="F3" s="1" t="s">
-        <v>991</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>1034</v>
-      </c>
-      <c r="H3" s="1" t="s">
+      <c r="I3" s="1" t="s">
+        <v>1036</v>
+      </c>
+      <c r="J3" s="1" t="s">
         <v>1097</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>1037</v>
-      </c>
-      <c r="J3" s="1" t="s">
-        <v>1098</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
+        <v>1098</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>825</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>1099</v>
       </c>
-      <c r="B4" s="2" t="s">
-        <v>826</v>
-      </c>
-      <c r="C4" s="2" t="s">
+      <c r="D4" s="2" t="s">
+        <v>1081</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>924</v>
+      </c>
+      <c r="F4" s="2" t="s">
         <v>1100</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>1082</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>925</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>1101</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>159</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="I4" s="2" t="s">
+        <v>1101</v>
+      </c>
+      <c r="J4" s="2" t="s">
         <v>1102</v>
-      </c>
-      <c r="J4" s="2" t="s">
-        <v>1103</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
+        <v>1103</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>825</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>1104</v>
       </c>
-      <c r="B5" s="2" t="s">
-        <v>826</v>
-      </c>
-      <c r="C5" s="2" t="s">
+      <c r="D5" s="2" t="s">
         <v>1105</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="E5" s="2" t="s">
         <v>1106</v>
       </c>
-      <c r="E5" s="2" t="s">
-        <v>1107</v>
-      </c>
       <c r="F5" s="2" t="s">
-        <v>1107</v>
+        <v>1106</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>159</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>1102</v>
+        <v>1101</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>1108</v>
+        <v>1107</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
+        <v>1108</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>829</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>1109</v>
       </c>
-      <c r="B6" s="2" t="s">
-        <v>830</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>1110</v>
-      </c>
       <c r="D6" s="2" t="s">
-        <v>1086</v>
+        <v>1085</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>159</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>1102</v>
+        <v>1101</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
+        <v>1038</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>825</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>1111</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>1112</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>929</v>
+      </c>
+      <c r="F7" s="2" t="s">
         <v>1039</v>
       </c>
-      <c r="B7" s="2" t="s">
-        <v>826</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>1112</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>1113</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>930</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>1040</v>
-      </c>
       <c r="G7" s="2" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="I7" s="2" t="s">
+        <v>1101</v>
+      </c>
+      <c r="J7" s="2" t="s">
         <v>1102</v>
-      </c>
-      <c r="J7" s="2" t="s">
-        <v>1103</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>1114</v>
+        <v>1113</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>945</v>
+        <v>944</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>945</v>
+        <v>944</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>159</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="I8" s="2" t="s">
+        <v>1101</v>
+      </c>
+      <c r="J8" s="2" t="s">
         <v>1102</v>
-      </c>
-      <c r="J8" s="2" t="s">
-        <v>1103</v>
       </c>
     </row>
     <row r="9" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A9" s="2" t="s">
+        <v>1114</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>825</v>
+      </c>
+      <c r="C9" s="2" t="s">
         <v>1115</v>
       </c>
-      <c r="B9" s="2" t="s">
-        <v>826</v>
-      </c>
-      <c r="C9" s="2" t="s">
+      <c r="D9" s="2" t="s">
+        <v>1081</v>
+      </c>
+      <c r="E9" s="2" t="s">
         <v>1116</v>
       </c>
-      <c r="D9" s="2" t="s">
-        <v>1082</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>1117</v>
-      </c>
       <c r="F9" s="2" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>159</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>1103</v>
+        <v>1102</v>
       </c>
     </row>
   </sheetData>
@@ -12532,7 +12570,7 @@
         <v>5</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
@@ -12558,7 +12596,7 @@
         <v>5</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="29" x14ac:dyDescent="0.35">
@@ -12569,7 +12607,7 @@
         <v>229</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>1128</v>
+        <v>1127</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>317</v>
@@ -12584,7 +12622,7 @@
         <v>5</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="29" x14ac:dyDescent="0.35">
@@ -12610,7 +12648,7 @@
         <v>5</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
@@ -12636,7 +12674,7 @@
         <v>5</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="29" x14ac:dyDescent="0.35">
@@ -12662,7 +12700,7 @@
         <v>5</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
@@ -12688,7 +12726,7 @@
         <v>5</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="58" x14ac:dyDescent="0.35">
@@ -12714,7 +12752,7 @@
         <v>5</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.35">
@@ -12725,22 +12763,22 @@
         <v>119</v>
       </c>
       <c r="C12" s="2" t="s">
+        <v>1132</v>
+      </c>
+      <c r="D12" s="2" t="s">
         <v>1133</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>1134</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>299</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>1135</v>
+        <v>1134</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>5</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
     </row>
   </sheetData>
@@ -12828,7 +12866,7 @@
         <v>5</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
@@ -12854,7 +12892,7 @@
         <v>5</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="29" x14ac:dyDescent="0.35">
@@ -12880,7 +12918,7 @@
         <v>5</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.35">
@@ -12891,13 +12929,13 @@
         <v>229</v>
       </c>
       <c r="C7" s="2" t="s">
+        <v>1124</v>
+      </c>
+      <c r="D7" s="2" t="s">
         <v>1125</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="E7" s="2" t="s">
         <v>1126</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>1127</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>292</v>
@@ -12906,7 +12944,7 @@
         <v>5</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
@@ -12932,7 +12970,7 @@
         <v>5</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="29" x14ac:dyDescent="0.35">
@@ -12943,13 +12981,13 @@
         <v>229</v>
       </c>
       <c r="C9" s="2" t="s">
+        <v>1128</v>
+      </c>
+      <c r="D9" s="2" t="s">
         <v>1129</v>
       </c>
-      <c r="D9" s="2" t="s">
+      <c r="E9" s="2" t="s">
         <v>1130</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>1131</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>300</v>
@@ -12958,7 +12996,7 @@
         <v>5</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="29" x14ac:dyDescent="0.35">
@@ -12984,7 +13022,7 @@
         <v>5</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="58" x14ac:dyDescent="0.35">
@@ -12995,7 +13033,7 @@
         <v>128</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>1132</v>
+        <v>1131</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>306</v>
@@ -13010,7 +13048,7 @@
         <v>5</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.35">
@@ -13021,22 +13059,22 @@
         <v>119</v>
       </c>
       <c r="C12" s="2" t="s">
+        <v>1135</v>
+      </c>
+      <c r="D12" s="2" t="s">
         <v>1136</v>
       </c>
-      <c r="D12" s="2" t="s">
+      <c r="E12" s="2" t="s">
+        <v>1141</v>
+      </c>
+      <c r="F12" s="2" t="s">
         <v>1137</v>
       </c>
-      <c r="E12" s="2" t="s">
-        <v>1142</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>1138</v>
-      </c>
       <c r="G12" s="2" t="s">
         <v>5</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
     </row>
   </sheetData>
@@ -13050,7 +13088,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
-  <dimension ref="A1:H25"/>
+  <dimension ref="A1:H26"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
@@ -13124,7 +13162,7 @@
         <v>5</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="87" x14ac:dyDescent="0.35">
@@ -13150,7 +13188,7 @@
         <v>5</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="29" x14ac:dyDescent="0.35">
@@ -13176,7 +13214,7 @@
         <v>5</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="29" x14ac:dyDescent="0.35">
@@ -13202,7 +13240,7 @@
         <v>5</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="29" x14ac:dyDescent="0.35">
@@ -13228,7 +13266,7 @@
         <v>5</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="29" x14ac:dyDescent="0.35">
@@ -13254,7 +13292,7 @@
         <v>5</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.35">
@@ -13280,7 +13318,7 @@
         <v>5</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="29" x14ac:dyDescent="0.35">
@@ -13306,7 +13344,7 @@
         <v>5</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="29" x14ac:dyDescent="0.35">
@@ -13332,7 +13370,7 @@
         <v>5</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="58" x14ac:dyDescent="0.35">
@@ -13358,7 +13396,7 @@
         <v>5</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="29" x14ac:dyDescent="0.35">
@@ -13384,7 +13422,7 @@
         <v>5</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
@@ -13395,10 +13433,10 @@
         <v>229</v>
       </c>
       <c r="C15" s="2" t="s">
+        <v>1148</v>
+      </c>
+      <c r="D15" s="2" t="s">
         <v>1149</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>1150</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>387</v>
@@ -13410,7 +13448,7 @@
         <v>5</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="29" x14ac:dyDescent="0.35">
@@ -13436,7 +13474,7 @@
         <v>5</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="72.5" x14ac:dyDescent="0.35">
@@ -13462,7 +13500,7 @@
         <v>5</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
@@ -13488,7 +13526,7 @@
         <v>5</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="72.5" x14ac:dyDescent="0.35">
@@ -13514,7 +13552,7 @@
         <v>5</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="20" spans="1:8" ht="29" x14ac:dyDescent="0.35">
@@ -13540,7 +13578,7 @@
         <v>5</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="21" spans="1:8" ht="29" x14ac:dyDescent="0.35">
@@ -13566,7 +13604,7 @@
         <v>5</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.35">
@@ -13577,22 +13615,22 @@
         <v>119</v>
       </c>
       <c r="C22" s="2" t="s">
+        <v>1138</v>
+      </c>
+      <c r="D22" s="2" t="s">
         <v>1139</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>1140</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>387</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>1141</v>
+        <v>1140</v>
       </c>
       <c r="G22" s="2" t="s">
         <v>5</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="23" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
@@ -13603,19 +13641,19 @@
         <v>128</v>
       </c>
       <c r="C23" s="4" t="s">
+        <v>1142</v>
+      </c>
+      <c r="D23" s="5" t="s">
         <v>1143</v>
-      </c>
-      <c r="D23" s="5" t="s">
-        <v>1144</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>387</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>1145</v>
+        <v>1144</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="24" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
@@ -13626,45 +13664,71 @@
         <v>128</v>
       </c>
       <c r="C24" s="4" t="s">
+        <v>1145</v>
+      </c>
+      <c r="D24" s="5" t="s">
         <v>1146</v>
-      </c>
-      <c r="D24" s="5" t="s">
-        <v>1147</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>387</v>
       </c>
       <c r="F24" s="4" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>1119</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.35">
+        <v>1118</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A25" s="2">
         <v>22</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>119</v>
+        <v>229</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>1152</v>
+        <v>1151</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>387</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>1141</v>
+        <v>1153</v>
       </c>
       <c r="G25" s="2" t="s">
         <v>5</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>1119</v>
+        <v>1118</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" ht="29" x14ac:dyDescent="0.35">
+      <c r="A26" s="2">
+        <v>23</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>385</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>386</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>1152</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="H26" s="3" t="s">
+        <v>1118</v>
       </c>
     </row>
   </sheetData>

--- a/docs/Dokumen_Testing_POS.xlsx
+++ b/docs/Dokumen_Testing_POS.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{382AFBE5-5776-4C77-AC99-F7AE9F037E43}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26743EBC-3E1C-49C3-A497-B0DF9D1142FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="867" firstSheet="6" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="867" firstSheet="6" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Daftar Isi" sheetId="1" r:id="rId1"/>
@@ -65,7 +65,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2309" uniqueCount="1158">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2310" uniqueCount="1158">
   <si>
     <t>DOKUMEN TESTING APLIKASI POS</t>
   </si>
@@ -1372,9 +1372,6 @@
   </si>
   <si>
     <t>TEST CASE - PEMBELIAN (SUPPLIER PURCHASE)</t>
-  </si>
-  <si>
-    <t>Generate kode pembelian otomatis</t>
   </si>
   <si>
     <t>1. Klik Tambah Pembelian</t>
@@ -3687,6 +3684,9 @@
   </si>
   <si>
     <t>name: PT Sumber Makmur (duplikat)</t>
+  </si>
+  <si>
+    <t>Generate kode PO otomatis</t>
   </si>
 </sst>
 </file>
@@ -4740,7 +4740,7 @@
         <v>5</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="72.5" x14ac:dyDescent="0.35">
@@ -4766,7 +4766,7 @@
         <v>5</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="29" x14ac:dyDescent="0.35">
@@ -4783,7 +4783,7 @@
         <v>401</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>1157</v>
+        <v>1156</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>246</v>
@@ -4792,7 +4792,7 @@
         <v>5</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
@@ -4818,7 +4818,7 @@
         <v>5</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="29" x14ac:dyDescent="0.35">
@@ -4844,7 +4844,7 @@
         <v>5</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
@@ -4870,7 +4870,7 @@
         <v>5</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.35">
@@ -4881,19 +4881,22 @@
         <v>119</v>
       </c>
       <c r="C10" s="2" t="s">
+        <v>1153</v>
+      </c>
+      <c r="D10" s="2" t="s">
         <v>1154</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>1155</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>407</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>1156</v>
+        <v>1155</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>5</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>1117</v>
       </c>
     </row>
   </sheetData>
@@ -4966,22 +4969,22 @@
         <v>229</v>
       </c>
       <c r="C4" s="2" t="s">
+        <v>1157</v>
+      </c>
+      <c r="D4" s="2" t="s">
         <v>414</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>415</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>159</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="2" t="s">
-        <v>5</v>
+      <c r="H4" s="3" t="s">
+        <v>1117</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="72.5" x14ac:dyDescent="0.35">
@@ -4992,22 +4995,22 @@
         <v>229</v>
       </c>
       <c r="C5" s="2" t="s">
+        <v>416</v>
+      </c>
+      <c r="D5" s="2" t="s">
         <v>417</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="E5" s="2" t="s">
         <v>418</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="F5" s="2" t="s">
         <v>419</v>
       </c>
-      <c r="F5" s="2" t="s">
-        <v>420</v>
-      </c>
       <c r="G5" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="H5" s="2" t="s">
-        <v>5</v>
+      <c r="H5" s="3" t="s">
+        <v>1117</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="29" x14ac:dyDescent="0.35">
@@ -5018,16 +5021,16 @@
         <v>229</v>
       </c>
       <c r="C6" s="2" t="s">
+        <v>420</v>
+      </c>
+      <c r="D6" s="2" t="s">
         <v>421</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="E6" s="2" t="s">
         <v>422</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="F6" s="2" t="s">
         <v>423</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>424</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>5</v>
@@ -5044,16 +5047,16 @@
         <v>229</v>
       </c>
       <c r="C7" s="2" t="s">
+        <v>424</v>
+      </c>
+      <c r="D7" s="2" t="s">
         <v>425</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="E7" s="2" t="s">
         <v>426</v>
       </c>
-      <c r="E7" s="2" t="s">
+      <c r="F7" s="2" t="s">
         <v>427</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>428</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>5</v>
@@ -5070,16 +5073,16 @@
         <v>229</v>
       </c>
       <c r="C8" s="2" t="s">
+        <v>428</v>
+      </c>
+      <c r="D8" s="2" t="s">
         <v>429</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="E8" s="2" t="s">
         <v>430</v>
       </c>
-      <c r="E8" s="2" t="s">
+      <c r="F8" s="2" t="s">
         <v>431</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>432</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>5</v>
@@ -5096,16 +5099,16 @@
         <v>229</v>
       </c>
       <c r="C9" s="2" t="s">
+        <v>432</v>
+      </c>
+      <c r="D9" s="2" t="s">
         <v>433</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>434</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>159</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>5</v>
@@ -5122,16 +5125,16 @@
         <v>229</v>
       </c>
       <c r="C10" s="2" t="s">
+        <v>435</v>
+      </c>
+      <c r="D10" s="2" t="s">
         <v>436</v>
       </c>
-      <c r="D10" s="2" t="s">
+      <c r="E10" s="2" t="s">
         <v>437</v>
       </c>
-      <c r="E10" s="2" t="s">
+      <c r="F10" s="2" t="s">
         <v>438</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>439</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>5</v>
@@ -5148,16 +5151,16 @@
         <v>229</v>
       </c>
       <c r="C11" s="2" t="s">
+        <v>439</v>
+      </c>
+      <c r="D11" s="2" t="s">
         <v>440</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>441</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>159</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>5</v>
@@ -5174,16 +5177,16 @@
         <v>229</v>
       </c>
       <c r="C12" s="2" t="s">
+        <v>442</v>
+      </c>
+      <c r="D12" s="2" t="s">
         <v>443</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>444</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>159</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>5</v>
@@ -5218,7 +5221,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A1" s="7" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="B1" s="7"/>
       <c r="C1" s="7"/>
@@ -5262,16 +5265,16 @@
         <v>229</v>
       </c>
       <c r="C4" s="2" t="s">
+        <v>446</v>
+      </c>
+      <c r="D4" s="2" t="s">
         <v>447</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="E4" s="2" t="s">
         <v>448</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="F4" s="2" t="s">
         <v>449</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>450</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>5</v>
@@ -5288,13 +5291,13 @@
         <v>229</v>
       </c>
       <c r="C5" s="2" t="s">
+        <v>450</v>
+      </c>
+      <c r="D5" s="2" t="s">
         <v>451</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="E5" s="2" t="s">
         <v>452</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>453</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>319</v>
@@ -5314,16 +5317,16 @@
         <v>229</v>
       </c>
       <c r="C6" s="2" t="s">
+        <v>453</v>
+      </c>
+      <c r="D6" s="2" t="s">
         <v>454</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="E6" s="2" t="s">
         <v>455</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="F6" s="2" t="s">
         <v>456</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>457</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>5</v>
@@ -5340,16 +5343,16 @@
         <v>229</v>
       </c>
       <c r="C7" s="2" t="s">
+        <v>457</v>
+      </c>
+      <c r="D7" s="2" t="s">
         <v>458</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="E7" s="2" t="s">
         <v>459</v>
       </c>
-      <c r="E7" s="2" t="s">
+      <c r="F7" s="2" t="s">
         <v>460</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>461</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>5</v>
@@ -5366,16 +5369,16 @@
         <v>229</v>
       </c>
       <c r="C8" s="2" t="s">
+        <v>461</v>
+      </c>
+      <c r="D8" s="2" t="s">
         <v>462</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>463</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>159</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>5</v>
@@ -5392,7 +5395,7 @@
         <v>229</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>1150</v>
+        <v>1149</v>
       </c>
     </row>
   </sheetData>
@@ -5421,7 +5424,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A1" s="7" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="B1" s="7"/>
       <c r="C1" s="7"/>
@@ -5465,16 +5468,16 @@
         <v>229</v>
       </c>
       <c r="C4" s="2" t="s">
+        <v>465</v>
+      </c>
+      <c r="D4" s="2" t="s">
         <v>466</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>467</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>159</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>5</v>
@@ -5491,16 +5494,16 @@
         <v>229</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>397</v>
       </c>
       <c r="E5" s="2" t="s">
+        <v>469</v>
+      </c>
+      <c r="F5" s="2" t="s">
         <v>470</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>471</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>5</v>
@@ -5517,13 +5520,13 @@
         <v>229</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>290</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>246</v>
@@ -5543,13 +5546,13 @@
         <v>229</v>
       </c>
       <c r="C7" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="D7" s="2" t="s">
         <v>474</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="E7" s="2" t="s">
         <v>475</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>476</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>296</v>
@@ -5569,16 +5572,16 @@
         <v>229</v>
       </c>
       <c r="C8" s="2" t="s">
+        <v>476</v>
+      </c>
+      <c r="D8" s="2" t="s">
         <v>477</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="E8" s="2" t="s">
         <v>478</v>
       </c>
-      <c r="E8" s="2" t="s">
+      <c r="F8" s="2" t="s">
         <v>479</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>480</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>5</v>
@@ -5595,16 +5598,16 @@
         <v>229</v>
       </c>
       <c r="C9" s="2" t="s">
+        <v>480</v>
+      </c>
+      <c r="D9" s="2" t="s">
         <v>481</v>
       </c>
-      <c r="D9" s="2" t="s">
+      <c r="E9" s="2" t="s">
         <v>482</v>
       </c>
-      <c r="E9" s="2" t="s">
+      <c r="F9" s="2" t="s">
         <v>483</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>484</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>5</v>
@@ -5639,7 +5642,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A1" s="7" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="B1" s="7"/>
       <c r="C1" s="7"/>
@@ -5683,16 +5686,16 @@
         <v>229</v>
       </c>
       <c r="C4" s="2" t="s">
+        <v>485</v>
+      </c>
+      <c r="D4" s="2" t="s">
         <v>486</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="E4" s="2" t="s">
         <v>487</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="F4" s="2" t="s">
         <v>488</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>489</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>5</v>
@@ -5709,16 +5712,16 @@
         <v>229</v>
       </c>
       <c r="C5" s="2" t="s">
+        <v>489</v>
+      </c>
+      <c r="D5" s="2" t="s">
         <v>490</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>491</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>159</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>5</v>
@@ -5735,16 +5738,16 @@
         <v>229</v>
       </c>
       <c r="C6" s="2" t="s">
+        <v>492</v>
+      </c>
+      <c r="D6" s="2" t="s">
         <v>493</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="E6" s="2" t="s">
         <v>494</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="F6" s="2" t="s">
         <v>495</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>496</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>5</v>
@@ -5761,16 +5764,16 @@
         <v>229</v>
       </c>
       <c r="C7" s="2" t="s">
+        <v>496</v>
+      </c>
+      <c r="D7" s="2" t="s">
         <v>497</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="E7" s="2" t="s">
+        <v>430</v>
+      </c>
+      <c r="F7" s="2" t="s">
         <v>498</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>431</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>499</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>5</v>
@@ -5787,16 +5790,16 @@
         <v>229</v>
       </c>
       <c r="C8" s="2" t="s">
+        <v>499</v>
+      </c>
+      <c r="D8" s="2" t="s">
         <v>500</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>501</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>159</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>5</v>
@@ -5813,16 +5816,16 @@
         <v>229</v>
       </c>
       <c r="C9" s="2" t="s">
+        <v>502</v>
+      </c>
+      <c r="D9" s="2" t="s">
         <v>503</v>
       </c>
-      <c r="D9" s="2" t="s">
+      <c r="E9" s="2" t="s">
         <v>504</v>
       </c>
-      <c r="E9" s="2" t="s">
+      <c r="F9" s="2" t="s">
         <v>505</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>506</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>5</v>
@@ -5857,7 +5860,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A1" s="7" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="B1" s="7"/>
       <c r="C1" s="7"/>
@@ -5901,16 +5904,16 @@
         <v>229</v>
       </c>
       <c r="C4" s="2" t="s">
+        <v>507</v>
+      </c>
+      <c r="D4" s="2" t="s">
         <v>508</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>509</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>159</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>5</v>
@@ -5927,16 +5930,16 @@
         <v>229</v>
       </c>
       <c r="C5" s="2" t="s">
+        <v>510</v>
+      </c>
+      <c r="D5" s="2" t="s">
         <v>511</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="E5" s="2" t="s">
         <v>512</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="F5" s="2" t="s">
         <v>513</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>514</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>5</v>
@@ -5953,16 +5956,16 @@
         <v>229</v>
       </c>
       <c r="C6" s="2" t="s">
+        <v>514</v>
+      </c>
+      <c r="D6" s="2" t="s">
         <v>515</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="E6" s="2" t="s">
         <v>516</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="F6" s="2" t="s">
         <v>517</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>518</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>5</v>
@@ -5979,13 +5982,13 @@
         <v>229</v>
       </c>
       <c r="C7" s="2" t="s">
+        <v>518</v>
+      </c>
+      <c r="D7" s="2" t="s">
         <v>519</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="E7" s="2" t="s">
         <v>520</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>521</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>296</v>
@@ -6005,16 +6008,16 @@
         <v>229</v>
       </c>
       <c r="C8" s="2" t="s">
+        <v>521</v>
+      </c>
+      <c r="D8" s="2" t="s">
         <v>522</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>523</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>159</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>5</v>
@@ -6031,16 +6034,16 @@
         <v>229</v>
       </c>
       <c r="C9" s="2" t="s">
+        <v>524</v>
+      </c>
+      <c r="D9" s="2" t="s">
         <v>525</v>
       </c>
-      <c r="D9" s="2" t="s">
+      <c r="E9" s="2" t="s">
         <v>526</v>
       </c>
-      <c r="E9" s="2" t="s">
+      <c r="F9" s="2" t="s">
         <v>527</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>528</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>5</v>
@@ -6075,7 +6078,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A1" s="7" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="B1" s="7"/>
       <c r="C1" s="7"/>
@@ -6119,16 +6122,16 @@
         <v>128</v>
       </c>
       <c r="C4" s="2" t="s">
+        <v>529</v>
+      </c>
+      <c r="D4" s="2" t="s">
         <v>530</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="E4" s="2" t="s">
         <v>531</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="F4" s="2" t="s">
         <v>532</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>533</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>5</v>
@@ -6145,16 +6148,16 @@
         <v>128</v>
       </c>
       <c r="C5" s="2" t="s">
+        <v>533</v>
+      </c>
+      <c r="D5" s="2" t="s">
         <v>534</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>535</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>159</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>5</v>
@@ -6171,16 +6174,16 @@
         <v>128</v>
       </c>
       <c r="C6" s="2" t="s">
+        <v>536</v>
+      </c>
+      <c r="D6" s="2" t="s">
         <v>537</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="E6" s="2" t="s">
         <v>538</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="F6" s="2" t="s">
         <v>539</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>540</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>5</v>
@@ -6197,16 +6200,16 @@
         <v>128</v>
       </c>
       <c r="C7" s="2" t="s">
+        <v>540</v>
+      </c>
+      <c r="D7" s="2" t="s">
         <v>541</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="E7" s="2" t="s">
         <v>542</v>
       </c>
-      <c r="E7" s="2" t="s">
+      <c r="F7" s="2" t="s">
         <v>543</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>544</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>5</v>
@@ -6223,16 +6226,16 @@
         <v>128</v>
       </c>
       <c r="C8" s="2" t="s">
+        <v>544</v>
+      </c>
+      <c r="D8" s="2" t="s">
         <v>545</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="E8" s="2" t="s">
         <v>546</v>
       </c>
-      <c r="E8" s="2" t="s">
+      <c r="F8" s="2" t="s">
         <v>547</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>548</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>5</v>
@@ -6249,16 +6252,16 @@
         <v>229</v>
       </c>
       <c r="C9" s="2" t="s">
+        <v>548</v>
+      </c>
+      <c r="D9" s="2" t="s">
         <v>549</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>550</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>159</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>5</v>
@@ -6275,16 +6278,16 @@
         <v>229</v>
       </c>
       <c r="C10" s="2" t="s">
+        <v>551</v>
+      </c>
+      <c r="D10" s="2" t="s">
         <v>552</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>553</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>159</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>5</v>
@@ -6319,7 +6322,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A1" s="7" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="B1" s="7"/>
       <c r="C1" s="7"/>
@@ -6360,19 +6363,19 @@
         <v>1</v>
       </c>
       <c r="B4" s="2" t="s">
+        <v>555</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>556</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="D4" s="2" t="s">
         <v>557</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="E4" s="2" t="s">
         <v>558</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="F4" s="2" t="s">
         <v>559</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>560</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>5</v>
@@ -6389,13 +6392,13 @@
         <v>132</v>
       </c>
       <c r="C5" s="2" t="s">
+        <v>560</v>
+      </c>
+      <c r="D5" s="2" t="s">
         <v>561</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="E5" s="2" t="s">
         <v>562</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>563</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>319</v>
@@ -6415,16 +6418,16 @@
         <v>229</v>
       </c>
       <c r="C6" s="2" t="s">
+        <v>563</v>
+      </c>
+      <c r="D6" s="2" t="s">
         <v>564</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="E6" s="2" t="s">
         <v>565</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="F6" s="2" t="s">
         <v>566</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>567</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>5</v>
@@ -6441,16 +6444,16 @@
         <v>229</v>
       </c>
       <c r="C7" s="2" t="s">
+        <v>567</v>
+      </c>
+      <c r="D7" s="2" t="s">
         <v>568</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>569</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>159</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>5</v>
@@ -6467,16 +6470,16 @@
         <v>229</v>
       </c>
       <c r="C8" s="2" t="s">
+        <v>570</v>
+      </c>
+      <c r="D8" s="2" t="s">
         <v>571</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="E8" s="2" t="s">
         <v>572</v>
       </c>
-      <c r="E8" s="2" t="s">
+      <c r="F8" s="2" t="s">
         <v>573</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>574</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>5</v>
@@ -6511,7 +6514,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A1" s="7" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="B1" s="7"/>
       <c r="C1" s="7"/>
@@ -6555,16 +6558,16 @@
         <v>128</v>
       </c>
       <c r="C4" s="2" t="s">
+        <v>575</v>
+      </c>
+      <c r="D4" s="2" t="s">
         <v>576</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="E4" s="2" t="s">
         <v>577</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="F4" s="2" t="s">
         <v>578</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>579</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>5</v>
@@ -6581,16 +6584,16 @@
         <v>128</v>
       </c>
       <c r="C5" s="2" t="s">
+        <v>579</v>
+      </c>
+      <c r="D5" s="2" t="s">
         <v>580</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="E5" s="2" t="s">
         <v>581</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="F5" s="2" t="s">
         <v>582</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>583</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>5</v>
@@ -6607,16 +6610,16 @@
         <v>128</v>
       </c>
       <c r="C6" s="2" t="s">
+        <v>583</v>
+      </c>
+      <c r="D6" s="2" t="s">
         <v>584</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="E6" s="2" t="s">
         <v>585</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="F6" s="2" t="s">
         <v>586</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>587</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>5</v>
@@ -6633,16 +6636,16 @@
         <v>128</v>
       </c>
       <c r="C7" s="2" t="s">
+        <v>587</v>
+      </c>
+      <c r="D7" s="2" t="s">
         <v>588</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="E7" s="2" t="s">
         <v>589</v>
       </c>
-      <c r="E7" s="2" t="s">
+      <c r="F7" s="2" t="s">
         <v>590</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>591</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>5</v>
@@ -6659,16 +6662,16 @@
         <v>128</v>
       </c>
       <c r="C8" s="2" t="s">
+        <v>591</v>
+      </c>
+      <c r="D8" s="2" t="s">
         <v>592</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="E8" s="2" t="s">
         <v>593</v>
       </c>
-      <c r="E8" s="2" t="s">
+      <c r="F8" s="2" t="s">
         <v>594</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>595</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>5</v>
@@ -6685,16 +6688,16 @@
         <v>128</v>
       </c>
       <c r="C9" s="2" t="s">
+        <v>595</v>
+      </c>
+      <c r="D9" s="2" t="s">
         <v>596</v>
       </c>
-      <c r="D9" s="2" t="s">
+      <c r="E9" s="2" t="s">
         <v>597</v>
       </c>
-      <c r="E9" s="2" t="s">
+      <c r="F9" s="2" t="s">
         <v>598</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>599</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>5</v>
@@ -6711,16 +6714,16 @@
         <v>128</v>
       </c>
       <c r="C10" s="2" t="s">
+        <v>599</v>
+      </c>
+      <c r="D10" s="2" t="s">
         <v>600</v>
       </c>
-      <c r="D10" s="2" t="s">
-        <v>601</v>
-      </c>
       <c r="E10" s="2" t="s">
+        <v>422</v>
+      </c>
+      <c r="F10" s="2" t="s">
         <v>423</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>424</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>5</v>
@@ -6737,13 +6740,13 @@
         <v>128</v>
       </c>
       <c r="C11" s="2" t="s">
+        <v>601</v>
+      </c>
+      <c r="D11" s="2" t="s">
         <v>602</v>
       </c>
-      <c r="D11" s="2" t="s">
+      <c r="E11" s="2" t="s">
         <v>603</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>604</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>368</v>
@@ -6763,16 +6766,16 @@
         <v>128</v>
       </c>
       <c r="C12" s="2" t="s">
+        <v>604</v>
+      </c>
+      <c r="D12" s="2" t="s">
         <v>605</v>
       </c>
-      <c r="D12" s="2" t="s">
+      <c r="E12" s="2" t="s">
         <v>606</v>
       </c>
-      <c r="E12" s="2" t="s">
+      <c r="F12" s="2" t="s">
         <v>607</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>608</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>5</v>
@@ -6789,16 +6792,16 @@
         <v>128</v>
       </c>
       <c r="C13" s="2" t="s">
+        <v>608</v>
+      </c>
+      <c r="D13" s="2" t="s">
         <v>609</v>
       </c>
-      <c r="D13" s="2" t="s">
+      <c r="E13" s="2" t="s">
         <v>610</v>
       </c>
-      <c r="E13" s="2" t="s">
+      <c r="F13" s="2" t="s">
         <v>611</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>612</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>5</v>
@@ -6815,16 +6818,16 @@
         <v>128</v>
       </c>
       <c r="C14" s="2" t="s">
+        <v>612</v>
+      </c>
+      <c r="D14" s="2" t="s">
         <v>613</v>
       </c>
-      <c r="D14" s="2" t="s">
+      <c r="E14" s="2" t="s">
         <v>614</v>
       </c>
-      <c r="E14" s="2" t="s">
+      <c r="F14" s="2" t="s">
         <v>615</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>616</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>5</v>
@@ -6841,16 +6844,16 @@
         <v>229</v>
       </c>
       <c r="C15" s="2" t="s">
+        <v>616</v>
+      </c>
+      <c r="D15" s="2" t="s">
         <v>617</v>
       </c>
-      <c r="D15" s="2" t="s">
+      <c r="E15" s="2" t="s">
         <v>618</v>
       </c>
-      <c r="E15" s="2" t="s">
+      <c r="F15" s="2" t="s">
         <v>619</v>
-      </c>
-      <c r="F15" s="2" t="s">
-        <v>620</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>5</v>
@@ -6867,16 +6870,16 @@
         <v>128</v>
       </c>
       <c r="C16" s="2" t="s">
+        <v>620</v>
+      </c>
+      <c r="D16" s="2" t="s">
         <v>621</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>622</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>159</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>5</v>
@@ -6893,16 +6896,16 @@
         <v>229</v>
       </c>
       <c r="C17" s="2" t="s">
+        <v>623</v>
+      </c>
+      <c r="D17" s="2" t="s">
         <v>624</v>
       </c>
-      <c r="D17" s="2" t="s">
+      <c r="E17" s="2" t="s">
+        <v>572</v>
+      </c>
+      <c r="F17" s="2" t="s">
         <v>625</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>573</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>626</v>
       </c>
       <c r="G17" s="2" t="s">
         <v>5</v>
@@ -6937,7 +6940,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A1" s="7" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="B1" s="7"/>
       <c r="C1" s="7"/>
@@ -6981,16 +6984,16 @@
         <v>229</v>
       </c>
       <c r="C4" s="2" t="s">
+        <v>627</v>
+      </c>
+      <c r="D4" s="2" t="s">
         <v>628</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>629</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>159</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>5</v>
@@ -7007,16 +7010,16 @@
         <v>229</v>
       </c>
       <c r="C5" s="2" t="s">
+        <v>630</v>
+      </c>
+      <c r="D5" s="2" t="s">
         <v>631</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="E5" s="2" t="s">
         <v>632</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="F5" s="2" t="s">
         <v>633</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>634</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>5</v>
@@ -7033,16 +7036,16 @@
         <v>229</v>
       </c>
       <c r="C6" s="2" t="s">
+        <v>634</v>
+      </c>
+      <c r="D6" s="2" t="s">
         <v>635</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>636</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>159</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>5</v>
@@ -7059,16 +7062,16 @@
         <v>229</v>
       </c>
       <c r="C7" s="2" t="s">
+        <v>637</v>
+      </c>
+      <c r="D7" s="2" t="s">
         <v>638</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>639</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>159</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>5</v>
@@ -7085,16 +7088,16 @@
         <v>229</v>
       </c>
       <c r="C8" s="2" t="s">
+        <v>640</v>
+      </c>
+      <c r="D8" s="2" t="s">
         <v>641</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>642</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>159</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>5</v>
@@ -7111,16 +7114,16 @@
         <v>128</v>
       </c>
       <c r="C9" s="2" t="s">
+        <v>643</v>
+      </c>
+      <c r="D9" s="2" t="s">
         <v>644</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>645</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>159</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>5</v>
@@ -7214,7 +7217,7 @@
         <v>5</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="29" x14ac:dyDescent="0.35">
@@ -7240,7 +7243,7 @@
         <v>5</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="29" x14ac:dyDescent="0.35">
@@ -7266,7 +7269,7 @@
         <v>5</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="29" x14ac:dyDescent="0.35">
@@ -7292,7 +7295,7 @@
         <v>5</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="29" x14ac:dyDescent="0.35">
@@ -7318,7 +7321,7 @@
         <v>5</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="29" x14ac:dyDescent="0.35">
@@ -7344,7 +7347,7 @@
         <v>5</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="29" x14ac:dyDescent="0.35">
@@ -7370,7 +7373,7 @@
         <v>5</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
@@ -7396,7 +7399,7 @@
         <v>5</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
@@ -7448,7 +7451,7 @@
         <v>5</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
@@ -7503,7 +7506,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A1" s="7" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="B1" s="7"/>
       <c r="C1" s="7"/>
@@ -7547,16 +7550,16 @@
         <v>229</v>
       </c>
       <c r="C4" s="2" t="s">
+        <v>647</v>
+      </c>
+      <c r="D4" s="2" t="s">
         <v>648</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="E4" s="2" t="s">
         <v>649</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="F4" s="2" t="s">
         <v>650</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>651</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>5</v>
@@ -7573,16 +7576,16 @@
         <v>229</v>
       </c>
       <c r="C5" s="2" t="s">
+        <v>651</v>
+      </c>
+      <c r="D5" s="2" t="s">
         <v>652</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>653</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>159</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>5</v>
@@ -7599,16 +7602,16 @@
         <v>229</v>
       </c>
       <c r="C6" s="2" t="s">
+        <v>654</v>
+      </c>
+      <c r="D6" s="2" t="s">
         <v>655</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>656</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>159</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>5</v>
@@ -7625,16 +7628,16 @@
         <v>229</v>
       </c>
       <c r="C7" s="2" t="s">
+        <v>657</v>
+      </c>
+      <c r="D7" s="2" t="s">
         <v>658</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="E7" s="2" t="s">
         <v>659</v>
       </c>
-      <c r="E7" s="2" t="s">
+      <c r="F7" s="2" t="s">
         <v>660</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>661</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>5</v>
@@ -7651,16 +7654,16 @@
         <v>229</v>
       </c>
       <c r="C8" s="2" t="s">
+        <v>661</v>
+      </c>
+      <c r="D8" s="2" t="s">
         <v>662</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>663</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>159</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>5</v>
@@ -7677,16 +7680,16 @@
         <v>229</v>
       </c>
       <c r="C9" s="2" t="s">
+        <v>664</v>
+      </c>
+      <c r="D9" s="2" t="s">
         <v>665</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>666</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>159</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>5</v>
@@ -7703,16 +7706,16 @@
         <v>229</v>
       </c>
       <c r="C10" s="2" t="s">
+        <v>667</v>
+      </c>
+      <c r="D10" s="2" t="s">
         <v>668</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>669</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>159</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>5</v>
@@ -7729,16 +7732,16 @@
         <v>229</v>
       </c>
       <c r="C11" s="2" t="s">
+        <v>670</v>
+      </c>
+      <c r="D11" s="2" t="s">
         <v>671</v>
       </c>
-      <c r="D11" s="2" t="s">
+      <c r="E11" s="2" t="s">
         <v>672</v>
       </c>
-      <c r="E11" s="2" t="s">
+      <c r="F11" s="2" t="s">
         <v>673</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>674</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>5</v>
@@ -7755,16 +7758,16 @@
         <v>229</v>
       </c>
       <c r="C12" s="2" t="s">
+        <v>674</v>
+      </c>
+      <c r="D12" s="2" t="s">
         <v>675</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>676</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>159</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>5</v>
@@ -7781,16 +7784,16 @@
         <v>128</v>
       </c>
       <c r="C13" s="2" t="s">
+        <v>676</v>
+      </c>
+      <c r="D13" s="2" t="s">
         <v>677</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>678</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>159</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>5</v>
@@ -7825,7 +7828,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A1" s="7" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="B1" s="7"/>
       <c r="C1" s="7"/>
@@ -7869,16 +7872,16 @@
         <v>229</v>
       </c>
       <c r="C4" s="2" t="s">
+        <v>680</v>
+      </c>
+      <c r="D4" s="2" t="s">
         <v>681</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>682</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>159</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>5</v>
@@ -7895,16 +7898,16 @@
         <v>229</v>
       </c>
       <c r="C5" s="2" t="s">
+        <v>683</v>
+      </c>
+      <c r="D5" s="2" t="s">
         <v>684</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>685</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>159</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>5</v>
@@ -7921,16 +7924,16 @@
         <v>229</v>
       </c>
       <c r="C6" s="2" t="s">
+        <v>686</v>
+      </c>
+      <c r="D6" s="2" t="s">
         <v>687</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>688</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>159</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>5</v>
@@ -7947,16 +7950,16 @@
         <v>229</v>
       </c>
       <c r="C7" s="2" t="s">
+        <v>689</v>
+      </c>
+      <c r="D7" s="2" t="s">
         <v>690</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>691</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>159</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>5</v>
@@ -7973,16 +7976,16 @@
         <v>128</v>
       </c>
       <c r="C8" s="2" t="s">
+        <v>692</v>
+      </c>
+      <c r="D8" s="2" t="s">
         <v>693</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>694</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>159</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>5</v>
@@ -8017,7 +8020,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A1" s="7" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="B1" s="7"/>
       <c r="C1" s="7"/>
@@ -8061,16 +8064,16 @@
         <v>132</v>
       </c>
       <c r="C4" s="2" t="s">
+        <v>696</v>
+      </c>
+      <c r="D4" s="2" t="s">
         <v>697</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>698</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>159</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>5</v>
@@ -8087,16 +8090,16 @@
         <v>229</v>
       </c>
       <c r="C5" s="2" t="s">
+        <v>699</v>
+      </c>
+      <c r="D5" s="2" t="s">
         <v>700</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="E5" s="2" t="s">
         <v>701</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="F5" s="2" t="s">
         <v>702</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>703</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>5</v>
@@ -8113,16 +8116,16 @@
         <v>124</v>
       </c>
       <c r="C6" s="2" t="s">
+        <v>703</v>
+      </c>
+      <c r="D6" s="2" t="s">
         <v>704</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>705</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>159</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>5</v>
@@ -8139,16 +8142,16 @@
         <v>119</v>
       </c>
       <c r="C7" s="2" t="s">
+        <v>706</v>
+      </c>
+      <c r="D7" s="2" t="s">
         <v>707</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>708</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>159</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>5</v>
@@ -8165,16 +8168,16 @@
         <v>229</v>
       </c>
       <c r="C8" s="2" t="s">
+        <v>709</v>
+      </c>
+      <c r="D8" s="2" t="s">
         <v>710</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="E8" s="2" t="s">
         <v>711</v>
       </c>
-      <c r="E8" s="2" t="s">
+      <c r="F8" s="2" t="s">
         <v>712</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>713</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>5</v>
@@ -8191,16 +8194,16 @@
         <v>229</v>
       </c>
       <c r="C9" s="2" t="s">
+        <v>713</v>
+      </c>
+      <c r="D9" s="2" t="s">
         <v>714</v>
       </c>
-      <c r="D9" s="2" t="s">
+      <c r="E9" s="2" t="s">
         <v>715</v>
       </c>
-      <c r="E9" s="2" t="s">
+      <c r="F9" s="2" t="s">
         <v>716</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>717</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>5</v>
@@ -8217,16 +8220,16 @@
         <v>128</v>
       </c>
       <c r="C10" s="2" t="s">
+        <v>717</v>
+      </c>
+      <c r="D10" s="2" t="s">
         <v>718</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>719</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>159</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>5</v>
@@ -8261,7 +8264,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A1" s="7" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="B1" s="7"/>
       <c r="C1" s="7"/>
@@ -8305,16 +8308,16 @@
         <v>229</v>
       </c>
       <c r="C4" s="2" t="s">
+        <v>721</v>
+      </c>
+      <c r="D4" s="2" t="s">
         <v>722</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>723</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>159</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>5</v>
@@ -8331,16 +8334,16 @@
         <v>229</v>
       </c>
       <c r="C5" s="2" t="s">
+        <v>724</v>
+      </c>
+      <c r="D5" s="2" t="s">
         <v>725</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>726</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>159</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>5</v>
@@ -8357,16 +8360,16 @@
         <v>229</v>
       </c>
       <c r="C6" s="2" t="s">
+        <v>727</v>
+      </c>
+      <c r="D6" s="2" t="s">
         <v>728</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>729</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>159</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>5</v>
@@ -8383,16 +8386,16 @@
         <v>124</v>
       </c>
       <c r="C7" s="2" t="s">
+        <v>730</v>
+      </c>
+      <c r="D7" s="2" t="s">
         <v>731</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="E7" s="2" t="s">
         <v>732</v>
       </c>
-      <c r="E7" s="2" t="s">
+      <c r="F7" s="2" t="s">
         <v>733</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>734</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>5</v>
@@ -8409,16 +8412,16 @@
         <v>119</v>
       </c>
       <c r="C8" s="2" t="s">
+        <v>734</v>
+      </c>
+      <c r="D8" s="2" t="s">
         <v>735</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>736</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>159</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>5</v>
@@ -8453,7 +8456,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A1" s="7" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="B1" s="7"/>
       <c r="C1" s="7"/>
@@ -8497,16 +8500,16 @@
         <v>229</v>
       </c>
       <c r="C4" s="2" t="s">
+        <v>738</v>
+      </c>
+      <c r="D4" s="2" t="s">
         <v>739</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>740</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>159</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>5</v>
@@ -8523,16 +8526,16 @@
         <v>229</v>
       </c>
       <c r="C5" s="2" t="s">
+        <v>741</v>
+      </c>
+      <c r="D5" s="2" t="s">
         <v>742</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>743</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>159</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>5</v>
@@ -8549,16 +8552,16 @@
         <v>229</v>
       </c>
       <c r="C6" s="2" t="s">
+        <v>744</v>
+      </c>
+      <c r="D6" s="2" t="s">
         <v>745</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="E6" s="2" t="s">
         <v>746</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="F6" s="2" t="s">
         <v>747</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>748</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>5</v>
@@ -8575,16 +8578,16 @@
         <v>229</v>
       </c>
       <c r="C7" s="2" t="s">
+        <v>748</v>
+      </c>
+      <c r="D7" s="2" t="s">
         <v>749</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="E7" s="2" t="s">
         <v>750</v>
       </c>
-      <c r="E7" s="2" t="s">
+      <c r="F7" s="2" t="s">
         <v>751</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>752</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>5</v>
@@ -8601,16 +8604,16 @@
         <v>229</v>
       </c>
       <c r="C8" s="2" t="s">
+        <v>752</v>
+      </c>
+      <c r="D8" s="2" t="s">
         <v>753</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>754</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>159</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>5</v>
@@ -8627,16 +8630,16 @@
         <v>229</v>
       </c>
       <c r="C9" s="2" t="s">
+        <v>755</v>
+      </c>
+      <c r="D9" s="2" t="s">
         <v>756</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>757</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>159</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>5</v>
@@ -8650,19 +8653,19 @@
         <v>7</v>
       </c>
       <c r="B10" s="2" t="s">
+        <v>758</v>
+      </c>
+      <c r="C10" s="2" t="s">
         <v>759</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="D10" s="2" t="s">
         <v>760</v>
       </c>
-      <c r="D10" s="2" t="s">
+      <c r="E10" s="2" t="s">
         <v>761</v>
       </c>
-      <c r="E10" s="2" t="s">
+      <c r="F10" s="2" t="s">
         <v>762</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>763</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>5</v>
@@ -8697,7 +8700,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A1" s="7" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="B1" s="7"/>
       <c r="C1" s="7"/>
@@ -8738,19 +8741,19 @@
         <v>1</v>
       </c>
       <c r="B4" s="2" t="s">
+        <v>764</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>765</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="D4" s="2" t="s">
         <v>766</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>767</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>159</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>5</v>
@@ -8767,16 +8770,16 @@
         <v>229</v>
       </c>
       <c r="C5" s="2" t="s">
+        <v>768</v>
+      </c>
+      <c r="D5" s="2" t="s">
         <v>769</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>770</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>159</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>5</v>
@@ -8793,16 +8796,16 @@
         <v>229</v>
       </c>
       <c r="C6" s="2" t="s">
+        <v>771</v>
+      </c>
+      <c r="D6" s="2" t="s">
         <v>772</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="E6" s="2" t="s">
         <v>773</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="F6" s="2" t="s">
         <v>774</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>775</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>5</v>
@@ -8819,16 +8822,16 @@
         <v>128</v>
       </c>
       <c r="C7" s="2" t="s">
+        <v>775</v>
+      </c>
+      <c r="D7" s="2" t="s">
         <v>776</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>777</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>159</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>5</v>
@@ -8863,7 +8866,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A1" s="7" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="B1" s="7"/>
       <c r="C1" s="7"/>
@@ -8907,16 +8910,16 @@
         <v>128</v>
       </c>
       <c r="C4" s="2" t="s">
+        <v>779</v>
+      </c>
+      <c r="D4" s="2" t="s">
         <v>780</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>781</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>159</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>5</v>
@@ -8933,16 +8936,16 @@
         <v>128</v>
       </c>
       <c r="C5" s="2" t="s">
+        <v>782</v>
+      </c>
+      <c r="D5" s="2" t="s">
         <v>783</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>784</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>159</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>5</v>
@@ -8959,16 +8962,16 @@
         <v>128</v>
       </c>
       <c r="C6" s="2" t="s">
+        <v>784</v>
+      </c>
+      <c r="D6" s="2" t="s">
         <v>785</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>786</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>159</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>5</v>
@@ -8985,16 +8988,16 @@
         <v>128</v>
       </c>
       <c r="C7" s="2" t="s">
+        <v>786</v>
+      </c>
+      <c r="D7" s="2" t="s">
         <v>787</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>788</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>159</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>5</v>
@@ -9011,16 +9014,16 @@
         <v>128</v>
       </c>
       <c r="C8" s="2" t="s">
+        <v>788</v>
+      </c>
+      <c r="D8" s="2" t="s">
         <v>789</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>790</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>159</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>5</v>
@@ -9037,16 +9040,16 @@
         <v>128</v>
       </c>
       <c r="C9" s="2" t="s">
+        <v>791</v>
+      </c>
+      <c r="D9" s="2" t="s">
         <v>792</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>793</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>159</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>5</v>
@@ -9063,16 +9066,16 @@
         <v>124</v>
       </c>
       <c r="C10" s="2" t="s">
+        <v>794</v>
+      </c>
+      <c r="D10" s="2" t="s">
         <v>795</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>796</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>159</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>5</v>
@@ -9089,16 +9092,16 @@
         <v>132</v>
       </c>
       <c r="C11" s="2" t="s">
+        <v>797</v>
+      </c>
+      <c r="D11" s="2" t="s">
         <v>798</v>
       </c>
-      <c r="D11" s="2" t="s">
+      <c r="E11" s="2" t="s">
         <v>799</v>
       </c>
-      <c r="E11" s="2" t="s">
+      <c r="F11" s="2" t="s">
         <v>800</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>801</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>5</v>
@@ -9115,16 +9118,16 @@
         <v>132</v>
       </c>
       <c r="C12" s="2" t="s">
+        <v>801</v>
+      </c>
+      <c r="D12" s="2" t="s">
         <v>802</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>803</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>159</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>5</v>
@@ -9141,16 +9144,16 @@
         <v>132</v>
       </c>
       <c r="C13" s="2" t="s">
+        <v>804</v>
+      </c>
+      <c r="D13" s="2" t="s">
         <v>805</v>
       </c>
-      <c r="D13" s="2" t="s">
+      <c r="E13" s="2" t="s">
         <v>806</v>
       </c>
-      <c r="E13" s="2" t="s">
+      <c r="F13" s="2" t="s">
         <v>807</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>808</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>5</v>
@@ -9182,7 +9185,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A1" s="10" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="B1" s="10"/>
       <c r="C1" s="10"/>
@@ -9192,22 +9195,22 @@
     </row>
     <row r="3" spans="1:6" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
+        <v>809</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>810</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="C3" s="1" t="s">
         <v>811</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="D3" s="1" t="s">
         <v>812</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="E3" s="1" t="s">
         <v>813</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="F3" s="1" t="s">
         <v>814</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>815</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="29" x14ac:dyDescent="0.35">
@@ -9215,19 +9218,19 @@
         <v>119</v>
       </c>
       <c r="B4" s="2" t="s">
+        <v>815</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>816</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="D4" s="2" t="s">
         <v>817</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="E4" s="2" t="s">
         <v>818</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="F4" s="2" t="s">
         <v>819</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>820</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.35">
@@ -9235,19 +9238,19 @@
         <v>124</v>
       </c>
       <c r="B5" s="2" t="s">
+        <v>820</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>821</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="D5" s="2" t="s">
         <v>822</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="E5" s="2" t="s">
+        <v>818</v>
+      </c>
+      <c r="F5" s="2" t="s">
         <v>823</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>819</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>824</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="29" x14ac:dyDescent="0.35">
@@ -9255,19 +9258,19 @@
         <v>128</v>
       </c>
       <c r="B6" s="2" t="s">
+        <v>824</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>825</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="D6" s="2" t="s">
         <v>826</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="E6" s="2" t="s">
+        <v>818</v>
+      </c>
+      <c r="F6" s="2" t="s">
         <v>827</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>819</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>828</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.35">
@@ -9275,59 +9278,59 @@
         <v>128</v>
       </c>
       <c r="B7" s="2" t="s">
+        <v>828</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>825</v>
+      </c>
+      <c r="D7" s="2" t="s">
         <v>829</v>
       </c>
-      <c r="C7" s="2" t="s">
-        <v>826</v>
-      </c>
-      <c r="D7" s="2" t="s">
+      <c r="E7" s="2" t="s">
+        <v>818</v>
+      </c>
+      <c r="F7" s="2" t="s">
         <v>830</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>819</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>831</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
+        <v>831</v>
+      </c>
+      <c r="B8" s="2" t="s">
         <v>832</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="C8" s="2" t="s">
+        <v>825</v>
+      </c>
+      <c r="D8" s="2" t="s">
         <v>833</v>
       </c>
-      <c r="C8" s="2" t="s">
-        <v>826</v>
-      </c>
-      <c r="D8" s="2" t="s">
+      <c r="E8" s="2" t="s">
         <v>834</v>
       </c>
-      <c r="E8" s="2" t="s">
+      <c r="F8" s="2" t="s">
         <v>835</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>836</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A9" s="2" t="s">
+        <v>836</v>
+      </c>
+      <c r="B9" s="2" t="s">
         <v>837</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="C9" s="2" t="s">
         <v>838</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="D9" s="2" t="s">
         <v>839</v>
       </c>
-      <c r="D9" s="2" t="s">
+      <c r="E9" s="2" t="s">
+        <v>818</v>
+      </c>
+      <c r="F9" s="2" t="s">
         <v>840</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>819</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>841</v>
       </c>
     </row>
   </sheetData>
@@ -9353,7 +9356,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A1" s="10" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="B1" s="10"/>
       <c r="C1" s="10"/>
@@ -9363,142 +9366,142 @@
     </row>
     <row r="3" spans="1:6" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
+        <v>842</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>843</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="C3" s="1" t="s">
         <v>844</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="D3" s="1" t="s">
         <v>845</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="E3" s="1" t="s">
         <v>846</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="F3" s="1" t="s">
         <v>847</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>848</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
+        <v>815</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>816</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="C4" s="2" t="s">
         <v>817</v>
       </c>
-      <c r="C4" s="2" t="s">
-        <v>818</v>
-      </c>
       <c r="D4" s="2" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="E4" s="2" t="s">
+        <v>848</v>
+      </c>
+      <c r="F4" s="2" t="s">
         <v>849</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>850</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
+        <v>820</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>821</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="C5" s="2" t="s">
         <v>822</v>
       </c>
-      <c r="C5" s="2" t="s">
-        <v>823</v>
-      </c>
       <c r="D5" s="2" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="E5" s="2" t="s">
+        <v>848</v>
+      </c>
+      <c r="F5" s="2" t="s">
         <v>849</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>850</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
+        <v>824</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>825</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="C6" s="2" t="s">
         <v>826</v>
       </c>
-      <c r="C6" s="2" t="s">
-        <v>827</v>
-      </c>
       <c r="D6" s="2" t="s">
+        <v>850</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>848</v>
+      </c>
+      <c r="F6" s="2" t="s">
         <v>851</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>849</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>852</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
+        <v>828</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>825</v>
+      </c>
+      <c r="C7" s="2" t="s">
         <v>829</v>
       </c>
-      <c r="B7" s="2" t="s">
-        <v>826</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>830</v>
-      </c>
       <c r="D7" s="2" t="s">
+        <v>850</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>848</v>
+      </c>
+      <c r="F7" s="2" t="s">
         <v>851</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>849</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>852</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
+        <v>832</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>825</v>
+      </c>
+      <c r="C8" s="2" t="s">
         <v>833</v>
       </c>
-      <c r="B8" s="2" t="s">
-        <v>826</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>834</v>
-      </c>
       <c r="D8" s="2" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="E8" s="2" t="s">
+        <v>852</v>
+      </c>
+      <c r="F8" s="2" t="s">
         <v>853</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>854</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A9" s="2" t="s">
+        <v>837</v>
+      </c>
+      <c r="B9" s="2" t="s">
         <v>838</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="C9" s="2" t="s">
         <v>839</v>
       </c>
-      <c r="C9" s="2" t="s">
-        <v>840</v>
-      </c>
       <c r="D9" s="2" t="s">
+        <v>854</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>848</v>
+      </c>
+      <c r="F9" s="2" t="s">
         <v>855</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>849</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>856</v>
       </c>
     </row>
   </sheetData>
@@ -9524,7 +9527,7 @@
   <sheetData>
     <row r="1" spans="1:5" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A1" s="10" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="B1" s="10"/>
       <c r="C1" s="10"/>
@@ -9533,189 +9536,189 @@
     </row>
     <row r="3" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
+        <v>857</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>858</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="C3" s="1" t="s">
         <v>859</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="D3" s="1" t="s">
         <v>860</v>
       </c>
-      <c r="D3" s="1" t="s">
-        <v>861</v>
-      </c>
       <c r="E3" s="1" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
+        <v>861</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>862</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="C4" s="2" t="s">
         <v>863</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="D4" s="2" t="s">
         <v>864</v>
       </c>
-      <c r="D4" s="2" t="s">
-        <v>865</v>
-      </c>
       <c r="E4" s="2" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="B5" s="2" t="s">
+        <v>865</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>866</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="D5" s="2" t="s">
         <v>867</v>
       </c>
-      <c r="D5" s="2" t="s">
-        <v>868</v>
-      </c>
       <c r="E5" s="2" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="B6" s="2" t="s">
+        <v>868</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>869</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="D6" s="2" t="s">
         <v>870</v>
       </c>
-      <c r="D6" s="2" t="s">
-        <v>871</v>
-      </c>
       <c r="E6" s="2" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="B7" s="2" t="s">
+        <v>871</v>
+      </c>
+      <c r="C7" s="2" t="s">
         <v>872</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="D7" s="2" t="s">
         <v>873</v>
       </c>
-      <c r="D7" s="2" t="s">
-        <v>874</v>
-      </c>
       <c r="E7" s="2" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="B8" s="2" t="s">
+        <v>874</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>874</v>
+      </c>
+      <c r="D8" s="2" t="s">
         <v>875</v>
       </c>
-      <c r="C8" s="2" t="s">
-        <v>875</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>876</v>
-      </c>
       <c r="E8" s="2" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A9" s="2" t="s">
+        <v>876</v>
+      </c>
+      <c r="B9" s="2" t="s">
         <v>877</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="C9" s="2" t="s">
+        <v>877</v>
+      </c>
+      <c r="D9" s="2" t="s">
         <v>878</v>
       </c>
-      <c r="C9" s="2" t="s">
-        <v>878</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>879</v>
-      </c>
       <c r="E9" s="2" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A10" s="2" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
       <c r="B10" s="2" t="s">
+        <v>879</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>879</v>
+      </c>
+      <c r="D10" s="2" t="s">
         <v>880</v>
       </c>
-      <c r="C10" s="2" t="s">
-        <v>880</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>881</v>
-      </c>
       <c r="E10" s="2" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A11" s="2" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
       <c r="B11" s="2" t="s">
+        <v>881</v>
+      </c>
+      <c r="C11" s="2" t="s">
         <v>882</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="D11" s="2" t="s">
         <v>883</v>
       </c>
-      <c r="D11" s="2" t="s">
-        <v>884</v>
-      </c>
       <c r="E11" s="2" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A12" s="2" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
       <c r="B12" s="2" t="s">
+        <v>884</v>
+      </c>
+      <c r="C12" s="2" t="s">
         <v>885</v>
       </c>
-      <c r="C12" s="2" t="s">
+      <c r="D12" s="2" t="s">
         <v>886</v>
       </c>
-      <c r="D12" s="2" t="s">
-        <v>887</v>
-      </c>
       <c r="E12" s="2" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A13" s="2" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
       <c r="B13" s="2" t="s">
+        <v>887</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>887</v>
+      </c>
+      <c r="D13" s="2" t="s">
         <v>888</v>
       </c>
-      <c r="C13" s="2" t="s">
-        <v>888</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>889</v>
-      </c>
       <c r="E13" s="2" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
     </row>
   </sheetData>
@@ -9962,7 +9965,7 @@
   <sheetData>
     <row r="1" spans="1:10" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A1" s="10" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="B1" s="10"/>
       <c r="C1" s="10"/>
@@ -9976,34 +9979,34 @@
     </row>
     <row r="3" spans="1:10" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
+        <v>890</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>891</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="C3" s="1" t="s">
+        <v>858</v>
+      </c>
+      <c r="D3" s="1" t="s">
         <v>892</v>
       </c>
-      <c r="C3" s="1" t="s">
-        <v>859</v>
-      </c>
-      <c r="D3" s="1" t="s">
+      <c r="E3" s="1" t="s">
         <v>893</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="F3" s="1" t="s">
         <v>894</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="G3" s="1" t="s">
         <v>895</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="H3" s="1" t="s">
         <v>896</v>
       </c>
-      <c r="H3" s="1" t="s">
+      <c r="I3" s="1" t="s">
         <v>897</v>
       </c>
-      <c r="I3" s="1" t="s">
-        <v>898</v>
-      </c>
       <c r="J3" s="1" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.35">
@@ -10011,16 +10014,16 @@
         <v>8991002100016</v>
       </c>
       <c r="B4" s="2" t="s">
+        <v>898</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>899</v>
       </c>
-      <c r="C4" s="2" t="s">
-        <v>900</v>
-      </c>
       <c r="D4" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="F4" s="2">
         <v>2500</v>
@@ -10029,13 +10032,13 @@
         <v>3000</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="I4" s="2" t="s">
         <v>63</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.35">
@@ -10043,16 +10046,16 @@
         <v>8992388123456</v>
       </c>
       <c r="B5" s="2" t="s">
+        <v>903</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>904</v>
       </c>
-      <c r="C5" s="2" t="s">
-        <v>905</v>
-      </c>
       <c r="D5" s="2" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="F5" s="2">
         <v>4000</v>
@@ -10061,13 +10064,13 @@
         <v>5000</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="I5" s="2" t="s">
         <v>48</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.35">
@@ -10075,16 +10078,16 @@
         <v>8996001600028</v>
       </c>
       <c r="B6" s="2" t="s">
+        <v>906</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>907</v>
       </c>
-      <c r="C6" s="2" t="s">
-        <v>908</v>
-      </c>
       <c r="D6" s="2" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="F6" s="2">
         <v>2800</v>
@@ -10093,45 +10096,45 @@
         <v>3500</v>
       </c>
       <c r="H6" s="2" t="s">
+        <v>910</v>
+      </c>
+      <c r="I6" s="2" t="s">
         <v>911</v>
       </c>
-      <c r="I6" s="2" t="s">
-        <v>912</v>
-      </c>
       <c r="J6" s="2" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
     </row>
     <row r="7" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
+        <v>912</v>
+      </c>
+      <c r="B7" s="2" t="s">
         <v>913</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="C7" s="2" t="s">
         <v>914</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="D7" s="2" t="s">
+        <v>868</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>877</v>
+      </c>
+      <c r="F7" s="2" t="s">
         <v>915</v>
       </c>
-      <c r="D7" s="2" t="s">
-        <v>869</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>878</v>
-      </c>
-      <c r="F7" s="2" t="s">
+      <c r="G7" s="2" t="s">
         <v>916</v>
       </c>
-      <c r="G7" s="2" t="s">
+      <c r="H7" s="2" t="s">
         <v>917</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>918</v>
       </c>
       <c r="I7" s="2" t="s">
         <v>18</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.35">
@@ -10139,16 +10142,16 @@
         <v>8991234567890</v>
       </c>
       <c r="B8" s="2" t="s">
+        <v>918</v>
+      </c>
+      <c r="C8" s="2" t="s">
         <v>919</v>
       </c>
-      <c r="C8" s="2" t="s">
-        <v>920</v>
-      </c>
       <c r="D8" s="2" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="F8" s="2">
         <v>22000</v>
@@ -10157,13 +10160,13 @@
         <v>24000</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="I8" s="2" t="s">
         <v>33</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
     </row>
     <row r="9" spans="1:10" ht="29" x14ac:dyDescent="0.35">
@@ -10171,16 +10174,16 @@
         <v>8990001112223</v>
       </c>
       <c r="B9" s="2" t="s">
+        <v>921</v>
+      </c>
+      <c r="C9" s="2" t="s">
         <v>922</v>
       </c>
-      <c r="C9" s="2" t="s">
-        <v>923</v>
-      </c>
       <c r="D9" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="F9" s="2">
         <v>8500</v>
@@ -10195,7 +10198,7 @@
         <v>33</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.35">
@@ -10203,16 +10206,16 @@
         <v>8990004445556</v>
       </c>
       <c r="B10" s="2" t="s">
+        <v>925</v>
+      </c>
+      <c r="C10" s="2" t="s">
         <v>926</v>
       </c>
-      <c r="C10" s="2" t="s">
-        <v>927</v>
-      </c>
       <c r="D10" s="2" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="F10" s="2">
         <v>1200</v>
@@ -10221,36 +10224,36 @@
         <v>1500</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="I10" s="2" t="s">
         <v>63</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
     </row>
     <row r="11" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A11" s="2" t="s">
+        <v>930</v>
+      </c>
+      <c r="B11" s="2" t="s">
         <v>931</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="C11" s="2" t="s">
         <v>932</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="D11" s="2" t="s">
+        <v>862</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>877</v>
+      </c>
+      <c r="F11" s="2" t="s">
         <v>933</v>
       </c>
-      <c r="D11" s="2" t="s">
-        <v>863</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>878</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>934</v>
-      </c>
       <c r="G11" s="2" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="H11" s="2" t="s">
         <v>33</v>
@@ -10259,7 +10262,7 @@
         <v>18</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
     </row>
   </sheetData>
@@ -10285,7 +10288,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A1" s="10" t="s">
-        <v>936</v>
+        <v>935</v>
       </c>
       <c r="B1" s="10"/>
       <c r="C1" s="10"/>
@@ -10296,105 +10299,105 @@
     </row>
     <row r="3" spans="1:7" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
+        <v>936</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>937</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="C3" s="1" t="s">
+        <v>893</v>
+      </c>
+      <c r="D3" s="1" t="s">
         <v>938</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="E3" s="1" t="s">
+        <v>895</v>
+      </c>
+      <c r="F3" s="1" t="s">
         <v>894</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="G3" s="1" t="s">
         <v>939</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>896</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>895</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>940</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>6</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="B5" s="2" t="s">
+        <v>941</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>881</v>
+      </c>
+      <c r="D5" s="2" t="s">
         <v>942</v>
       </c>
-      <c r="C5" s="2" t="s">
-        <v>882</v>
-      </c>
-      <c r="D5" s="2" t="s">
+      <c r="E5" s="2" t="s">
         <v>943</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="F5" s="2" t="s">
         <v>944</v>
       </c>
-      <c r="F5" s="2" t="s">
-        <v>945</v>
-      </c>
       <c r="G5" s="2" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>6</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>946</v>
+        <v>945</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>75</v>
@@ -10406,7 +10409,7 @@
         <v>65000</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
     </row>
   </sheetData>
@@ -10429,7 +10432,7 @@
   <sheetData>
     <row r="1" spans="1:4" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A1" s="10" t="s">
-        <v>947</v>
+        <v>946</v>
       </c>
       <c r="B1" s="10"/>
       <c r="C1" s="10"/>
@@ -10437,58 +10440,58 @@
     </row>
     <row r="3" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
-        <v>937</v>
+        <v>936</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>947</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>948</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="D3" s="1" t="s">
         <v>949</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>950</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>39</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="B5" s="2" t="s">
+        <v>951</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>942</v>
+      </c>
+      <c r="D5" s="2" t="s">
         <v>952</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>943</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>953</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>75</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
     </row>
   </sheetData>
@@ -10516,7 +10519,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A1" s="10" t="s">
-        <v>956</v>
+        <v>955</v>
       </c>
       <c r="B1" s="10"/>
       <c r="C1" s="10"/>
@@ -10527,117 +10530,117 @@
     </row>
     <row r="3" spans="1:7" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
+        <v>956</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>858</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>957</v>
       </c>
-      <c r="B3" s="1" t="s">
-        <v>859</v>
-      </c>
-      <c r="C3" s="1" t="s">
+      <c r="D3" s="1" t="s">
         <v>958</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="E3" s="1" t="s">
         <v>959</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="F3" s="1" t="s">
         <v>960</v>
       </c>
-      <c r="F3" s="1" t="s">
-        <v>961</v>
-      </c>
       <c r="G3" s="1" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
+        <v>961</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>962</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="C4" s="2" t="s">
         <v>963</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>964</v>
       </c>
       <c r="D4" s="2">
         <v>81234567890</v>
       </c>
       <c r="E4" s="6" t="s">
+        <v>964</v>
+      </c>
+      <c r="F4" s="2" t="s">
         <v>965</v>
       </c>
-      <c r="F4" s="2" t="s">
-        <v>966</v>
-      </c>
       <c r="G4" s="2" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
+        <v>966</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>967</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="C5" s="2" t="s">
         <v>968</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>969</v>
       </c>
       <c r="D5" s="2">
         <v>82198765432</v>
       </c>
       <c r="E5" s="6" t="s">
+        <v>969</v>
+      </c>
+      <c r="F5" s="2" t="s">
         <v>970</v>
       </c>
-      <c r="F5" s="2" t="s">
-        <v>971</v>
-      </c>
       <c r="G5" s="2" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
+        <v>971</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>972</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="C6" s="2" t="s">
         <v>973</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="D6" s="2" t="s">
         <v>974</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="E6" s="2" t="s">
         <v>975</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="F6" s="2" t="s">
         <v>976</v>
       </c>
-      <c r="F6" s="2" t="s">
-        <v>977</v>
-      </c>
       <c r="G6" s="2" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
+        <v>977</v>
+      </c>
+      <c r="B7" s="2" t="s">
         <v>978</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="C7" s="2" t="s">
         <v>979</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="D7" s="2" t="s">
         <v>980</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="E7" s="2" t="s">
         <v>981</v>
       </c>
-      <c r="E7" s="2" t="s">
+      <c r="F7" s="2" t="s">
         <v>982</v>
       </c>
-      <c r="F7" s="2" t="s">
-        <v>983</v>
-      </c>
       <c r="G7" s="2" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
     </row>
   </sheetData>
@@ -10667,7 +10670,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A1" s="10" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="B1" s="10"/>
       <c r="C1" s="10"/>
@@ -10679,106 +10682,106 @@
     </row>
     <row r="3" spans="1:8" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
+        <v>984</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>985</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="C3" s="1" t="s">
         <v>986</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="D3" s="1" t="s">
         <v>987</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="E3" s="1" t="s">
         <v>988</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="F3" s="1" t="s">
         <v>989</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="G3" s="1" t="s">
         <v>990</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="H3" s="1" t="s">
         <v>991</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>992</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
+        <v>992</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>962</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>993</v>
       </c>
-      <c r="B4" s="2" t="s">
-        <v>963</v>
-      </c>
-      <c r="C4" s="2" t="s">
+      <c r="D4" s="2" t="s">
         <v>994</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="E4" s="2" t="s">
+        <v>923</v>
+      </c>
+      <c r="F4" s="2" t="s">
         <v>995</v>
       </c>
-      <c r="E4" s="2" t="s">
-        <v>924</v>
-      </c>
-      <c r="F4" s="2" t="s">
+      <c r="G4" s="2" t="s">
         <v>996</v>
       </c>
-      <c r="G4" s="2" t="s">
-        <v>997</v>
-      </c>
       <c r="H4" s="2" t="s">
-        <v>996</v>
+        <v>995</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
+        <v>997</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>967</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>998</v>
       </c>
-      <c r="B5" s="2" t="s">
-        <v>968</v>
-      </c>
-      <c r="C5" s="2" t="s">
+      <c r="D5" s="2" t="s">
         <v>999</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="E5" s="2" t="s">
+        <v>928</v>
+      </c>
+      <c r="F5" s="2" t="s">
         <v>1000</v>
       </c>
-      <c r="E5" s="2" t="s">
-        <v>929</v>
-      </c>
-      <c r="F5" s="2" t="s">
+      <c r="G5" s="2" t="s">
         <v>1001</v>
       </c>
-      <c r="G5" s="2" t="s">
+      <c r="H5" s="2" t="s">
         <v>1002</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>1003</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
+        <v>1003</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>972</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>1004</v>
       </c>
-      <c r="B6" s="2" t="s">
-        <v>973</v>
-      </c>
-      <c r="C6" s="2" t="s">
+      <c r="D6" s="2" t="s">
         <v>1005</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="E6" s="2" t="s">
         <v>1006</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="F6" s="2" t="s">
         <v>1007</v>
       </c>
-      <c r="F6" s="2" t="s">
+      <c r="G6" s="2" t="s">
         <v>1008</v>
       </c>
-      <c r="G6" s="2" t="s">
-        <v>1009</v>
-      </c>
       <c r="H6" s="2" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
     </row>
   </sheetData>
@@ -10805,7 +10808,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A1" s="10" t="s">
-        <v>1010</v>
+        <v>1009</v>
       </c>
       <c r="B1" s="10"/>
       <c r="C1" s="10"/>
@@ -10815,102 +10818,102 @@
     </row>
     <row r="3" spans="1:6" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
+        <v>1010</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>858</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>958</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>957</v>
+      </c>
+      <c r="E3" s="1" t="s">
         <v>1011</v>
       </c>
-      <c r="B3" s="1" t="s">
-        <v>859</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>959</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>958</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>1012</v>
-      </c>
       <c r="F3" s="1" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
+        <v>1012</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>1013</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="C4" s="2" t="s">
         <v>1014</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="D4" s="2" t="s">
         <v>1015</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="E4" s="2" t="s">
         <v>1016</v>
       </c>
-      <c r="E4" s="2" t="s">
-        <v>1017</v>
-      </c>
       <c r="F4" s="2" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
+        <v>1017</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>1018</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="C5" s="2" t="s">
         <v>1019</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="D5" s="2" t="s">
         <v>1020</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="E5" s="2" t="s">
         <v>1021</v>
       </c>
-      <c r="E5" s="2" t="s">
-        <v>1022</v>
-      </c>
       <c r="F5" s="2" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
+        <v>1022</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>1023</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="C6" s="2" t="s">
         <v>1024</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="D6" s="2" t="s">
         <v>1025</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="E6" s="2" t="s">
         <v>1026</v>
       </c>
-      <c r="E6" s="2" t="s">
-        <v>1027</v>
-      </c>
       <c r="F6" s="2" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
+        <v>1027</v>
+      </c>
+      <c r="B7" s="2" t="s">
         <v>1028</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="C7" s="2" t="s">
         <v>1029</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="D7" s="2" t="s">
         <v>1030</v>
       </c>
-      <c r="D7" s="2" t="s">
-        <v>1031</v>
-      </c>
       <c r="E7" s="2" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
     </row>
   </sheetData>
@@ -10937,7 +10940,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A1" s="10" t="s">
-        <v>1032</v>
+        <v>1031</v>
       </c>
       <c r="B1" s="10"/>
       <c r="C1" s="10"/>
@@ -10948,94 +10951,94 @@
     </row>
     <row r="3" spans="1:7" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
+        <v>1032</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>1033</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="C3" s="1" t="s">
+        <v>989</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>991</v>
+      </c>
+      <c r="E3" s="1" t="s">
         <v>1034</v>
       </c>
-      <c r="C3" s="1" t="s">
-        <v>990</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>992</v>
-      </c>
-      <c r="E3" s="1" t="s">
+      <c r="F3" s="1" t="s">
         <v>1035</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="G3" s="1" t="s">
         <v>1036</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>1037</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="B4" s="2" t="s">
+        <v>1037</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>1038</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="D4" s="2" t="s">
+        <v>928</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>1038</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>1008</v>
+      </c>
+      <c r="G4" s="2" t="s">
         <v>1039</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>929</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>1039</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>1009</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>1040</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
-        <v>1019</v>
+        <v>1018</v>
       </c>
       <c r="B5" s="2" t="s">
+        <v>1040</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>1016</v>
+      </c>
+      <c r="D5" s="2" t="s">
         <v>1041</v>
       </c>
-      <c r="C5" s="2" t="s">
-        <v>1017</v>
-      </c>
-      <c r="D5" s="2" t="s">
+      <c r="E5" s="2" t="s">
+        <v>1041</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>1001</v>
+      </c>
+      <c r="G5" s="2" t="s">
         <v>1042</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>1042</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>1002</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>1043</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
-        <v>1024</v>
+        <v>1023</v>
       </c>
       <c r="B6" s="2" t="s">
+        <v>1043</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>1044</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="D6" s="2" t="s">
+        <v>1044</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>928</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>996</v>
+      </c>
+      <c r="G6" s="2" t="s">
         <v>1045</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>1045</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>929</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>997</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>1046</v>
       </c>
     </row>
   </sheetData>
@@ -11059,7 +11062,7 @@
   <sheetData>
     <row r="1" spans="1:4" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A1" s="10" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="B1" s="10"/>
       <c r="C1" s="10"/>
@@ -11067,58 +11070,58 @@
     </row>
     <row r="3" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>1047</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>1048</v>
       </c>
-      <c r="C3" s="1" t="s">
-        <v>1049</v>
-      </c>
       <c r="D3" s="1" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
+        <v>1049</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>1050</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="C4" s="2" t="s">
         <v>1051</v>
       </c>
-      <c r="C4" s="2" t="s">
-        <v>1052</v>
-      </c>
       <c r="D4" s="2" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
+        <v>1052</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>1051</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>1053</v>
       </c>
-      <c r="B5" s="2" t="s">
-        <v>1052</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>1054</v>
-      </c>
       <c r="D5" s="2" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
-        <v>1055</v>
+        <v>1054</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>1051</v>
+        <v>1050</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
     </row>
   </sheetData>
@@ -11145,7 +11148,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A1" s="10" t="s">
-        <v>1056</v>
+        <v>1055</v>
       </c>
       <c r="B1" s="10"/>
       <c r="C1" s="10"/>
@@ -11157,106 +11160,106 @@
     </row>
     <row r="3" spans="1:8" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>1056</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>1057</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="D3" s="1" t="s">
         <v>1058</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="E3" s="1" t="s">
         <v>1059</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="F3" s="1" t="s">
         <v>1060</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="G3" s="1" t="s">
+        <v>1035</v>
+      </c>
+      <c r="H3" s="1" t="s">
         <v>1061</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>1036</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>1062</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>1050</v>
+        <v>1049</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
       <c r="D4" s="2" t="s">
+        <v>1062</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>1062</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>928</v>
+      </c>
+      <c r="G4" s="2" t="s">
         <v>1063</v>
       </c>
-      <c r="E4" s="2" t="s">
-        <v>1063</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>929</v>
-      </c>
-      <c r="G4" s="2" t="s">
+      <c r="H4" s="2" t="s">
         <v>1064</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>1065</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>1053</v>
+        <v>1052</v>
       </c>
       <c r="C5" s="2" t="s">
+        <v>1065</v>
+      </c>
+      <c r="D5" s="2" t="s">
         <v>1066</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="E5" s="2" t="s">
+        <v>1021</v>
+      </c>
+      <c r="F5" s="2" t="s">
         <v>1067</v>
       </c>
-      <c r="E5" s="2" t="s">
-        <v>1022</v>
-      </c>
-      <c r="F5" s="2" t="s">
+      <c r="G5" s="2" t="s">
+        <v>1063</v>
+      </c>
+      <c r="H5" s="2" t="s">
         <v>1068</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>1064</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>1069</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>1055</v>
+        <v>1054</v>
       </c>
       <c r="C6" s="2" t="s">
+        <v>1069</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G6" s="2" t="s">
         <v>1070</v>
       </c>
-      <c r="D6" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="G6" s="2" t="s">
+      <c r="H6" s="2" t="s">
         <v>1071</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>1072</v>
       </c>
     </row>
   </sheetData>
@@ -11283,7 +11286,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A1" s="10" t="s">
-        <v>1073</v>
+        <v>1072</v>
       </c>
       <c r="B1" s="10"/>
       <c r="C1" s="10"/>
@@ -11293,102 +11296,102 @@
     </row>
     <row r="3" spans="1:6" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
+        <v>1073</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>892</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>860</v>
+      </c>
+      <c r="D3" s="1" t="s">
         <v>1074</v>
       </c>
-      <c r="B3" s="1" t="s">
-        <v>893</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>861</v>
-      </c>
-      <c r="D3" s="1" t="s">
+      <c r="E3" s="1" t="s">
         <v>1075</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="F3" s="1" t="s">
         <v>1076</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>1077</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="B4" s="2" t="s">
+        <v>1077</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>1078</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="D4" s="2" t="s">
         <v>1079</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="E4" s="2" t="s">
         <v>1080</v>
       </c>
-      <c r="E4" s="2" t="s">
-        <v>1081</v>
-      </c>
       <c r="F4" s="2" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="B5" s="2" t="s">
+        <v>1081</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>1082</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="D5" s="2" t="s">
         <v>1083</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="E5" s="2" t="s">
         <v>1084</v>
       </c>
-      <c r="E5" s="2" t="s">
-        <v>1085</v>
-      </c>
       <c r="F5" s="2" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
+        <v>1085</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>1086</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="C6" s="2" t="s">
         <v>1087</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="D6" s="2" t="s">
         <v>1088</v>
       </c>
-      <c r="D6" s="2" t="s">
-        <v>1089</v>
-      </c>
       <c r="E6" s="2" t="s">
-        <v>1081</v>
+        <v>1080</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
-        <v>1086</v>
+        <v>1085</v>
       </c>
       <c r="B7" s="2" t="s">
+        <v>1089</v>
+      </c>
+      <c r="C7" s="2" t="s">
         <v>1090</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="D7" s="2" t="s">
         <v>1091</v>
       </c>
-      <c r="D7" s="2" t="s">
-        <v>1092</v>
-      </c>
       <c r="E7" s="2" t="s">
-        <v>1081</v>
+        <v>1080</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
     </row>
   </sheetData>
@@ -11476,7 +11479,7 @@
         <v>5</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="29" x14ac:dyDescent="0.35">
@@ -11502,7 +11505,7 @@
         <v>5</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
@@ -11528,7 +11531,7 @@
         <v>5</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="29" x14ac:dyDescent="0.35">
@@ -11554,7 +11557,7 @@
         <v>5</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="29" x14ac:dyDescent="0.35">
@@ -11580,7 +11583,7 @@
         <v>5</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="29" x14ac:dyDescent="0.35">
@@ -11606,7 +11609,7 @@
         <v>5</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="58" x14ac:dyDescent="0.35">
@@ -11632,7 +11635,7 @@
         <v>5</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="29" x14ac:dyDescent="0.35">
@@ -11658,7 +11661,7 @@
         <v>5</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.35">
@@ -11684,7 +11687,7 @@
         <v>5</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="58" x14ac:dyDescent="0.35">
@@ -11704,13 +11707,13 @@
         <v>227</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>5</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="58" x14ac:dyDescent="0.35">
@@ -11721,19 +11724,19 @@
         <v>119</v>
       </c>
       <c r="C14" s="2" t="s">
+        <v>1118</v>
+      </c>
+      <c r="D14" s="2" t="s">
         <v>1119</v>
       </c>
-      <c r="D14" s="2" t="s">
+      <c r="E14" s="2" t="s">
         <v>1120</v>
       </c>
-      <c r="E14" s="2" t="s">
+      <c r="F14" s="2" t="s">
         <v>1121</v>
       </c>
-      <c r="F14" s="2" t="s">
-        <v>1122</v>
-      </c>
       <c r="H14" s="3" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
     </row>
   </sheetData>
@@ -11761,7 +11764,7 @@
   <sheetData>
     <row r="1" spans="1:10" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A1" s="10" t="s">
-        <v>1093</v>
+        <v>1092</v>
       </c>
       <c r="B1" s="10"/>
       <c r="C1" s="10"/>
@@ -11775,226 +11778,226 @@
     </row>
     <row r="3" spans="1:10" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
+        <v>1093</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>850</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>987</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>1075</v>
+      </c>
+      <c r="E3" s="1" t="s">
         <v>1094</v>
       </c>
-      <c r="B3" s="1" t="s">
-        <v>851</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>988</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>1076</v>
-      </c>
-      <c r="E3" s="1" t="s">
+      <c r="F3" s="1" t="s">
+        <v>989</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>1032</v>
+      </c>
+      <c r="H3" s="1" t="s">
         <v>1095</v>
       </c>
-      <c r="F3" s="1" t="s">
-        <v>990</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>1033</v>
-      </c>
-      <c r="H3" s="1" t="s">
+      <c r="I3" s="1" t="s">
+        <v>1035</v>
+      </c>
+      <c r="J3" s="1" t="s">
         <v>1096</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>1036</v>
-      </c>
-      <c r="J3" s="1" t="s">
-        <v>1097</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
+        <v>1097</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>824</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>1098</v>
       </c>
-      <c r="B4" s="2" t="s">
-        <v>825</v>
-      </c>
-      <c r="C4" s="2" t="s">
+      <c r="D4" s="2" t="s">
+        <v>1080</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>923</v>
+      </c>
+      <c r="F4" s="2" t="s">
         <v>1099</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>1081</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>924</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>1100</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>159</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="I4" s="2" t="s">
+        <v>1100</v>
+      </c>
+      <c r="J4" s="2" t="s">
         <v>1101</v>
-      </c>
-      <c r="J4" s="2" t="s">
-        <v>1102</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
+        <v>1102</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>824</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>1103</v>
       </c>
-      <c r="B5" s="2" t="s">
-        <v>825</v>
-      </c>
-      <c r="C5" s="2" t="s">
+      <c r="D5" s="2" t="s">
         <v>1104</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="E5" s="2" t="s">
         <v>1105</v>
       </c>
-      <c r="E5" s="2" t="s">
-        <v>1106</v>
-      </c>
       <c r="F5" s="2" t="s">
-        <v>1106</v>
+        <v>1105</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>159</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>1101</v>
+        <v>1100</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>1107</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
+        <v>1107</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>828</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>1108</v>
       </c>
-      <c r="B6" s="2" t="s">
-        <v>829</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>1109</v>
-      </c>
       <c r="D6" s="2" t="s">
-        <v>1085</v>
+        <v>1084</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>159</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>1101</v>
+        <v>1100</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>1110</v>
+        <v>1109</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
+        <v>1037</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>824</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>1110</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>1111</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>928</v>
+      </c>
+      <c r="F7" s="2" t="s">
         <v>1038</v>
       </c>
-      <c r="B7" s="2" t="s">
-        <v>825</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>1111</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>1112</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>929</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>1039</v>
-      </c>
       <c r="G7" s="2" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="I7" s="2" t="s">
+        <v>1100</v>
+      </c>
+      <c r="J7" s="2" t="s">
         <v>1101</v>
-      </c>
-      <c r="J7" s="2" t="s">
-        <v>1102</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>1113</v>
+        <v>1112</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>1081</v>
+        <v>1080</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>159</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="I8" s="2" t="s">
+        <v>1100</v>
+      </c>
+      <c r="J8" s="2" t="s">
         <v>1101</v>
-      </c>
-      <c r="J8" s="2" t="s">
-        <v>1102</v>
       </c>
     </row>
     <row r="9" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A9" s="2" t="s">
+        <v>1113</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>824</v>
+      </c>
+      <c r="C9" s="2" t="s">
         <v>1114</v>
       </c>
-      <c r="B9" s="2" t="s">
-        <v>825</v>
-      </c>
-      <c r="C9" s="2" t="s">
+      <c r="D9" s="2" t="s">
+        <v>1080</v>
+      </c>
+      <c r="E9" s="2" t="s">
         <v>1115</v>
       </c>
-      <c r="D9" s="2" t="s">
-        <v>1081</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>1116</v>
-      </c>
       <c r="F9" s="2" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>159</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>1102</v>
+        <v>1101</v>
       </c>
     </row>
   </sheetData>
@@ -12570,7 +12573,7 @@
         <v>5</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
@@ -12596,7 +12599,7 @@
         <v>5</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="29" x14ac:dyDescent="0.35">
@@ -12607,7 +12610,7 @@
         <v>229</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>1127</v>
+        <v>1126</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>317</v>
@@ -12622,7 +12625,7 @@
         <v>5</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="29" x14ac:dyDescent="0.35">
@@ -12648,7 +12651,7 @@
         <v>5</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
@@ -12674,7 +12677,7 @@
         <v>5</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="29" x14ac:dyDescent="0.35">
@@ -12700,7 +12703,7 @@
         <v>5</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
@@ -12726,7 +12729,7 @@
         <v>5</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="58" x14ac:dyDescent="0.35">
@@ -12752,7 +12755,7 @@
         <v>5</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.35">
@@ -12763,22 +12766,22 @@
         <v>119</v>
       </c>
       <c r="C12" s="2" t="s">
+        <v>1131</v>
+      </c>
+      <c r="D12" s="2" t="s">
         <v>1132</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>1133</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>299</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>1134</v>
+        <v>1133</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>5</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
     </row>
   </sheetData>
@@ -12866,7 +12869,7 @@
         <v>5</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
@@ -12892,7 +12895,7 @@
         <v>5</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="29" x14ac:dyDescent="0.35">
@@ -12918,7 +12921,7 @@
         <v>5</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.35">
@@ -12929,13 +12932,13 @@
         <v>229</v>
       </c>
       <c r="C7" s="2" t="s">
+        <v>1123</v>
+      </c>
+      <c r="D7" s="2" t="s">
         <v>1124</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="E7" s="2" t="s">
         <v>1125</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>1126</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>292</v>
@@ -12944,7 +12947,7 @@
         <v>5</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
@@ -12970,7 +12973,7 @@
         <v>5</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="29" x14ac:dyDescent="0.35">
@@ -12981,13 +12984,13 @@
         <v>229</v>
       </c>
       <c r="C9" s="2" t="s">
+        <v>1127</v>
+      </c>
+      <c r="D9" s="2" t="s">
         <v>1128</v>
       </c>
-      <c r="D9" s="2" t="s">
+      <c r="E9" s="2" t="s">
         <v>1129</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>1130</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>300</v>
@@ -12996,7 +12999,7 @@
         <v>5</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="29" x14ac:dyDescent="0.35">
@@ -13022,7 +13025,7 @@
         <v>5</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="58" x14ac:dyDescent="0.35">
@@ -13033,7 +13036,7 @@
         <v>128</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>1131</v>
+        <v>1130</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>306</v>
@@ -13048,7 +13051,7 @@
         <v>5</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.35">
@@ -13059,22 +13062,22 @@
         <v>119</v>
       </c>
       <c r="C12" s="2" t="s">
+        <v>1134</v>
+      </c>
+      <c r="D12" s="2" t="s">
         <v>1135</v>
       </c>
-      <c r="D12" s="2" t="s">
+      <c r="E12" s="2" t="s">
+        <v>1140</v>
+      </c>
+      <c r="F12" s="2" t="s">
         <v>1136</v>
       </c>
-      <c r="E12" s="2" t="s">
-        <v>1141</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>1137</v>
-      </c>
       <c r="G12" s="2" t="s">
         <v>5</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
     </row>
   </sheetData>
@@ -13162,7 +13165,7 @@
         <v>5</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="87" x14ac:dyDescent="0.35">
@@ -13188,7 +13191,7 @@
         <v>5</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="29" x14ac:dyDescent="0.35">
@@ -13214,7 +13217,7 @@
         <v>5</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="29" x14ac:dyDescent="0.35">
@@ -13240,7 +13243,7 @@
         <v>5</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="29" x14ac:dyDescent="0.35">
@@ -13266,7 +13269,7 @@
         <v>5</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="29" x14ac:dyDescent="0.35">
@@ -13292,7 +13295,7 @@
         <v>5</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.35">
@@ -13318,7 +13321,7 @@
         <v>5</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="29" x14ac:dyDescent="0.35">
@@ -13344,7 +13347,7 @@
         <v>5</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="29" x14ac:dyDescent="0.35">
@@ -13370,7 +13373,7 @@
         <v>5</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="58" x14ac:dyDescent="0.35">
@@ -13396,7 +13399,7 @@
         <v>5</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="29" x14ac:dyDescent="0.35">
@@ -13422,7 +13425,7 @@
         <v>5</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
@@ -13433,10 +13436,10 @@
         <v>229</v>
       </c>
       <c r="C15" s="2" t="s">
+        <v>1147</v>
+      </c>
+      <c r="D15" s="2" t="s">
         <v>1148</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>1149</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>387</v>
@@ -13448,7 +13451,7 @@
         <v>5</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="29" x14ac:dyDescent="0.35">
@@ -13474,7 +13477,7 @@
         <v>5</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="72.5" x14ac:dyDescent="0.35">
@@ -13500,7 +13503,7 @@
         <v>5</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
@@ -13526,7 +13529,7 @@
         <v>5</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="72.5" x14ac:dyDescent="0.35">
@@ -13552,7 +13555,7 @@
         <v>5</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="20" spans="1:8" ht="29" x14ac:dyDescent="0.35">
@@ -13578,7 +13581,7 @@
         <v>5</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="21" spans="1:8" ht="29" x14ac:dyDescent="0.35">
@@ -13604,7 +13607,7 @@
         <v>5</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.35">
@@ -13615,22 +13618,22 @@
         <v>119</v>
       </c>
       <c r="C22" s="2" t="s">
+        <v>1137</v>
+      </c>
+      <c r="D22" s="2" t="s">
         <v>1138</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>1139</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>387</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
       <c r="G22" s="2" t="s">
         <v>5</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="23" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
@@ -13641,19 +13644,19 @@
         <v>128</v>
       </c>
       <c r="C23" s="4" t="s">
+        <v>1141</v>
+      </c>
+      <c r="D23" s="5" t="s">
         <v>1142</v>
-      </c>
-      <c r="D23" s="5" t="s">
-        <v>1143</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>387</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="24" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
@@ -13664,19 +13667,19 @@
         <v>128</v>
       </c>
       <c r="C24" s="4" t="s">
+        <v>1144</v>
+      </c>
+      <c r="D24" s="5" t="s">
         <v>1145</v>
-      </c>
-      <c r="D24" s="5" t="s">
-        <v>1146</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>387</v>
       </c>
       <c r="F24" s="4" t="s">
-        <v>1147</v>
+        <v>1146</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="25" spans="1:8" ht="29" x14ac:dyDescent="0.35">
@@ -13687,22 +13690,22 @@
         <v>229</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>1151</v>
+        <v>1150</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>1139</v>
+        <v>1138</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>387</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>1153</v>
+        <v>1152</v>
       </c>
       <c r="G25" s="2" t="s">
         <v>5</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="26" spans="1:8" ht="29" x14ac:dyDescent="0.35">
@@ -13722,13 +13725,13 @@
         <v>387</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>1152</v>
+        <v>1151</v>
       </c>
       <c r="G26" s="2" t="s">
         <v>5</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
     </row>
   </sheetData>

--- a/docs/Dokumen_Testing_POS.xlsx
+++ b/docs/Dokumen_Testing_POS.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26743EBC-3E1C-49C3-A497-B0DF9D1142FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C140F0F7-CF66-4114-9387-0943E25FE45C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="867" firstSheet="6" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="867" firstSheet="9" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Daftar Isi" sheetId="1" r:id="rId1"/>
@@ -65,7 +65,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2310" uniqueCount="1158">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2326" uniqueCount="1167">
   <si>
     <t>DOKUMEN TESTING APLIKASI POS</t>
   </si>
@@ -3687,6 +3687,33 @@
   </si>
   <si>
     <t>Generate kode PO otomatis</t>
+  </si>
+  <si>
+    <t>Pembelian yang terhapus adalah pembelian yang statusnya Hutang</t>
+  </si>
+  <si>
+    <t>1. Klik menu Retur</t>
+  </si>
+  <si>
+    <t>List Retur gagal muncul, jika faktur pembelian belum ada</t>
+  </si>
+  <si>
+    <t>Lihat daftar pembelian (supplier)</t>
+  </si>
+  <si>
+    <t>1. Buka menu Pembelian (Supplier)</t>
+  </si>
+  <si>
+    <t>List pembelian (supplier) tampil</t>
+  </si>
+  <si>
+    <t>Lihat daftar retur supplier</t>
+  </si>
+  <si>
+    <t>1. Buka menu retur supplier</t>
+  </si>
+  <si>
+    <t>List retur supplier tampil</t>
   </si>
 </sst>
 </file>
@@ -3806,7 +3833,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -3832,6 +3859,9 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -4910,7 +4940,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
-  <dimension ref="A1:H12"/>
+  <dimension ref="A1:H13"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
@@ -4961,7 +4991,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="29" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A4" s="2">
         <v>1</v>
       </c>
@@ -4969,16 +4999,16 @@
         <v>229</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>1157</v>
+        <v>1161</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>414</v>
+        <v>1162</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>159</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>415</v>
+        <v>1163</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>5</v>
@@ -4987,7 +5017,7 @@
         <v>1117</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A5" s="2">
         <v>2</v>
       </c>
@@ -4995,16 +5025,16 @@
         <v>229</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>416</v>
+        <v>1157</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>418</v>
+        <v>159</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>419</v>
+        <v>415</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>5</v>
@@ -5013,7 +5043,7 @@
         <v>1117</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="29" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:8" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A6" s="2">
         <v>3</v>
       </c>
@@ -5021,25 +5051,25 @@
         <v>229</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>420</v>
+        <v>416</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>421</v>
+        <v>417</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>422</v>
+        <v>418</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>423</v>
+        <v>419</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="H6" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="H6" s="3" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A7" s="2">
         <v>4</v>
       </c>
@@ -5047,22 +5077,22 @@
         <v>229</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>424</v>
+        <v>420</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>425</v>
+        <v>421</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>426</v>
+        <v>422</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>427</v>
+        <v>423</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="H7" s="2" t="s">
-        <v>5</v>
+      <c r="H7" s="3" t="s">
+        <v>1117</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
@@ -5073,22 +5103,22 @@
         <v>229</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>428</v>
+        <v>424</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>429</v>
+        <v>425</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>430</v>
+        <v>426</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="H8" s="2" t="s">
-        <v>5</v>
+      <c r="H8" s="3" t="s">
+        <v>1117</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
@@ -5099,22 +5129,22 @@
         <v>229</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>433</v>
+        <v>429</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>159</v>
+        <v>430</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="H9" s="2" t="s">
-        <v>5</v>
+      <c r="H9" s="3" t="s">
+        <v>1117</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
@@ -5125,22 +5155,22 @@
         <v>229</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>437</v>
+        <v>159</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>438</v>
+        <v>434</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="H10" s="2" t="s">
-        <v>5</v>
+      <c r="H10" s="3" t="s">
+        <v>1117</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
@@ -5151,22 +5181,22 @@
         <v>229</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>439</v>
+        <v>435</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>440</v>
+        <v>436</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>159</v>
+        <v>437</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="H11" s="2" t="s">
-        <v>5</v>
+      <c r="H11" s="3" t="s">
+        <v>1117</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
@@ -5177,22 +5207,48 @@
         <v>229</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>159</v>
       </c>
       <c r="F12" s="2" t="s">
+        <v>441</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A13" s="2">
+        <v>10</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>442</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>443</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>1158</v>
+      </c>
+      <c r="F13" s="2" t="s">
         <v>444</v>
       </c>
-      <c r="G12" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="H12" s="2" t="s">
-        <v>5</v>
+      <c r="G13" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="H13" s="3" t="s">
+        <v>1117</v>
       </c>
     </row>
   </sheetData>
@@ -5206,7 +5262,7 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:H10"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
@@ -5257,7 +5313,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="58" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A4" s="2">
         <v>1</v>
       </c>
@@ -5265,94 +5321,94 @@
         <v>229</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>446</v>
+        <v>1164</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>447</v>
+        <v>1165</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>448</v>
+        <v>159</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>449</v>
+        <v>1166</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" ht="29" x14ac:dyDescent="0.35">
+      <c r="H4" s="3" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="58" x14ac:dyDescent="0.35">
       <c r="A5" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>229</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>450</v>
+        <v>446</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>451</v>
+        <v>447</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>452</v>
+        <v>448</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>319</v>
+        <v>449</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="H5" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" ht="58" x14ac:dyDescent="0.35">
+      <c r="H5" s="3" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A6" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>229</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>453</v>
+        <v>450</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>456</v>
+        <v>319</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="H6" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" ht="29" x14ac:dyDescent="0.35">
+      <c r="H6" s="3" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="58" x14ac:dyDescent="0.35">
       <c r="A7" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>229</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>457</v>
+        <v>453</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>458</v>
+        <v>454</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>459</v>
+        <v>455</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>460</v>
+        <v>456</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>5</v>
@@ -5361,24 +5417,24 @@
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A8" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>229</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>461</v>
+        <v>457</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>462</v>
+        <v>458</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>159</v>
+        <v>459</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>5</v>
@@ -5387,15 +5443,47 @@
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="29" x14ac:dyDescent="0.35">
-      <c r="A9" s="4">
-        <v>6</v>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A9" s="2">
+        <v>5</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>229</v>
       </c>
       <c r="C9" s="2" t="s">
+        <v>461</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>463</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="29" x14ac:dyDescent="0.35">
+      <c r="A10" s="4">
+        <v>6</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="C10" s="2" t="s">
         <v>1149</v>
+      </c>
+      <c r="D10" s="11" t="s">
+        <v>1159</v>
+      </c>
+      <c r="F10" s="11" t="s">
+        <v>1160</v>
       </c>
     </row>
   </sheetData>
@@ -5403,7 +5491,7 @@
     <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" r:id="rId1"/>
 </worksheet>
 </file>
 
